--- a/input/reg_wages.xlsx
+++ b/input/reg_wages.xlsx
@@ -1,30 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patryk\git\SimPaths_HU\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{999FCE25-15E9-48C9-9D98-CFB688F080CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57C6D0B7-89AA-4521-AABC-E866EEFD1CA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-83" yWindow="0" windowWidth="14566" windowHeight="17363" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" tabRatio="932" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
-    <sheet name="PL_Wages_FemalesNE" sheetId="2" r:id="rId2"/>
-    <sheet name="PL_Wages_MalesNE" sheetId="3" r:id="rId3"/>
-    <sheet name="PL_Wages_FemalesE" sheetId="4" r:id="rId4"/>
-    <sheet name="PL_Wages_MalesE" sheetId="5" r:id="rId5"/>
+    <sheet name="IT_Wages_FemalesNE" sheetId="6" r:id="rId2"/>
+    <sheet name="IT_Wages_MalesNE" sheetId="7" r:id="rId3"/>
+    <sheet name="IT_Wages_FemalesE" sheetId="8" r:id="rId4"/>
+    <sheet name="IT_Wages_MalesE" sheetId="9" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="39">
   <si>
     <t>Description:</t>
   </si>
@@ -69,9 +69,6 @@
   </si>
   <si>
     <t>Two-step Heckman command is used which does not permit weights</t>
-  </si>
-  <si>
-    <t>Estimate the models without the lagged wage observation on the full working age sample. Choice made because otherwise the reduction in the sample size makes the sigma used when correcting the bias when transforming the log wages to wage levels too large.</t>
   </si>
   <si>
     <t>REGRESSOR</t>
@@ -131,26 +128,26 @@
     <t>L1_log_hourly_wage</t>
   </si>
   <si>
-    <t>PL4</t>
+    <t>Regions: ITF = South, ITG = Islands, ITH = Northeast, ITI = Central. Northwest (ITC) is the omitted region.</t>
   </si>
   <si>
-    <t>PL5</t>
+    <t>ITF</t>
   </si>
   <si>
-    <t>PL6</t>
+    <t>ITG</t>
   </si>
   <si>
-    <t>Regions: PL4 = Polnocno-Zachodni, PL5 = Poludniowo-Zachodni, PL6 = Polnocy, PL10 = Central + East. Poludniowy is the omitted category.</t>
+    <t>ITH</t>
   </si>
   <si>
-    <t>PL10</t>
+    <t>ITI</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -162,16 +159,8 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -182,21 +171,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -212,17 +187,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1"/>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{9B3E72A2-D84B-4C06-9252-0946458EB6A4}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -554,11 +531,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="14.796875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -566,7 +546,7 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -606,7 +586,7 @@
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B11" t="s">
@@ -625,12 +605,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B15" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -639,49 +614,50 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB2C99E6-AF73-4362-A209-1CD525536559}">
   <dimension ref="A1:V21"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="23.265625" customWidth="1"/>
+    <col min="1" max="1" width="21" style="3" customWidth="1"/>
+    <col min="2" max="16384" width="8.796875" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>18</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>19</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>20</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>21</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>22</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>23</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>24</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>25</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>26</v>
-      </c>
-      <c r="L1" t="s">
-        <v>27</v>
       </c>
       <c r="M1" t="s">
         <v>35</v>
@@ -693,705 +669,705 @@
         <v>37</v>
       </c>
       <c r="P1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q1" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" t="s">
         <v>28</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>29</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>30</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>31</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>32</v>
-      </c>
-      <c r="V1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B2">
-        <v>1.4127942989029306E-2</v>
+        <v>2.5436320865368629E-2</v>
       </c>
       <c r="C2">
-        <v>6.6893400358688662E-6</v>
+        <v>1.6394836554125037E-4</v>
       </c>
       <c r="D2">
-        <v>-7.5172351829064714E-8</v>
+        <v>-1.940173728820808E-6</v>
       </c>
       <c r="E2">
-        <v>1.4200738752403053E-5</v>
+        <v>1.7612282316757224E-4</v>
       </c>
       <c r="F2">
-        <v>1.6326411118274609E-5</v>
+        <v>-2.3345986039571015E-4</v>
       </c>
       <c r="G2">
-        <v>-3.1390895529854434E-7</v>
+        <v>-9.3680138732286656E-6</v>
       </c>
       <c r="H2">
-        <v>-3.5306934052010016E-7</v>
+        <v>-3.362430436697574E-6</v>
       </c>
       <c r="I2">
-        <v>5.2191933898302608E-7</v>
+        <v>4.7105205314027296E-4</v>
       </c>
       <c r="J2">
-        <v>1.5333570311600105E-6</v>
+        <v>5.4099170654948775E-4</v>
       </c>
       <c r="K2">
-        <v>1.1389036250969674E-6</v>
+        <v>5.7640449670552456E-4</v>
       </c>
       <c r="L2">
-        <v>3.8684506068066719E-6</v>
+        <v>6.4674039660667202E-4</v>
       </c>
       <c r="M2">
-        <v>-3.100608382898743E-8</v>
+        <v>-1.749208999402189E-4</v>
       </c>
       <c r="N2">
-        <v>7.7706159693911757E-7</v>
+        <v>-2.1360007519683209E-4</v>
       </c>
       <c r="O2">
-        <v>1.0873296208038032E-7</v>
+        <v>6.7007436290012043E-5</v>
       </c>
       <c r="P2">
-        <v>1.2737303853425186E-7</v>
+        <v>1.850901370848642E-7</v>
       </c>
       <c r="Q2">
-        <v>7.6020354002806439E-7</v>
+        <v>-2.4740028022701483E-5</v>
       </c>
       <c r="R2">
-        <v>-6.0182714182736144E-7</v>
+        <v>-3.8238617730593032E-4</v>
       </c>
       <c r="S2">
-        <v>1.6723042664373846E-6</v>
+        <v>1.2999972952604054E-4</v>
       </c>
       <c r="T2">
-        <v>1.306520123698462E-6</v>
+        <v>3.8183766205598235E-4</v>
       </c>
       <c r="U2">
-        <v>-1.4909008787779339E-4</v>
+        <v>-4.4001154657403816E-3</v>
       </c>
       <c r="V2">
-        <v>8.6004851812019255E-6</v>
+        <v>7.9591477924982894E-4</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B3">
-        <v>6.6769217454640004E-6</v>
+        <v>-9.9442795588634714E-5</v>
       </c>
       <c r="C3">
-        <v>-7.5172351829064714E-8</v>
+        <v>-1.940173728820808E-6</v>
       </c>
       <c r="D3">
-        <v>8.8112427337910947E-10</v>
+        <v>2.3720836992773504E-8</v>
       </c>
       <c r="E3">
-        <v>-4.0459038695721613E-8</v>
+        <v>2.4563192174037968E-7</v>
       </c>
       <c r="F3">
-        <v>-6.5795851982129797E-8</v>
+        <v>5.2546146444083756E-6</v>
       </c>
       <c r="G3">
-        <v>6.2399804685593934E-10</v>
+        <v>5.2422896552103234E-8</v>
       </c>
       <c r="H3">
-        <v>1.1019388075021572E-9</v>
+        <v>-2.0960584102242777E-8</v>
       </c>
       <c r="I3">
-        <v>-6.5843705748059433E-9</v>
+        <v>-5.9805886387292323E-6</v>
       </c>
       <c r="J3">
-        <v>-1.7337317680154612E-8</v>
+        <v>-6.7640489084881196E-6</v>
       </c>
       <c r="K3">
-        <v>-7.2640635384731349E-9</v>
+        <v>-7.1442242311663476E-6</v>
       </c>
       <c r="L3">
-        <v>-3.0220150384792202E-8</v>
+        <v>-7.9460824939888855E-6</v>
       </c>
       <c r="M3">
-        <v>-3.416234983635163E-10</v>
+        <v>2.1434261261617941E-6</v>
       </c>
       <c r="N3">
-        <v>-9.3900051489581933E-9</v>
+        <v>2.6116226047795972E-6</v>
       </c>
       <c r="O3">
-        <v>-2.6171936184743102E-9</v>
+        <v>-7.9323432294775308E-7</v>
       </c>
       <c r="P3">
-        <v>-1.9750139829535358E-9</v>
+        <v>-8.2744893217838418E-9</v>
       </c>
       <c r="Q3">
-        <v>-1.0622229993644364E-8</v>
+        <v>2.8089554223575157E-7</v>
       </c>
       <c r="R3">
-        <v>-6.3744218054156889E-9</v>
+        <v>5.1241338089540094E-6</v>
       </c>
       <c r="S3">
-        <v>-1.8232313064430036E-8</v>
+        <v>-1.6162160863925796E-6</v>
       </c>
       <c r="T3">
-        <v>-1.4326424739272051E-8</v>
+        <v>-4.8521421125753751E-6</v>
       </c>
       <c r="U3">
-        <v>1.6205969464593366E-6</v>
+        <v>5.1068068989269206E-5</v>
       </c>
       <c r="V3">
-        <v>-9.8269788264392313E-8</v>
+        <v>-9.7768939686272123E-6</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B4">
-        <v>-3.6912674709195736E-2</v>
+        <v>-8.3212528071994488E-2</v>
       </c>
       <c r="C4">
-        <v>1.4200738752403053E-5</v>
+        <v>1.7612282316757224E-4</v>
       </c>
       <c r="D4">
-        <v>-4.0459038695721613E-8</v>
+        <v>2.4563192174037968E-7</v>
       </c>
       <c r="E4">
-        <v>7.9128381688149923E-4</v>
+        <v>1.233269116350964E-2</v>
       </c>
       <c r="F4">
-        <v>4.8379469601322959E-4</v>
+        <v>8.3879515858163098E-3</v>
       </c>
       <c r="G4">
-        <v>-1.7611317740275793E-5</v>
+        <v>-2.8558812212106394E-4</v>
       </c>
       <c r="H4">
-        <v>-1.1002311805839985E-5</v>
+        <v>-1.9046224365598175E-4</v>
       </c>
       <c r="I4">
-        <v>-7.865472667699858E-6</v>
+        <v>-1.3911502880833444E-3</v>
       </c>
       <c r="J4">
-        <v>-1.3320142693466829E-5</v>
+        <v>-1.3271723444661151E-3</v>
       </c>
       <c r="K4">
-        <v>-1.8117103300378176E-5</v>
+        <v>-1.3906501903379392E-3</v>
       </c>
       <c r="L4">
-        <v>-8.2831931574261925E-6</v>
+        <v>-1.4525606013858741E-3</v>
       </c>
       <c r="M4">
-        <v>-6.334927569330672E-6</v>
+        <v>2.2220543106336079E-4</v>
       </c>
       <c r="N4">
-        <v>1.0641887004716853E-6</v>
+        <v>1.8725887266969572E-4</v>
       </c>
       <c r="O4">
-        <v>-4.3346540775572345E-6</v>
+        <v>-5.5656860961452946E-5</v>
       </c>
       <c r="P4">
-        <v>2.7854452812609953E-6</v>
+        <v>-2.3943494467838302E-5</v>
       </c>
       <c r="Q4">
-        <v>-6.8873252340333591E-7</v>
+        <v>-1.1959580129725287E-4</v>
       </c>
       <c r="R4">
-        <v>-3.8733377050689871E-6</v>
+        <v>-1.8748297432304904E-4</v>
       </c>
       <c r="S4">
-        <v>-1.5110731512861124E-7</v>
+        <v>-8.0600599087710247E-5</v>
       </c>
       <c r="T4">
-        <v>-1.3160597573091725E-6</v>
+        <v>-5.4369636128645494E-4</v>
       </c>
       <c r="U4">
-        <v>-5.1045451649922374E-4</v>
+        <v>-4.8929467061598619E-3</v>
       </c>
       <c r="V4">
-        <v>-8.4639509762888575E-6</v>
+        <v>-9.9873072646448641E-4</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B5">
-        <v>-5.1626368399867062E-2</v>
+        <v>-0.22783090673449602</v>
       </c>
       <c r="C5">
-        <v>1.6326411118274609E-5</v>
+        <v>-2.3345986039571015E-4</v>
       </c>
       <c r="D5">
-        <v>-6.5795851982129797E-8</v>
+        <v>5.2546146444083756E-6</v>
       </c>
       <c r="E5">
-        <v>4.8379469601322959E-4</v>
+        <v>8.3879515858163098E-3</v>
       </c>
       <c r="F5">
-        <v>3.7793165632434198E-3</v>
+        <v>2.0521614328149581E-2</v>
       </c>
       <c r="G5">
-        <v>-1.0948598845358577E-5</v>
+        <v>-1.8375827991104604E-4</v>
       </c>
       <c r="H5">
-        <v>-7.9016785077437999E-5</v>
+        <v>-4.2414711611733107E-4</v>
       </c>
       <c r="I5">
-        <v>-5.539426667007558E-5</v>
+        <v>-2.6347930415596284E-3</v>
       </c>
       <c r="J5">
-        <v>-7.3916246237321225E-5</v>
+        <v>-2.8407613334950495E-3</v>
       </c>
       <c r="K5">
-        <v>-8.0358843661520777E-5</v>
+        <v>-3.1384509701010851E-3</v>
       </c>
       <c r="L5">
-        <v>-6.116903916242425E-5</v>
+        <v>-3.3070154860624307E-3</v>
       </c>
       <c r="M5">
-        <v>-7.7391183593353212E-6</v>
+        <v>5.1170044442761355E-4</v>
       </c>
       <c r="N5">
-        <v>8.1410886955374992E-6</v>
+        <v>4.8792858602404206E-4</v>
       </c>
       <c r="O5">
-        <v>-1.3202955628964108E-6</v>
+        <v>-8.8588823600110759E-5</v>
       </c>
       <c r="P5">
-        <v>8.7063768746210081E-6</v>
+        <v>3.9479249936121684E-5</v>
       </c>
       <c r="Q5">
-        <v>-3.3396181597798519E-6</v>
+        <v>-1.5371132259709943E-4</v>
       </c>
       <c r="R5">
-        <v>-2.0536583593198589E-5</v>
+        <v>-2.051110400056282E-3</v>
       </c>
       <c r="S5">
-        <v>-4.6724798017734076E-6</v>
+        <v>-2.8195107445244433E-4</v>
       </c>
       <c r="T5">
-        <v>-7.9777537268594786E-6</v>
+        <v>-1.5058002440121805E-3</v>
       </c>
       <c r="U5">
-        <v>-4.3898166601645397E-4</v>
+        <v>8.8085569933950437E-3</v>
       </c>
       <c r="V5">
-        <v>-5.7297673208809368E-5</v>
+        <v>-2.8778994419941971E-3</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B6">
-        <v>-9.8341271429091531E-3</v>
+        <v>-5.2959442803548152E-3</v>
       </c>
       <c r="C6">
-        <v>-3.1390895529854434E-7</v>
+        <v>-9.3680138732286656E-6</v>
       </c>
       <c r="D6">
-        <v>6.2399804685593934E-10</v>
+        <v>5.2422896552103234E-8</v>
       </c>
       <c r="E6">
-        <v>-1.7611317740275793E-5</v>
+        <v>-2.8558812212106394E-4</v>
       </c>
       <c r="F6">
-        <v>-1.0948598845358577E-5</v>
+        <v>-1.8375827991104604E-4</v>
       </c>
       <c r="G6">
-        <v>4.1642172073558963E-7</v>
+        <v>7.462237205378919E-6</v>
       </c>
       <c r="H6">
-        <v>2.6551616765533746E-7</v>
+        <v>4.9976680668069179E-6</v>
       </c>
       <c r="I6">
-        <v>4.10826020822006E-8</v>
+        <v>1.053556201968413E-5</v>
       </c>
       <c r="J6">
-        <v>1.7120710914847456E-7</v>
+        <v>2.161755450795132E-6</v>
       </c>
       <c r="K6">
-        <v>3.7509380629311956E-7</v>
+        <v>1.563052923723596E-6</v>
       </c>
       <c r="L6">
-        <v>2.2813911364762507E-7</v>
+        <v>7.6963091676077292E-8</v>
       </c>
       <c r="M6">
-        <v>1.1343049775971018E-7</v>
+        <v>2.7261930927279043E-6</v>
       </c>
       <c r="N6">
-        <v>7.8546663538919346E-9</v>
+        <v>6.267467877346954E-6</v>
       </c>
       <c r="O6">
-        <v>1.089806462690597E-7</v>
+        <v>-3.1522496561707523E-6</v>
       </c>
       <c r="P6">
-        <v>-5.4679950134618622E-9</v>
+        <v>-9.5672012432598871E-7</v>
       </c>
       <c r="Q6">
-        <v>1.2006212049751726E-7</v>
+        <v>3.0251054641463584E-6</v>
       </c>
       <c r="R6">
-        <v>4.0970008435576205E-7</v>
+        <v>1.2364215652430843E-5</v>
       </c>
       <c r="S6">
-        <v>-1.8666865736887262E-8</v>
+        <v>-3.4865252881937108E-6</v>
       </c>
       <c r="T6">
-        <v>4.6432941710986602E-9</v>
+        <v>-6.2647933874519696E-6</v>
       </c>
       <c r="U6">
-        <v>1.0964031381647645E-5</v>
+        <v>2.8645474604507663E-4</v>
       </c>
       <c r="V6">
-        <v>4.150578894592855E-8</v>
+        <v>-1.9206655342458081E-5</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B7">
-        <v>-1.3186557885890449E-2</v>
+        <v>-7.0453206658569285E-3</v>
       </c>
       <c r="C7">
-        <v>-3.5306934052010016E-7</v>
+        <v>-3.362430436697574E-6</v>
       </c>
       <c r="D7">
-        <v>1.1019388075021572E-9</v>
+        <v>-2.0960584102242777E-8</v>
       </c>
       <c r="E7">
-        <v>-1.1002311805839985E-5</v>
+        <v>-1.9046224365598175E-4</v>
       </c>
       <c r="F7">
-        <v>-7.9016785077437999E-5</v>
+        <v>-4.2414711611733107E-4</v>
       </c>
       <c r="G7">
-        <v>2.6551616765533746E-7</v>
+        <v>4.9976680668069179E-6</v>
       </c>
       <c r="H7">
-        <v>1.7724769526214488E-6</v>
+        <v>1.0129264667709616E-5</v>
       </c>
       <c r="I7">
-        <v>1.5365725381973936E-6</v>
+        <v>1.8460011237635669E-5</v>
       </c>
       <c r="J7">
-        <v>2.0033696908774094E-6</v>
+        <v>1.4677220051661651E-5</v>
       </c>
       <c r="K7">
-        <v>2.368215489957859E-6</v>
+        <v>2.033546549201903E-5</v>
       </c>
       <c r="L7">
-        <v>2.0532796698277411E-6</v>
+        <v>1.9389534187140499E-5</v>
       </c>
       <c r="M7">
-        <v>3.9839231209358005E-8</v>
+        <v>5.5974118325599094E-7</v>
       </c>
       <c r="N7">
-        <v>-1.3715144143958095E-7</v>
+        <v>3.6842275101691257E-6</v>
       </c>
       <c r="O7">
-        <v>-8.198849708304484E-8</v>
+        <v>-3.9792124518817337E-6</v>
       </c>
       <c r="P7">
-        <v>-1.5605197627059473E-7</v>
+        <v>-1.6418138085716725E-6</v>
       </c>
       <c r="Q7">
-        <v>9.6208930351677977E-8</v>
+        <v>3.8730051560912073E-6</v>
       </c>
       <c r="R7">
-        <v>8.9332821825992187E-7</v>
+        <v>3.6942521814441489E-5</v>
       </c>
       <c r="S7">
-        <v>3.5809783503687078E-8</v>
+        <v>-2.9336995718296662E-7</v>
       </c>
       <c r="T7">
-        <v>1.1100070132392949E-7</v>
+        <v>4.6701889924085084E-6</v>
       </c>
       <c r="U7">
-        <v>8.8086976822022036E-6</v>
+        <v>1.0943763645504119E-4</v>
       </c>
       <c r="V7">
-        <v>7.6765534369444682E-7</v>
+        <v>-3.4499374508852628E-6</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B8">
-        <v>0.25266283698278746</v>
+        <v>-2.6062419482344289E-2</v>
       </c>
       <c r="C8">
-        <v>5.2191933898302608E-7</v>
+        <v>4.7105205314027296E-4</v>
       </c>
       <c r="D8">
-        <v>-6.5843705748059433E-9</v>
+        <v>-5.9805886387292323E-6</v>
       </c>
       <c r="E8">
-        <v>-7.865472667699858E-6</v>
+        <v>-1.3911502880833444E-3</v>
       </c>
       <c r="F8">
-        <v>-5.539426667007558E-5</v>
+        <v>-2.6347930415596284E-3</v>
       </c>
       <c r="G8">
-        <v>4.10826020822006E-8</v>
+        <v>1.053556201968413E-5</v>
       </c>
       <c r="H8">
-        <v>1.5365725381973936E-6</v>
+        <v>1.8460011237635669E-5</v>
       </c>
       <c r="I8">
-        <v>4.9814160041648948E-3</v>
+        <v>9.6581367292502648E-2</v>
       </c>
       <c r="J8">
-        <v>4.642987910200163E-3</v>
+        <v>9.0645570088195779E-2</v>
       </c>
       <c r="K8">
-        <v>4.6440059131953341E-3</v>
+        <v>9.0856222784729393E-2</v>
       </c>
       <c r="L8">
-        <v>4.6430454194559892E-3</v>
+        <v>9.1146006910698574E-2</v>
       </c>
       <c r="M8">
-        <v>8.7571890926467982E-7</v>
+        <v>-8.8951944418063917E-4</v>
       </c>
       <c r="N8">
-        <v>-4.4767064247061674E-6</v>
+        <v>-9.0858776315488562E-4</v>
       </c>
       <c r="O8">
-        <v>5.764249474513149E-7</v>
+        <v>6.7028825939564418E-5</v>
       </c>
       <c r="P8">
-        <v>-5.2626834488531347E-6</v>
+        <v>2.2030414203348443E-5</v>
       </c>
       <c r="Q8">
-        <v>-4.5357289000522897E-6</v>
+        <v>-1.1308127289165649E-4</v>
       </c>
       <c r="R8">
-        <v>2.4194926851590166E-5</v>
+        <v>2.8881097458283199E-3</v>
       </c>
       <c r="S8">
-        <v>-1.9783342120422524E-7</v>
+        <v>3.1064610612354499E-4</v>
       </c>
       <c r="T8">
-        <v>5.1170373967533359E-6</v>
+        <v>1.7018835840419834E-3</v>
       </c>
       <c r="U8">
-        <v>-4.6960094683195733E-3</v>
+        <v>-0.10692744616444759</v>
       </c>
       <c r="V8">
-        <v>2.5454487580777366E-5</v>
+        <v>3.8280020027675328E-3</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B9">
-        <v>0.29410427287171287</v>
+        <v>-6.1238473009558557E-2</v>
       </c>
       <c r="C9">
-        <v>1.5333570311600105E-6</v>
+        <v>5.4099170654948775E-4</v>
       </c>
       <c r="D9">
-        <v>-1.7337317680154612E-8</v>
+        <v>-6.7640489084881196E-6</v>
       </c>
       <c r="E9">
-        <v>-1.3320142693466829E-5</v>
+        <v>-1.3271723444661151E-3</v>
       </c>
       <c r="F9">
-        <v>-7.3916246237321225E-5</v>
+        <v>-2.8407613334950495E-3</v>
       </c>
       <c r="G9">
-        <v>1.7120710914847456E-7</v>
+        <v>2.161755450795132E-6</v>
       </c>
       <c r="H9">
-        <v>2.0033696908774094E-6</v>
+        <v>1.4677220051661651E-5</v>
       </c>
       <c r="I9">
-        <v>4.642987910200163E-3</v>
+        <v>9.0645570088195779E-2</v>
       </c>
       <c r="J9">
-        <v>4.6978913669749106E-3</v>
+        <v>9.2430530845569306E-2</v>
       </c>
       <c r="K9">
-        <v>4.6525024714090396E-3</v>
+        <v>9.1369564158280653E-2</v>
       </c>
       <c r="L9">
-        <v>4.6526163724035091E-3</v>
+        <v>9.1716522200272182E-2</v>
       </c>
       <c r="M9">
-        <v>9.1024168433282592E-7</v>
+        <v>-1.0574363652000266E-3</v>
       </c>
       <c r="N9">
-        <v>-2.8192306166854556E-6</v>
+        <v>-1.0571718624436742E-3</v>
       </c>
       <c r="O9">
-        <v>9.5263544203907789E-7</v>
+        <v>1.4680517044961798E-4</v>
       </c>
       <c r="P9">
-        <v>-4.2182862533434023E-6</v>
+        <v>6.3915464237709039E-5</v>
       </c>
       <c r="Q9">
-        <v>-4.1540721187930334E-6</v>
+        <v>-9.8027294940902283E-5</v>
       </c>
       <c r="R9">
-        <v>2.1352725318492084E-5</v>
+        <v>2.3448777804044138E-3</v>
       </c>
       <c r="S9">
-        <v>2.5414739963321016E-6</v>
+        <v>4.4188724903328896E-4</v>
       </c>
       <c r="T9">
-        <v>6.4098652877563625E-6</v>
+        <v>2.1026754193476218E-3</v>
       </c>
       <c r="U9">
-        <v>-4.7361894065869568E-3</v>
+        <v>-0.10919714688044999</v>
       </c>
       <c r="V9">
-        <v>3.8894849895047118E-5</v>
+        <v>4.513835269719357E-3</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B10">
-        <v>0.35873814592203379</v>
+        <v>1.6140266443714923E-2</v>
       </c>
       <c r="C10">
-        <v>1.1389036250969674E-6</v>
+        <v>5.7640449670552456E-4</v>
       </c>
       <c r="D10">
-        <v>-7.2640635384731349E-9</v>
+        <v>-7.1442242311663476E-6</v>
       </c>
       <c r="E10">
-        <v>-1.8117103300378176E-5</v>
+        <v>-1.3906501903379392E-3</v>
       </c>
       <c r="F10">
-        <v>-8.0358843661520777E-5</v>
+        <v>-3.1384509701010851E-3</v>
       </c>
       <c r="G10">
-        <v>3.7509380629311956E-7</v>
+        <v>1.563052923723596E-6</v>
       </c>
       <c r="H10">
-        <v>2.368215489957859E-6</v>
+        <v>2.033546549201903E-5</v>
       </c>
       <c r="I10">
-        <v>4.6440059131953341E-3</v>
+        <v>9.0856222784729393E-2</v>
       </c>
       <c r="J10">
-        <v>4.6525024714090396E-3</v>
+        <v>9.1369564158280653E-2</v>
       </c>
       <c r="K10">
-        <v>4.6773847922887144E-3</v>
+        <v>9.2005016390276584E-2</v>
       </c>
       <c r="L10">
-        <v>4.6642742399150595E-3</v>
+        <v>9.2162776601109914E-2</v>
       </c>
       <c r="M10">
-        <v>2.2501797838620241E-7</v>
+        <v>-1.1031736460954513E-3</v>
       </c>
       <c r="N10">
-        <v>-2.5275191433853335E-6</v>
+        <v>-1.1397117037361499E-3</v>
       </c>
       <c r="O10">
-        <v>6.608814400247033E-7</v>
+        <v>1.6540192691081348E-4</v>
       </c>
       <c r="P10">
-        <v>-3.9527787390018319E-6</v>
+        <v>9.2895449377482841E-5</v>
       </c>
       <c r="Q10">
-        <v>-2.4499808589349135E-6</v>
+        <v>-1.3968121930578919E-4</v>
       </c>
       <c r="R10">
-        <v>1.2530601748771119E-5</v>
+        <v>2.9874743074261301E-3</v>
       </c>
       <c r="S10">
-        <v>2.6039138551776302E-6</v>
+        <v>6.565299668557182E-4</v>
       </c>
       <c r="T10">
-        <v>5.3954385962878996E-6</v>
+        <v>2.2895906071473153E-3</v>
       </c>
       <c r="U10">
-        <v>-4.7412987243796636E-3</v>
+        <v>-0.11156476857144779</v>
       </c>
       <c r="V10">
-        <v>4.1282103330686993E-5</v>
+        <v>4.9240621591487644E-3</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B11">
-        <v>0.40095122004670641</v>
+        <v>3.9681247247912138E-2</v>
       </c>
       <c r="C11">
-        <v>3.8684506068066719E-6</v>
+        <v>6.4674039660667202E-4</v>
       </c>
       <c r="D11">
-        <v>-3.0220150384792202E-8</v>
+        <v>-7.9460824939888855E-6</v>
       </c>
       <c r="E11">
-        <v>-8.2831931574261925E-6</v>
+        <v>-1.4525606013858741E-3</v>
       </c>
       <c r="F11">
-        <v>-6.116903916242425E-5</v>
+        <v>-3.3070154860624307E-3</v>
       </c>
       <c r="G11">
-        <v>2.2813911364762507E-7</v>
+        <v>7.6963091676077292E-8</v>
       </c>
       <c r="H11">
-        <v>2.0532796698277411E-6</v>
+        <v>1.9389534187140499E-5</v>
       </c>
       <c r="I11">
-        <v>4.6430454194559892E-3</v>
+        <v>9.1146006910698574E-2</v>
       </c>
       <c r="J11">
-        <v>4.6526163724035091E-3</v>
+        <v>9.1716522200272182E-2</v>
       </c>
       <c r="K11">
-        <v>4.6642742399150595E-3</v>
+        <v>9.2162776601109914E-2</v>
       </c>
       <c r="L11">
-        <v>4.7324516091255282E-3</v>
+        <v>9.3400116919707885E-2</v>
       </c>
       <c r="M11">
-        <v>1.1887182061167092E-6</v>
+        <v>-1.2321033944326576E-3</v>
       </c>
       <c r="N11">
-        <v>-1.2672049938006944E-6</v>
+        <v>-1.2512254646217667E-3</v>
       </c>
       <c r="O11">
-        <v>6.9135600228445518E-7</v>
+        <v>2.5196717318878381E-4</v>
       </c>
       <c r="P11">
-        <v>-2.0099333693214594E-6</v>
+        <v>1.3666586484161879E-4</v>
       </c>
       <c r="Q11">
-        <v>-1.8111083809447791E-6</v>
+        <v>-1.1999188326779785E-4</v>
       </c>
       <c r="R11">
-        <v>1.139598804064136E-5</v>
+        <v>2.5315197087920674E-3</v>
       </c>
       <c r="S11">
-        <v>3.946935447268987E-6</v>
+        <v>7.5624436370591585E-4</v>
       </c>
       <c r="T11">
-        <v>6.06715764828386E-6</v>
+        <v>2.4504579611552644E-3</v>
       </c>
       <c r="U11">
-        <v>-4.8201081387825809E-3</v>
+        <v>-0.11360098510254368</v>
       </c>
       <c r="V11">
-        <v>4.1543267275669267E-5</v>
+        <v>5.426156981275224E-3</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.45">
@@ -1399,67 +1375,67 @@
         <v>35</v>
       </c>
       <c r="B12">
-        <v>-8.9199940310972243E-3</v>
+        <v>-0.17777408674849585</v>
       </c>
       <c r="C12">
-        <v>-3.100608382898743E-8</v>
+        <v>-1.749208999402189E-4</v>
       </c>
       <c r="D12">
-        <v>-3.416234983635163E-10</v>
+        <v>2.1434261261617941E-6</v>
       </c>
       <c r="E12">
-        <v>-6.334927569330672E-6</v>
+        <v>2.2220543106336079E-4</v>
       </c>
       <c r="F12">
-        <v>-7.7391183593353212E-6</v>
+        <v>5.1170044442761355E-4</v>
       </c>
       <c r="G12">
-        <v>1.1343049775971018E-7</v>
+        <v>2.7261930927279043E-6</v>
       </c>
       <c r="H12">
-        <v>3.9839231209358005E-8</v>
+        <v>5.5974118325599094E-7</v>
       </c>
       <c r="I12">
-        <v>8.7571890926467982E-7</v>
+        <v>-8.8951944418063917E-4</v>
       </c>
       <c r="J12">
-        <v>9.1024168433282592E-7</v>
+        <v>-1.0574363652000266E-3</v>
       </c>
       <c r="K12">
-        <v>2.2501797838620241E-7</v>
+        <v>-1.1031736460954513E-3</v>
       </c>
       <c r="L12">
-        <v>1.1887182061167092E-6</v>
+        <v>-1.2321033944326576E-3</v>
       </c>
       <c r="M12">
-        <v>1.2301889008553186E-4</v>
+        <v>1.8270483502629516E-3</v>
       </c>
       <c r="N12">
-        <v>5.9457007376851358E-5</v>
+        <v>1.1182534791166899E-3</v>
       </c>
       <c r="O12">
-        <v>5.9825777446713687E-5</v>
+        <v>6.5062221529567029E-4</v>
       </c>
       <c r="P12">
-        <v>5.9517611767108685E-5</v>
+        <v>7.4801487074346688E-4</v>
       </c>
       <c r="Q12">
-        <v>2.7783891052751376E-6</v>
+        <v>1.8150064821113531E-5</v>
       </c>
       <c r="R12">
-        <v>-1.3177164999498923E-5</v>
+        <v>1.2064221123264341E-3</v>
       </c>
       <c r="S12">
-        <v>-2.6235525453672721E-7</v>
+        <v>-2.4062783268692021E-4</v>
       </c>
       <c r="T12">
-        <v>-6.0972876199782736E-7</v>
+        <v>-6.8169546146573277E-4</v>
       </c>
       <c r="U12">
-        <v>-4.4212135527625123E-5</v>
+        <v>4.1908342218757444E-3</v>
       </c>
       <c r="V12">
-        <v>1.7258603046282383E-6</v>
+        <v>-1.351217411376508E-3</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.45">
@@ -1467,67 +1443,67 @@
         <v>36</v>
       </c>
       <c r="B13">
-        <v>1.3449135636994387E-2</v>
+        <v>-0.19847482200694386</v>
       </c>
       <c r="C13">
-        <v>7.7706159693911757E-7</v>
+        <v>-2.1360007519683209E-4</v>
       </c>
       <c r="D13">
-        <v>-9.3900051489581933E-9</v>
+        <v>2.6116226047795972E-6</v>
       </c>
       <c r="E13">
-        <v>1.0641887004716853E-6</v>
+        <v>1.8725887266969572E-4</v>
       </c>
       <c r="F13">
-        <v>8.1410886955374992E-6</v>
+        <v>4.8792858602404206E-4</v>
       </c>
       <c r="G13">
-        <v>7.8546663538919346E-9</v>
+        <v>6.267467877346954E-6</v>
       </c>
       <c r="H13">
-        <v>-1.3715144143958095E-7</v>
+        <v>3.6842275101691257E-6</v>
       </c>
       <c r="I13">
-        <v>-4.4767064247061674E-6</v>
+        <v>-9.0858776315488562E-4</v>
       </c>
       <c r="J13">
-        <v>-2.8192306166854556E-6</v>
+        <v>-1.0571718624436742E-3</v>
       </c>
       <c r="K13">
-        <v>-2.5275191433853335E-6</v>
+        <v>-1.1397117037361499E-3</v>
       </c>
       <c r="L13">
-        <v>-1.2672049938006944E-6</v>
+        <v>-1.2512254646217667E-3</v>
       </c>
       <c r="M13">
-        <v>5.9457007376851358E-5</v>
+        <v>1.1182534791166899E-3</v>
       </c>
       <c r="N13">
-        <v>1.5752153404082584E-4</v>
+        <v>3.3683438755707442E-3</v>
       </c>
       <c r="O13">
-        <v>5.9547185732558176E-5</v>
+        <v>6.2294898017937615E-4</v>
       </c>
       <c r="P13">
-        <v>5.9585445088241518E-5</v>
+        <v>7.4281589209324104E-4</v>
       </c>
       <c r="Q13">
-        <v>1.3827517990428919E-6</v>
+        <v>1.2094670603611547E-5</v>
       </c>
       <c r="R13">
-        <v>-7.5082575300085826E-6</v>
+        <v>2.6933984859881053E-3</v>
       </c>
       <c r="S13">
-        <v>-5.6925125257676772E-8</v>
+        <v>-4.1507904617950353E-4</v>
       </c>
       <c r="T13">
-        <v>-2.8923685899761343E-7</v>
+        <v>-8.8489101380520964E-4</v>
       </c>
       <c r="U13">
-        <v>-6.6044690678816447E-5</v>
+        <v>3.9118650118738253E-3</v>
       </c>
       <c r="V13">
-        <v>1.5353650857194497E-6</v>
+        <v>-1.6797866840371082E-3</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.45">
@@ -1535,543 +1511,543 @@
         <v>37</v>
       </c>
       <c r="B14">
-        <v>-9.9265634294780983E-3</v>
+        <v>-2.8039147385485025E-3</v>
       </c>
       <c r="C14">
-        <v>1.0873296208038032E-7</v>
+        <v>6.7007436290012043E-5</v>
       </c>
       <c r="D14">
-        <v>-2.6171936184743102E-9</v>
+        <v>-7.9323432294775308E-7</v>
       </c>
       <c r="E14">
-        <v>-4.3346540775572345E-6</v>
+        <v>-5.5656860961452946E-5</v>
       </c>
       <c r="F14">
-        <v>-1.3202955628964108E-6</v>
+        <v>-8.8588823600110759E-5</v>
       </c>
       <c r="G14">
-        <v>1.089806462690597E-7</v>
+        <v>-3.1522496561707523E-6</v>
       </c>
       <c r="H14">
-        <v>-8.198849708304484E-8</v>
+        <v>-3.9792124518817337E-6</v>
       </c>
       <c r="I14">
-        <v>5.764249474513149E-7</v>
+        <v>6.7028825939564418E-5</v>
       </c>
       <c r="J14">
-        <v>9.5263544203907789E-7</v>
+        <v>1.4680517044961798E-4</v>
       </c>
       <c r="K14">
-        <v>6.608814400247033E-7</v>
+        <v>1.6540192691081348E-4</v>
       </c>
       <c r="L14">
-        <v>6.9135600228445518E-7</v>
+        <v>2.5196717318878381E-4</v>
       </c>
       <c r="M14">
-        <v>5.9825777446713687E-5</v>
+        <v>6.5062221529567029E-4</v>
       </c>
       <c r="N14">
-        <v>5.9547185732558176E-5</v>
+        <v>6.2294898017937615E-4</v>
       </c>
       <c r="O14">
-        <v>1.1913720391624752E-4</v>
+        <v>1.4466114539657248E-3</v>
       </c>
       <c r="P14">
-        <v>5.964780316520743E-5</v>
+        <v>7.7277893388397732E-4</v>
       </c>
       <c r="Q14">
-        <v>1.6251272993979422E-6</v>
+        <v>4.5117756285089599E-6</v>
       </c>
       <c r="R14">
-        <v>-1.5086877588142124E-5</v>
+        <v>-9.7824641992792023E-4</v>
       </c>
       <c r="S14">
-        <v>7.5268002930410567E-7</v>
+        <v>1.0957233009678633E-4</v>
       </c>
       <c r="T14">
-        <v>-7.7487311624946921E-9</v>
+        <v>2.2806369012781715E-4</v>
       </c>
       <c r="U14">
-        <v>-4.4969180346210916E-5</v>
+        <v>-1.9282376813378054E-3</v>
       </c>
       <c r="V14">
-        <v>1.6461849389177788E-6</v>
+        <v>5.3514325010901496E-4</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B15">
-        <v>-4.5004641239292258E-2</v>
+        <v>-6.1505877395688503E-2</v>
       </c>
       <c r="C15">
-        <v>1.2737303853425186E-7</v>
+        <v>1.850901370848642E-7</v>
       </c>
       <c r="D15">
-        <v>-1.9750139829535358E-9</v>
+        <v>-8.2744893217838418E-9</v>
       </c>
       <c r="E15">
-        <v>2.7854452812609953E-6</v>
+        <v>-2.3943494467838302E-5</v>
       </c>
       <c r="F15">
-        <v>8.7063768746210081E-6</v>
+        <v>3.9479249936121684E-5</v>
       </c>
       <c r="G15">
-        <v>-5.4679950134618622E-9</v>
+        <v>-9.5672012432598871E-7</v>
       </c>
       <c r="H15">
-        <v>-1.5605197627059473E-7</v>
+        <v>-1.6418138085716725E-6</v>
       </c>
       <c r="I15">
-        <v>-5.2626834488531347E-6</v>
+        <v>2.2030414203348443E-5</v>
       </c>
       <c r="J15">
-        <v>-4.2182862533434023E-6</v>
+        <v>6.3915464237709039E-5</v>
       </c>
       <c r="K15">
-        <v>-3.9527787390018319E-6</v>
+        <v>9.2895449377482841E-5</v>
       </c>
       <c r="L15">
-        <v>-2.0099333693214594E-6</v>
+        <v>1.3666586484161879E-4</v>
       </c>
       <c r="M15">
-        <v>5.9517611767108685E-5</v>
+        <v>7.4801487074346688E-4</v>
       </c>
       <c r="N15">
-        <v>5.9585445088241518E-5</v>
+        <v>7.4281589209324104E-4</v>
       </c>
       <c r="O15">
-        <v>5.964780316520743E-5</v>
+        <v>7.7277893388397732E-4</v>
       </c>
       <c r="P15">
-        <v>8.5160854250551594E-5</v>
+        <v>1.3800441039014703E-3</v>
       </c>
       <c r="Q15">
-        <v>2.1381320190663249E-6</v>
+        <v>1.5554794786081872E-5</v>
       </c>
       <c r="R15">
-        <v>-1.1092558206494613E-5</v>
+        <v>1.0681945987410578E-4</v>
       </c>
       <c r="S15">
-        <v>-8.0140731069668757E-8</v>
+        <v>-5.8708703395426678E-6</v>
       </c>
       <c r="T15">
-        <v>-2.8637878540146369E-7</v>
+        <v>9.3353140351223857E-6</v>
       </c>
       <c r="U15">
-        <v>-4.6134763612868178E-5</v>
+        <v>-1.0406581705662919E-3</v>
       </c>
       <c r="V15">
-        <v>-9.2366252541108526E-7</v>
+        <v>7.9087015533610582E-5</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B16">
-        <v>0.28079649297649306</v>
+        <v>0.22638519924772518</v>
       </c>
       <c r="C16">
-        <v>7.6020354002806439E-7</v>
+        <v>-2.4740028022701483E-5</v>
       </c>
       <c r="D16">
-        <v>-1.0622229993644364E-8</v>
+        <v>2.8089554223575157E-7</v>
       </c>
       <c r="E16">
-        <v>-6.8873252340333591E-7</v>
+        <v>-1.1959580129725287E-4</v>
       </c>
       <c r="F16">
-        <v>-3.3396181597798519E-6</v>
+        <v>-1.5371132259709943E-4</v>
       </c>
       <c r="G16">
-        <v>1.2006212049751726E-7</v>
+        <v>3.0251054641463584E-6</v>
       </c>
       <c r="H16">
-        <v>9.6208930351677977E-8</v>
+        <v>3.8730051560912073E-6</v>
       </c>
       <c r="I16">
-        <v>-4.5357289000522897E-6</v>
+        <v>-1.1308127289165649E-4</v>
       </c>
       <c r="J16">
-        <v>-4.1540721187930334E-6</v>
+        <v>-9.8027294940902283E-5</v>
       </c>
       <c r="K16">
-        <v>-2.4499808589349135E-6</v>
+        <v>-1.3968121930578919E-4</v>
       </c>
       <c r="L16">
-        <v>-1.8111083809447791E-6</v>
+        <v>-1.1999188326779785E-4</v>
       </c>
       <c r="M16">
-        <v>2.7783891052751376E-6</v>
+        <v>1.8150064821113531E-5</v>
       </c>
       <c r="N16">
-        <v>1.3827517990428919E-6</v>
+        <v>1.2094670603611547E-5</v>
       </c>
       <c r="O16">
-        <v>1.6251272993979422E-6</v>
+        <v>4.5117756285089599E-6</v>
       </c>
       <c r="P16">
-        <v>2.1381320190663249E-6</v>
+        <v>1.5554794786081872E-5</v>
       </c>
       <c r="Q16">
-        <v>1.5487180219899395E-4</v>
+        <v>8.0485541134912917E-4</v>
       </c>
       <c r="R16">
-        <v>1.7847213122547239E-5</v>
+        <v>9.8119311318216481E-4</v>
       </c>
       <c r="S16">
-        <v>-2.1847180456207114E-6</v>
+        <v>-1.1216893719790134E-4</v>
       </c>
       <c r="T16">
-        <v>-1.2501419709545241E-6</v>
+        <v>-8.3860062582489036E-5</v>
       </c>
       <c r="U16">
-        <v>-3.4494254653873996E-5</v>
+        <v>-2.8717662976465426E-4</v>
       </c>
       <c r="V16">
-        <v>-1.038499870096442E-5</v>
+        <v>-1.8943193793154417E-4</v>
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B17">
-        <v>0.46644608003998045</v>
+        <v>0.14201612750564807</v>
       </c>
       <c r="C17">
-        <v>-6.0182714182736144E-7</v>
+        <v>-3.8238617730593032E-4</v>
       </c>
       <c r="D17">
-        <v>-6.3744218054156889E-9</v>
+        <v>5.1241338089540094E-6</v>
       </c>
       <c r="E17">
-        <v>-3.8733377050689871E-6</v>
+        <v>-1.8748297432304904E-4</v>
       </c>
       <c r="F17">
-        <v>-2.0536583593198589E-5</v>
+        <v>-2.051110400056282E-3</v>
       </c>
       <c r="G17">
-        <v>4.0970008435576205E-7</v>
+        <v>1.2364215652430843E-5</v>
       </c>
       <c r="H17">
-        <v>8.9332821825992187E-7</v>
+        <v>3.6942521814441489E-5</v>
       </c>
       <c r="I17">
-        <v>2.4194926851590166E-5</v>
+        <v>2.8881097458283199E-3</v>
       </c>
       <c r="J17">
-        <v>2.1352725318492084E-5</v>
+        <v>2.3448777804044138E-3</v>
       </c>
       <c r="K17">
-        <v>1.2530601748771119E-5</v>
+        <v>2.9874743074261301E-3</v>
       </c>
       <c r="L17">
-        <v>1.139598804064136E-5</v>
+        <v>2.5315197087920674E-3</v>
       </c>
       <c r="M17">
-        <v>-1.3177164999498923E-5</v>
+        <v>1.2064221123264341E-3</v>
       </c>
       <c r="N17">
-        <v>-7.5082575300085826E-6</v>
+        <v>2.6933984859881053E-3</v>
       </c>
       <c r="O17">
-        <v>-1.5086877588142124E-5</v>
+        <v>-9.7824641992792023E-4</v>
       </c>
       <c r="P17">
-        <v>-1.1092558206494613E-5</v>
+        <v>1.0681945987410578E-4</v>
       </c>
       <c r="Q17">
-        <v>1.7847213122547239E-5</v>
+        <v>9.8119311318216481E-4</v>
       </c>
       <c r="R17">
-        <v>8.1902626246768489E-4</v>
+        <v>1.0144047046431655</v>
       </c>
       <c r="S17">
-        <v>-1.4087317886538192E-4</v>
+        <v>-4.7135620688310509E-2</v>
       </c>
       <c r="T17">
-        <v>-1.616471109135661E-4</v>
+        <v>-7.9902379597508507E-3</v>
       </c>
       <c r="U17">
-        <v>-8.370977666342979E-4</v>
+        <v>-0.99812461564508381</v>
       </c>
       <c r="V17">
-        <v>-4.8168792072994974E-6</v>
+        <v>-3.5179069176411999E-3</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B18">
-        <v>-4.0781018843480737E-3</v>
+        <v>-0.18062406896603223</v>
       </c>
       <c r="C18">
-        <v>1.6723042664373846E-6</v>
+        <v>1.2999972952604054E-4</v>
       </c>
       <c r="D18">
-        <v>-1.8232313064430036E-8</v>
+        <v>-1.6162160863925796E-6</v>
       </c>
       <c r="E18">
-        <v>-1.5110731512861124E-7</v>
+        <v>-8.0600599087710247E-5</v>
       </c>
       <c r="F18">
-        <v>-4.6724798017734076E-6</v>
+        <v>-2.8195107445244433E-4</v>
       </c>
       <c r="G18">
-        <v>-1.8666865736887262E-8</v>
+        <v>-3.4865252881937108E-6</v>
       </c>
       <c r="H18">
-        <v>3.5809783503687078E-8</v>
+        <v>-2.9336995718296662E-7</v>
       </c>
       <c r="I18">
-        <v>-1.9783342120422524E-7</v>
+        <v>3.1064610612354499E-4</v>
       </c>
       <c r="J18">
-        <v>2.5414739963321016E-6</v>
+        <v>4.4188724903328896E-4</v>
       </c>
       <c r="K18">
-        <v>2.6039138551776302E-6</v>
+        <v>6.565299668557182E-4</v>
       </c>
       <c r="L18">
-        <v>3.946935447268987E-6</v>
+        <v>7.5624436370591585E-4</v>
       </c>
       <c r="M18">
-        <v>-2.6235525453672721E-7</v>
+        <v>-2.4062783268692021E-4</v>
       </c>
       <c r="N18">
-        <v>-5.6925125257676772E-8</v>
+        <v>-4.1507904617950353E-4</v>
       </c>
       <c r="O18">
-        <v>7.5268002930410567E-7</v>
+        <v>1.0957233009678633E-4</v>
       </c>
       <c r="P18">
-        <v>-8.0140731069668757E-8</v>
+        <v>-5.8708703395426678E-6</v>
       </c>
       <c r="Q18">
-        <v>-2.1847180456207114E-6</v>
+        <v>-1.1216893719790134E-4</v>
       </c>
       <c r="R18">
-        <v>-1.4087317886538192E-4</v>
+        <v>-4.7135620688310509E-2</v>
       </c>
       <c r="S18">
-        <v>1.1796417293124136E-4</v>
+        <v>4.6658772898475641E-3</v>
       </c>
       <c r="T18">
-        <v>4.432242358333788E-5</v>
+        <v>1.0289481561818355E-3</v>
       </c>
       <c r="U18">
-        <v>8.1291031329707944E-5</v>
+        <v>4.2181682727426284E-2</v>
       </c>
       <c r="V18">
-        <v>1.8545150473114667E-5</v>
+        <v>1.0171249859269745E-3</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B19">
-        <v>7.9235929379585634E-3</v>
+        <v>0.2011207480003466</v>
       </c>
       <c r="C19">
-        <v>1.306520123698462E-6</v>
+        <v>3.8183766205598235E-4</v>
       </c>
       <c r="D19">
-        <v>-1.4326424739272051E-8</v>
+        <v>-4.8521421125753751E-6</v>
       </c>
       <c r="E19">
-        <v>-1.3160597573091725E-6</v>
+        <v>-5.4369636128645494E-4</v>
       </c>
       <c r="F19">
-        <v>-7.9777537268594786E-6</v>
+        <v>-1.5058002440121805E-3</v>
       </c>
       <c r="G19">
-        <v>4.6432941710986602E-9</v>
+        <v>-6.2647933874519696E-6</v>
       </c>
       <c r="H19">
-        <v>1.1100070132392949E-7</v>
+        <v>4.6701889924085084E-6</v>
       </c>
       <c r="I19">
-        <v>5.1170373967533359E-6</v>
+        <v>1.7018835840419834E-3</v>
       </c>
       <c r="J19">
-        <v>6.4098652877563625E-6</v>
+        <v>2.1026754193476218E-3</v>
       </c>
       <c r="K19">
-        <v>5.3954385962878996E-6</v>
+        <v>2.2895906071473153E-3</v>
       </c>
       <c r="L19">
-        <v>6.06715764828386E-6</v>
+        <v>2.4504579611552644E-3</v>
       </c>
       <c r="M19">
-        <v>-6.0972876199782736E-7</v>
+        <v>-6.8169546146573277E-4</v>
       </c>
       <c r="N19">
-        <v>-2.8923685899761343E-7</v>
+        <v>-8.8489101380520964E-4</v>
       </c>
       <c r="O19">
-        <v>-7.7487311624946921E-9</v>
+        <v>2.2806369012781715E-4</v>
       </c>
       <c r="P19">
-        <v>-2.8637878540146369E-7</v>
+        <v>9.3353140351223857E-6</v>
       </c>
       <c r="Q19">
-        <v>-1.2501419709545241E-6</v>
+        <v>-8.3860062582489036E-5</v>
       </c>
       <c r="R19">
-        <v>-1.616471109135661E-4</v>
+        <v>-7.9902379597508507E-3</v>
       </c>
       <c r="S19">
-        <v>4.432242358333788E-5</v>
+        <v>1.0289481561818355E-3</v>
       </c>
       <c r="T19">
-        <v>1.5609827590040652E-4</v>
+        <v>2.6286196956847091E-3</v>
       </c>
       <c r="U19">
-        <v>1.1056673832271717E-4</v>
+        <v>-5.6574496396115514E-3</v>
       </c>
       <c r="V19">
-        <v>1.6304672789199459E-5</v>
+        <v>3.2641922777059619E-3</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B20">
-        <v>0.34326791602459061</v>
+        <v>1.4666441633260661</v>
       </c>
       <c r="C20">
-        <v>-1.4909008787779339E-4</v>
+        <v>-4.4001154657403816E-3</v>
       </c>
       <c r="D20">
-        <v>1.6205969464593366E-6</v>
+        <v>5.1068068989269206E-5</v>
       </c>
       <c r="E20">
-        <v>-5.1045451649922374E-4</v>
+        <v>-4.8929467061598619E-3</v>
       </c>
       <c r="F20">
-        <v>-4.3898166601645397E-4</v>
+        <v>8.8085569933950437E-3</v>
       </c>
       <c r="G20">
-        <v>1.0964031381647645E-5</v>
+        <v>2.8645474604507663E-4</v>
       </c>
       <c r="H20">
-        <v>8.8086976822022036E-6</v>
+        <v>1.0943763645504119E-4</v>
       </c>
       <c r="I20">
-        <v>-4.6960094683195733E-3</v>
+        <v>-0.10692744616444759</v>
       </c>
       <c r="J20">
-        <v>-4.7361894065869568E-3</v>
+        <v>-0.10919714688044999</v>
       </c>
       <c r="K20">
-        <v>-4.7412987243796636E-3</v>
+        <v>-0.11156476857144779</v>
       </c>
       <c r="L20">
-        <v>-4.8201081387825809E-3</v>
+        <v>-0.11360098510254368</v>
       </c>
       <c r="M20">
-        <v>-4.4212135527625123E-5</v>
+        <v>4.1908342218757444E-3</v>
       </c>
       <c r="N20">
-        <v>-6.6044690678816447E-5</v>
+        <v>3.9118650118738253E-3</v>
       </c>
       <c r="O20">
-        <v>-4.4969180346210916E-5</v>
+        <v>-1.9282376813378054E-3</v>
       </c>
       <c r="P20">
-        <v>-4.6134763612868178E-5</v>
+        <v>-1.0406581705662919E-3</v>
       </c>
       <c r="Q20">
-        <v>-3.4494254653873996E-5</v>
+        <v>-2.8717662976465426E-4</v>
       </c>
       <c r="R20">
-        <v>-8.370977666342979E-4</v>
+        <v>-0.99812461564508381</v>
       </c>
       <c r="S20">
-        <v>8.1291031329707944E-5</v>
+        <v>4.2181682727426284E-2</v>
       </c>
       <c r="T20">
-        <v>1.1056673832271717E-4</v>
+        <v>-5.6574496396115514E-3</v>
       </c>
       <c r="U20">
-        <v>9.1804771868372777E-3</v>
+        <v>1.2211123254787692</v>
       </c>
       <c r="V20">
-        <v>-2.8811305494300663E-4</v>
+        <v>-2.4737473280106677E-2</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B21">
-        <v>-0.21114204408453274</v>
+        <v>-8.0415068536276321E-2</v>
       </c>
       <c r="C21">
-        <v>8.6004851812019255E-6</v>
+        <v>7.9591477924982894E-4</v>
       </c>
       <c r="D21">
-        <v>-9.8269788264392313E-8</v>
+        <v>-9.7768939686272123E-6</v>
       </c>
       <c r="E21">
-        <v>-8.4639509762888575E-6</v>
+        <v>-9.9873072646448641E-4</v>
       </c>
       <c r="F21">
-        <v>-5.7297673208809368E-5</v>
+        <v>-2.8778994419941971E-3</v>
       </c>
       <c r="G21">
-        <v>4.150578894592855E-8</v>
+        <v>-1.9206655342458081E-5</v>
       </c>
       <c r="H21">
-        <v>7.6765534369444682E-7</v>
+        <v>-3.4499374508852628E-6</v>
       </c>
       <c r="I21">
-        <v>2.5454487580777366E-5</v>
+        <v>3.8280020027675328E-3</v>
       </c>
       <c r="J21">
-        <v>3.8894849895047118E-5</v>
+        <v>4.513835269719357E-3</v>
       </c>
       <c r="K21">
-        <v>4.1282103330686993E-5</v>
+        <v>4.9240621591487644E-3</v>
       </c>
       <c r="L21">
-        <v>4.1543267275669267E-5</v>
+        <v>5.426156981275224E-3</v>
       </c>
       <c r="M21">
-        <v>1.7258603046282383E-6</v>
+        <v>-1.351217411376508E-3</v>
       </c>
       <c r="N21">
-        <v>1.5353650857194497E-6</v>
+        <v>-1.6797866840371082E-3</v>
       </c>
       <c r="O21">
-        <v>1.6461849389177788E-6</v>
+        <v>5.3514325010901496E-4</v>
       </c>
       <c r="P21">
-        <v>-9.2366252541108526E-7</v>
+        <v>7.9087015533610582E-5</v>
       </c>
       <c r="Q21">
-        <v>-1.038499870096442E-5</v>
+        <v>-1.8943193793154417E-4</v>
       </c>
       <c r="R21">
-        <v>-4.8168792072994974E-6</v>
+        <v>-3.5179069176411999E-3</v>
       </c>
       <c r="S21">
-        <v>1.8545150473114667E-5</v>
+        <v>1.0171249859269745E-3</v>
       </c>
       <c r="T21">
-        <v>1.6304672789199459E-5</v>
+        <v>3.2641922777059619E-3</v>
       </c>
       <c r="U21">
-        <v>-2.8811305494300663E-4</v>
+        <v>-2.4737473280106677E-2</v>
       </c>
       <c r="V21">
-        <v>9.205685756101138E-5</v>
+        <v>6.6293679132419453E-3</v>
       </c>
     </row>
   </sheetData>
@@ -2080,49 +2056,50 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3490A41A-6D87-4B5B-B2D0-88E95CB6FBA7}">
   <dimension ref="A1:V21"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="26.86328125" customWidth="1"/>
+    <col min="1" max="1" width="25.3984375" style="3" customWidth="1"/>
+    <col min="2" max="16384" width="8.796875" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>18</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>19</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>20</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>21</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>22</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>23</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>24</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>25</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>26</v>
-      </c>
-      <c r="L1" t="s">
-        <v>27</v>
       </c>
       <c r="M1" t="s">
         <v>35</v>
@@ -2134,705 +2111,705 @@
         <v>37</v>
       </c>
       <c r="P1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q1" t="s">
+        <v>27</v>
+      </c>
+      <c r="R1" t="s">
         <v>28</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>29</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>30</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>31</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>32</v>
-      </c>
-      <c r="V1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B2">
-        <v>3.4840436671963071E-2</v>
+        <v>-2.9669433051061064E-2</v>
       </c>
       <c r="C2">
-        <v>5.6986737332425552E-6</v>
+        <v>3.9081627803521984E-4</v>
       </c>
       <c r="D2">
-        <v>-6.0545424197484031E-8</v>
+        <v>-4.4090162002385397E-6</v>
       </c>
       <c r="E2">
-        <v>2.4413032086452932E-5</v>
+        <v>1.3281992412589587E-3</v>
       </c>
       <c r="F2">
-        <v>2.6739169880584209E-5</v>
+        <v>9.9990881479170121E-4</v>
       </c>
       <c r="G2">
-        <v>-5.37858196646436E-7</v>
+        <v>-3.538218719325758E-5</v>
       </c>
       <c r="H2">
-        <v>-5.7026376543130317E-7</v>
+        <v>-3.1486079503783646E-5</v>
       </c>
       <c r="I2">
-        <v>1.3623841683726606E-6</v>
+        <v>5.5639976230833252E-4</v>
       </c>
       <c r="J2">
-        <v>2.4554866032939656E-6</v>
+        <v>1.1675637912848015E-3</v>
       </c>
       <c r="K2">
-        <v>1.3993846477356379E-6</v>
+        <v>1.3869164121795507E-3</v>
       </c>
       <c r="L2">
-        <v>4.1160719898843348E-6</v>
+        <v>1.4345653258132879E-3</v>
       </c>
       <c r="M2">
-        <v>2.949769031611062E-7</v>
+        <v>-2.6373133297332026E-4</v>
       </c>
       <c r="N2">
-        <v>3.595065784127528E-7</v>
+        <v>-3.4561764356110436E-4</v>
       </c>
       <c r="O2">
-        <v>8.1987497585462563E-8</v>
+        <v>7.1041371454418236E-5</v>
       </c>
       <c r="P2">
-        <v>-2.3281841882983873E-8</v>
+        <v>-7.4514739287516376E-5</v>
       </c>
       <c r="Q2">
-        <v>2.3311234559516306E-6</v>
+        <v>-4.0069415354043638E-5</v>
       </c>
       <c r="R2">
-        <v>3.7076167952441818E-7</v>
+        <v>1.0178535903602043E-3</v>
       </c>
       <c r="S2">
-        <v>2.0939892724427558E-6</v>
+        <v>3.2956356521372985E-5</v>
       </c>
       <c r="T2">
-        <v>1.6005814415967465E-6</v>
+        <v>8.9855585784334529E-4</v>
       </c>
       <c r="U2">
-        <v>-1.3581812153349269E-4</v>
+        <v>-1.233507789616157E-2</v>
       </c>
       <c r="V2">
-        <v>9.1279307263844744E-6</v>
+        <v>1.7378040542857525E-3</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B3">
-        <v>-3.0679660477702883E-4</v>
+        <v>6.9275212565199828E-4</v>
       </c>
       <c r="C3">
-        <v>-6.0545424197484031E-8</v>
+        <v>-4.4090162002385397E-6</v>
       </c>
       <c r="D3">
-        <v>6.9995335127539854E-10</v>
+        <v>5.0594339158211628E-8</v>
       </c>
       <c r="E3">
-        <v>-7.0104119907341718E-8</v>
+        <v>-1.2246621300320244E-5</v>
       </c>
       <c r="F3">
-        <v>-9.8225845135557766E-8</v>
+        <v>-8.4501949221243826E-6</v>
       </c>
       <c r="G3">
-        <v>1.081915034740086E-9</v>
+        <v>3.3302845748964256E-7</v>
       </c>
       <c r="H3">
-        <v>1.4848708539475569E-9</v>
+        <v>2.8744642199376778E-7</v>
       </c>
       <c r="I3">
-        <v>-1.6941232216605479E-8</v>
+        <v>-6.4335519140185978E-6</v>
       </c>
       <c r="J3">
-        <v>-2.6945657646358621E-8</v>
+        <v>-1.3353152540078492E-5</v>
       </c>
       <c r="K3">
-        <v>-8.7092626712178219E-9</v>
+        <v>-1.5790325323833678E-5</v>
       </c>
       <c r="L3">
-        <v>-3.071046900091008E-8</v>
+        <v>-1.6265507169830022E-5</v>
       </c>
       <c r="M3">
-        <v>-4.4417171990954327E-9</v>
+        <v>2.9691023313931107E-6</v>
       </c>
       <c r="N3">
-        <v>-6.3442595729857358E-9</v>
+        <v>3.9225620470159594E-6</v>
       </c>
       <c r="O3">
-        <v>-2.5743511654047842E-9</v>
+        <v>-7.9851759209663876E-7</v>
       </c>
       <c r="P3">
-        <v>3.1046221292538584E-11</v>
+        <v>8.2171609349213053E-7</v>
       </c>
       <c r="Q3">
-        <v>-3.2458175100124355E-8</v>
+        <v>4.5786965271716905E-7</v>
       </c>
       <c r="R3">
-        <v>-1.2670265087721762E-8</v>
+        <v>-1.1835931006264559E-5</v>
       </c>
       <c r="S3">
-        <v>-2.2899823452566937E-8</v>
+        <v>-3.5181683395019974E-7</v>
       </c>
       <c r="T3">
-        <v>-1.7813978746361688E-8</v>
+        <v>-1.0374106540976592E-5</v>
       </c>
       <c r="U3">
-        <v>1.3486738456722985E-6</v>
+        <v>1.3839164502240899E-4</v>
       </c>
       <c r="V3">
-        <v>-1.0185170581099823E-7</v>
+        <v>-1.9841065727807784E-5</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B4">
-        <v>-0.10108301463226016</v>
+        <v>0.14504045343199626</v>
       </c>
       <c r="C4">
-        <v>2.4413032086452932E-5</v>
+        <v>1.3281992412589587E-3</v>
       </c>
       <c r="D4">
-        <v>-7.0104119907341718E-8</v>
+        <v>-1.2246621300320244E-5</v>
       </c>
       <c r="E4">
-        <v>1.0326858147472002E-3</v>
+        <v>1.8234957794154412E-2</v>
       </c>
       <c r="F4">
-        <v>8.1035090340074293E-4</v>
+        <v>1.3769353347883331E-2</v>
       </c>
       <c r="G4">
-        <v>-2.3221766806219256E-5</v>
+        <v>-4.2632374621440829E-4</v>
       </c>
       <c r="H4">
-        <v>-1.8445815668539957E-5</v>
+        <v>-3.3067013684280811E-4</v>
       </c>
       <c r="I4">
-        <v>-6.532436236298054E-6</v>
+        <v>1.5221934197969514E-3</v>
       </c>
       <c r="J4">
-        <v>-4.9804172615751079E-6</v>
+        <v>3.242490434337753E-3</v>
       </c>
       <c r="K4">
-        <v>-1.3382264093969E-5</v>
+        <v>3.8336879372775183E-3</v>
       </c>
       <c r="L4">
-        <v>-2.7937605784065891E-6</v>
+        <v>3.9892822878292138E-3</v>
       </c>
       <c r="M4">
-        <v>-3.6886490946937121E-6</v>
+        <v>-8.0969661463702416E-4</v>
       </c>
       <c r="N4">
-        <v>-3.37180437211594E-6</v>
+        <v>-1.0002781621347794E-3</v>
       </c>
       <c r="O4">
-        <v>-4.2549242598393153E-6</v>
+        <v>1.6447298587878571E-4</v>
       </c>
       <c r="P4">
-        <v>6.5054749629529081E-7</v>
+        <v>-3.0494613737578924E-4</v>
       </c>
       <c r="Q4">
-        <v>-4.119942267194147E-6</v>
+        <v>-3.1121627742052526E-4</v>
       </c>
       <c r="R4">
-        <v>1.499408458050277E-5</v>
+        <v>5.2315677125590451E-4</v>
       </c>
       <c r="S4">
-        <v>3.4008964754771031E-6</v>
+        <v>7.8714768903603974E-5</v>
       </c>
       <c r="T4">
-        <v>2.1805580686902072E-6</v>
+        <v>2.4994528145818669E-3</v>
       </c>
       <c r="U4">
-        <v>-9.4751014556620095E-4</v>
+        <v>-4.2678044263341978E-2</v>
       </c>
       <c r="V4">
-        <v>1.8413144912225894E-5</v>
+        <v>4.7002637835900076E-3</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B5">
-        <v>-1.6354157064779717E-2</v>
+        <v>0.18721283302142613</v>
       </c>
       <c r="C5">
-        <v>2.6739169880584209E-5</v>
+        <v>9.9990881479170121E-4</v>
       </c>
       <c r="D5">
-        <v>-9.8225845135557766E-8</v>
+        <v>-8.4501949221243826E-6</v>
       </c>
       <c r="E5">
-        <v>8.1035090340074293E-4</v>
+        <v>1.3769353347883331E-2</v>
       </c>
       <c r="F5">
-        <v>2.4126845211709133E-3</v>
+        <v>2.0493805313787885E-2</v>
       </c>
       <c r="G5">
-        <v>-1.846456669034658E-5</v>
+        <v>-3.181360082471566E-4</v>
       </c>
       <c r="H5">
-        <v>-5.2469089308068972E-5</v>
+        <v>-4.6587706113753336E-4</v>
       </c>
       <c r="I5">
-        <v>-3.8028399428972491E-5</v>
+        <v>-1.36609577614722E-4</v>
       </c>
       <c r="J5">
-        <v>-5.3268640940138764E-5</v>
+        <v>1.0928958375391613E-3</v>
       </c>
       <c r="K5">
-        <v>-6.511173297974387E-5</v>
+        <v>1.4885454725493542E-3</v>
       </c>
       <c r="L5">
-        <v>-5.2180432419043218E-5</v>
+        <v>1.6517948896749754E-3</v>
       </c>
       <c r="M5">
-        <v>-1.1327668934678029E-5</v>
+        <v>-7.0968306316874282E-4</v>
       </c>
       <c r="N5">
-        <v>-4.8496502370130173E-6</v>
+        <v>-8.9583803321836289E-4</v>
       </c>
       <c r="O5">
-        <v>-1.0781356924684606E-5</v>
+        <v>2.0106389131541516E-4</v>
       </c>
       <c r="P5">
-        <v>5.5600771944695675E-6</v>
+        <v>-2.3246087189905426E-4</v>
       </c>
       <c r="Q5">
-        <v>-1.5547578247912876E-5</v>
+        <v>-3.329510704714162E-4</v>
       </c>
       <c r="R5">
-        <v>-7.4744298684988527E-6</v>
+        <v>2.2307657966652958E-3</v>
       </c>
       <c r="S5">
-        <v>-1.0070726085223427E-5</v>
+        <v>-1.4138094750184623E-5</v>
       </c>
       <c r="T5">
-        <v>-5.712838351681779E-6</v>
+        <v>1.7667635796654849E-3</v>
       </c>
       <c r="U5">
-        <v>-8.6410843228728771E-4</v>
+        <v>-3.407189062287648E-2</v>
       </c>
       <c r="V5">
-        <v>-4.5895415781448083E-5</v>
+        <v>3.4514272779636707E-3</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B6">
-        <v>-7.3915049005992793E-3</v>
+        <v>-1.23299551377318E-2</v>
       </c>
       <c r="C6">
-        <v>-5.37858196646436E-7</v>
+        <v>-3.538218719325758E-5</v>
       </c>
       <c r="D6">
-        <v>1.081915034740086E-9</v>
+        <v>3.3302845748964256E-7</v>
       </c>
       <c r="E6">
-        <v>-2.3221766806219256E-5</v>
+        <v>-4.2632374621440829E-4</v>
       </c>
       <c r="F6">
-        <v>-1.846456669034658E-5</v>
+        <v>-3.181360082471566E-4</v>
       </c>
       <c r="G6">
-        <v>5.5808160833680496E-7</v>
+        <v>1.0795289941747121E-5</v>
       </c>
       <c r="H6">
-        <v>4.4831048520835548E-7</v>
+        <v>8.284040416473615E-6</v>
       </c>
       <c r="I6">
-        <v>1.4392676360290159E-7</v>
+        <v>-4.5043453403720651E-5</v>
       </c>
       <c r="J6">
-        <v>1.3166668628301518E-7</v>
+        <v>-9.3212306797243522E-5</v>
       </c>
       <c r="K6">
-        <v>4.0745865422078428E-7</v>
+        <v>-1.0826356545556584E-4</v>
       </c>
       <c r="L6">
-        <v>2.7070409411438739E-7</v>
+        <v>-1.1182664198758501E-4</v>
       </c>
       <c r="M6">
-        <v>-2.6915295097430125E-8</v>
+        <v>2.1489722676526881E-5</v>
       </c>
       <c r="N6">
-        <v>7.2623739533446615E-8</v>
+        <v>2.7138390148315107E-5</v>
       </c>
       <c r="O6">
-        <v>3.2923552959201947E-8</v>
+        <v>-5.040817583620771E-6</v>
       </c>
       <c r="P6">
-        <v>-4.3036992442897991E-8</v>
+        <v>7.2214226431414631E-6</v>
       </c>
       <c r="Q6">
-        <v>2.6899986951472137E-7</v>
+        <v>8.4572136529967825E-6</v>
       </c>
       <c r="R6">
-        <v>-4.2323382836181997E-9</v>
+        <v>-2.4766365197365221E-5</v>
       </c>
       <c r="S6">
-        <v>-6.7898478951046268E-8</v>
+        <v>-2.0059177052181282E-6</v>
       </c>
       <c r="T6">
-        <v>-3.2283158252683384E-8</v>
+        <v>-7.1055525657525066E-5</v>
       </c>
       <c r="U6">
-        <v>2.0080090501533579E-5</v>
+        <v>1.1259234136053887E-3</v>
       </c>
       <c r="V6">
-        <v>-2.719494429391718E-7</v>
+        <v>-1.33190021725481E-4</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B7">
-        <v>-1.4348777439292146E-2</v>
+        <v>-1.6268975160127111E-2</v>
       </c>
       <c r="C7">
-        <v>-5.7026376543130317E-7</v>
+        <v>-3.1486079503783646E-5</v>
       </c>
       <c r="D7">
-        <v>1.4848708539475569E-9</v>
+        <v>2.8744642199376778E-7</v>
       </c>
       <c r="E7">
-        <v>-1.8445815668539957E-5</v>
+        <v>-3.3067013684280811E-4</v>
       </c>
       <c r="F7">
-        <v>-5.2469089308068972E-5</v>
+        <v>-4.6587706113753336E-4</v>
       </c>
       <c r="G7">
-        <v>4.4831048520835548E-7</v>
+        <v>8.284040416473615E-6</v>
       </c>
       <c r="H7">
-        <v>1.2431769155845353E-6</v>
+        <v>1.1630355764769475E-5</v>
       </c>
       <c r="I7">
-        <v>8.8331233538064331E-7</v>
+        <v>-4.8974518579546894E-6</v>
       </c>
       <c r="J7">
-        <v>1.2048929140618313E-6</v>
+        <v>-4.8937729878632314E-5</v>
       </c>
       <c r="K7">
-        <v>1.5985663449147936E-6</v>
+        <v>-6.0650401049983401E-5</v>
       </c>
       <c r="L7">
-        <v>1.4403627030885985E-6</v>
+        <v>-6.3695924668608561E-5</v>
       </c>
       <c r="M7">
-        <v>8.2004733635208744E-8</v>
+        <v>1.9545271264859205E-5</v>
       </c>
       <c r="N7">
-        <v>7.1965242527789975E-8</v>
+        <v>2.5494989094964224E-5</v>
       </c>
       <c r="O7">
-        <v>6.7482296630195276E-8</v>
+        <v>-6.2740710132694839E-6</v>
       </c>
       <c r="P7">
-        <v>-2.4122153715414899E-7</v>
+        <v>6.5863261958690026E-6</v>
       </c>
       <c r="Q7">
-        <v>3.2542737255945559E-7</v>
+        <v>8.7131140757192834E-6</v>
       </c>
       <c r="R7">
-        <v>6.4148439819486487E-7</v>
+        <v>-5.4063141510708385E-5</v>
       </c>
       <c r="S7">
-        <v>1.6312560004224657E-7</v>
+        <v>-1.3074468063656592E-6</v>
       </c>
       <c r="T7">
-        <v>7.771277598722228E-8</v>
+        <v>-6.2632347463372669E-5</v>
       </c>
       <c r="U7">
-        <v>1.7986736255274053E-5</v>
+        <v>1.0200372494442761E-3</v>
       </c>
       <c r="V7">
-        <v>8.0800389682367631E-7</v>
+        <v>-1.239755230482082E-4</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B8">
-        <v>-8.8705833021006139E-2</v>
+        <v>-0.39641428648557525</v>
       </c>
       <c r="C8">
-        <v>1.3623841683726606E-6</v>
+        <v>5.5639976230833252E-4</v>
       </c>
       <c r="D8">
-        <v>-1.6941232216605479E-8</v>
+        <v>-6.4335519140185978E-6</v>
       </c>
       <c r="E8">
-        <v>-6.532436236298054E-6</v>
+        <v>1.5221934197969514E-3</v>
       </c>
       <c r="F8">
-        <v>-3.8028399428972491E-5</v>
+        <v>-1.36609577614722E-4</v>
       </c>
       <c r="G8">
-        <v>1.4392676360290159E-7</v>
+        <v>-4.5043453403720651E-5</v>
       </c>
       <c r="H8">
-        <v>8.8331233538064331E-7</v>
+        <v>-4.8974518579546894E-6</v>
       </c>
       <c r="I8">
-        <v>4.8194164762390005E-3</v>
+        <v>7.8527449118659262E-2</v>
       </c>
       <c r="J8">
-        <v>4.4500994265630877E-3</v>
+        <v>7.0583155696546551E-2</v>
       </c>
       <c r="K8">
-        <v>4.4515727480572906E-3</v>
+        <v>7.1071168061882489E-2</v>
       </c>
       <c r="L8">
-        <v>4.4516411812655782E-3</v>
+        <v>7.1200654185635745E-2</v>
       </c>
       <c r="M8">
-        <v>2.7244344753638281E-6</v>
+        <v>-6.359701777776366E-4</v>
       </c>
       <c r="N8">
-        <v>2.9882155646952901E-6</v>
+        <v>-7.6042543741273896E-4</v>
       </c>
       <c r="O8">
-        <v>6.1355318876248853E-7</v>
+        <v>-1.5474673756698984E-4</v>
       </c>
       <c r="P8">
-        <v>-2.9837235401468715E-6</v>
+        <v>-2.0961243839632041E-4</v>
       </c>
       <c r="Q8">
-        <v>-3.6263597194265199E-6</v>
+        <v>6.3319631257792208E-5</v>
       </c>
       <c r="R8">
-        <v>6.736875302017909E-6</v>
+        <v>1.9975789608798855E-3</v>
       </c>
       <c r="S8">
-        <v>2.3916564297223943E-6</v>
+        <v>-2.3261887349925971E-4</v>
       </c>
       <c r="T8">
-        <v>5.5295837727037128E-6</v>
+        <v>1.9202472109283333E-3</v>
       </c>
       <c r="U8">
-        <v>-4.5114645261043404E-3</v>
+        <v>-8.7952893035028373E-2</v>
       </c>
       <c r="V8">
-        <v>3.599024376947505E-5</v>
+        <v>3.3520492765034631E-3</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B9">
-        <v>-5.1564762867642659E-2</v>
+        <v>-0.30849427442773475</v>
       </c>
       <c r="C9">
-        <v>2.4554866032939656E-6</v>
+        <v>1.1675637912848015E-3</v>
       </c>
       <c r="D9">
-        <v>-2.6945657646358621E-8</v>
+        <v>-1.3353152540078492E-5</v>
       </c>
       <c r="E9">
-        <v>-4.9804172615751079E-6</v>
+        <v>3.242490434337753E-3</v>
       </c>
       <c r="F9">
-        <v>-5.3268640940138764E-5</v>
+        <v>1.0928958375391613E-3</v>
       </c>
       <c r="G9">
-        <v>1.3166668628301518E-7</v>
+        <v>-9.3212306797243522E-5</v>
       </c>
       <c r="H9">
-        <v>1.2048929140618313E-6</v>
+        <v>-4.8937729878632314E-5</v>
       </c>
       <c r="I9">
-        <v>4.4500994265630877E-3</v>
+        <v>7.0583155696546551E-2</v>
       </c>
       <c r="J9">
-        <v>4.5228179848468292E-3</v>
+        <v>7.4727896750541048E-2</v>
       </c>
       <c r="K9">
-        <v>4.4710199405521237E-3</v>
+        <v>7.4068544090974159E-2</v>
       </c>
       <c r="L9">
-        <v>4.4722646133619551E-3</v>
+        <v>7.4311635666193629E-2</v>
       </c>
       <c r="M9">
-        <v>3.1855212694371666E-6</v>
+        <v>-1.1739395603458293E-3</v>
       </c>
       <c r="N9">
-        <v>3.1804175559043622E-6</v>
+        <v>-1.5010885137434404E-3</v>
       </c>
       <c r="O9">
-        <v>-8.0943494483226186E-8</v>
+        <v>1.9699563673611444E-5</v>
       </c>
       <c r="P9">
-        <v>-4.8703422599011252E-6</v>
+        <v>-4.7984800121741138E-4</v>
       </c>
       <c r="Q9">
-        <v>8.7954911366892145E-6</v>
+        <v>5.0244816251763109E-5</v>
       </c>
       <c r="R9">
-        <v>-3.2474026218060261E-6</v>
+        <v>6.2866410532908413E-3</v>
       </c>
       <c r="S9">
-        <v>1.2559599052851983E-5</v>
+        <v>-4.0094291647785964E-4</v>
       </c>
       <c r="T9">
-        <v>1.2505753271091705E-5</v>
+        <v>3.615740519479496E-3</v>
       </c>
       <c r="U9">
-        <v>-4.5731332264543857E-3</v>
+        <v>-0.11147378422487911</v>
       </c>
       <c r="V9">
-        <v>6.7748653785755313E-5</v>
+        <v>6.7737990161020082E-3</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B10">
-        <v>9.6834806541594327E-3</v>
+        <v>-0.25285882864262527</v>
       </c>
       <c r="C10">
-        <v>1.3993846477356379E-6</v>
+        <v>1.3869164121795507E-3</v>
       </c>
       <c r="D10">
-        <v>-8.7092626712178219E-9</v>
+        <v>-1.5790325323833678E-5</v>
       </c>
       <c r="E10">
-        <v>-1.3382264093969E-5</v>
+        <v>3.8336879372775183E-3</v>
       </c>
       <c r="F10">
-        <v>-6.511173297974387E-5</v>
+        <v>1.4885454725493542E-3</v>
       </c>
       <c r="G10">
-        <v>4.0745865422078428E-7</v>
+        <v>-1.0826356545556584E-4</v>
       </c>
       <c r="H10">
-        <v>1.5985663449147936E-6</v>
+        <v>-6.0650401049983401E-5</v>
       </c>
       <c r="I10">
-        <v>4.4515727480572906E-3</v>
+        <v>7.1071168061882489E-2</v>
       </c>
       <c r="J10">
-        <v>4.4710199405521237E-3</v>
+        <v>7.4068544090974159E-2</v>
       </c>
       <c r="K10">
-        <v>4.5013231878842114E-3</v>
+        <v>7.5512390596420315E-2</v>
       </c>
       <c r="L10">
-        <v>4.4884630368118997E-3</v>
+        <v>7.5548869592013651E-2</v>
       </c>
       <c r="M10">
-        <v>2.9915551892416007E-6</v>
+        <v>-1.3471022602528273E-3</v>
       </c>
       <c r="N10">
-        <v>3.5714373510706628E-6</v>
+        <v>-1.64012926260927E-3</v>
       </c>
       <c r="O10">
-        <v>2.6480015483035129E-7</v>
+        <v>6.499989546751228E-5</v>
       </c>
       <c r="P10">
-        <v>-3.5830539745832624E-6</v>
+        <v>-4.7227265177631693E-4</v>
       </c>
       <c r="Q10">
-        <v>1.2085668782808015E-5</v>
+        <v>2.4605016995901176E-5</v>
       </c>
       <c r="R10">
-        <v>-1.2987835127945289E-5</v>
+        <v>7.8820102478737459E-3</v>
       </c>
       <c r="S10">
-        <v>1.3054145041939306E-5</v>
+        <v>-2.421942066308685E-4</v>
       </c>
       <c r="T10">
-        <v>1.1503337722759279E-5</v>
+        <v>4.1850029766218669E-3</v>
       </c>
       <c r="U10">
-        <v>-4.5702996244230722E-3</v>
+        <v>-0.12020328721952006</v>
       </c>
       <c r="V10">
-        <v>7.1653071228394276E-5</v>
+        <v>7.9635336881279974E-3</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B11">
-        <v>4.5648394710861302E-2</v>
+        <v>-0.24406721372254361</v>
       </c>
       <c r="C11">
-        <v>4.1160719898843348E-6</v>
+        <v>1.4345653258132879E-3</v>
       </c>
       <c r="D11">
-        <v>-3.071046900091008E-8</v>
+        <v>-1.6265507169830022E-5</v>
       </c>
       <c r="E11">
-        <v>-2.7937605784065891E-6</v>
+        <v>3.9892822878292138E-3</v>
       </c>
       <c r="F11">
-        <v>-5.2180432419043218E-5</v>
+        <v>1.6517948896749754E-3</v>
       </c>
       <c r="G11">
-        <v>2.7070409411438739E-7</v>
+        <v>-1.1182664198758501E-4</v>
       </c>
       <c r="H11">
-        <v>1.4403627030885985E-6</v>
+        <v>-6.3695924668608561E-5</v>
       </c>
       <c r="I11">
-        <v>4.4516411812655782E-3</v>
+        <v>7.1200654185635745E-2</v>
       </c>
       <c r="J11">
-        <v>4.4722646133619551E-3</v>
+        <v>7.4311635666193629E-2</v>
       </c>
       <c r="K11">
-        <v>4.4884630368118997E-3</v>
+        <v>7.5548869592013651E-2</v>
       </c>
       <c r="L11">
-        <v>4.5546002384389316E-3</v>
+        <v>7.6688587354726778E-2</v>
       </c>
       <c r="M11">
-        <v>3.006014048495382E-6</v>
+        <v>-1.4252928366447486E-3</v>
       </c>
       <c r="N11">
-        <v>5.3542296365095791E-6</v>
+        <v>-1.7205446957052947E-3</v>
       </c>
       <c r="O11">
-        <v>3.2618223043460696E-7</v>
+        <v>9.6531722887065299E-5</v>
       </c>
       <c r="P11">
-        <v>-3.0582820180085781E-6</v>
+        <v>-4.5703150725911427E-4</v>
       </c>
       <c r="Q11">
-        <v>1.199537587238855E-5</v>
+        <v>3.8294655318349345E-5</v>
       </c>
       <c r="R11">
-        <v>-1.3143692511056237E-5</v>
+        <v>8.5579214500962619E-3</v>
       </c>
       <c r="S11">
-        <v>1.2921330916555514E-5</v>
+        <v>-2.6898142877523527E-4</v>
       </c>
       <c r="T11">
-        <v>1.185367266240246E-5</v>
+        <v>4.2159512317142076E-3</v>
       </c>
       <c r="U11">
-        <v>-4.6544832507781977E-3</v>
+        <v>-0.12257202324942776</v>
       </c>
       <c r="V11">
-        <v>7.2775823502468332E-5</v>
+        <v>8.2102293173974411E-3</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.45">
@@ -2840,67 +2817,67 @@
         <v>35</v>
       </c>
       <c r="B12">
-        <v>-4.1009520207858648E-2</v>
+        <v>-0.28784111128955792</v>
       </c>
       <c r="C12">
-        <v>2.949769031611062E-7</v>
+        <v>-2.6373133297332026E-4</v>
       </c>
       <c r="D12">
-        <v>-4.4417171990954327E-9</v>
+        <v>2.9691023313931107E-6</v>
       </c>
       <c r="E12">
-        <v>-3.6886490946937121E-6</v>
+        <v>-8.0969661463702416E-4</v>
       </c>
       <c r="F12">
-        <v>-1.1327668934678029E-5</v>
+        <v>-7.0968306316874282E-4</v>
       </c>
       <c r="G12">
-        <v>-2.6915295097430125E-8</v>
+        <v>2.1489722676526881E-5</v>
       </c>
       <c r="H12">
-        <v>8.2004733635208744E-8</v>
+        <v>1.9545271264859205E-5</v>
       </c>
       <c r="I12">
-        <v>2.7244344753638281E-6</v>
+        <v>-6.359701777776366E-4</v>
       </c>
       <c r="J12">
-        <v>3.1855212694371666E-6</v>
+        <v>-1.1739395603458293E-3</v>
       </c>
       <c r="K12">
-        <v>2.9915551892416007E-6</v>
+        <v>-1.3471022602528273E-3</v>
       </c>
       <c r="L12">
-        <v>3.006014048495382E-6</v>
+        <v>-1.4252928366447486E-3</v>
       </c>
       <c r="M12">
-        <v>1.3418773549330254E-4</v>
+        <v>1.7885131564973312E-3</v>
       </c>
       <c r="N12">
-        <v>6.5643249303240956E-5</v>
+        <v>1.1327007643671433E-3</v>
       </c>
       <c r="O12">
-        <v>6.5909904673133764E-5</v>
+        <v>7.92652227466468E-4</v>
       </c>
       <c r="P12">
-        <v>6.5514208354696624E-5</v>
+        <v>9.0604686135746081E-4</v>
       </c>
       <c r="Q12">
-        <v>3.1693172847536746E-6</v>
+        <v>-1.0935612360929478E-4</v>
       </c>
       <c r="R12">
-        <v>-1.2996193363187645E-5</v>
+        <v>-8.348619400626511E-4</v>
       </c>
       <c r="S12">
-        <v>5.3452059334860041E-7</v>
+        <v>-3.197473674906556E-5</v>
       </c>
       <c r="T12">
-        <v>4.4644545223549961E-7</v>
+        <v>-7.48074739260978E-4</v>
       </c>
       <c r="U12">
-        <v>-5.7819169517711795E-5</v>
+        <v>8.3338935773214304E-3</v>
       </c>
       <c r="V12">
-        <v>4.3277350063823145E-6</v>
+        <v>-1.3433702867380055E-3</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.45">
@@ -2908,67 +2885,67 @@
         <v>36</v>
       </c>
       <c r="B13">
-        <v>6.2273959829214152E-2</v>
+        <v>-0.28446322535757856</v>
       </c>
       <c r="C13">
-        <v>3.595065784127528E-7</v>
+        <v>-3.4561764356110436E-4</v>
       </c>
       <c r="D13">
-        <v>-6.3442595729857358E-9</v>
+        <v>3.9225620470159594E-6</v>
       </c>
       <c r="E13">
-        <v>-3.37180437211594E-6</v>
+        <v>-1.0002781621347794E-3</v>
       </c>
       <c r="F13">
-        <v>-4.8496502370130173E-6</v>
+        <v>-8.9583803321836289E-4</v>
       </c>
       <c r="G13">
-        <v>7.2623739533446615E-8</v>
+        <v>2.7138390148315107E-5</v>
       </c>
       <c r="H13">
-        <v>7.1965242527789975E-8</v>
+        <v>2.5494989094964224E-5</v>
       </c>
       <c r="I13">
-        <v>2.9882155646952901E-6</v>
+        <v>-7.6042543741273896E-4</v>
       </c>
       <c r="J13">
-        <v>3.1804175559043622E-6</v>
+        <v>-1.5010885137434404E-3</v>
       </c>
       <c r="K13">
-        <v>3.5714373510706628E-6</v>
+        <v>-1.64012926260927E-3</v>
       </c>
       <c r="L13">
-        <v>5.3542296365095791E-6</v>
+        <v>-1.7205446957052947E-3</v>
       </c>
       <c r="M13">
-        <v>6.5643249303240956E-5</v>
+        <v>1.1327007643671433E-3</v>
       </c>
       <c r="N13">
-        <v>1.7318561454483664E-4</v>
+        <v>3.0089488049155249E-3</v>
       </c>
       <c r="O13">
-        <v>6.5665430336381671E-5</v>
+        <v>7.7815616981531015E-4</v>
       </c>
       <c r="P13">
-        <v>6.5450769051177062E-5</v>
+        <v>9.2606777267711232E-4</v>
       </c>
       <c r="Q13">
-        <v>4.4606433650293859E-6</v>
+        <v>-8.9938223164022572E-5</v>
       </c>
       <c r="R13">
-        <v>-1.2153697979402808E-5</v>
+        <v>-1.6202409493283249E-3</v>
       </c>
       <c r="S13">
-        <v>3.020615171256352E-7</v>
+        <v>-6.2337682859058533E-5</v>
       </c>
       <c r="T13">
-        <v>9.9339962425815193E-7</v>
+        <v>-9.7096183821023473E-4</v>
       </c>
       <c r="U13">
-        <v>-6.1413736609797494E-5</v>
+        <v>1.1518218726753189E-2</v>
       </c>
       <c r="V13">
-        <v>3.322856165865744E-6</v>
+        <v>-1.7702229038183573E-3</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.45">
@@ -2976,543 +2953,543 @@
         <v>37</v>
       </c>
       <c r="B14">
-        <v>-3.921508967154326E-2</v>
+        <v>-9.4620165516397944E-2</v>
       </c>
       <c r="C14">
-        <v>8.1987497585462563E-8</v>
+        <v>7.1041371454418236E-5</v>
       </c>
       <c r="D14">
-        <v>-2.5743511654047842E-9</v>
+        <v>-7.9851759209663876E-7</v>
       </c>
       <c r="E14">
-        <v>-4.2549242598393153E-6</v>
+        <v>1.6447298587878571E-4</v>
       </c>
       <c r="F14">
-        <v>-1.0781356924684606E-5</v>
+        <v>2.0106389131541516E-4</v>
       </c>
       <c r="G14">
-        <v>3.2923552959201947E-8</v>
+        <v>-5.040817583620771E-6</v>
       </c>
       <c r="H14">
-        <v>6.7482296630195276E-8</v>
+        <v>-6.2740710132694839E-6</v>
       </c>
       <c r="I14">
-        <v>6.1355318876248853E-7</v>
+        <v>-1.5474673756698984E-4</v>
       </c>
       <c r="J14">
-        <v>-8.0943494483226186E-8</v>
+        <v>1.9699563673611444E-5</v>
       </c>
       <c r="K14">
-        <v>2.6480015483035129E-7</v>
+        <v>6.499989546751228E-5</v>
       </c>
       <c r="L14">
-        <v>3.2618223043460696E-7</v>
+        <v>9.6531722887065299E-5</v>
       </c>
       <c r="M14">
-        <v>6.5909904673133764E-5</v>
+        <v>7.92652227466468E-4</v>
       </c>
       <c r="N14">
-        <v>6.5665430336381671E-5</v>
+        <v>7.7815616981531015E-4</v>
       </c>
       <c r="O14">
-        <v>1.2952244372627547E-4</v>
+        <v>1.7222089635572509E-3</v>
       </c>
       <c r="P14">
-        <v>6.556201847487329E-5</v>
+        <v>8.285407989719652E-4</v>
       </c>
       <c r="Q14">
-        <v>3.2352246398359208E-6</v>
+        <v>-6.3363926394498286E-5</v>
       </c>
       <c r="R14">
-        <v>-1.4888136750538953E-5</v>
+        <v>-2.9591776057674197E-4</v>
       </c>
       <c r="S14">
-        <v>1.6303204947681391E-6</v>
+        <v>8.6991517679262827E-6</v>
       </c>
       <c r="T14">
-        <v>1.3686157552775058E-6</v>
+        <v>1.0522118485355687E-4</v>
       </c>
       <c r="U14">
-        <v>-4.9159091156030703E-5</v>
+        <v>-2.3893455076486629E-3</v>
       </c>
       <c r="V14">
-        <v>4.3296922017281402E-6</v>
+        <v>3.151558691569424E-4</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B15">
-        <v>-9.8226405484498944E-2</v>
+        <v>-0.16227143399654154</v>
       </c>
       <c r="C15">
-        <v>-2.3281841882983873E-8</v>
+        <v>-7.4514739287516376E-5</v>
       </c>
       <c r="D15">
-        <v>3.1046221292538584E-11</v>
+        <v>8.2171609349213053E-7</v>
       </c>
       <c r="E15">
-        <v>6.5054749629529081E-7</v>
+        <v>-3.0494613737578924E-4</v>
       </c>
       <c r="F15">
-        <v>5.5600771944695675E-6</v>
+        <v>-2.3246087189905426E-4</v>
       </c>
       <c r="G15">
-        <v>-4.3036992442897991E-8</v>
+        <v>7.2214226431414631E-6</v>
       </c>
       <c r="H15">
-        <v>-2.4122153715414899E-7</v>
+        <v>6.5863261958690026E-6</v>
       </c>
       <c r="I15">
-        <v>-2.9837235401468715E-6</v>
+        <v>-2.0961243839632041E-4</v>
       </c>
       <c r="J15">
-        <v>-4.8703422599011252E-6</v>
+        <v>-4.7984800121741138E-4</v>
       </c>
       <c r="K15">
-        <v>-3.5830539745832624E-6</v>
+        <v>-4.7227265177631693E-4</v>
       </c>
       <c r="L15">
-        <v>-3.0582820180085781E-6</v>
+        <v>-4.5703150725911427E-4</v>
       </c>
       <c r="M15">
-        <v>6.5514208354696624E-5</v>
+        <v>9.0604686135746081E-4</v>
       </c>
       <c r="N15">
-        <v>6.5450769051177062E-5</v>
+        <v>9.2606777267711232E-4</v>
       </c>
       <c r="O15">
-        <v>6.556201847487329E-5</v>
+        <v>8.285407989719652E-4</v>
       </c>
       <c r="P15">
-        <v>9.2685869867560589E-5</v>
+        <v>1.6527953819159564E-3</v>
       </c>
       <c r="Q15">
-        <v>2.5787129519944006E-6</v>
+        <v>-3.9398339655465704E-5</v>
       </c>
       <c r="R15">
-        <v>-1.1118958659300825E-5</v>
+        <v>-4.7948422165328337E-4</v>
       </c>
       <c r="S15">
-        <v>-6.3408684105038968E-8</v>
+        <v>-1.656438191792344E-5</v>
       </c>
       <c r="T15">
-        <v>-1.3199493747572004E-7</v>
+        <v>-2.6323040627437952E-4</v>
       </c>
       <c r="U15">
-        <v>-4.8216519231986875E-5</v>
+        <v>2.1662198583644503E-3</v>
       </c>
       <c r="V15">
-        <v>1.0058047075186908E-6</v>
+        <v>-4.0273379679480224E-4</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B16">
-        <v>0.17427172234685118</v>
+        <v>0.19105694479741814</v>
       </c>
       <c r="C16">
-        <v>2.3311234559516306E-6</v>
+        <v>-4.0069415354043638E-5</v>
       </c>
       <c r="D16">
-        <v>-3.2458175100124355E-8</v>
+        <v>4.5786965271716905E-7</v>
       </c>
       <c r="E16">
-        <v>-4.119942267194147E-6</v>
+        <v>-3.1121627742052526E-4</v>
       </c>
       <c r="F16">
-        <v>-1.5547578247912876E-5</v>
+        <v>-3.329510704714162E-4</v>
       </c>
       <c r="G16">
-        <v>2.6899986951472137E-7</v>
+        <v>8.4572136529967825E-6</v>
       </c>
       <c r="H16">
-        <v>3.2542737255945559E-7</v>
+        <v>8.7131140757192834E-6</v>
       </c>
       <c r="I16">
-        <v>-3.6263597194265199E-6</v>
+        <v>6.3319631257792208E-5</v>
       </c>
       <c r="J16">
-        <v>8.7954911366892145E-6</v>
+        <v>5.0244816251763109E-5</v>
       </c>
       <c r="K16">
-        <v>1.2085668782808015E-5</v>
+        <v>2.4605016995901176E-5</v>
       </c>
       <c r="L16">
-        <v>1.199537587238855E-5</v>
+        <v>3.8294655318349345E-5</v>
       </c>
       <c r="M16">
-        <v>3.1693172847536746E-6</v>
+        <v>-1.0935612360929478E-4</v>
       </c>
       <c r="N16">
-        <v>4.4606433650293859E-6</v>
+        <v>-8.9938223164022572E-5</v>
       </c>
       <c r="O16">
-        <v>3.2352246398359208E-6</v>
+        <v>-6.3363926394498286E-5</v>
       </c>
       <c r="P16">
-        <v>2.5787129519944006E-6</v>
+        <v>-3.9398339655465704E-5</v>
       </c>
       <c r="Q16">
-        <v>5.8031824711238787E-4</v>
+        <v>1.8808340461037324E-3</v>
       </c>
       <c r="R16">
-        <v>1.8985272691404358E-5</v>
+        <v>1.0177609892077482E-3</v>
       </c>
       <c r="S16">
-        <v>-5.8715215078727868E-6</v>
+        <v>-6.6507812811103761E-5</v>
       </c>
       <c r="T16">
-        <v>-5.055724048259883E-6</v>
+        <v>-9.1183202878818967E-5</v>
       </c>
       <c r="U16">
-        <v>-6.9379689896345619E-5</v>
+        <v>-1.6803802571622362E-5</v>
       </c>
       <c r="V16">
-        <v>-1.9858735223044794E-5</v>
+        <v>-2.9806649915364023E-4</v>
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B17">
-        <v>0.57448370350814926</v>
+        <v>3.7748185520421057E-3</v>
       </c>
       <c r="C17">
-        <v>3.7076167952441818E-7</v>
+        <v>1.0178535903602043E-3</v>
       </c>
       <c r="D17">
-        <v>-1.2670265087721762E-8</v>
+        <v>-1.1835931006264559E-5</v>
       </c>
       <c r="E17">
-        <v>1.499408458050277E-5</v>
+        <v>5.2315677125590451E-4</v>
       </c>
       <c r="F17">
-        <v>-7.4744298684988527E-6</v>
+        <v>2.2307657966652958E-3</v>
       </c>
       <c r="G17">
-        <v>-4.2323382836181997E-9</v>
+        <v>-2.4766365197365221E-5</v>
       </c>
       <c r="H17">
-        <v>6.4148439819486487E-7</v>
+        <v>-5.4063141510708385E-5</v>
       </c>
       <c r="I17">
-        <v>6.736875302017909E-6</v>
+        <v>1.9975789608798855E-3</v>
       </c>
       <c r="J17">
-        <v>-3.2474026218060261E-6</v>
+        <v>6.2866410532908413E-3</v>
       </c>
       <c r="K17">
-        <v>-1.2987835127945289E-5</v>
+        <v>7.8820102478737459E-3</v>
       </c>
       <c r="L17">
-        <v>-1.3143692511056237E-5</v>
+        <v>8.5579214500962619E-3</v>
       </c>
       <c r="M17">
-        <v>-1.2996193363187645E-5</v>
+        <v>-8.348619400626511E-4</v>
       </c>
       <c r="N17">
-        <v>-1.2153697979402808E-5</v>
+        <v>-1.6202409493283249E-3</v>
       </c>
       <c r="O17">
-        <v>-1.4888136750538953E-5</v>
+        <v>-2.9591776057674197E-4</v>
       </c>
       <c r="P17">
-        <v>-1.1118958659300825E-5</v>
+        <v>-4.7948422165328337E-4</v>
       </c>
       <c r="Q17">
-        <v>1.8985272691404358E-5</v>
+        <v>1.0177609892077482E-3</v>
       </c>
       <c r="R17">
-        <v>8.7598904304059982E-4</v>
+        <v>1.1751762426028149</v>
       </c>
       <c r="S17">
-        <v>-1.5402962393720336E-4</v>
+        <v>-5.3656696730576527E-2</v>
       </c>
       <c r="T17">
-        <v>-1.7657669317334447E-4</v>
+        <v>-4.0170271131596026E-3</v>
       </c>
       <c r="U17">
-        <v>-9.0583391620158507E-4</v>
+        <v>-1.2004932883604431</v>
       </c>
       <c r="V17">
-        <v>3.0560925618840727E-6</v>
+        <v>5.4473525965925244E-3</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B18">
-        <v>-2.8982680365170016E-2</v>
+        <v>-0.12699552434998035</v>
       </c>
       <c r="C18">
-        <v>2.0939892724427558E-6</v>
+        <v>3.2956356521372985E-5</v>
       </c>
       <c r="D18">
-        <v>-2.2899823452566937E-8</v>
+        <v>-3.5181683395019974E-7</v>
       </c>
       <c r="E18">
-        <v>3.4008964754771031E-6</v>
+        <v>7.8714768903603974E-5</v>
       </c>
       <c r="F18">
-        <v>-1.0070726085223427E-5</v>
+        <v>-1.4138094750184623E-5</v>
       </c>
       <c r="G18">
-        <v>-6.7898478951046268E-8</v>
+        <v>-2.0059177052181282E-6</v>
       </c>
       <c r="H18">
-        <v>1.6312560004224657E-7</v>
+        <v>-1.3074468063656592E-6</v>
       </c>
       <c r="I18">
-        <v>2.3916564297223943E-6</v>
+        <v>-2.3261887349925971E-4</v>
       </c>
       <c r="J18">
-        <v>1.2559599052851983E-5</v>
+        <v>-4.0094291647785964E-4</v>
       </c>
       <c r="K18">
-        <v>1.3054145041939306E-5</v>
+        <v>-2.421942066308685E-4</v>
       </c>
       <c r="L18">
-        <v>1.2921330916555514E-5</v>
+        <v>-2.6898142877523527E-4</v>
       </c>
       <c r="M18">
-        <v>5.3452059334860041E-7</v>
+        <v>-3.197473674906556E-5</v>
       </c>
       <c r="N18">
-        <v>3.020615171256352E-7</v>
+        <v>-6.2337682859058533E-5</v>
       </c>
       <c r="O18">
-        <v>1.6303204947681391E-6</v>
+        <v>8.6991517679262827E-6</v>
       </c>
       <c r="P18">
-        <v>-6.3408684105038968E-8</v>
+        <v>-1.656438191792344E-5</v>
       </c>
       <c r="Q18">
-        <v>-5.8715215078727868E-6</v>
+        <v>-6.6507812811103761E-5</v>
       </c>
       <c r="R18">
-        <v>-1.5402962393720336E-4</v>
+        <v>-5.3656696730576527E-2</v>
       </c>
       <c r="S18">
-        <v>1.3278772794685843E-4</v>
+        <v>5.7753008254731513E-3</v>
       </c>
       <c r="T18">
-        <v>5.1451894860847389E-5</v>
+        <v>5.9696487525139129E-4</v>
       </c>
       <c r="U18">
-        <v>6.3063757134275227E-5</v>
+        <v>5.2492418216069439E-2</v>
       </c>
       <c r="V18">
-        <v>3.320797210910334E-5</v>
+        <v>7.4388529200147536E-5</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B19">
-        <v>-2.8506905737782064E-2</v>
+        <v>-3.8344144679979479E-2</v>
       </c>
       <c r="C19">
-        <v>1.6005814415967465E-6</v>
+        <v>8.9855585784334529E-4</v>
       </c>
       <c r="D19">
-        <v>-1.7813978746361688E-8</v>
+        <v>-1.0374106540976592E-5</v>
       </c>
       <c r="E19">
-        <v>2.1805580686902072E-6</v>
+        <v>2.4994528145818669E-3</v>
       </c>
       <c r="F19">
-        <v>-5.712838351681779E-6</v>
+        <v>1.7667635796654849E-3</v>
       </c>
       <c r="G19">
-        <v>-3.2283158252683384E-8</v>
+        <v>-7.1055525657525066E-5</v>
       </c>
       <c r="H19">
-        <v>7.771277598722228E-8</v>
+        <v>-6.2632347463372669E-5</v>
       </c>
       <c r="I19">
-        <v>5.5295837727037128E-6</v>
+        <v>1.9202472109283333E-3</v>
       </c>
       <c r="J19">
-        <v>1.2505753271091705E-5</v>
+        <v>3.615740519479496E-3</v>
       </c>
       <c r="K19">
-        <v>1.1503337722759279E-5</v>
+        <v>4.1850029766218669E-3</v>
       </c>
       <c r="L19">
-        <v>1.185367266240246E-5</v>
+        <v>4.2159512317142076E-3</v>
       </c>
       <c r="M19">
-        <v>4.4644545223549961E-7</v>
+        <v>-7.48074739260978E-4</v>
       </c>
       <c r="N19">
-        <v>9.9339962425815193E-7</v>
+        <v>-9.7096183821023473E-4</v>
       </c>
       <c r="O19">
-        <v>1.3686157552775058E-6</v>
+        <v>1.0522118485355687E-4</v>
       </c>
       <c r="P19">
-        <v>-1.3199493747572004E-7</v>
+        <v>-2.6323040627437952E-4</v>
       </c>
       <c r="Q19">
-        <v>-5.055724048259883E-6</v>
+        <v>-9.1183202878818967E-5</v>
       </c>
       <c r="R19">
-        <v>-1.7657669317334447E-4</v>
+        <v>-4.0170271131596026E-3</v>
       </c>
       <c r="S19">
-        <v>5.1451894860847389E-5</v>
+        <v>5.9696487525139129E-4</v>
       </c>
       <c r="T19">
-        <v>1.7317003731916634E-4</v>
+        <v>3.6682744097145362E-3</v>
       </c>
       <c r="U19">
-        <v>1.0463344949107422E-4</v>
+        <v>-2.4029722648938108E-2</v>
       </c>
       <c r="V19">
-        <v>2.5869244040823447E-5</v>
+        <v>4.9771212603583626E-3</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B20">
-        <v>0.46989316624259214</v>
+        <v>3.4531576224331753</v>
       </c>
       <c r="C20">
-        <v>-1.3581812153349269E-4</v>
+        <v>-1.233507789616157E-2</v>
       </c>
       <c r="D20">
-        <v>1.3486738456722985E-6</v>
+        <v>1.3839164502240899E-4</v>
       </c>
       <c r="E20">
-        <v>-9.4751014556620095E-4</v>
+        <v>-4.2678044263341978E-2</v>
       </c>
       <c r="F20">
-        <v>-8.6410843228728771E-4</v>
+        <v>-3.407189062287648E-2</v>
       </c>
       <c r="G20">
-        <v>2.0080090501533579E-5</v>
+        <v>1.1259234136053887E-3</v>
       </c>
       <c r="H20">
-        <v>1.7986736255274053E-5</v>
+        <v>1.0200372494442761E-3</v>
       </c>
       <c r="I20">
-        <v>-4.5114645261043404E-3</v>
+        <v>-8.7952893035028373E-2</v>
       </c>
       <c r="J20">
-        <v>-4.5731332264543857E-3</v>
+        <v>-0.11147378422487911</v>
       </c>
       <c r="K20">
-        <v>-4.5702996244230722E-3</v>
+        <v>-0.12020328721952006</v>
       </c>
       <c r="L20">
-        <v>-4.6544832507781977E-3</v>
+        <v>-0.12257202324942776</v>
       </c>
       <c r="M20">
-        <v>-5.7819169517711795E-5</v>
+        <v>8.3338935773214304E-3</v>
       </c>
       <c r="N20">
-        <v>-6.1413736609797494E-5</v>
+        <v>1.1518218726753189E-2</v>
       </c>
       <c r="O20">
-        <v>-4.9159091156030703E-5</v>
+        <v>-2.3893455076486629E-3</v>
       </c>
       <c r="P20">
-        <v>-4.8216519231986875E-5</v>
+        <v>2.1662198583644503E-3</v>
       </c>
       <c r="Q20">
-        <v>-6.9379689896345619E-5</v>
+        <v>-1.6803802571622362E-5</v>
       </c>
       <c r="R20">
-        <v>-9.0583391620158507E-4</v>
+        <v>-1.2004932883604431</v>
       </c>
       <c r="S20">
-        <v>6.3063757134275227E-5</v>
+        <v>5.2492418216069439E-2</v>
       </c>
       <c r="T20">
-        <v>1.0463344949107422E-4</v>
+        <v>-2.4029722648938108E-2</v>
       </c>
       <c r="U20">
-        <v>9.1241469539011574E-3</v>
+        <v>1.6330943179458481</v>
       </c>
       <c r="V20">
-        <v>-3.9013101193907489E-4</v>
+        <v>-5.9092536508592426E-2</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B21">
-        <v>-0.26860491363099981</v>
+        <v>-0.44444973705211444</v>
       </c>
       <c r="C21">
-        <v>9.1279307263844744E-6</v>
+        <v>1.7378040542857525E-3</v>
       </c>
       <c r="D21">
-        <v>-1.0185170581099823E-7</v>
+        <v>-1.9841065727807784E-5</v>
       </c>
       <c r="E21">
-        <v>1.8413144912225894E-5</v>
+        <v>4.7002637835900076E-3</v>
       </c>
       <c r="F21">
-        <v>-4.5895415781448083E-5</v>
+        <v>3.4514272779636707E-3</v>
       </c>
       <c r="G21">
-        <v>-2.719494429391718E-7</v>
+        <v>-1.33190021725481E-4</v>
       </c>
       <c r="H21">
-        <v>8.0800389682367631E-7</v>
+        <v>-1.239755230482082E-4</v>
       </c>
       <c r="I21">
-        <v>3.599024376947505E-5</v>
+        <v>3.3520492765034631E-3</v>
       </c>
       <c r="J21">
-        <v>6.7748653785755313E-5</v>
+        <v>6.7737990161020082E-3</v>
       </c>
       <c r="K21">
-        <v>7.1653071228394276E-5</v>
+        <v>7.9635336881279974E-3</v>
       </c>
       <c r="L21">
-        <v>7.2775823502468332E-5</v>
+        <v>8.2102293173974411E-3</v>
       </c>
       <c r="M21">
-        <v>4.3277350063823145E-6</v>
+        <v>-1.3433702867380055E-3</v>
       </c>
       <c r="N21">
-        <v>3.322856165865744E-6</v>
+        <v>-1.7702229038183573E-3</v>
       </c>
       <c r="O21">
-        <v>4.3296922017281402E-6</v>
+        <v>3.151558691569424E-4</v>
       </c>
       <c r="P21">
-        <v>1.0058047075186908E-6</v>
+        <v>-4.0273379679480224E-4</v>
       </c>
       <c r="Q21">
-        <v>-1.9858735223044794E-5</v>
+        <v>-2.9806649915364023E-4</v>
       </c>
       <c r="R21">
-        <v>3.0560925618840727E-6</v>
+        <v>5.4473525965925244E-3</v>
       </c>
       <c r="S21">
-        <v>3.320797210910334E-5</v>
+        <v>7.4388529200147536E-5</v>
       </c>
       <c r="T21">
-        <v>2.5869244040823447E-5</v>
+        <v>4.9771212603583626E-3</v>
       </c>
       <c r="U21">
-        <v>-3.9013101193907489E-4</v>
+        <v>-5.9092536508592426E-2</v>
       </c>
       <c r="V21">
-        <v>1.4723012525599691E-4</v>
+        <v>9.4283437431565819E-3</v>
       </c>
     </row>
   </sheetData>
@@ -3521,52 +3498,53 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A591251-B8B9-4A10-AB23-25F5FD4E43E4}">
   <dimension ref="A1:W22"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="37.3984375" customWidth="1"/>
+    <col min="1" max="1" width="22.796875" style="3" customWidth="1"/>
+    <col min="2" max="16384" width="8.796875" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>18</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>19</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>20</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>21</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>22</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>23</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>24</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>25</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>26</v>
-      </c>
-      <c r="M1" t="s">
-        <v>27</v>
       </c>
       <c r="N1" t="s">
         <v>35</v>
@@ -3578,806 +3556,806 @@
         <v>37</v>
       </c>
       <c r="Q1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="R1" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" t="s">
         <v>28</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>29</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>30</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>31</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>32</v>
-      </c>
-      <c r="W1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2">
-        <v>0.65493635925190907</v>
+        <v>0.68199805324324614</v>
       </c>
       <c r="C2">
-        <v>1.9059346603558915E-5</v>
+        <v>1.913777950428031E-5</v>
       </c>
       <c r="D2">
-        <v>-8.6000997790478567E-7</v>
+        <v>1.2062722649235683E-6</v>
       </c>
       <c r="E2">
-        <v>6.5833370101400614E-9</v>
+        <v>-1.5335942244663383E-8</v>
       </c>
       <c r="F2">
-        <v>2.5815287862041771E-6</v>
+        <v>5.6212268631333927E-6</v>
       </c>
       <c r="G2">
-        <v>6.2122722714125124E-6</v>
+        <v>6.6107113643827647E-7</v>
       </c>
       <c r="H2">
-        <v>1.6027587317936903E-7</v>
+        <v>-2.7293942404443159E-8</v>
       </c>
       <c r="I2">
-        <v>1.7721779842000854E-7</v>
+        <v>1.426627382113471E-7</v>
       </c>
       <c r="J2">
-        <v>-5.6976714104845028E-6</v>
+        <v>-3.7084880603664447E-7</v>
       </c>
       <c r="K2">
-        <v>-6.9014266545178116E-6</v>
+        <v>1.4129040881132856E-6</v>
       </c>
       <c r="L2">
-        <v>-8.2162222025952288E-6</v>
+        <v>1.3478501141988566E-6</v>
       </c>
       <c r="M2">
-        <v>-8.9891244627903394E-6</v>
+        <v>1.0375116457096504E-6</v>
       </c>
       <c r="N2">
-        <v>1.2661970906163399E-7</v>
+        <v>5.7398308912253866E-7</v>
       </c>
       <c r="O2">
-        <v>-6.9518493894611307E-8</v>
+        <v>7.7075650811588849E-7</v>
       </c>
       <c r="P2">
-        <v>2.5798700839611718E-7</v>
+        <v>-2.9784157159202246E-7</v>
       </c>
       <c r="Q2">
-        <v>8.3306930155372634E-7</v>
+        <v>1.5001927198533433E-6</v>
       </c>
       <c r="R2">
-        <v>-1.8094256791904283E-6</v>
+        <v>1.3906312380880917E-6</v>
       </c>
       <c r="S2">
-        <v>-7.638810731636932E-6</v>
+        <v>-7.0691951341782136E-6</v>
       </c>
       <c r="T2">
-        <v>-1.1465682683918667E-6</v>
+        <v>-7.5948170724471779E-7</v>
       </c>
       <c r="U2">
-        <v>-1.0630336282290113E-6</v>
+        <v>8.6317135121308638E-7</v>
       </c>
       <c r="V2">
-        <v>9.3022942377407939E-6</v>
+        <v>-7.4086508817265836E-5</v>
       </c>
       <c r="W2">
-        <v>-3.9804410411673696E-6</v>
+        <v>3.2240865191396875E-5</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B3">
-        <v>4.8869417376104611E-3</v>
+        <v>6.9976285246309096E-3</v>
       </c>
       <c r="C3">
-        <v>-8.6000997790478567E-7</v>
+        <v>1.2062722649235683E-6</v>
       </c>
       <c r="D3">
-        <v>2.8306116272505912E-5</v>
+        <v>8.5742690850671856E-5</v>
       </c>
       <c r="E3">
-        <v>-3.1522980496079686E-7</v>
+        <v>-8.6415738549963426E-7</v>
       </c>
       <c r="F3">
-        <v>-6.6652925054609161E-6</v>
+        <v>2.0654309350709086E-4</v>
       </c>
       <c r="G3">
-        <v>-7.923517373037985E-5</v>
+        <v>1.4541237358777534E-4</v>
       </c>
       <c r="H3">
-        <v>-3.2474287091841127E-7</v>
+        <v>-5.2373873195704753E-6</v>
       </c>
       <c r="I3">
-        <v>7.70839157869008E-7</v>
+        <v>-5.8841786333292284E-6</v>
       </c>
       <c r="J3">
-        <v>3.9583365777945032E-5</v>
+        <v>-2.540163134975293E-5</v>
       </c>
       <c r="K3">
-        <v>8.1416534515752875E-5</v>
+        <v>3.2703675722657206E-5</v>
       </c>
       <c r="L3">
-        <v>9.3302368470046218E-5</v>
+        <v>5.6300441924130787E-5</v>
       </c>
       <c r="M3">
-        <v>9.7300430334447635E-5</v>
+        <v>5.559680290513329E-5</v>
       </c>
       <c r="N3">
-        <v>5.2546956420048831E-6</v>
+        <v>-1.0746006814810015E-4</v>
       </c>
       <c r="O3">
-        <v>1.5215252554740551E-6</v>
+        <v>-5.7565696572321141E-5</v>
       </c>
       <c r="P3">
-        <v>-6.0713117218063579E-7</v>
+        <v>-2.7754129565687366E-6</v>
       </c>
       <c r="Q3">
-        <v>-3.5737912806322696E-6</v>
+        <v>-2.5813570343207516E-5</v>
       </c>
       <c r="R3">
-        <v>-2.4174388696472871E-6</v>
+        <v>1.627180787194121E-6</v>
       </c>
       <c r="S3">
-        <v>-2.3288747794297768E-6</v>
+        <v>5.467962896406415E-6</v>
       </c>
       <c r="T3">
-        <v>-1.2011560041361067E-5</v>
+        <v>-3.9780246746363259E-5</v>
       </c>
       <c r="U3">
-        <v>3.6721627883471212E-6</v>
+        <v>1.8019385684666995E-5</v>
       </c>
       <c r="V3">
-        <v>-7.3442857595154803E-4</v>
+        <v>-2.2652255543339898E-3</v>
       </c>
       <c r="W3">
-        <v>3.4473550948212645E-4</v>
+        <v>1.1875109946579677E-3</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B4">
-        <v>-1.090864030679191E-5</v>
+        <v>-3.6881000130816143E-5</v>
       </c>
       <c r="C4">
-        <v>6.5833370101400614E-9</v>
+        <v>-1.5335942244663383E-8</v>
       </c>
       <c r="D4">
-        <v>-3.1522980496079686E-7</v>
+        <v>-8.6415738549963426E-7</v>
       </c>
       <c r="E4">
-        <v>3.530960030493122E-9</v>
+        <v>8.7385684962492631E-9</v>
       </c>
       <c r="F4">
-        <v>1.4071100442493119E-7</v>
+        <v>-1.9796566657837449E-6</v>
       </c>
       <c r="G4">
-        <v>9.4759598504475022E-7</v>
+        <v>-1.3532304079459995E-6</v>
       </c>
       <c r="H4">
-        <v>1.9785606840727647E-9</v>
+        <v>5.0464555632425923E-8</v>
       </c>
       <c r="I4">
-        <v>-1.0209826380098016E-8</v>
+        <v>5.6705086261879623E-8</v>
       </c>
       <c r="J4">
-        <v>-4.3981695760348006E-7</v>
+        <v>2.5664571837439581E-7</v>
       </c>
       <c r="K4">
-        <v>-9.050022493727554E-7</v>
+        <v>-3.2565318431923075E-7</v>
       </c>
       <c r="L4">
-        <v>-1.0339765347455164E-6</v>
+        <v>-5.6007045846756847E-7</v>
       </c>
       <c r="M4">
-        <v>-1.0740431484015635E-6</v>
+        <v>-5.503446542352879E-7</v>
       </c>
       <c r="N4">
-        <v>-5.8915762565559313E-8</v>
+        <v>1.0781525743160867E-6</v>
       </c>
       <c r="O4">
-        <v>-1.728569909033523E-8</v>
+        <v>5.7533296806500287E-7</v>
       </c>
       <c r="P4">
-        <v>5.9579792976407265E-9</v>
+        <v>2.8281866792697337E-8</v>
       </c>
       <c r="Q4">
-        <v>3.9340621499817277E-8</v>
+        <v>2.5846477606465287E-7</v>
       </c>
       <c r="R4">
-        <v>2.5712388004624476E-8</v>
+        <v>-1.5991186959250754E-8</v>
       </c>
       <c r="S4">
-        <v>1.9964741322797355E-8</v>
+        <v>-2.5448308861917681E-8</v>
       </c>
       <c r="T4">
-        <v>1.3434161569865041E-7</v>
+        <v>3.9794192450660095E-7</v>
       </c>
       <c r="U4">
-        <v>-4.0311005139486502E-8</v>
+        <v>-1.8334525627835875E-7</v>
       </c>
       <c r="V4">
-        <v>8.1480030688777704E-6</v>
+        <v>2.2736778076506119E-5</v>
       </c>
       <c r="W4">
-        <v>-3.8377086730127302E-6</v>
+        <v>-1.1937540316577405E-5</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B5">
-        <v>4.1421043731995587E-3</v>
+        <v>-8.1135991991942574E-2</v>
       </c>
       <c r="C5">
-        <v>2.5815287862041771E-6</v>
+        <v>5.6212268631333927E-6</v>
       </c>
       <c r="D5">
-        <v>-6.6652925054609161E-6</v>
+        <v>2.0654309350709086E-4</v>
       </c>
       <c r="E5">
-        <v>1.4071100442493119E-7</v>
+        <v>-1.9796566657837449E-6</v>
       </c>
       <c r="F5">
-        <v>4.7634081059959668E-4</v>
+        <v>1.1983033493765611E-3</v>
       </c>
       <c r="G5">
-        <v>3.1569438400348856E-4</v>
+        <v>8.0367069169660595E-4</v>
       </c>
       <c r="H5">
-        <v>-1.0205890539477948E-5</v>
+        <v>-2.7366327288283479E-5</v>
       </c>
       <c r="I5">
-        <v>-6.5582710243005488E-6</v>
+        <v>-2.357063202698037E-5</v>
       </c>
       <c r="J5">
-        <v>-2.5789985308893408E-5</v>
+        <v>-6.1710564716978749E-5</v>
       </c>
       <c r="K5">
-        <v>-5.1509009140939901E-5</v>
+        <v>7.7171593957509082E-5</v>
       </c>
       <c r="L5">
-        <v>-6.0565364043603856E-5</v>
+        <v>1.3302421491643581E-4</v>
       </c>
       <c r="M5">
-        <v>-5.6261975882459649E-5</v>
+        <v>1.3163072179445904E-4</v>
       </c>
       <c r="N5">
-        <v>-7.0815441203368106E-6</v>
+        <v>-2.536675896453388E-4</v>
       </c>
       <c r="O5">
-        <v>8.242789506296652E-7</v>
+        <v>-1.4153668741321608E-4</v>
       </c>
       <c r="P5">
-        <v>-1.5120695527670823E-6</v>
+        <v>-6.6659062486234025E-6</v>
       </c>
       <c r="Q5">
-        <v>4.0492306247985855E-6</v>
+        <v>-6.329812428127924E-5</v>
       </c>
       <c r="R5">
-        <v>2.3124537256061089E-6</v>
+        <v>1.610155841920046E-7</v>
       </c>
       <c r="S5">
-        <v>-9.7893174518942825E-7</v>
+        <v>-3.9226460914701242E-5</v>
       </c>
       <c r="T5">
-        <v>7.1616666509452442E-6</v>
+        <v>-8.8653091652942132E-5</v>
       </c>
       <c r="U5">
-        <v>-1.5890262900624007E-6</v>
+        <v>4.3662075074686928E-5</v>
       </c>
       <c r="V5">
-        <v>8.5618214057655776E-5</v>
+        <v>-5.6321439965972223E-3</v>
       </c>
       <c r="W5">
-        <v>-1.8916149681202706E-4</v>
+        <v>2.7802959490674716E-3</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B6">
-        <v>1.286669848501985E-2</v>
+        <v>-4.5838392236215018E-2</v>
       </c>
       <c r="C6">
-        <v>6.2122722714125124E-6</v>
+        <v>6.6107113643827647E-7</v>
       </c>
       <c r="D6">
-        <v>-7.923517373037985E-5</v>
+        <v>1.4541237358777534E-4</v>
       </c>
       <c r="E6">
-        <v>9.4759598504475022E-7</v>
+        <v>-1.3532304079459995E-6</v>
       </c>
       <c r="F6">
-        <v>3.1569438400348856E-4</v>
+        <v>8.0367069169660595E-4</v>
       </c>
       <c r="G6">
-        <v>3.1109900291074154E-3</v>
+        <v>1.6096149882882185E-3</v>
       </c>
       <c r="H6">
-        <v>-5.3881922403952672E-6</v>
+        <v>-1.8552602411372245E-5</v>
       </c>
       <c r="I6">
-        <v>-6.0697756048079386E-5</v>
+        <v>-3.7772340557620939E-5</v>
       </c>
       <c r="J6">
-        <v>-1.9430753933216552E-4</v>
+        <v>-3.4079829090298148E-5</v>
       </c>
       <c r="K6">
-        <v>-3.5181364120181373E-4</v>
+        <v>6.3380973823649167E-5</v>
       </c>
       <c r="L6">
-        <v>-3.9873747540823267E-4</v>
+        <v>1.0285443519936444E-4</v>
       </c>
       <c r="M6">
-        <v>-3.9648793457203668E-4</v>
+        <v>1.0658971475805844E-4</v>
       </c>
       <c r="N6">
-        <v>-2.3376317780741311E-5</v>
+        <v>-1.9197720208730812E-4</v>
       </c>
       <c r="O6">
-        <v>2.5565518385991422E-6</v>
+        <v>-1.0328493783283753E-4</v>
       </c>
       <c r="P6">
-        <v>5.1405605933026E-6</v>
+        <v>2.0422376462822073E-7</v>
       </c>
       <c r="Q6">
-        <v>1.8472014403955481E-5</v>
+        <v>-4.083919170041362E-5</v>
       </c>
       <c r="R6">
-        <v>7.2920127248009296E-6</v>
+        <v>-1.8121544406037796E-6</v>
       </c>
       <c r="S6">
-        <v>4.111706877664224E-6</v>
+        <v>-5.8921022495535959E-5</v>
       </c>
       <c r="T6">
-        <v>4.6121558840662034E-5</v>
+        <v>-5.9915900245017501E-5</v>
       </c>
       <c r="U6">
-        <v>-1.2937138249507326E-5</v>
+        <v>3.7105349461015292E-5</v>
       </c>
       <c r="V6">
-        <v>2.0823410431065666E-3</v>
+        <v>-4.0411483732586111E-3</v>
       </c>
       <c r="W6">
-        <v>-1.2330880286022979E-3</v>
+        <v>2.0359568289005175E-3</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B7">
-        <v>-3.2382357430452077E-3</v>
+        <v>-4.4875491933232906E-4</v>
       </c>
       <c r="C7">
-        <v>1.6027587317936903E-7</v>
+        <v>-2.7293942404443159E-8</v>
       </c>
       <c r="D7">
-        <v>-3.2474287091841127E-7</v>
+        <v>-5.2373873195704753E-6</v>
       </c>
       <c r="E7">
-        <v>1.9785606840727647E-9</v>
+        <v>5.0464555632425923E-8</v>
       </c>
       <c r="F7">
-        <v>-1.0205890539477948E-5</v>
+        <v>-2.7366327288283479E-5</v>
       </c>
       <c r="G7">
-        <v>-5.3881922403952672E-6</v>
+        <v>-1.8552602411372245E-5</v>
       </c>
       <c r="H7">
-        <v>2.4290266211954658E-7</v>
+        <v>6.4715594227930877E-7</v>
       </c>
       <c r="I7">
-        <v>1.4068548901363407E-7</v>
+        <v>5.7252754356328463E-7</v>
       </c>
       <c r="J7">
-        <v>-3.1950932896227382E-7</v>
+        <v>1.5962264268634294E-6</v>
       </c>
       <c r="K7">
-        <v>-5.4972616012511739E-7</v>
+        <v>-1.9606571559199221E-6</v>
       </c>
       <c r="L7">
-        <v>-5.4485382243105407E-7</v>
+        <v>-3.3716940174969441E-6</v>
       </c>
       <c r="M7">
-        <v>-6.5772627917917458E-7</v>
+        <v>-3.3191059559450883E-6</v>
       </c>
       <c r="N7">
-        <v>4.2365679773938872E-8</v>
+        <v>6.5476651279201855E-6</v>
       </c>
       <c r="O7">
-        <v>-2.1729568684264149E-8</v>
+        <v>3.6464293863072883E-6</v>
       </c>
       <c r="P7">
-        <v>5.7380381254192762E-8</v>
+        <v>1.6099206125369656E-7</v>
       </c>
       <c r="Q7">
-        <v>2.2200708155012414E-8</v>
+        <v>1.6385784382750396E-6</v>
       </c>
       <c r="R7">
-        <v>6.0561680090871548E-8</v>
+        <v>-3.3500612307447998E-8</v>
       </c>
       <c r="S7">
-        <v>1.8315129449694071E-7</v>
+        <v>9.8153138123749723E-9</v>
       </c>
       <c r="T7">
-        <v>5.6901951212809838E-8</v>
+        <v>2.3738642955860579E-6</v>
       </c>
       <c r="U7">
-        <v>-5.1889532429139078E-8</v>
+        <v>-1.0597640867246595E-6</v>
       </c>
       <c r="V7">
-        <v>1.0301303485391382E-5</v>
+        <v>1.4248623538029207E-4</v>
       </c>
       <c r="W7">
-        <v>-2.4601043376857489E-6</v>
+        <v>-7.1339167302083472E-5</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B8">
-        <v>-4.4994366116995971E-3</v>
+        <v>-3.449279352949787E-3</v>
       </c>
       <c r="C8">
-        <v>1.7721779842000854E-7</v>
+        <v>1.426627382113471E-7</v>
       </c>
       <c r="D8">
-        <v>7.70839157869008E-7</v>
+        <v>-5.8841786333292284E-6</v>
       </c>
       <c r="E8">
-        <v>-1.0209826380098016E-8</v>
+        <v>5.6705086261879623E-8</v>
       </c>
       <c r="F8">
-        <v>-6.5582710243005488E-6</v>
+        <v>-2.357063202698037E-5</v>
       </c>
       <c r="G8">
-        <v>-6.0697756048079386E-5</v>
+        <v>-3.7772340557620939E-5</v>
       </c>
       <c r="H8">
-        <v>1.4068548901363407E-7</v>
+        <v>5.7252754356328463E-7</v>
       </c>
       <c r="I8">
-        <v>1.2837244723289613E-6</v>
+        <v>1.0002211703389787E-6</v>
       </c>
       <c r="J8">
-        <v>2.830573149224847E-6</v>
+        <v>1.5663691944885896E-6</v>
       </c>
       <c r="K8">
-        <v>4.658912122360981E-6</v>
+        <v>-2.4777930228292852E-6</v>
       </c>
       <c r="L8">
-        <v>5.3053558690130104E-6</v>
+        <v>-4.0556197383099327E-6</v>
       </c>
       <c r="M8">
-        <v>5.2040068415561265E-6</v>
+        <v>-4.0597873330843452E-6</v>
       </c>
       <c r="N8">
-        <v>2.3745757529987608E-7</v>
+        <v>7.7990107241565899E-6</v>
       </c>
       <c r="O8">
-        <v>-6.4093377719123066E-8</v>
+        <v>4.2202690337804907E-6</v>
       </c>
       <c r="P8">
-        <v>-1.2783805269460975E-7</v>
+        <v>1.0260164020246128E-7</v>
       </c>
       <c r="Q8">
-        <v>-2.2329774810566435E-7</v>
+        <v>1.8121790944371676E-6</v>
       </c>
       <c r="R8">
-        <v>-6.7465645008383177E-8</v>
+        <v>-9.3580775300956445E-8</v>
       </c>
       <c r="S8">
-        <v>1.8190676294545632E-7</v>
+        <v>-5.0551416430700296E-7</v>
       </c>
       <c r="T8">
-        <v>-5.4830564957133893E-7</v>
+        <v>2.7901328274622864E-6</v>
       </c>
       <c r="U8">
-        <v>1.1503473760666792E-7</v>
+        <v>-1.3050336012559556E-6</v>
       </c>
       <c r="V8">
-        <v>-2.0710492214583206E-5</v>
+        <v>1.6100255253928916E-4</v>
       </c>
       <c r="W8">
-        <v>1.3237742946188823E-5</v>
+        <v>-8.3881507304688877E-5</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B9">
-        <v>0.16167612244374621</v>
+        <v>3.6146009348822436E-2</v>
       </c>
       <c r="C9">
-        <v>-5.6976714104845028E-6</v>
+        <v>-3.7084880603664447E-7</v>
       </c>
       <c r="D9">
-        <v>3.9583365777945032E-5</v>
+        <v>-2.540163134975293E-5</v>
       </c>
       <c r="E9">
-        <v>-4.3981695760348006E-7</v>
+        <v>2.5664571837439581E-7</v>
       </c>
       <c r="F9">
-        <v>-2.5789985308893408E-5</v>
+        <v>-6.1710564716978749E-5</v>
       </c>
       <c r="G9">
-        <v>-1.9430753933216552E-4</v>
+        <v>-3.4079829090298148E-5</v>
       </c>
       <c r="H9">
-        <v>-3.1950932896227382E-7</v>
+        <v>1.5962264268634294E-6</v>
       </c>
       <c r="I9">
-        <v>2.830573149224847E-6</v>
+        <v>1.5663691944885896E-6</v>
       </c>
       <c r="J9">
-        <v>3.2837608197614355E-3</v>
+        <v>2.1062253287329811E-3</v>
       </c>
       <c r="K9">
-        <v>3.1625816526356619E-3</v>
+        <v>1.836834620196784E-3</v>
       </c>
       <c r="L9">
-        <v>3.1833652638951094E-3</v>
+        <v>1.8316860588078652E-3</v>
       </c>
       <c r="M9">
-        <v>3.1873626920500241E-3</v>
+        <v>1.8324813797798265E-3</v>
       </c>
       <c r="N9">
-        <v>9.9080770162347396E-6</v>
+        <v>3.6184611053922967E-5</v>
       </c>
       <c r="O9">
-        <v>5.9494935563580898E-7</v>
+        <v>1.7180071106018847E-5</v>
       </c>
       <c r="P9">
-        <v>1.8700704428425198E-6</v>
+        <v>-2.553400153066509E-6</v>
       </c>
       <c r="Q9">
-        <v>-7.8370437410436407E-6</v>
+        <v>7.381091666825412E-6</v>
       </c>
       <c r="R9">
-        <v>-8.5472579157798499E-6</v>
+        <v>-8.2137912488988113E-7</v>
       </c>
       <c r="S9">
-        <v>1.4207074890481747E-5</v>
+        <v>-4.5526137591991797E-6</v>
       </c>
       <c r="T9">
-        <v>-2.1790482295466835E-5</v>
+        <v>2.9314539417184183E-5</v>
       </c>
       <c r="U9">
-        <v>6.0913651543852054E-6</v>
+        <v>-5.3787837133823911E-6</v>
       </c>
       <c r="V9">
-        <v>-4.1017031403905498E-3</v>
+        <v>-1.1754736240627934E-3</v>
       </c>
       <c r="W9">
-        <v>5.6759748676092755E-4</v>
+        <v>-3.6194870595737623E-4</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B10">
-        <v>0.18973741410203654</v>
+        <v>3.6740312485211028E-2</v>
       </c>
       <c r="C10">
-        <v>-6.9014266545178116E-6</v>
+        <v>1.4129040881132856E-6</v>
       </c>
       <c r="D10">
-        <v>8.1416534515752875E-5</v>
+        <v>3.2703675722657206E-5</v>
       </c>
       <c r="E10">
-        <v>-9.050022493727554E-7</v>
+        <v>-3.2565318431923075E-7</v>
       </c>
       <c r="F10">
-        <v>-5.1509009140939901E-5</v>
+        <v>7.7171593957509082E-5</v>
       </c>
       <c r="G10">
-        <v>-3.5181364120181373E-4</v>
+        <v>6.3380973823649167E-5</v>
       </c>
       <c r="H10">
-        <v>-5.4972616012511739E-7</v>
+        <v>-1.9606571559199221E-6</v>
       </c>
       <c r="I10">
-        <v>4.658912122360981E-6</v>
+        <v>-2.4777930228292852E-6</v>
       </c>
       <c r="J10">
-        <v>3.1625816526356619E-3</v>
+        <v>1.836834620196784E-3</v>
       </c>
       <c r="K10">
-        <v>3.330544332883685E-3</v>
+        <v>1.9055937108851176E-3</v>
       </c>
       <c r="L10">
-        <v>3.3464812395687369E-3</v>
+        <v>1.8761558155290328E-3</v>
       </c>
       <c r="M10">
-        <v>3.3553058359356977E-3</v>
+        <v>1.8763102210595686E-3</v>
       </c>
       <c r="N10">
-        <v>1.888232428344625E-5</v>
+        <v>-4.2465302452158812E-5</v>
       </c>
       <c r="O10">
-        <v>3.6887404228962898E-6</v>
+        <v>-2.3796836505771281E-5</v>
       </c>
       <c r="P10">
-        <v>8.7708916391257764E-7</v>
+        <v>-4.338520810470387E-6</v>
       </c>
       <c r="Q10">
-        <v>-1.3316266556745697E-5</v>
+        <v>-1.0682151576128863E-5</v>
       </c>
       <c r="R10">
-        <v>-1.3060196754304832E-5</v>
+        <v>1.2291135965287135E-6</v>
       </c>
       <c r="S10">
-        <v>8.605497912210492E-6</v>
+        <v>1.3930702664055563E-5</v>
       </c>
       <c r="T10">
-        <v>-4.171583904291808E-5</v>
+        <v>2.8579166551748782E-6</v>
       </c>
       <c r="U10">
-        <v>1.2141635783602395E-5</v>
+        <v>6.3538034709517348E-6</v>
       </c>
       <c r="V10">
-        <v>-5.2212564622056909E-3</v>
+        <v>-2.750179872518705E-3</v>
       </c>
       <c r="W10">
-        <v>1.1562173899322644E-3</v>
+        <v>4.9904101544946764E-4</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B11">
-        <v>0.21212185294897459</v>
+        <v>3.6978234740322739E-2</v>
       </c>
       <c r="C11">
-        <v>-8.2162222025952288E-6</v>
+        <v>1.3478501141988566E-6</v>
       </c>
       <c r="D11">
-        <v>9.3302368470046218E-5</v>
+        <v>5.6300441924130787E-5</v>
       </c>
       <c r="E11">
-        <v>-1.0339765347455164E-6</v>
+        <v>-5.6007045846756847E-7</v>
       </c>
       <c r="F11">
-        <v>-6.0565364043603856E-5</v>
+        <v>1.3302421491643581E-4</v>
       </c>
       <c r="G11">
-        <v>-3.9873747540823267E-4</v>
+        <v>1.0285443519936444E-4</v>
       </c>
       <c r="H11">
-        <v>-5.4485382243105407E-7</v>
+        <v>-3.3716940174969441E-6</v>
       </c>
       <c r="I11">
-        <v>5.3053558690130104E-6</v>
+        <v>-4.0556197383099327E-6</v>
       </c>
       <c r="J11">
-        <v>3.1833652638951094E-3</v>
+        <v>1.8316860588078652E-3</v>
       </c>
       <c r="K11">
-        <v>3.3464812395687369E-3</v>
+        <v>1.8761558155290328E-3</v>
       </c>
       <c r="L11">
-        <v>3.4068925215203186E-3</v>
+        <v>1.907242560913365E-3</v>
       </c>
       <c r="M11">
-        <v>3.4096375164412778E-3</v>
+        <v>1.8993070393110143E-3</v>
       </c>
       <c r="N11">
-        <v>2.1259373765465343E-5</v>
+        <v>-7.32204663600155E-5</v>
       </c>
       <c r="O11">
-        <v>4.402967444260334E-6</v>
+        <v>-4.0966640079084679E-5</v>
       </c>
       <c r="P11">
-        <v>5.8272237350252336E-7</v>
+        <v>-6.1134282176976586E-6</v>
       </c>
       <c r="Q11">
-        <v>-1.4954245164430802E-5</v>
+        <v>-1.8775840803964985E-5</v>
       </c>
       <c r="R11">
-        <v>-1.3507609366260723E-5</v>
+        <v>2.0551628121100457E-6</v>
       </c>
       <c r="S11">
-        <v>2.5277616941142774E-6</v>
+        <v>3.0636856456968994E-5</v>
       </c>
       <c r="T11">
-        <v>-4.7714175864834933E-5</v>
+        <v>-2.8332843778281255E-6</v>
       </c>
       <c r="U11">
-        <v>1.3304948543835776E-5</v>
+        <v>1.0493262944508814E-5</v>
       </c>
       <c r="V11">
-        <v>-5.5452823308483334E-3</v>
+        <v>-3.4062851109594606E-3</v>
       </c>
       <c r="W11">
-        <v>1.3270136214409999E-3</v>
+        <v>8.4688284908119779E-4</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B12">
-        <v>0.22636365858606519</v>
+        <v>4.2913822300698422E-2</v>
       </c>
       <c r="C12">
-        <v>-8.9891244627903394E-6</v>
+        <v>1.0375116457096504E-6</v>
       </c>
       <c r="D12">
-        <v>9.7300430334447635E-5</v>
+        <v>5.559680290513329E-5</v>
       </c>
       <c r="E12">
-        <v>-1.0740431484015635E-6</v>
+        <v>-5.503446542352879E-7</v>
       </c>
       <c r="F12">
-        <v>-5.6261975882459649E-5</v>
+        <v>1.3163072179445904E-4</v>
       </c>
       <c r="G12">
-        <v>-3.9648793457203668E-4</v>
+        <v>1.0658971475805844E-4</v>
       </c>
       <c r="H12">
-        <v>-6.5772627917917458E-7</v>
+        <v>-3.3191059559450883E-6</v>
       </c>
       <c r="I12">
-        <v>5.2040068415561265E-6</v>
+        <v>-4.0597873330843452E-6</v>
       </c>
       <c r="J12">
-        <v>3.1873626920500241E-3</v>
+        <v>1.8324813797798265E-3</v>
       </c>
       <c r="K12">
-        <v>3.3553058359356977E-3</v>
+        <v>1.8763102210595686E-3</v>
       </c>
       <c r="L12">
-        <v>3.4096375164412778E-3</v>
+        <v>1.8993070393110143E-3</v>
       </c>
       <c r="M12">
-        <v>3.4588229173083767E-3</v>
+        <v>1.9453502921422863E-3</v>
       </c>
       <c r="N12">
-        <v>2.2359840298451983E-5</v>
+        <v>-7.131298125782464E-5</v>
       </c>
       <c r="O12">
-        <v>5.1616597157373258E-6</v>
+        <v>-3.8954860224197613E-5</v>
       </c>
       <c r="P12">
-        <v>5.407295903706677E-7</v>
+        <v>-3.9108617258394377E-6</v>
       </c>
       <c r="Q12">
-        <v>-1.4231341862010386E-5</v>
+        <v>-1.7327950802995363E-5</v>
       </c>
       <c r="R12">
-        <v>-1.3626308887664722E-5</v>
+        <v>3.1371917244796915E-6</v>
       </c>
       <c r="S12">
-        <v>2.2265893624223426E-6</v>
+        <v>5.6268678595463889E-5</v>
       </c>
       <c r="T12">
-        <v>-4.8252409326986841E-5</v>
+        <v>-2.0125873921162316E-6</v>
       </c>
       <c r="U12">
-        <v>1.4034662792986058E-5</v>
+        <v>6.182308034329773E-6</v>
       </c>
       <c r="V12">
-        <v>-5.6559134183112088E-3</v>
+        <v>-3.4190645496195793E-3</v>
       </c>
       <c r="W12">
-        <v>1.3620000551586274E-3</v>
+        <v>8.2353806270582476E-4</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.45">
@@ -4385,70 +4363,70 @@
         <v>35</v>
       </c>
       <c r="B13">
-        <v>-7.4342097182633375E-3</v>
+        <v>-6.2786905017787303E-2</v>
       </c>
       <c r="C13">
-        <v>1.2661970906163399E-7</v>
+        <v>5.7398308912253866E-7</v>
       </c>
       <c r="D13">
-        <v>5.2546956420048831E-6</v>
+        <v>-1.0746006814810015E-4</v>
       </c>
       <c r="E13">
-        <v>-5.8915762565559313E-8</v>
+        <v>1.0781525743160867E-6</v>
       </c>
       <c r="F13">
-        <v>-7.0815441203368106E-6</v>
+        <v>-2.536675896453388E-4</v>
       </c>
       <c r="G13">
-        <v>-2.3376317780741311E-5</v>
+        <v>-1.9197720208730812E-4</v>
       </c>
       <c r="H13">
-        <v>4.2365679773938872E-8</v>
+        <v>6.5476651279201855E-6</v>
       </c>
       <c r="I13">
-        <v>2.3745757529987608E-7</v>
+        <v>7.7990107241565899E-6</v>
       </c>
       <c r="J13">
-        <v>9.9080770162347396E-6</v>
+        <v>3.6184611053922967E-5</v>
       </c>
       <c r="K13">
-        <v>1.888232428344625E-5</v>
+        <v>-4.2465302452158812E-5</v>
       </c>
       <c r="L13">
-        <v>2.1259373765465343E-5</v>
+        <v>-7.32204663600155E-5</v>
       </c>
       <c r="M13">
-        <v>2.2359840298451983E-5</v>
+        <v>-7.131298125782464E-5</v>
       </c>
       <c r="N13">
-        <v>6.8773196863339947E-5</v>
+        <v>2.1407971357716271E-4</v>
       </c>
       <c r="O13">
-        <v>3.3090843969030949E-5</v>
+        <v>1.0062938331568394E-4</v>
       </c>
       <c r="P13">
-        <v>3.2905924990475407E-5</v>
+        <v>2.671941348306832E-5</v>
       </c>
       <c r="Q13">
-        <v>3.2094126045819074E-5</v>
+        <v>5.7826264804505199E-5</v>
       </c>
       <c r="R13">
-        <v>5.4150531919788664E-7</v>
+        <v>-3.8142493212426126E-6</v>
       </c>
       <c r="S13">
-        <v>-8.8129052333525527E-6</v>
+        <v>4.0443986987236523E-6</v>
       </c>
       <c r="T13">
-        <v>-2.866647960646127E-6</v>
+        <v>5.3783725873561484E-5</v>
       </c>
       <c r="U13">
-        <v>3.5418332925924737E-7</v>
+        <v>-2.3192887817426128E-5</v>
       </c>
       <c r="V13">
-        <v>-1.6457776308506091E-4</v>
+        <v>2.8248111853020497E-3</v>
       </c>
       <c r="W13">
-        <v>7.4806736932902737E-5</v>
+        <v>-1.5784969544392696E-3</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.45">
@@ -4456,70 +4434,70 @@
         <v>36</v>
       </c>
       <c r="B14">
-        <v>8.6272601741241659E-3</v>
+        <v>-3.6690909025168139E-2</v>
       </c>
       <c r="C14">
-        <v>-6.9518493894611307E-8</v>
+        <v>7.7075650811588849E-7</v>
       </c>
       <c r="D14">
-        <v>1.5215252554740551E-6</v>
+        <v>-5.7565696572321141E-5</v>
       </c>
       <c r="E14">
-        <v>-1.728569909033523E-8</v>
+        <v>5.7533296806500287E-7</v>
       </c>
       <c r="F14">
-        <v>8.242789506296652E-7</v>
+        <v>-1.4153668741321608E-4</v>
       </c>
       <c r="G14">
-        <v>2.5565518385991422E-6</v>
+        <v>-1.0328493783283753E-4</v>
       </c>
       <c r="H14">
-        <v>-2.1729568684264149E-8</v>
+        <v>3.6464293863072883E-6</v>
       </c>
       <c r="I14">
-        <v>-6.4093377719123066E-8</v>
+        <v>4.2202690337804907E-6</v>
       </c>
       <c r="J14">
-        <v>5.9494935563580898E-7</v>
+        <v>1.7180071106018847E-5</v>
       </c>
       <c r="K14">
-        <v>3.6887404228962898E-6</v>
+        <v>-2.3796836505771281E-5</v>
       </c>
       <c r="L14">
-        <v>4.402967444260334E-6</v>
+        <v>-4.0966640079084679E-5</v>
       </c>
       <c r="M14">
-        <v>5.1616597157373258E-6</v>
+        <v>-3.8954860224197613E-5</v>
       </c>
       <c r="N14">
-        <v>3.3090843969030949E-5</v>
+        <v>1.0062938331568394E-4</v>
       </c>
       <c r="O14">
-        <v>8.7408098994077693E-5</v>
+        <v>1.7269037588486081E-4</v>
       </c>
       <c r="P14">
-        <v>3.2873917247482316E-5</v>
+        <v>2.5180825863007809E-5</v>
       </c>
       <c r="Q14">
-        <v>3.2766508495468833E-5</v>
+        <v>4.1947629783644746E-5</v>
       </c>
       <c r="R14">
-        <v>8.2071768636296974E-7</v>
+        <v>-3.970860629549847E-6</v>
       </c>
       <c r="S14">
-        <v>-4.7797111860285313E-6</v>
+        <v>-9.4241981174902815E-6</v>
       </c>
       <c r="T14">
-        <v>-8.0363386787651864E-7</v>
+        <v>2.8203438483300844E-5</v>
       </c>
       <c r="U14">
-        <v>-9.7824359039269792E-8</v>
+        <v>-1.4177483850043127E-5</v>
       </c>
       <c r="V14">
-        <v>-6.6289282635189167E-5</v>
+        <v>1.51914610809646E-3</v>
       </c>
       <c r="W14">
-        <v>1.6886916987252356E-5</v>
+        <v>-8.4625518848837256E-4</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.45">
@@ -4527,567 +4505,567 @@
         <v>37</v>
       </c>
       <c r="B15">
-        <v>-1.1672282220383994E-3</v>
+        <v>3.7913005940314096E-3</v>
       </c>
       <c r="C15">
-        <v>2.5798700839611718E-7</v>
+        <v>-2.9784157159202246E-7</v>
       </c>
       <c r="D15">
-        <v>-6.0713117218063579E-7</v>
+        <v>-2.7754129565687366E-6</v>
       </c>
       <c r="E15">
-        <v>5.9579792976407265E-9</v>
+        <v>2.8281866792697337E-8</v>
       </c>
       <c r="F15">
-        <v>-1.5120695527670823E-6</v>
+        <v>-6.6659062486234025E-6</v>
       </c>
       <c r="G15">
-        <v>5.1405605933026E-6</v>
+        <v>2.0422376462822073E-7</v>
       </c>
       <c r="H15">
-        <v>5.7380381254192762E-8</v>
+        <v>1.6099206125369656E-7</v>
       </c>
       <c r="I15">
-        <v>-1.2783805269460975E-7</v>
+        <v>1.0260164020246128E-7</v>
       </c>
       <c r="J15">
-        <v>1.8700704428425198E-6</v>
+        <v>-2.553400153066509E-6</v>
       </c>
       <c r="K15">
-        <v>8.7708916391257764E-7</v>
+        <v>-4.338520810470387E-6</v>
       </c>
       <c r="L15">
-        <v>5.8272237350252336E-7</v>
+        <v>-6.1134282176976586E-6</v>
       </c>
       <c r="M15">
-        <v>5.407295903706677E-7</v>
+        <v>-3.9108617258394377E-6</v>
       </c>
       <c r="N15">
-        <v>3.2905924990475407E-5</v>
+        <v>2.671941348306832E-5</v>
       </c>
       <c r="O15">
-        <v>3.2873917247482316E-5</v>
+        <v>2.5180825863007809E-5</v>
       </c>
       <c r="P15">
-        <v>6.6046356122941626E-5</v>
+        <v>4.4479702942609576E-5</v>
       </c>
       <c r="Q15">
-        <v>3.3050708144639963E-5</v>
+        <v>2.4100973915409327E-5</v>
       </c>
       <c r="R15">
-        <v>9.1231396466698654E-7</v>
+        <v>-6.8818256352395403E-7</v>
       </c>
       <c r="S15">
-        <v>-8.3489369278263319E-6</v>
+        <v>-1.1665975927933552E-5</v>
       </c>
       <c r="T15">
-        <v>3.6967798489379838E-7</v>
+        <v>1.222620573190338E-6</v>
       </c>
       <c r="U15">
-        <v>-1.6459620265211745E-7</v>
+        <v>-2.2647862753571203E-6</v>
       </c>
       <c r="V15">
-        <v>-9.6978097838441269E-6</v>
+        <v>6.5999442224629626E-5</v>
       </c>
       <c r="W15">
-        <v>-6.844438910271103E-6</v>
+        <v>-4.0579380572970645E-5</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B16">
-        <v>-9.2334790253776212E-3</v>
+        <v>-3.6365925836343155E-2</v>
       </c>
       <c r="C16">
-        <v>8.3306930155372634E-7</v>
+        <v>1.5001927198533433E-6</v>
       </c>
       <c r="D16">
-        <v>-3.5737912806322696E-6</v>
+        <v>-2.5813570343207516E-5</v>
       </c>
       <c r="E16">
-        <v>3.9340621499817277E-8</v>
+        <v>2.5846477606465287E-7</v>
       </c>
       <c r="F16">
-        <v>4.0492306247985855E-6</v>
+        <v>-6.329812428127924E-5</v>
       </c>
       <c r="G16">
-        <v>1.8472014403955481E-5</v>
+        <v>-4.083919170041362E-5</v>
       </c>
       <c r="H16">
-        <v>2.2200708155012414E-8</v>
+        <v>1.6385784382750396E-6</v>
       </c>
       <c r="I16">
-        <v>-2.2329774810566435E-7</v>
+        <v>1.8121790944371676E-6</v>
       </c>
       <c r="J16">
-        <v>-7.8370437410436407E-6</v>
+        <v>7.381091666825412E-6</v>
       </c>
       <c r="K16">
-        <v>-1.3316266556745697E-5</v>
+        <v>-1.0682151576128863E-5</v>
       </c>
       <c r="L16">
-        <v>-1.4954245164430802E-5</v>
+        <v>-1.8775840803964985E-5</v>
       </c>
       <c r="M16">
-        <v>-1.4231341862010386E-5</v>
+        <v>-1.7327950802995363E-5</v>
       </c>
       <c r="N16">
-        <v>3.2094126045819074E-5</v>
+        <v>5.7826264804505199E-5</v>
       </c>
       <c r="O16">
-        <v>3.2766508495468833E-5</v>
+        <v>4.1947629783644746E-5</v>
       </c>
       <c r="P16">
-        <v>3.3050708144639963E-5</v>
+        <v>2.4100973915409327E-5</v>
       </c>
       <c r="Q16">
-        <v>4.7743215965229756E-5</v>
+        <v>5.5310630585243274E-5</v>
       </c>
       <c r="R16">
-        <v>1.2873935043765611E-6</v>
+        <v>-3.5587051547677424E-7</v>
       </c>
       <c r="S16">
-        <v>-6.1106390858646713E-6</v>
+        <v>9.7628022692527762E-6</v>
       </c>
       <c r="T16">
-        <v>1.7605756789283017E-6</v>
+        <v>1.1471251804363177E-5</v>
       </c>
       <c r="U16">
-        <v>-7.0442337689148468E-7</v>
+        <v>-6.7615312172203561E-6</v>
       </c>
       <c r="V16">
-        <v>6.9511915320588088E-5</v>
+        <v>6.4989906821625904E-4</v>
       </c>
       <c r="W16">
-        <v>-5.0797504197031804E-5</v>
+        <v>-3.7794635132694523E-4</v>
       </c>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B17">
-        <v>0.1985418854001314</v>
+        <v>0.15740567496528374</v>
       </c>
       <c r="C17">
-        <v>-1.8094256791904283E-6</v>
+        <v>1.3906312380880917E-6</v>
       </c>
       <c r="D17">
-        <v>-2.4174388696472871E-6</v>
+        <v>1.627180787194121E-6</v>
       </c>
       <c r="E17">
-        <v>2.5712388004624476E-8</v>
+        <v>-1.5991186959250754E-8</v>
       </c>
       <c r="F17">
-        <v>2.3124537256061089E-6</v>
+        <v>1.610155841920046E-7</v>
       </c>
       <c r="G17">
-        <v>7.2920127248009296E-6</v>
+        <v>-1.8121544406037796E-6</v>
       </c>
       <c r="H17">
-        <v>6.0561680090871548E-8</v>
+        <v>-3.3500612307447998E-8</v>
       </c>
       <c r="I17">
-        <v>-6.7465645008383177E-8</v>
+        <v>-9.3580775300956445E-8</v>
       </c>
       <c r="J17">
-        <v>-8.5472579157798499E-6</v>
+        <v>-8.2137912488988113E-7</v>
       </c>
       <c r="K17">
-        <v>-1.3060196754304832E-5</v>
+        <v>1.2291135965287135E-6</v>
       </c>
       <c r="L17">
-        <v>-1.3507609366260723E-5</v>
+        <v>2.0551628121100457E-6</v>
       </c>
       <c r="M17">
-        <v>-1.3626308887664722E-5</v>
+        <v>3.1371917244796915E-6</v>
       </c>
       <c r="N17">
-        <v>5.4150531919788664E-7</v>
+        <v>-3.8142493212426126E-6</v>
       </c>
       <c r="O17">
-        <v>8.2071768636296974E-7</v>
+        <v>-3.970860629549847E-6</v>
       </c>
       <c r="P17">
-        <v>9.1231396466698654E-7</v>
+        <v>-6.8818256352395403E-7</v>
       </c>
       <c r="Q17">
-        <v>1.2873935043765611E-6</v>
+        <v>-3.5587051547677424E-7</v>
       </c>
       <c r="R17">
-        <v>9.8146439784850022E-5</v>
+        <v>4.1438530826023537E-5</v>
       </c>
       <c r="S17">
-        <v>1.305529739308122E-5</v>
+        <v>3.264676691871017E-5</v>
       </c>
       <c r="T17">
-        <v>1.5395918378208393E-6</v>
+        <v>-5.2613657812706994E-6</v>
       </c>
       <c r="U17">
-        <v>-1.9328955441376705E-7</v>
+        <v>-2.626628956494159E-6</v>
       </c>
       <c r="V17">
-        <v>5.3976139089689344E-5</v>
+        <v>-8.6812781026367354E-5</v>
       </c>
       <c r="W17">
-        <v>-4.8236549934383171E-5</v>
+        <v>2.6232957421267347E-5</v>
       </c>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B18">
-        <v>0.19831954916870392</v>
+        <v>0.48015576231408746</v>
       </c>
       <c r="C18">
-        <v>-7.638810731636932E-6</v>
+        <v>-7.0691951341782136E-6</v>
       </c>
       <c r="D18">
-        <v>-2.3288747794297768E-6</v>
+        <v>5.467962896406415E-6</v>
       </c>
       <c r="E18">
-        <v>1.9964741322797355E-8</v>
+        <v>-2.5448308861917681E-8</v>
       </c>
       <c r="F18">
-        <v>-9.7893174518942825E-7</v>
+        <v>-3.9226460914701242E-5</v>
       </c>
       <c r="G18">
-        <v>4.111706877664224E-6</v>
+        <v>-5.8921022495535959E-5</v>
       </c>
       <c r="H18">
-        <v>1.8315129449694071E-7</v>
+        <v>9.8153138123749723E-9</v>
       </c>
       <c r="I18">
-        <v>1.8190676294545632E-7</v>
+        <v>-5.0551416430700296E-7</v>
       </c>
       <c r="J18">
-        <v>1.4207074890481747E-5</v>
+        <v>-4.5526137591991797E-6</v>
       </c>
       <c r="K18">
-        <v>8.605497912210492E-6</v>
+        <v>1.3930702664055563E-5</v>
       </c>
       <c r="L18">
-        <v>2.5277616941142774E-6</v>
+        <v>3.0636856456968994E-5</v>
       </c>
       <c r="M18">
-        <v>2.2265893624223426E-6</v>
+        <v>5.6268678595463889E-5</v>
       </c>
       <c r="N18">
-        <v>-8.8129052333525527E-6</v>
+        <v>4.0443986987236523E-6</v>
       </c>
       <c r="O18">
-        <v>-4.7797111860285313E-6</v>
+        <v>-9.4241981174902815E-6</v>
       </c>
       <c r="P18">
-        <v>-8.3489369278263319E-6</v>
+        <v>-1.1665975927933552E-5</v>
       </c>
       <c r="Q18">
-        <v>-6.1106390858646713E-6</v>
+        <v>9.7628022692527762E-6</v>
       </c>
       <c r="R18">
-        <v>1.305529739308122E-5</v>
+        <v>3.264676691871017E-5</v>
       </c>
       <c r="S18">
-        <v>4.7109046394717524E-4</v>
+        <v>2.9054198014762712E-2</v>
       </c>
       <c r="T18">
-        <v>-7.7782780792084858E-5</v>
+        <v>-1.3551738159395081E-3</v>
       </c>
       <c r="U18">
-        <v>-9.158772839177199E-5</v>
+        <v>-1.8630420779778591E-4</v>
       </c>
       <c r="V18">
-        <v>-4.228463788945396E-4</v>
+        <v>-2.904110621973164E-2</v>
       </c>
       <c r="W18">
-        <v>-3.8721322988050121E-5</v>
+        <v>1.9977937923217913E-4</v>
       </c>
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B19">
-        <v>-1.8413823806612776E-2</v>
+        <v>-3.2030001731774463E-2</v>
       </c>
       <c r="C19">
-        <v>-1.1465682683918667E-6</v>
+        <v>-7.5948170724471779E-7</v>
       </c>
       <c r="D19">
-        <v>-1.2011560041361067E-5</v>
+        <v>-3.9780246746363259E-5</v>
       </c>
       <c r="E19">
-        <v>1.3434161569865041E-7</v>
+        <v>3.9794192450660095E-7</v>
       </c>
       <c r="F19">
-        <v>7.1616666509452442E-6</v>
+        <v>-8.8653091652942132E-5</v>
       </c>
       <c r="G19">
-        <v>4.6121558840662034E-5</v>
+        <v>-5.9915900245017501E-5</v>
       </c>
       <c r="H19">
-        <v>5.6901951212809838E-8</v>
+        <v>2.3738642955860579E-6</v>
       </c>
       <c r="I19">
-        <v>-5.4830564957133893E-7</v>
+        <v>2.7901328274622864E-6</v>
       </c>
       <c r="J19">
-        <v>-2.1790482295466835E-5</v>
+        <v>2.9314539417184183E-5</v>
       </c>
       <c r="K19">
-        <v>-4.171583904291808E-5</v>
+        <v>2.8579166551748782E-6</v>
       </c>
       <c r="L19">
-        <v>-4.7714175864834933E-5</v>
+        <v>-2.8332843778281255E-6</v>
       </c>
       <c r="M19">
-        <v>-4.8252409326986841E-5</v>
+        <v>-2.0125873921162316E-6</v>
       </c>
       <c r="N19">
-        <v>-2.866647960646127E-6</v>
+        <v>5.3783725873561484E-5</v>
       </c>
       <c r="O19">
-        <v>-8.0363386787651864E-7</v>
+        <v>2.8203438483300844E-5</v>
       </c>
       <c r="P19">
-        <v>3.6967798489379838E-7</v>
+        <v>1.222620573190338E-6</v>
       </c>
       <c r="Q19">
-        <v>1.7605756789283017E-6</v>
+        <v>1.1471251804363177E-5</v>
       </c>
       <c r="R19">
-        <v>1.5395918378208393E-6</v>
+        <v>-5.2613657812706994E-6</v>
       </c>
       <c r="S19">
-        <v>-7.7782780792084858E-5</v>
+        <v>-1.3551738159395081E-3</v>
       </c>
       <c r="T19">
-        <v>6.9186083500088853E-5</v>
+        <v>1.5146730138316944E-4</v>
       </c>
       <c r="U19">
-        <v>2.1363187666334755E-5</v>
+        <v>7.6094633783630541E-6</v>
       </c>
       <c r="V19">
-        <v>3.9922483096676903E-4</v>
+        <v>2.3752172976495849E-3</v>
       </c>
       <c r="W19">
-        <v>-1.6684617514025609E-4</v>
+        <v>-5.9669651050922221E-4</v>
       </c>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B20">
-        <v>-4.4481752906808817E-3</v>
+        <v>1.0533777099858411E-2</v>
       </c>
       <c r="C20">
-        <v>-1.0630336282290113E-6</v>
+        <v>8.6317135121308638E-7</v>
       </c>
       <c r="D20">
-        <v>3.6721627883471212E-6</v>
+        <v>1.8019385684666995E-5</v>
       </c>
       <c r="E20">
-        <v>-4.0311005139486502E-8</v>
+        <v>-1.8334525627835875E-7</v>
       </c>
       <c r="F20">
-        <v>-1.5890262900624007E-6</v>
+        <v>4.3662075074686928E-5</v>
       </c>
       <c r="G20">
-        <v>-1.2937138249507326E-5</v>
+        <v>3.7105349461015292E-5</v>
       </c>
       <c r="H20">
-        <v>-5.1889532429139078E-8</v>
+        <v>-1.0597640867246595E-6</v>
       </c>
       <c r="I20">
-        <v>1.1503473760666792E-7</v>
+        <v>-1.3050336012559556E-6</v>
       </c>
       <c r="J20">
-        <v>6.0913651543852054E-6</v>
+        <v>-5.3787837133823911E-6</v>
       </c>
       <c r="K20">
-        <v>1.2141635783602395E-5</v>
+        <v>6.3538034709517348E-6</v>
       </c>
       <c r="L20">
-        <v>1.3304948543835776E-5</v>
+        <v>1.0493262944508814E-5</v>
       </c>
       <c r="M20">
-        <v>1.4034662792986058E-5</v>
+        <v>6.182308034329773E-6</v>
       </c>
       <c r="N20">
-        <v>3.5418332925924737E-7</v>
+        <v>-2.3192887817426128E-5</v>
       </c>
       <c r="O20">
-        <v>-9.7824359039269792E-8</v>
+        <v>-1.4177483850043127E-5</v>
       </c>
       <c r="P20">
-        <v>-1.6459620265211745E-7</v>
+        <v>-2.2647862753571203E-6</v>
       </c>
       <c r="Q20">
-        <v>-7.0442337689148468E-7</v>
+        <v>-6.7615312172203561E-6</v>
       </c>
       <c r="R20">
-        <v>-1.9328955441376705E-7</v>
+        <v>-2.626628956494159E-6</v>
       </c>
       <c r="S20">
-        <v>-9.158772839177199E-5</v>
+        <v>-1.8630420779778591E-4</v>
       </c>
       <c r="T20">
-        <v>2.1363187666334755E-5</v>
+        <v>7.6094633783630541E-6</v>
       </c>
       <c r="U20">
-        <v>8.4967800266105216E-5</v>
+        <v>1.1630635122169052E-4</v>
       </c>
       <c r="V20">
-        <v>-8.0667985886098933E-6</v>
+        <v>-2.9439591014323641E-4</v>
       </c>
       <c r="W20">
-        <v>5.392090702991862E-5</v>
+        <v>2.5389509136379936E-4</v>
       </c>
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B21">
-        <v>-2.8699191890553016E-2</v>
+        <v>0.11509229884264148</v>
       </c>
       <c r="C21">
-        <v>9.3022942377407939E-6</v>
+        <v>-7.4086508817265836E-5</v>
       </c>
       <c r="D21">
-        <v>-7.3442857595154803E-4</v>
+        <v>-2.2652255543339898E-3</v>
       </c>
       <c r="E21">
-        <v>8.1480030688777704E-6</v>
+        <v>2.2736778076506119E-5</v>
       </c>
       <c r="F21">
-        <v>8.5618214057655776E-5</v>
+        <v>-5.6321439965972223E-3</v>
       </c>
       <c r="G21">
-        <v>2.0823410431065666E-3</v>
+        <v>-4.0411483732586111E-3</v>
       </c>
       <c r="H21">
-        <v>1.0301303485391382E-5</v>
+        <v>1.4248623538029207E-4</v>
       </c>
       <c r="I21">
-        <v>-2.0710492214583206E-5</v>
+        <v>1.6100255253928916E-4</v>
       </c>
       <c r="J21">
-        <v>-4.1017031403905498E-3</v>
+        <v>-1.1754736240627934E-3</v>
       </c>
       <c r="K21">
-        <v>-5.2212564622056909E-3</v>
+        <v>-2.750179872518705E-3</v>
       </c>
       <c r="L21">
-        <v>-5.5452823308483334E-3</v>
+        <v>-3.4062851109594606E-3</v>
       </c>
       <c r="M21">
-        <v>-5.6559134183112088E-3</v>
+        <v>-3.4190645496195793E-3</v>
       </c>
       <c r="N21">
-        <v>-1.6457776308506091E-4</v>
+        <v>2.8248111853020497E-3</v>
       </c>
       <c r="O21">
-        <v>-6.6289282635189167E-5</v>
+        <v>1.51914610809646E-3</v>
       </c>
       <c r="P21">
-        <v>-9.6978097838441269E-6</v>
+        <v>6.5999442224629626E-5</v>
       </c>
       <c r="Q21">
-        <v>6.9511915320588088E-5</v>
+        <v>6.4989906821625904E-4</v>
       </c>
       <c r="R21">
-        <v>5.3976139089689344E-5</v>
+        <v>-8.6812781026367354E-5</v>
       </c>
       <c r="S21">
-        <v>-4.228463788945396E-4</v>
+        <v>-2.904110621973164E-2</v>
       </c>
       <c r="T21">
-        <v>3.9922483096676903E-4</v>
+        <v>2.3752172976495849E-3</v>
       </c>
       <c r="U21">
-        <v>-8.0667985886098933E-6</v>
+        <v>-2.9439591014323641E-4</v>
       </c>
       <c r="V21">
-        <v>2.2837815923078337E-2</v>
+        <v>9.0830545642533622E-2</v>
       </c>
       <c r="W21">
-        <v>-9.2094558434223633E-3</v>
+        <v>-3.1806348184477369E-2</v>
       </c>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B22">
-        <v>-8.641368807047331E-2</v>
+        <v>3.265821705265709E-2</v>
       </c>
       <c r="C22">
-        <v>-3.9804410411673696E-6</v>
+        <v>3.2240865191396875E-5</v>
       </c>
       <c r="D22">
-        <v>3.4473550948212645E-4</v>
+        <v>1.1875109946579677E-3</v>
       </c>
       <c r="E22">
-        <v>-3.8377086730127302E-6</v>
+        <v>-1.1937540316577405E-5</v>
       </c>
       <c r="F22">
-        <v>-1.8916149681202706E-4</v>
+        <v>2.7802959490674716E-3</v>
       </c>
       <c r="G22">
-        <v>-1.2330880286022979E-3</v>
+        <v>2.0359568289005175E-3</v>
       </c>
       <c r="H22">
-        <v>-2.4601043376857489E-6</v>
+        <v>-7.1339167302083472E-5</v>
       </c>
       <c r="I22">
-        <v>1.3237742946188823E-5</v>
+        <v>-8.3881507304688877E-5</v>
       </c>
       <c r="J22">
-        <v>5.6759748676092755E-4</v>
+        <v>-3.6194870595737623E-4</v>
       </c>
       <c r="K22">
-        <v>1.1562173899322644E-3</v>
+        <v>4.9904101544946764E-4</v>
       </c>
       <c r="L22">
-        <v>1.3270136214409999E-3</v>
+        <v>8.4688284908119779E-4</v>
       </c>
       <c r="M22">
-        <v>1.3620000551586274E-3</v>
+        <v>8.2353806270582476E-4</v>
       </c>
       <c r="N22">
-        <v>7.4806736932902737E-5</v>
+        <v>-1.5784969544392696E-3</v>
       </c>
       <c r="O22">
-        <v>1.6886916987252356E-5</v>
+        <v>-8.4625518848837256E-4</v>
       </c>
       <c r="P22">
-        <v>-6.844438910271103E-6</v>
+        <v>-4.0579380572970645E-5</v>
       </c>
       <c r="Q22">
-        <v>-5.0797504197031804E-5</v>
+        <v>-3.7794635132694523E-4</v>
       </c>
       <c r="R22">
-        <v>-4.8236549934383171E-5</v>
+        <v>2.6232957421267347E-5</v>
       </c>
       <c r="S22">
-        <v>-3.8721322988050121E-5</v>
+        <v>1.9977937923217913E-4</v>
       </c>
       <c r="T22">
-        <v>-1.6684617514025609E-4</v>
+        <v>-5.9669651050922221E-4</v>
       </c>
       <c r="U22">
-        <v>5.392090702991862E-5</v>
+        <v>2.5389509136379936E-4</v>
       </c>
       <c r="V22">
-        <v>-9.2094558434223633E-3</v>
+        <v>-3.1806348184477369E-2</v>
       </c>
       <c r="W22">
-        <v>4.8369230058739774E-3</v>
+        <v>1.7410829615613594E-2</v>
       </c>
     </row>
   </sheetData>
@@ -5096,52 +5074,53 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73F2BEA0-597B-4485-ACA5-1CD080E9A9A0}">
   <dimension ref="A1:W22"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="35.59765625" customWidth="1"/>
+    <col min="1" max="1" width="20.1328125" style="3" customWidth="1"/>
+    <col min="2" max="16384" width="8.796875" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>18</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>19</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>20</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>21</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>22</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>23</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>24</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>25</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>26</v>
-      </c>
-      <c r="M1" t="s">
-        <v>27</v>
       </c>
       <c r="N1" t="s">
         <v>35</v>
@@ -5153,806 +5132,806 @@
         <v>37</v>
       </c>
       <c r="Q1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="R1" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" t="s">
         <v>28</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>29</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>30</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>31</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>32</v>
-      </c>
-      <c r="W1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2">
-        <v>0.66513137342541562</v>
+        <v>0.71835254988724717</v>
       </c>
       <c r="C2">
-        <v>2.9781511664421791E-5</v>
+        <v>1.6303351396028679E-5</v>
       </c>
       <c r="D2">
-        <v>6.8256281522153695E-7</v>
+        <v>1.7547339333539598E-7</v>
       </c>
       <c r="E2">
-        <v>-9.4512066764574648E-9</v>
+        <v>-4.4945874167293671E-9</v>
       </c>
       <c r="F2">
-        <v>4.1719635973396052E-6</v>
+        <v>1.4090401949160334E-6</v>
       </c>
       <c r="G2">
-        <v>3.3065079964484152E-6</v>
+        <v>1.5004864624340579E-6</v>
       </c>
       <c r="H2">
-        <v>1.8644903319177992E-7</v>
+        <v>7.2056975055918557E-8</v>
       </c>
       <c r="I2">
-        <v>3.0626406483810354E-7</v>
+        <v>1.2285768535794783E-7</v>
       </c>
       <c r="J2">
-        <v>6.3553108297252137E-6</v>
+        <v>4.9465286511252464E-7</v>
       </c>
       <c r="K2">
-        <v>1.4773082306740613E-5</v>
+        <v>2.8687659084389223E-6</v>
       </c>
       <c r="L2">
-        <v>1.4693147504545025E-5</v>
+        <v>2.6335966356199407E-6</v>
       </c>
       <c r="M2">
-        <v>1.3919221228742484E-5</v>
+        <v>2.7992277031282489E-6</v>
       </c>
       <c r="N2">
-        <v>1.9584464511641179E-6</v>
+        <v>2.9718236342099566E-6</v>
       </c>
       <c r="O2">
-        <v>-2.5765482103170512E-6</v>
+        <v>2.8473061505325477E-6</v>
       </c>
       <c r="P2">
-        <v>4.2304774982416232E-7</v>
+        <v>1.15861999703872E-7</v>
       </c>
       <c r="Q2">
-        <v>2.8525685469102263E-6</v>
+        <v>1.324184518156341E-6</v>
       </c>
       <c r="R2">
-        <v>2.6251198159765253E-6</v>
+        <v>1.8573554142188454E-6</v>
       </c>
       <c r="S2">
-        <v>-1.6269071106821978E-5</v>
+        <v>-1.8239916828318502E-6</v>
       </c>
       <c r="T2">
-        <v>-2.0373534725566378E-6</v>
+        <v>2.8199712562863171E-7</v>
       </c>
       <c r="U2">
-        <v>1.1097631830486151E-6</v>
+        <v>1.0127149257330256E-6</v>
       </c>
       <c r="V2">
-        <v>-6.8222665579085348E-5</v>
+        <v>-5.0012701591296718E-5</v>
       </c>
       <c r="W2">
-        <v>5.6486469901159332E-5</v>
+        <v>2.1378860634480102E-5</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B3">
-        <v>-1.7188620575499507E-2</v>
+        <v>-2.0515540037959162E-2</v>
       </c>
       <c r="C3">
-        <v>6.8256281522153695E-7</v>
+        <v>1.7547339333539598E-7</v>
       </c>
       <c r="D3">
-        <v>2.7649286348083136E-5</v>
+        <v>2.2441357944678571E-5</v>
       </c>
       <c r="E3">
-        <v>-2.9488127730571164E-7</v>
+        <v>-2.2900972211353223E-7</v>
       </c>
       <c r="F3">
-        <v>4.6934138400046775E-5</v>
+        <v>7.3246045950192825E-5</v>
       </c>
       <c r="G3">
-        <v>2.599296934784017E-5</v>
+        <v>6.7655169636937244E-5</v>
       </c>
       <c r="H3">
-        <v>-1.1165485194864804E-6</v>
+        <v>-1.5395413879801532E-6</v>
       </c>
       <c r="I3">
-        <v>-1.2530462522651799E-6</v>
+        <v>-1.6938742646853549E-6</v>
       </c>
       <c r="J3">
-        <v>8.9583551745998972E-5</v>
+        <v>2.9813033533101482E-6</v>
       </c>
       <c r="K3">
-        <v>1.8540578587004667E-4</v>
+        <v>3.1464499328568696E-5</v>
       </c>
       <c r="L3">
-        <v>2.0286437590948995E-4</v>
+        <v>3.9246793016656807E-5</v>
       </c>
       <c r="M3">
-        <v>2.0886791259893403E-4</v>
+        <v>4.2234062237637261E-5</v>
       </c>
       <c r="N3">
-        <v>7.1353645036278818E-6</v>
+        <v>-1.2437899613630297E-5</v>
       </c>
       <c r="O3">
-        <v>-3.0203027600992794E-6</v>
+        <v>-1.5764014027498564E-5</v>
       </c>
       <c r="P3">
-        <v>-4.2716785834327737E-6</v>
+        <v>4.2467888931914201E-6</v>
       </c>
       <c r="Q3">
-        <v>1.0714533484162646E-6</v>
+        <v>-2.1119288033155075E-6</v>
       </c>
       <c r="R3">
-        <v>-9.1167430224432692E-7</v>
+        <v>-1.2944719989901626E-6</v>
       </c>
       <c r="S3">
-        <v>-4.6957929476915422E-6</v>
+        <v>1.9190157050088914E-5</v>
       </c>
       <c r="T3">
-        <v>-2.3443821466183038E-6</v>
+        <v>1.2052841715803317E-7</v>
       </c>
       <c r="U3">
-        <v>2.0614582664868834E-5</v>
+        <v>2.3051571026915804E-6</v>
       </c>
       <c r="V3">
-        <v>-8.8216434290872394E-4</v>
+        <v>-6.2685745198527731E-4</v>
       </c>
       <c r="W3">
-        <v>5.3838961033084252E-4</v>
+        <v>2.9465105283169789E-4</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B4">
-        <v>1.9115586891031879E-4</v>
+        <v>2.2551036474475957E-4</v>
       </c>
       <c r="C4">
-        <v>-9.4512066764574648E-9</v>
+        <v>-4.4945874167293671E-9</v>
       </c>
       <c r="D4">
-        <v>-2.9488127730571164E-7</v>
+        <v>-2.2900972211353223E-7</v>
       </c>
       <c r="E4">
-        <v>3.2223481795290922E-9</v>
+        <v>2.3832923850630445E-9</v>
       </c>
       <c r="F4">
-        <v>-2.3600606195081159E-7</v>
+        <v>-5.6972855985963401E-7</v>
       </c>
       <c r="G4">
-        <v>-1.6730320791878851E-8</v>
+        <v>-5.0479782193885858E-7</v>
       </c>
       <c r="H4">
-        <v>5.467048335159627E-9</v>
+        <v>1.1761313779342742E-8</v>
       </c>
       <c r="I4">
-        <v>6.9949201850977831E-9</v>
+        <v>1.3176124712494457E-8</v>
       </c>
       <c r="J4">
-        <v>-9.5979542984271217E-7</v>
+        <v>-3.3462492476694522E-8</v>
       </c>
       <c r="K4">
-        <v>-1.9820018708235795E-6</v>
+        <v>-3.2250573770744651E-7</v>
       </c>
       <c r="L4">
-        <v>-2.1594179743056322E-6</v>
+        <v>-3.9887005209638081E-7</v>
       </c>
       <c r="M4">
-        <v>-2.2137578788436691E-6</v>
+        <v>-4.2635381214481957E-7</v>
       </c>
       <c r="N4">
-        <v>-7.7933408688775533E-8</v>
+        <v>1.2524339671124664E-7</v>
       </c>
       <c r="O4">
-        <v>2.9478668387934686E-8</v>
+        <v>1.5820641188975016E-7</v>
       </c>
       <c r="P4">
-        <v>4.3556206259883316E-8</v>
+        <v>-4.3608499776935663E-8</v>
       </c>
       <c r="Q4">
-        <v>-1.1891419062024247E-8</v>
+        <v>2.0638354094057532E-8</v>
       </c>
       <c r="R4">
-        <v>-1.0536473093768127E-9</v>
+        <v>1.238923164125611E-8</v>
       </c>
       <c r="S4">
-        <v>4.1682756049469515E-8</v>
+        <v>-1.7693622905436588E-7</v>
       </c>
       <c r="T4">
-        <v>2.5486870801268651E-8</v>
+        <v>-2.1626391960687828E-9</v>
       </c>
       <c r="U4">
-        <v>-2.2082415698646037E-7</v>
+        <v>-2.5269969845861938E-8</v>
       </c>
       <c r="V4">
-        <v>9.2798651119866901E-6</v>
+        <v>6.2862118604283118E-6</v>
       </c>
       <c r="W4">
-        <v>-5.7638091288243958E-6</v>
+        <v>-3.0122832065336327E-6</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B5">
-        <v>-4.8796990773666227E-2</v>
+        <v>-0.14039038314715069</v>
       </c>
       <c r="C5">
-        <v>4.1719635973396052E-6</v>
+        <v>1.4090401949160334E-6</v>
       </c>
       <c r="D5">
-        <v>4.6934138400046775E-5</v>
+        <v>7.3246045950192825E-5</v>
       </c>
       <c r="E5">
-        <v>-2.3600606195081159E-7</v>
+        <v>-5.6972855985963401E-7</v>
       </c>
       <c r="F5">
-        <v>1.4510849589925219E-3</v>
+        <v>1.2674475002104127E-3</v>
       </c>
       <c r="G5">
-        <v>1.115818666552536E-3</v>
+        <v>9.9626996479717372E-4</v>
       </c>
       <c r="H5">
-        <v>-3.255081439744038E-5</v>
+        <v>-2.6696692483678875E-5</v>
       </c>
       <c r="I5">
-        <v>-2.5848127212191492E-5</v>
+        <v>-2.1636183270292765E-5</v>
       </c>
       <c r="J5">
-        <v>5.4226072143142689E-5</v>
+        <v>-1.3105769678143396E-5</v>
       </c>
       <c r="K5">
-        <v>1.2928191597663934E-4</v>
+        <v>6.8000449396316858E-5</v>
       </c>
       <c r="L5">
-        <v>1.3224222617762668E-4</v>
+        <v>8.7380955628812079E-5</v>
       </c>
       <c r="M5">
-        <v>1.4822706997866443E-4</v>
+        <v>9.4866471937474705E-5</v>
       </c>
       <c r="N5">
-        <v>8.0012880450271602E-7</v>
+        <v>-3.7107296506780204E-5</v>
       </c>
       <c r="O5">
-        <v>-6.111359095921477E-6</v>
+        <v>-4.6972799054695908E-5</v>
       </c>
       <c r="P5">
-        <v>-9.2296842888718964E-6</v>
+        <v>8.9277054095561946E-6</v>
       </c>
       <c r="Q5">
-        <v>3.1217641143433062E-6</v>
+        <v>-8.0531133634012627E-6</v>
       </c>
       <c r="R5">
-        <v>-7.4535373665715263E-6</v>
+        <v>-6.5516493156464271E-6</v>
       </c>
       <c r="S5">
-        <v>1.0628255073795765E-5</v>
+        <v>2.3382755582126885E-7</v>
       </c>
       <c r="T5">
-        <v>-2.2739142806513155E-6</v>
+        <v>5.7316363664208842E-6</v>
       </c>
       <c r="U5">
-        <v>1.6135998153020653E-5</v>
+        <v>9.5561292791707846E-6</v>
       </c>
       <c r="V5">
-        <v>-1.793565155674562E-3</v>
+        <v>-2.3377388348329526E-3</v>
       </c>
       <c r="W5">
-        <v>4.3798414943035122E-4</v>
+        <v>7.7653937438297777E-4</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B6">
-        <v>3.0777413594922282E-2</v>
+        <v>-0.12567972791506374</v>
       </c>
       <c r="C6">
-        <v>3.3065079964484152E-6</v>
+        <v>1.5004864624340579E-6</v>
       </c>
       <c r="D6">
-        <v>2.599296934784017E-5</v>
+        <v>6.7655169636937244E-5</v>
       </c>
       <c r="E6">
-        <v>-1.6730320791878851E-8</v>
+        <v>-5.0479782193885858E-7</v>
       </c>
       <c r="F6">
-        <v>1.115818666552536E-3</v>
+        <v>9.9626996479717372E-4</v>
       </c>
       <c r="G6">
-        <v>3.6131293902987214E-3</v>
+        <v>1.5797697825240336E-3</v>
       </c>
       <c r="H6">
-        <v>-2.5231872610735981E-5</v>
+        <v>-2.0947994067738106E-5</v>
       </c>
       <c r="I6">
-        <v>-7.7280398953966345E-5</v>
+        <v>-3.3479396769055127E-5</v>
       </c>
       <c r="J6">
-        <v>-7.5622432076323005E-5</v>
+        <v>-6.6736555344113776E-6</v>
       </c>
       <c r="K6">
-        <v>-1.4507295416177124E-4</v>
+        <v>7.7547953123757566E-5</v>
       </c>
       <c r="L6">
-        <v>-1.7064285092967458E-4</v>
+        <v>9.728112798719897E-5</v>
       </c>
       <c r="M6">
-        <v>-1.523926671876794E-4</v>
+        <v>1.0932698119692947E-4</v>
       </c>
       <c r="N6">
-        <v>-1.8628060050685004E-5</v>
+        <v>-4.0503602467025285E-5</v>
       </c>
       <c r="O6">
-        <v>-4.7358756026565378E-6</v>
+        <v>-5.2123255469744171E-5</v>
       </c>
       <c r="P6">
-        <v>-1.2352416588411184E-5</v>
+        <v>1.2946824081673961E-5</v>
       </c>
       <c r="Q6">
-        <v>8.0951486031747971E-6</v>
+        <v>-7.9645095598033423E-6</v>
       </c>
       <c r="R6">
-        <v>-1.6914154235454237E-5</v>
+        <v>-9.1421173142486355E-6</v>
       </c>
       <c r="S6">
-        <v>-9.6277973158491497E-6</v>
+        <v>3.4509049998175171E-6</v>
       </c>
       <c r="T6">
-        <v>3.8525949966782458E-6</v>
+        <v>7.0481532951945561E-6</v>
       </c>
       <c r="U6">
-        <v>-8.3460188608950432E-6</v>
+        <v>1.0746960888671472E-5</v>
       </c>
       <c r="V6">
-        <v>-8.9708497792628436E-4</v>
+        <v>-2.2464638235496596E-3</v>
       </c>
       <c r="W6">
-        <v>-3.1729074343592899E-4</v>
+        <v>8.2786208586273777E-4</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B7">
-        <v>-1.6821429362250397E-3</v>
+        <v>1.1175813526407461E-3</v>
       </c>
       <c r="C7">
-        <v>1.8644903319177992E-7</v>
+        <v>7.2056975055918557E-8</v>
       </c>
       <c r="D7">
-        <v>-1.1165485194864804E-6</v>
+        <v>-1.5395413879801532E-6</v>
       </c>
       <c r="E7">
-        <v>5.467048335159627E-9</v>
+        <v>1.1761313779342742E-8</v>
       </c>
       <c r="F7">
-        <v>-3.255081439744038E-5</v>
+        <v>-2.6696692483678875E-5</v>
       </c>
       <c r="G7">
-        <v>-2.5231872610735981E-5</v>
+        <v>-2.0947994067738106E-5</v>
       </c>
       <c r="H7">
-        <v>7.8087850555728825E-7</v>
+        <v>5.8771165788142284E-7</v>
       </c>
       <c r="I7">
-        <v>6.2832689650211725E-7</v>
+        <v>4.7368926516382002E-7</v>
       </c>
       <c r="J7">
-        <v>-1.5344180365191802E-6</v>
+        <v>3.5756064061246721E-7</v>
       </c>
       <c r="K7">
-        <v>-3.493082587817043E-6</v>
+        <v>-1.3182754850795199E-6</v>
       </c>
       <c r="L7">
-        <v>-3.5201201612067897E-6</v>
+        <v>-1.6955197855407486E-6</v>
       </c>
       <c r="M7">
-        <v>-3.7585666969942962E-6</v>
+        <v>-1.8326968270670328E-6</v>
       </c>
       <c r="N7">
-        <v>-1.8041687434528069E-7</v>
+        <v>7.9997492373173848E-7</v>
       </c>
       <c r="O7">
-        <v>1.1791368830457743E-7</v>
+        <v>1.0112088385392049E-6</v>
       </c>
       <c r="P7">
-        <v>1.3464951566794879E-7</v>
+        <v>-1.9533043758396552E-7</v>
       </c>
       <c r="Q7">
-        <v>-8.3515324418544894E-8</v>
+        <v>1.8793086379134331E-7</v>
       </c>
       <c r="R7">
-        <v>4.6098465433206522E-7</v>
+        <v>1.8993985454557722E-7</v>
       </c>
       <c r="S7">
-        <v>-9.0432052359300635E-9</v>
+        <v>-4.5496877356901355E-7</v>
       </c>
       <c r="T7">
-        <v>2.4271349238855517E-8</v>
+        <v>-6.7847864033554756E-8</v>
       </c>
       <c r="U7">
-        <v>-4.2558055364176782E-7</v>
+        <v>-1.6356565566752908E-7</v>
       </c>
       <c r="V7">
-        <v>4.1114133081886934E-5</v>
+        <v>4.8744899103976281E-5</v>
       </c>
       <c r="W7">
-        <v>-1.1232261729371656E-5</v>
+        <v>-1.603347548514183E-5</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B8">
-        <v>-4.2482803486530822E-3</v>
+        <v>-1.0944786890884469E-4</v>
       </c>
       <c r="C8">
-        <v>3.0626406483810354E-7</v>
+        <v>1.2285768535794783E-7</v>
       </c>
       <c r="D8">
-        <v>-1.2530462522651799E-6</v>
+        <v>-1.6938742646853549E-6</v>
       </c>
       <c r="E8">
-        <v>6.9949201850977831E-9</v>
+        <v>1.3176124712494457E-8</v>
       </c>
       <c r="F8">
-        <v>-2.5848127212191492E-5</v>
+        <v>-2.1636183270292765E-5</v>
       </c>
       <c r="G8">
-        <v>-7.7280398953966345E-5</v>
+        <v>-3.3479396769055127E-5</v>
       </c>
       <c r="H8">
-        <v>6.2832689650211725E-7</v>
+        <v>4.7368926516382002E-7</v>
       </c>
       <c r="I8">
-        <v>1.8227059179464656E-6</v>
+        <v>7.4269359601156429E-7</v>
       </c>
       <c r="J8">
-        <v>-1.6187665907439844E-6</v>
+        <v>1.3589538522893591E-7</v>
       </c>
       <c r="K8">
-        <v>-3.4722521847018917E-6</v>
+        <v>-2.0039981976639221E-6</v>
       </c>
       <c r="L8">
-        <v>-3.4384468965446624E-6</v>
+        <v>-2.4634162913635244E-6</v>
       </c>
       <c r="M8">
-        <v>-3.7545269768199586E-6</v>
+        <v>-2.7084393352035457E-6</v>
       </c>
       <c r="N8">
-        <v>-4.8149041607695311E-8</v>
+        <v>1.0221062166961624E-6</v>
       </c>
       <c r="O8">
-        <v>1.4638845071684591E-7</v>
+        <v>1.298110209157914E-6</v>
       </c>
       <c r="P8">
-        <v>1.9962198674895822E-7</v>
+        <v>-3.2669584848022407E-7</v>
       </c>
       <c r="Q8">
-        <v>-3.3815270174726978E-7</v>
+        <v>2.2016969511219327E-7</v>
       </c>
       <c r="R8">
-        <v>5.6619139983105389E-7</v>
+        <v>2.7087888057171046E-7</v>
       </c>
       <c r="S8">
-        <v>7.4772800746042425E-7</v>
+        <v>-1.1964061610944252E-6</v>
       </c>
       <c r="T8">
-        <v>-3.2848113589278396E-8</v>
+        <v>-5.4238952475956513E-8</v>
       </c>
       <c r="U8">
-        <v>-5.5841964993455373E-7</v>
+        <v>-1.976633410679357E-7</v>
       </c>
       <c r="V8">
-        <v>4.3090618403197366E-5</v>
+        <v>5.4894777969478775E-5</v>
       </c>
       <c r="W8">
-        <v>-1.1994285555958712E-5</v>
+        <v>-2.1509721161781432E-5</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B9">
-        <v>-0.2279827149235332</v>
+        <v>3.2255952797199158E-2</v>
       </c>
       <c r="C9">
-        <v>6.3553108297252137E-6</v>
+        <v>4.9465286511252464E-7</v>
       </c>
       <c r="D9">
-        <v>8.9583551745998972E-5</v>
+        <v>2.9813033533101482E-6</v>
       </c>
       <c r="E9">
-        <v>-9.5979542984271217E-7</v>
+        <v>-3.3462492476694522E-8</v>
       </c>
       <c r="F9">
-        <v>5.4226072143142689E-5</v>
+        <v>-1.3105769678143396E-5</v>
       </c>
       <c r="G9">
-        <v>-7.5622432076323005E-5</v>
+        <v>-6.6736555344113776E-6</v>
       </c>
       <c r="H9">
-        <v>-1.5344180365191802E-6</v>
+        <v>3.5756064061246721E-7</v>
       </c>
       <c r="I9">
-        <v>-1.6187665907439844E-6</v>
+        <v>1.3589538522893591E-7</v>
       </c>
       <c r="J9">
-        <v>6.5035113745984642E-3</v>
+        <v>2.8642247129168075E-3</v>
       </c>
       <c r="K9">
-        <v>6.4557016470475678E-3</v>
+        <v>2.5392754093704218E-3</v>
       </c>
       <c r="L9">
-        <v>6.5446456463101616E-3</v>
+        <v>2.5426559848724826E-3</v>
       </c>
       <c r="M9">
-        <v>6.5552036715116977E-3</v>
+        <v>2.5435396742546821E-3</v>
       </c>
       <c r="N9">
-        <v>3.5340110747310984E-5</v>
+        <v>-3.7250265582858625E-6</v>
       </c>
       <c r="O9">
-        <v>-1.0096055926097615E-5</v>
+        <v>7.0032496232342435E-8</v>
       </c>
       <c r="P9">
-        <v>-1.7793715146064902E-5</v>
+        <v>-1.9914024795460371E-7</v>
       </c>
       <c r="Q9">
-        <v>3.1354973377504787E-6</v>
+        <v>-1.7697519355566548E-6</v>
       </c>
       <c r="R9">
-        <v>-3.6810906402640474E-7</v>
+        <v>4.0388644227300385E-6</v>
       </c>
       <c r="S9">
-        <v>-2.3155898290259449E-5</v>
+        <v>7.8306577448568995E-6</v>
       </c>
       <c r="T9">
-        <v>-1.5244041990520065E-5</v>
+        <v>9.2735509986471001E-6</v>
       </c>
       <c r="U9">
-        <v>9.7911128076162663E-5</v>
+        <v>-2.6720890300179575E-6</v>
       </c>
       <c r="V9">
-        <v>-8.8270040702563245E-3</v>
+        <v>-2.6267445222933842E-3</v>
       </c>
       <c r="W9">
-        <v>2.4497581054538408E-3</v>
+        <v>6.7844952853593699E-5</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B10">
-        <v>-0.31754265331877812</v>
+        <v>-3.356420120250022E-2</v>
       </c>
       <c r="C10">
-        <v>1.4773082306740613E-5</v>
+        <v>2.8687659084389223E-6</v>
       </c>
       <c r="D10">
-        <v>1.8540578587004667E-4</v>
+        <v>3.1464499328568696E-5</v>
       </c>
       <c r="E10">
-        <v>-1.9820018708235795E-6</v>
+        <v>-3.2250573770744651E-7</v>
       </c>
       <c r="F10">
-        <v>1.2928191597663934E-4</v>
+        <v>6.8000449396316858E-5</v>
       </c>
       <c r="G10">
-        <v>-1.4507295416177124E-4</v>
+        <v>7.7547953123757566E-5</v>
       </c>
       <c r="H10">
-        <v>-3.493082587817043E-6</v>
+        <v>-1.3182754850795199E-6</v>
       </c>
       <c r="I10">
-        <v>-3.4722521847018917E-6</v>
+        <v>-2.0039981976639221E-6</v>
       </c>
       <c r="J10">
-        <v>6.4557016470475678E-3</v>
+        <v>2.5392754093704218E-3</v>
       </c>
       <c r="K10">
-        <v>7.4499782848301555E-3</v>
+        <v>2.6484806083585956E-3</v>
       </c>
       <c r="L10">
-        <v>7.55980572652846E-3</v>
+        <v>2.6134892070101522E-3</v>
       </c>
       <c r="M10">
-        <v>7.582710385656154E-3</v>
+        <v>2.6185485390188925E-3</v>
       </c>
       <c r="N10">
-        <v>6.7894804121600643E-5</v>
+        <v>-2.3223182967144752E-5</v>
       </c>
       <c r="O10">
-        <v>-2.8451337317572575E-5</v>
+        <v>-2.6111584476447046E-5</v>
       </c>
       <c r="P10">
-        <v>-3.9669319499853294E-5</v>
+        <v>6.9181164143731065E-6</v>
       </c>
       <c r="Q10">
-        <v>5.6845997546717381E-6</v>
+        <v>-7.0719894357277852E-6</v>
       </c>
       <c r="R10">
-        <v>-9.4565346857397998E-6</v>
+        <v>2.3848706351348173E-6</v>
       </c>
       <c r="S10">
-        <v>-6.4579276546405289E-5</v>
+        <v>1.1807934433278602E-4</v>
       </c>
       <c r="T10">
-        <v>-2.2990270178747252E-5</v>
+        <v>8.1734425687767358E-6</v>
       </c>
       <c r="U10">
-        <v>1.9990472869835379E-4</v>
+        <v>-6.2444390719011679E-7</v>
       </c>
       <c r="V10">
-        <v>-1.227730709421425E-2</v>
+        <v>-3.5554864354012351E-3</v>
       </c>
       <c r="W10">
-        <v>5.0706164084508383E-3</v>
+        <v>5.5799824350713392E-4</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B11">
-        <v>-0.3286590085893718</v>
+        <v>-2.4551514403650481E-2</v>
       </c>
       <c r="C11">
-        <v>1.4693147504545025E-5</v>
+        <v>2.6335966356199407E-6</v>
       </c>
       <c r="D11">
-        <v>2.0286437590948995E-4</v>
+        <v>3.9246793016656807E-5</v>
       </c>
       <c r="E11">
-        <v>-2.1594179743056322E-6</v>
+        <v>-3.9887005209638081E-7</v>
       </c>
       <c r="F11">
-        <v>1.3224222617762668E-4</v>
+        <v>8.7380955628812079E-5</v>
       </c>
       <c r="G11">
-        <v>-1.7064285092967458E-4</v>
+        <v>9.728112798719897E-5</v>
       </c>
       <c r="H11">
-        <v>-3.5201201612067897E-6</v>
+        <v>-1.6955197855407486E-6</v>
       </c>
       <c r="I11">
-        <v>-3.4384468965446624E-6</v>
+        <v>-2.4634162913635244E-6</v>
       </c>
       <c r="J11">
-        <v>6.5446456463101616E-3</v>
+        <v>2.5426559848724826E-3</v>
       </c>
       <c r="K11">
-        <v>7.55980572652846E-3</v>
+        <v>2.6134892070101522E-3</v>
       </c>
       <c r="L11">
-        <v>7.7984303673808483E-3</v>
+        <v>2.6482413915537959E-3</v>
       </c>
       <c r="M11">
-        <v>7.8042112245766517E-3</v>
+        <v>2.6454446604495963E-3</v>
       </c>
       <c r="N11">
-        <v>7.4363440625789401E-5</v>
+        <v>-2.8960234355481772E-5</v>
       </c>
       <c r="O11">
-        <v>-3.1054280066371967E-5</v>
+        <v>-3.4185088637758902E-5</v>
       </c>
       <c r="P11">
-        <v>-4.3281801591472799E-5</v>
+        <v>7.145411072683734E-6</v>
       </c>
       <c r="Q11">
-        <v>8.4643963056943843E-6</v>
+        <v>-8.1763748841089523E-6</v>
       </c>
       <c r="R11">
-        <v>-1.0548416619711486E-5</v>
+        <v>2.256350803842415E-6</v>
       </c>
       <c r="S11">
-        <v>-8.1033022969494316E-5</v>
+        <v>1.4107667849242535E-4</v>
       </c>
       <c r="T11">
-        <v>-2.6093748558443494E-5</v>
+        <v>1.5362881205400485E-5</v>
       </c>
       <c r="U11">
-        <v>2.1694949663149989E-4</v>
+        <v>-4.4731984229143145E-7</v>
       </c>
       <c r="V11">
-        <v>-1.2948036033849961E-2</v>
+        <v>-3.8124755160822833E-3</v>
       </c>
       <c r="W11">
-        <v>5.5878758083060176E-3</v>
+        <v>6.9560184880447669E-4</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B12">
-        <v>-0.32153539739433995</v>
+        <v>-3.4192332210288862E-2</v>
       </c>
       <c r="C12">
-        <v>1.3919221228742484E-5</v>
+        <v>2.7992277031282489E-6</v>
       </c>
       <c r="D12">
-        <v>2.0886791259893403E-4</v>
+        <v>4.2234062237637261E-5</v>
       </c>
       <c r="E12">
-        <v>-2.2137578788436691E-6</v>
+        <v>-4.2635381214481957E-7</v>
       </c>
       <c r="F12">
-        <v>1.4822706997866443E-4</v>
+        <v>9.4866471937474705E-5</v>
       </c>
       <c r="G12">
-        <v>-1.523926671876794E-4</v>
+        <v>1.0932698119692947E-4</v>
       </c>
       <c r="H12">
-        <v>-3.7585666969942962E-6</v>
+        <v>-1.8326968270670328E-6</v>
       </c>
       <c r="I12">
-        <v>-3.7545269768199586E-6</v>
+        <v>-2.7084393352035457E-6</v>
       </c>
       <c r="J12">
-        <v>6.5552036715116977E-3</v>
+        <v>2.5435396742546821E-3</v>
       </c>
       <c r="K12">
-        <v>7.582710385656154E-3</v>
+        <v>2.6185485390188925E-3</v>
       </c>
       <c r="L12">
-        <v>7.8042112245766517E-3</v>
+        <v>2.6454446604495963E-3</v>
       </c>
       <c r="M12">
-        <v>7.9191640505357763E-3</v>
+        <v>2.6994461973817835E-3</v>
       </c>
       <c r="N12">
-        <v>7.5010111481105544E-5</v>
+        <v>-3.0612549629151339E-5</v>
       </c>
       <c r="O12">
-        <v>-2.9148891128002836E-5</v>
+        <v>-3.6565603226693423E-5</v>
       </c>
       <c r="P12">
-        <v>-4.3785164233834386E-5</v>
+        <v>9.7911810835837239E-6</v>
       </c>
       <c r="Q12">
-        <v>9.205086849772695E-6</v>
+        <v>-6.7291821495881638E-6</v>
       </c>
       <c r="R12">
-        <v>-1.1504615352314001E-5</v>
+        <v>2.2569700347841747E-6</v>
       </c>
       <c r="S12">
-        <v>-8.1461117168970854E-5</v>
+        <v>1.7483824373639963E-4</v>
       </c>
       <c r="T12">
-        <v>-2.6697244956639329E-5</v>
+        <v>1.5044757119755261E-5</v>
       </c>
       <c r="U12">
-        <v>2.1950842438440233E-4</v>
+        <v>-3.6228831573026625E-6</v>
       </c>
       <c r="V12">
-        <v>-1.3142842165320967E-2</v>
+        <v>-3.9380059355757476E-3</v>
       </c>
       <c r="W12">
-        <v>5.6487356498155158E-3</v>
+        <v>7.3398082930585138E-4</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.45">
@@ -5960,70 +5939,70 @@
         <v>35</v>
       </c>
       <c r="B13">
-        <v>-2.6089298240572718E-2</v>
+        <v>-5.3266211276001334E-2</v>
       </c>
       <c r="C13">
-        <v>1.9584464511641179E-6</v>
+        <v>2.9718236342099566E-6</v>
       </c>
       <c r="D13">
-        <v>7.1353645036278818E-6</v>
+        <v>-1.2437899613630297E-5</v>
       </c>
       <c r="E13">
-        <v>-7.7933408688775533E-8</v>
+        <v>1.2524339671124664E-7</v>
       </c>
       <c r="F13">
-        <v>8.0012880450271602E-7</v>
+        <v>-3.7107296506780204E-5</v>
       </c>
       <c r="G13">
-        <v>-1.8628060050685004E-5</v>
+        <v>-4.0503602467025285E-5</v>
       </c>
       <c r="H13">
-        <v>-1.8041687434528069E-7</v>
+        <v>7.9997492373173848E-7</v>
       </c>
       <c r="I13">
-        <v>-4.8149041607695311E-8</v>
+        <v>1.0221062166961624E-6</v>
       </c>
       <c r="J13">
-        <v>3.5340110747310984E-5</v>
+        <v>-3.7250265582858625E-6</v>
       </c>
       <c r="K13">
-        <v>6.7894804121600643E-5</v>
+        <v>-2.3223182967144752E-5</v>
       </c>
       <c r="L13">
-        <v>7.4363440625789401E-5</v>
+        <v>-2.8960234355481772E-5</v>
       </c>
       <c r="M13">
-        <v>7.5010111481105544E-5</v>
+        <v>-3.0612549629151339E-5</v>
       </c>
       <c r="N13">
-        <v>1.8453015839366409E-4</v>
+        <v>8.0445399332861476E-5</v>
       </c>
       <c r="O13">
-        <v>8.8518422065899031E-5</v>
+        <v>4.225335034183435E-5</v>
       </c>
       <c r="P13">
-        <v>8.8757218887009176E-5</v>
+        <v>2.6759482897629269E-5</v>
       </c>
       <c r="Q13">
-        <v>9.0291676640330998E-5</v>
+        <v>3.1553857507695399E-5</v>
       </c>
       <c r="R13">
-        <v>2.2255930078584726E-6</v>
+        <v>-1.7509455489535438E-6</v>
       </c>
       <c r="S13">
-        <v>-1.854734955115871E-5</v>
+        <v>-3.7119641501914243E-6</v>
       </c>
       <c r="T13">
-        <v>-1.7618990395407039E-6</v>
+        <v>7.9498183436670184E-8</v>
       </c>
       <c r="U13">
-        <v>6.3555278355155413E-6</v>
+        <v>-1.6756877274354683E-6</v>
       </c>
       <c r="V13">
-        <v>-3.2092802780812044E-4</v>
+        <v>3.1924699009309255E-4</v>
       </c>
       <c r="W13">
-        <v>1.8946298994221126E-4</v>
+        <v>-2.0546633531777535E-4</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.45">
@@ -6031,70 +6010,70 @@
         <v>36</v>
       </c>
       <c r="B14">
-        <v>2.3218564983323309E-2</v>
+        <v>-3.8830409663654634E-2</v>
       </c>
       <c r="C14">
-        <v>-2.5765482103170512E-6</v>
+        <v>2.8473061505325477E-6</v>
       </c>
       <c r="D14">
-        <v>-3.0203027600992794E-6</v>
+        <v>-1.5764014027498564E-5</v>
       </c>
       <c r="E14">
-        <v>2.9478668387934686E-8</v>
+        <v>1.5820641188975016E-7</v>
       </c>
       <c r="F14">
-        <v>-6.111359095921477E-6</v>
+        <v>-4.6972799054695908E-5</v>
       </c>
       <c r="G14">
-        <v>-4.7358756026565378E-6</v>
+        <v>-5.2123255469744171E-5</v>
       </c>
       <c r="H14">
-        <v>1.1791368830457743E-7</v>
+        <v>1.0112088385392049E-6</v>
       </c>
       <c r="I14">
-        <v>1.4638845071684591E-7</v>
+        <v>1.298110209157914E-6</v>
       </c>
       <c r="J14">
-        <v>-1.0096055926097615E-5</v>
+        <v>7.0032496232342435E-8</v>
       </c>
       <c r="K14">
-        <v>-2.8451337317572575E-5</v>
+        <v>-2.6111584476447046E-5</v>
       </c>
       <c r="L14">
-        <v>-3.1054280066371967E-5</v>
+        <v>-3.4185088637758902E-5</v>
       </c>
       <c r="M14">
-        <v>-2.9148891128002836E-5</v>
+        <v>-3.6565603226693423E-5</v>
       </c>
       <c r="N14">
-        <v>8.8518422065899031E-5</v>
+        <v>4.225335034183435E-5</v>
       </c>
       <c r="O14">
-        <v>2.3601326712013312E-4</v>
+        <v>1.4919833252049507E-4</v>
       </c>
       <c r="P14">
-        <v>9.0492951907489655E-5</v>
+        <v>2.5879443800240732E-5</v>
       </c>
       <c r="Q14">
-        <v>8.9257891324464678E-5</v>
+        <v>3.2011420996526319E-5</v>
       </c>
       <c r="R14">
-        <v>5.8732300644982525E-6</v>
+        <v>-2.58443613349294E-6</v>
       </c>
       <c r="S14">
-        <v>-1.3729158095305954E-5</v>
+        <v>-1.4327073570559808E-5</v>
       </c>
       <c r="T14">
-        <v>1.1677879895805038E-7</v>
+        <v>-3.5292826003465642E-7</v>
       </c>
       <c r="U14">
-        <v>-3.4933476770768082E-6</v>
+        <v>-2.8082113530195288E-6</v>
       </c>
       <c r="V14">
-        <v>4.5645745279004188E-5</v>
+        <v>4.2442419265868215E-4</v>
       </c>
       <c r="W14">
-        <v>-9.2394273094004886E-5</v>
+        <v>-2.6651702802524778E-4</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.45">
@@ -6102,567 +6081,567 @@
         <v>37</v>
       </c>
       <c r="B15">
-        <v>-1.1907480589959956E-2</v>
+        <v>9.3279193436869266E-3</v>
       </c>
       <c r="C15">
-        <v>4.2304774982416232E-7</v>
+        <v>1.15861999703872E-7</v>
       </c>
       <c r="D15">
-        <v>-4.2716785834327737E-6</v>
+        <v>4.2467888931914201E-6</v>
       </c>
       <c r="E15">
-        <v>4.3556206259883316E-8</v>
+        <v>-4.3608499776935663E-8</v>
       </c>
       <c r="F15">
-        <v>-9.2296842888718964E-6</v>
+        <v>8.9277054095561946E-6</v>
       </c>
       <c r="G15">
-        <v>-1.2352416588411184E-5</v>
+        <v>1.2946824081673961E-5</v>
       </c>
       <c r="H15">
-        <v>1.3464951566794879E-7</v>
+        <v>-1.9533043758396552E-7</v>
       </c>
       <c r="I15">
-        <v>1.9962198674895822E-7</v>
+        <v>-3.2669584848022407E-7</v>
       </c>
       <c r="J15">
-        <v>-1.7793715146064902E-5</v>
+        <v>-1.9914024795460371E-7</v>
       </c>
       <c r="K15">
-        <v>-3.9669319499853294E-5</v>
+        <v>6.9181164143731065E-6</v>
       </c>
       <c r="L15">
-        <v>-4.3281801591472799E-5</v>
+        <v>7.145411072683734E-6</v>
       </c>
       <c r="M15">
-        <v>-4.3785164233834386E-5</v>
+        <v>9.7911810835837239E-6</v>
       </c>
       <c r="N15">
-        <v>8.8757218887009176E-5</v>
+        <v>2.6759482897629269E-5</v>
       </c>
       <c r="O15">
-        <v>9.0492951907489655E-5</v>
+        <v>2.5879443800240732E-5</v>
       </c>
       <c r="P15">
-        <v>1.7690892231018345E-4</v>
+        <v>5.7322698331140436E-5</v>
       </c>
       <c r="Q15">
-        <v>8.9619433880310624E-5</v>
+        <v>2.9446666584593115E-5</v>
       </c>
       <c r="R15">
-        <v>4.6458068427497187E-6</v>
+        <v>-1.3038066367662722E-6</v>
       </c>
       <c r="S15">
-        <v>-1.76049576912886E-5</v>
+        <v>-6.8044908192458442E-6</v>
       </c>
       <c r="T15">
-        <v>9.7445236952594654E-7</v>
+        <v>-4.3124288494604043E-7</v>
       </c>
       <c r="U15">
-        <v>-3.9273519584806212E-6</v>
+        <v>-1.1666680441287802E-6</v>
       </c>
       <c r="V15">
-        <v>8.834097129596015E-5</v>
+        <v>-1.4001632013869336E-4</v>
       </c>
       <c r="W15">
-        <v>-1.0854251782751141E-4</v>
+        <v>7.1833566270694156E-5</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B16">
-        <v>-3.707633825185612E-2</v>
+        <v>-2.2586640404677161E-2</v>
       </c>
       <c r="C16">
-        <v>2.8525685469102263E-6</v>
+        <v>1.324184518156341E-6</v>
       </c>
       <c r="D16">
-        <v>1.0714533484162646E-6</v>
+        <v>-2.1119288033155075E-6</v>
       </c>
       <c r="E16">
-        <v>-1.1891419062024247E-8</v>
+        <v>2.0638354094057532E-8</v>
       </c>
       <c r="F16">
-        <v>3.1217641143433062E-6</v>
+        <v>-8.0531133634012627E-6</v>
       </c>
       <c r="G16">
-        <v>8.0951486031747971E-6</v>
+        <v>-7.9645095598033423E-6</v>
       </c>
       <c r="H16">
-        <v>-8.3515324418544894E-8</v>
+        <v>1.8793086379134331E-7</v>
       </c>
       <c r="I16">
-        <v>-3.3815270174726978E-7</v>
+        <v>2.2016969511219327E-7</v>
       </c>
       <c r="J16">
-        <v>3.1354973377504787E-6</v>
+        <v>-1.7697519355566548E-6</v>
       </c>
       <c r="K16">
-        <v>5.6845997546717381E-6</v>
+        <v>-7.0719894357277852E-6</v>
       </c>
       <c r="L16">
-        <v>8.4643963056943843E-6</v>
+        <v>-8.1763748841089523E-6</v>
       </c>
       <c r="M16">
-        <v>9.205086849772695E-6</v>
+        <v>-6.7291821495881638E-6</v>
       </c>
       <c r="N16">
-        <v>9.0291676640330998E-5</v>
+        <v>3.1553857507695399E-5</v>
       </c>
       <c r="O16">
-        <v>8.9257891324464678E-5</v>
+        <v>3.2011420996526319E-5</v>
       </c>
       <c r="P16">
-        <v>8.9619433880310624E-5</v>
+        <v>2.9446666584593115E-5</v>
       </c>
       <c r="Q16">
-        <v>1.2726542889930265E-4</v>
+        <v>5.8661286931204477E-5</v>
       </c>
       <c r="R16">
-        <v>2.8993465529373358E-6</v>
+        <v>-1.4973123295637502E-6</v>
       </c>
       <c r="S16">
-        <v>-1.548626374087402E-5</v>
+        <v>4.6569588712090673E-6</v>
       </c>
       <c r="T16">
-        <v>-8.7646076881646965E-7</v>
+        <v>-1.9453218024746484E-6</v>
       </c>
       <c r="U16">
-        <v>4.14837419089043E-7</v>
+        <v>-2.3796589842250263E-6</v>
       </c>
       <c r="V16">
-        <v>-1.1172037643280357E-4</v>
+        <v>2.5459858211885287E-5</v>
       </c>
       <c r="W16">
-        <v>3.4178228187264511E-5</v>
+        <v>-3.1928770958030743E-5</v>
       </c>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B17">
-        <v>0.2303915654557693</v>
+        <v>0.22062206853999652</v>
       </c>
       <c r="C17">
-        <v>2.6251198159765253E-6</v>
+        <v>1.8573554142188454E-6</v>
       </c>
       <c r="D17">
-        <v>-9.1167430224432692E-7</v>
+        <v>-1.2944719989901626E-6</v>
       </c>
       <c r="E17">
-        <v>-1.0536473093768127E-9</v>
+        <v>1.238923164125611E-8</v>
       </c>
       <c r="F17">
-        <v>-7.4535373665715263E-6</v>
+        <v>-6.5516493156464271E-6</v>
       </c>
       <c r="G17">
-        <v>-1.6914154235454237E-5</v>
+        <v>-9.1421173142486355E-6</v>
       </c>
       <c r="H17">
-        <v>4.6098465433206522E-7</v>
+        <v>1.8993985454557722E-7</v>
       </c>
       <c r="I17">
-        <v>5.6619139983105389E-7</v>
+        <v>2.7087888057171046E-7</v>
       </c>
       <c r="J17">
-        <v>-3.6810906402640474E-7</v>
+        <v>4.0388644227300385E-6</v>
       </c>
       <c r="K17">
-        <v>-9.4565346857397998E-6</v>
+        <v>2.3848706351348173E-6</v>
       </c>
       <c r="L17">
-        <v>-1.0548416619711486E-5</v>
+        <v>2.256350803842415E-6</v>
       </c>
       <c r="M17">
-        <v>-1.1504615352314001E-5</v>
+        <v>2.2569700347841747E-6</v>
       </c>
       <c r="N17">
-        <v>2.2255930078584726E-6</v>
+        <v>-1.7509455489535438E-6</v>
       </c>
       <c r="O17">
-        <v>5.8732300644982525E-6</v>
+        <v>-2.58443613349294E-6</v>
       </c>
       <c r="P17">
-        <v>4.6458068427497187E-6</v>
+        <v>-1.3038066367662722E-6</v>
       </c>
       <c r="Q17">
-        <v>2.8993465529373358E-6</v>
+        <v>-1.4973123295637502E-6</v>
       </c>
       <c r="R17">
-        <v>7.3979523549087031E-4</v>
+        <v>1.7020519363412096E-4</v>
       </c>
       <c r="S17">
-        <v>2.982025433601584E-5</v>
+        <v>1.7911955084868853E-5</v>
       </c>
       <c r="T17">
-        <v>-2.5892774943330862E-6</v>
+        <v>-3.6344338966347246E-6</v>
       </c>
       <c r="U17">
-        <v>-7.0979973946274516E-6</v>
+        <v>-3.1376794018717686E-6</v>
       </c>
       <c r="V17">
-        <v>1.1179717180480282E-5</v>
+        <v>8.8089808868483223E-6</v>
       </c>
       <c r="W17">
-        <v>-1.1901311046036851E-4</v>
+        <v>-4.5819555673522193E-5</v>
       </c>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B18">
-        <v>0.24240892199063058</v>
+        <v>0.30187284346812931</v>
       </c>
       <c r="C18">
-        <v>-1.6269071106821978E-5</v>
+        <v>-1.8239916828318502E-6</v>
       </c>
       <c r="D18">
-        <v>-4.6957929476915422E-6</v>
+        <v>1.9190157050088914E-5</v>
       </c>
       <c r="E18">
-        <v>4.1682756049469515E-8</v>
+        <v>-1.7693622905436588E-7</v>
       </c>
       <c r="F18">
-        <v>1.0628255073795765E-5</v>
+        <v>2.3382755582126885E-7</v>
       </c>
       <c r="G18">
-        <v>-9.6277973158491497E-6</v>
+        <v>3.4509049998175171E-6</v>
       </c>
       <c r="H18">
-        <v>-9.0432052359300635E-9</v>
+        <v>-4.5496877356901355E-7</v>
       </c>
       <c r="I18">
-        <v>7.4772800746042425E-7</v>
+        <v>-1.1964061610944252E-6</v>
       </c>
       <c r="J18">
-        <v>-2.3155898290259449E-5</v>
+        <v>7.8306577448568995E-6</v>
       </c>
       <c r="K18">
-        <v>-6.4579276546405289E-5</v>
+        <v>1.1807934433278602E-4</v>
       </c>
       <c r="L18">
-        <v>-8.1033022969494316E-5</v>
+        <v>1.4107667849242535E-4</v>
       </c>
       <c r="M18">
-        <v>-8.1461117168970854E-5</v>
+        <v>1.7483824373639963E-4</v>
       </c>
       <c r="N18">
-        <v>-1.854734955115871E-5</v>
+        <v>-3.7119641501914243E-6</v>
       </c>
       <c r="O18">
-        <v>-1.3729158095305954E-5</v>
+        <v>-1.4327073570559808E-5</v>
       </c>
       <c r="P18">
-        <v>-1.76049576912886E-5</v>
+        <v>-6.8044908192458442E-6</v>
       </c>
       <c r="Q18">
-        <v>-1.548626374087402E-5</v>
+        <v>4.6569588712090673E-6</v>
       </c>
       <c r="R18">
-        <v>2.982025433601584E-5</v>
+        <v>1.7911955084868853E-5</v>
       </c>
       <c r="S18">
-        <v>1.0171604366249489E-3</v>
+        <v>2.7609622359417128E-2</v>
       </c>
       <c r="T18">
-        <v>-1.7513827172201479E-4</v>
+        <v>-1.2742169894164879E-3</v>
       </c>
       <c r="U18">
-        <v>-2.0845457955343905E-4</v>
+        <v>-1.7314808494309463E-4</v>
       </c>
       <c r="V18">
-        <v>-8.2147461466213682E-4</v>
+        <v>-2.8064748417598172E-2</v>
       </c>
       <c r="W18">
-        <v>-1.6858637860914198E-4</v>
+        <v>4.4980673216845528E-4</v>
       </c>
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B19">
-        <v>-1.7219079304506082E-2</v>
+        <v>-4.7752604057982422E-2</v>
       </c>
       <c r="C19">
-        <v>-2.0373534725566378E-6</v>
+        <v>2.8199712562863171E-7</v>
       </c>
       <c r="D19">
-        <v>-2.3443821466183038E-6</v>
+        <v>1.2052841715803317E-7</v>
       </c>
       <c r="E19">
-        <v>2.5486870801268651E-8</v>
+        <v>-2.1626391960687828E-9</v>
       </c>
       <c r="F19">
-        <v>-2.2739142806513155E-6</v>
+        <v>5.7316363664208842E-6</v>
       </c>
       <c r="G19">
-        <v>3.8525949966782458E-6</v>
+        <v>7.0481532951945561E-6</v>
       </c>
       <c r="H19">
-        <v>2.4271349238855517E-8</v>
+        <v>-6.7847864033554756E-8</v>
       </c>
       <c r="I19">
-        <v>-3.2848113589278396E-8</v>
+        <v>-5.4238952475956513E-8</v>
       </c>
       <c r="J19">
-        <v>-1.5244041990520065E-5</v>
+        <v>9.2735509986471001E-6</v>
       </c>
       <c r="K19">
-        <v>-2.2990270178747252E-5</v>
+        <v>8.1734425687767358E-6</v>
       </c>
       <c r="L19">
-        <v>-2.6093748558443494E-5</v>
+        <v>1.5362881205400485E-5</v>
       </c>
       <c r="M19">
-        <v>-2.6697244956639329E-5</v>
+        <v>1.5044757119755261E-5</v>
       </c>
       <c r="N19">
-        <v>-1.7618990395407039E-6</v>
+        <v>7.9498183436670184E-8</v>
       </c>
       <c r="O19">
-        <v>1.1677879895805038E-7</v>
+        <v>-3.5292826003465642E-7</v>
       </c>
       <c r="P19">
-        <v>9.7445236952594654E-7</v>
+        <v>-4.3124288494604043E-7</v>
       </c>
       <c r="Q19">
-        <v>-8.7646076881646965E-7</v>
+        <v>-1.9453218024746484E-6</v>
       </c>
       <c r="R19">
-        <v>-2.5892774943330862E-6</v>
+        <v>-3.6344338966347246E-6</v>
       </c>
       <c r="S19">
-        <v>-1.7513827172201479E-4</v>
+        <v>-1.2742169894164879E-3</v>
       </c>
       <c r="T19">
-        <v>1.621431484644642E-4</v>
+        <v>1.415254419010871E-4</v>
       </c>
       <c r="U19">
-        <v>5.2806656392030528E-5</v>
+        <v>1.6534183169072125E-5</v>
       </c>
       <c r="V19">
-        <v>2.5471522321693834E-4</v>
+        <v>1.2394124261522954E-3</v>
       </c>
       <c r="W19">
-        <v>-6.2484415108760279E-5</v>
+        <v>-8.5820753660859732E-6</v>
       </c>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B20">
-        <v>-4.1553134452478081E-2</v>
+        <v>3.5865700987642544E-2</v>
       </c>
       <c r="C20">
-        <v>1.1097631830486151E-6</v>
+        <v>1.0127149257330256E-6</v>
       </c>
       <c r="D20">
-        <v>2.0614582664868834E-5</v>
+        <v>2.3051571026915804E-6</v>
       </c>
       <c r="E20">
-        <v>-2.2082415698646037E-7</v>
+        <v>-2.5269969845861938E-8</v>
       </c>
       <c r="F20">
-        <v>1.6135998153020653E-5</v>
+        <v>9.5561292791707846E-6</v>
       </c>
       <c r="G20">
-        <v>-8.3460188608950432E-6</v>
+        <v>1.0746960888671472E-5</v>
       </c>
       <c r="H20">
-        <v>-4.2558055364176782E-7</v>
+        <v>-1.6356565566752908E-7</v>
       </c>
       <c r="I20">
-        <v>-5.5841964993455373E-7</v>
+        <v>-1.976633410679357E-7</v>
       </c>
       <c r="J20">
-        <v>9.7911128076162663E-5</v>
+        <v>-2.6720890300179575E-6</v>
       </c>
       <c r="K20">
-        <v>1.9990472869835379E-4</v>
+        <v>-6.2444390719011679E-7</v>
       </c>
       <c r="L20">
-        <v>2.1694949663149989E-4</v>
+        <v>-4.4731984229143145E-7</v>
       </c>
       <c r="M20">
-        <v>2.1950842438440233E-4</v>
+        <v>-3.6228831573026625E-6</v>
       </c>
       <c r="N20">
-        <v>6.3555278355155413E-6</v>
+        <v>-1.6756877274354683E-6</v>
       </c>
       <c r="O20">
-        <v>-3.4933476770768082E-6</v>
+        <v>-2.8082113530195288E-6</v>
       </c>
       <c r="P20">
-        <v>-3.9273519584806212E-6</v>
+        <v>-1.1666680441287802E-6</v>
       </c>
       <c r="Q20">
-        <v>4.14837419089043E-7</v>
+        <v>-2.3796589842250263E-6</v>
       </c>
       <c r="R20">
-        <v>-7.0979973946274516E-6</v>
+        <v>-3.1376794018717686E-6</v>
       </c>
       <c r="S20">
-        <v>-2.0845457955343905E-4</v>
+        <v>-1.7314808494309463E-4</v>
       </c>
       <c r="T20">
-        <v>5.2806656392030528E-5</v>
+        <v>1.6534183169072125E-5</v>
       </c>
       <c r="U20">
-        <v>2.4258148706027456E-4</v>
+        <v>1.4408137156465565E-4</v>
       </c>
       <c r="V20">
-        <v>-5.4692147873705251E-4</v>
+        <v>1.0668213322493742E-4</v>
       </c>
       <c r="W20">
-        <v>5.5791115485019291E-4</v>
+        <v>2.995462991893964E-5</v>
       </c>
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B21">
-        <v>1.1470436162993092</v>
+        <v>1.0681872028844559</v>
       </c>
       <c r="C21">
-        <v>-6.8222665579085348E-5</v>
+        <v>-5.0012701591296718E-5</v>
       </c>
       <c r="D21">
-        <v>-8.8216434290872394E-4</v>
+        <v>-6.2685745198527731E-4</v>
       </c>
       <c r="E21">
-        <v>9.2798651119866901E-6</v>
+        <v>6.2862118604283118E-6</v>
       </c>
       <c r="F21">
-        <v>-1.793565155674562E-3</v>
+        <v>-2.3377388348329526E-3</v>
       </c>
       <c r="G21">
-        <v>-8.9708497792628436E-4</v>
+        <v>-2.2464638235496596E-3</v>
       </c>
       <c r="H21">
-        <v>4.1114133081886934E-5</v>
+        <v>4.8744899103976281E-5</v>
       </c>
       <c r="I21">
-        <v>4.3090618403197366E-5</v>
+        <v>5.4894777969478775E-5</v>
       </c>
       <c r="J21">
-        <v>-8.8270040702563245E-3</v>
+        <v>-2.6267445222933842E-3</v>
       </c>
       <c r="K21">
-        <v>-1.227730709421425E-2</v>
+        <v>-3.5554864354012351E-3</v>
       </c>
       <c r="L21">
-        <v>-1.2948036033849961E-2</v>
+        <v>-3.8124755160822833E-3</v>
       </c>
       <c r="M21">
-        <v>-1.3142842165320967E-2</v>
+        <v>-3.9380059355757476E-3</v>
       </c>
       <c r="N21">
-        <v>-3.2092802780812044E-4</v>
+        <v>3.1924699009309255E-4</v>
       </c>
       <c r="O21">
-        <v>4.5645745279004188E-5</v>
+        <v>4.2442419265868215E-4</v>
       </c>
       <c r="P21">
-        <v>8.834097129596015E-5</v>
+        <v>-1.4001632013869336E-4</v>
       </c>
       <c r="Q21">
-        <v>-1.1172037643280357E-4</v>
+        <v>2.5459858211885287E-5</v>
       </c>
       <c r="R21">
-        <v>1.1179717180480282E-5</v>
+        <v>8.8089808868483223E-6</v>
       </c>
       <c r="S21">
-        <v>-8.2147461466213682E-4</v>
+        <v>-2.8064748417598172E-2</v>
       </c>
       <c r="T21">
-        <v>2.5471522321693834E-4</v>
+        <v>1.2394124261522954E-3</v>
       </c>
       <c r="U21">
-        <v>-5.4692147873705251E-4</v>
+        <v>1.0668213322493742E-4</v>
       </c>
       <c r="V21">
-        <v>3.6363804447306899E-2</v>
+        <v>4.8032124416744884E-2</v>
       </c>
       <c r="W21">
-        <v>-1.9295705440239817E-2</v>
+        <v>-8.8081470588456078E-3</v>
       </c>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B22">
-        <v>-0.78011504561163858</v>
+        <v>-0.52313008397066696</v>
       </c>
       <c r="C22">
-        <v>5.6486469901159332E-5</v>
+        <v>2.1378860634480102E-5</v>
       </c>
       <c r="D22">
-        <v>5.3838961033084252E-4</v>
+        <v>2.9465105283169789E-4</v>
       </c>
       <c r="E22">
-        <v>-5.7638091288243958E-6</v>
+        <v>-3.0122832065336327E-6</v>
       </c>
       <c r="F22">
-        <v>4.3798414943035122E-4</v>
+        <v>7.7653937438297777E-4</v>
       </c>
       <c r="G22">
-        <v>-3.1729074343592899E-4</v>
+        <v>8.2786208586273777E-4</v>
       </c>
       <c r="H22">
-        <v>-1.1232261729371656E-5</v>
+        <v>-1.603347548514183E-5</v>
       </c>
       <c r="I22">
-        <v>-1.1994285555958712E-5</v>
+        <v>-2.1509721161781432E-5</v>
       </c>
       <c r="J22">
-        <v>2.4497581054538408E-3</v>
+        <v>6.7844952853593699E-5</v>
       </c>
       <c r="K22">
-        <v>5.0706164084508383E-3</v>
+        <v>5.5799824350713392E-4</v>
       </c>
       <c r="L22">
-        <v>5.5878758083060176E-3</v>
+        <v>6.9560184880447669E-4</v>
       </c>
       <c r="M22">
-        <v>5.6487356498155158E-3</v>
+        <v>7.3398082930585138E-4</v>
       </c>
       <c r="N22">
-        <v>1.8946298994221126E-4</v>
+        <v>-2.0546633531777535E-4</v>
       </c>
       <c r="O22">
-        <v>-9.2394273094004886E-5</v>
+        <v>-2.6651702802524778E-4</v>
       </c>
       <c r="P22">
-        <v>-1.0854251782751141E-4</v>
+        <v>7.1833566270694156E-5</v>
       </c>
       <c r="Q22">
-        <v>3.4178228187264511E-5</v>
+        <v>-3.1928770958030743E-5</v>
       </c>
       <c r="R22">
-        <v>-1.1901311046036851E-4</v>
+        <v>-4.5819555673522193E-5</v>
       </c>
       <c r="S22">
-        <v>-1.6858637860914198E-4</v>
+        <v>4.4980673216845528E-4</v>
       </c>
       <c r="T22">
-        <v>-6.2484415108760279E-5</v>
+        <v>-8.5820753660859732E-6</v>
       </c>
       <c r="U22">
-        <v>5.5791115485019291E-4</v>
+        <v>2.995462991893964E-5</v>
       </c>
       <c r="V22">
-        <v>-1.9295705440239817E-2</v>
+        <v>-8.8081470588456078E-3</v>
       </c>
       <c r="W22">
-        <v>1.4510623059623168E-2</v>
+        <v>4.973116826669793E-3</v>
       </c>
     </row>
   </sheetData>

--- a/input/reg_wages.xlsx
+++ b/input/reg_wages.xlsx
@@ -1,30 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patryk\git\SimPaths_HU\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57C6D0B7-89AA-4521-AABC-E866EEFD1CA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC3E48BB-F35A-45D2-B40B-84B0C014BA5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" tabRatio="932" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="932" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
-    <sheet name="IT_Wages_FemalesNE" sheetId="6" r:id="rId2"/>
-    <sheet name="IT_Wages_MalesNE" sheetId="7" r:id="rId3"/>
-    <sheet name="IT_Wages_FemalesE" sheetId="8" r:id="rId4"/>
-    <sheet name="IT_Wages_MalesE" sheetId="9" r:id="rId5"/>
+    <sheet name="EL_Wages_FemalesNE" sheetId="10" r:id="rId2"/>
+    <sheet name="EL_Wages_MalesNE" sheetId="11" r:id="rId3"/>
+    <sheet name="EL_Wages_FemalesE" sheetId="12" r:id="rId4"/>
+    <sheet name="EL_Wages_MalesE" sheetId="13" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="38">
   <si>
     <t>Description:</t>
   </si>
@@ -128,19 +128,16 @@
     <t>L1_log_hourly_wage</t>
   </si>
   <si>
-    <t>Regions: ITF = South, ITG = Islands, ITH = Northeast, ITI = Central. Northwest (ITC) is the omitted region.</t>
+    <t>Regions: EL3 = Attika (omitted), EL4 = Aegean Islands, EL7 = Central and Northern Greece</t>
   </si>
   <si>
-    <t>ITF</t>
+    <t>Estimate the models without the lagged wage observation on the full working age sample. Choice made because otherwise the reduction in the sample size makes the sigma used when correcting the bias when transforming the log wages to wage levels too large.</t>
   </si>
   <si>
-    <t>ITG</t>
+    <t>EL4</t>
   </si>
   <si>
-    <t>ITH</t>
-  </si>
-  <si>
-    <t>ITI</t>
+    <t>EL7</t>
   </si>
 </sst>
 </file>
@@ -153,12 +150,11 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -189,13 +185,11 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -531,29 +525,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="14.796875" bestFit="1" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:B15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -561,7 +552,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -569,7 +560,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -577,7 +568,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -585,27 +576,32 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A11" s="2" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -614,15 +610,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB2C99E6-AF73-4362-A209-1CD525536559}">
-  <dimension ref="A1:V21"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="21" style="3" customWidth="1"/>
-    <col min="2" max="16384" width="8.796875" style="3"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF0B1B18-F257-4AB0-93E8-A642D3D22D0B}">
+  <dimension ref="A1:T19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -660,1394 +652,1144 @@
         <v>26</v>
       </c>
       <c r="M1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="P1" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="Q1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="R1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="S1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="T1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U1" t="s">
-        <v>31</v>
-      </c>
-      <c r="V1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>17</v>
       </c>
       <c r="B2">
-        <v>2.5436320865368629E-2</v>
+        <v>-6.1124123989693462E-2</v>
       </c>
       <c r="C2">
-        <v>1.6394836554125037E-4</v>
+        <v>1.6297405509596533E-3</v>
       </c>
       <c r="D2">
-        <v>-1.940173728820808E-6</v>
+        <v>-2.2265283791892348E-5</v>
       </c>
       <c r="E2">
-        <v>1.7612282316757224E-4</v>
+        <v>-8.347730696052557E-3</v>
       </c>
       <c r="F2">
-        <v>-2.3345986039571015E-4</v>
+        <v>-2.0265612303830071E-2</v>
       </c>
       <c r="G2">
-        <v>-9.3680138732286656E-6</v>
+        <v>1.3370746407315295E-4</v>
       </c>
       <c r="H2">
-        <v>-3.362430436697574E-6</v>
+        <v>3.7653398782235557E-4</v>
       </c>
       <c r="I2">
-        <v>4.7105205314027296E-4</v>
+        <v>7.9968457581548389E-4</v>
       </c>
       <c r="J2">
-        <v>5.4099170654948775E-4</v>
+        <v>4.3769034469558826E-3</v>
       </c>
       <c r="K2">
-        <v>5.7640449670552456E-4</v>
+        <v>5.9237165945301117E-3</v>
       </c>
       <c r="L2">
-        <v>6.4674039660667202E-4</v>
+        <v>6.2927493875592124E-3</v>
       </c>
       <c r="M2">
-        <v>-1.749208999402189E-4</v>
+        <v>1.0621101977395953E-3</v>
       </c>
       <c r="N2">
-        <v>-2.1360007519683209E-4</v>
+        <v>-2.9044547678024025E-4</v>
       </c>
       <c r="O2">
-        <v>6.7007436290012043E-5</v>
+        <v>-1.4804344080751913E-5</v>
       </c>
       <c r="P2">
-        <v>1.850901370848642E-7</v>
+        <v>2.6058364040966117E-4</v>
       </c>
       <c r="Q2">
-        <v>-2.4740028022701483E-5</v>
+        <v>7.200729730301328E-4</v>
       </c>
       <c r="R2">
-        <v>-3.8238617730593032E-4</v>
+        <v>1.1985530162859139E-2</v>
       </c>
       <c r="S2">
-        <v>1.2999972952604054E-4</v>
+        <v>-5.737608421471091E-2</v>
       </c>
       <c r="T2">
-        <v>3.8183766205598235E-4</v>
-      </c>
-      <c r="U2">
-        <v>-4.4001154657403816E-3</v>
-      </c>
-      <c r="V2">
-        <v>7.9591477924982894E-4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.45">
+        <v>1.4594643561502252E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>18</v>
       </c>
       <c r="B3">
-        <v>-9.9442795588634714E-5</v>
+        <v>9.0407101597025777E-4</v>
       </c>
       <c r="C3">
-        <v>-1.940173728820808E-6</v>
+        <v>-2.2265283791892348E-5</v>
       </c>
       <c r="D3">
-        <v>2.3720836992773504E-8</v>
+        <v>3.0558162027425435E-7</v>
       </c>
       <c r="E3">
-        <v>2.4563192174037968E-7</v>
+        <v>1.185486576390504E-4</v>
       </c>
       <c r="F3">
-        <v>5.2546146444083756E-6</v>
+        <v>2.8188516631445044E-4</v>
       </c>
       <c r="G3">
-        <v>5.2422896552103234E-8</v>
+        <v>-1.9314483790608535E-6</v>
       </c>
       <c r="H3">
-        <v>-2.0960584102242777E-8</v>
+        <v>-5.2578493946430514E-6</v>
       </c>
       <c r="I3">
-        <v>-5.9805886387292323E-6</v>
+        <v>-1.1168184523026909E-5</v>
       </c>
       <c r="J3">
-        <v>-6.7640489084881196E-6</v>
+        <v>-6.0518588547725908E-5</v>
       </c>
       <c r="K3">
-        <v>-7.1442242311663476E-6</v>
+        <v>-8.1860568817845208E-5</v>
       </c>
       <c r="L3">
-        <v>-7.9460824939888855E-6</v>
+        <v>-8.6800235235100044E-5</v>
       </c>
       <c r="M3">
-        <v>2.1434261261617941E-6</v>
+        <v>-1.4683002654785681E-5</v>
       </c>
       <c r="N3">
-        <v>2.6116226047795972E-6</v>
+        <v>3.9952425566370544E-6</v>
       </c>
       <c r="O3">
-        <v>-7.9323432294775308E-7</v>
+        <v>1.7884259920910494E-7</v>
       </c>
       <c r="P3">
-        <v>-8.2744893217838418E-9</v>
+        <v>-2.8279888469960352E-6</v>
       </c>
       <c r="Q3">
-        <v>2.8089554223575157E-7</v>
+        <v>-1.0010809839111577E-5</v>
       </c>
       <c r="R3">
-        <v>5.1241338089540094E-6</v>
+        <v>-1.6572941647627175E-4</v>
       </c>
       <c r="S3">
-        <v>-1.6162160863925796E-6</v>
+        <v>7.8522209373004361E-4</v>
       </c>
       <c r="T3">
-        <v>-4.8521421125753751E-6</v>
-      </c>
-      <c r="U3">
-        <v>5.1068068989269206E-5</v>
-      </c>
-      <c r="V3">
-        <v>-9.7768939686272123E-6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.45">
+        <v>-2.0144398707996807E-4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>19</v>
       </c>
       <c r="B4">
-        <v>-8.3212528071994488E-2</v>
+        <v>0.16085082153252064</v>
       </c>
       <c r="C4">
-        <v>1.7612282316757224E-4</v>
+        <v>-8.347730696052557E-3</v>
       </c>
       <c r="D4">
-        <v>2.4563192174037968E-7</v>
+        <v>1.185486576390504E-4</v>
       </c>
       <c r="E4">
-        <v>1.233269116350964E-2</v>
+        <v>6.4958620789612578E-2</v>
       </c>
       <c r="F4">
-        <v>8.3879515858163098E-3</v>
+        <v>0.12126255143521461</v>
       </c>
       <c r="G4">
-        <v>-2.8558812212106394E-4</v>
+        <v>-1.1755877478465294E-3</v>
       </c>
       <c r="H4">
-        <v>-1.9046224365598175E-4</v>
+        <v>-2.2998894430969023E-3</v>
       </c>
       <c r="I4">
-        <v>-1.3911502880833444E-3</v>
+        <v>-4.4471348229542145E-3</v>
       </c>
       <c r="J4">
-        <v>-1.3271723444661151E-3</v>
+        <v>-2.4710801373249946E-2</v>
       </c>
       <c r="K4">
-        <v>-1.3906501903379392E-3</v>
+        <v>-3.3575132480315642E-2</v>
       </c>
       <c r="L4">
-        <v>-1.4525606013858741E-3</v>
+        <v>-3.570252592071399E-2</v>
       </c>
       <c r="M4">
-        <v>2.2220543106336079E-4</v>
+        <v>-6.3007133029446853E-3</v>
       </c>
       <c r="N4">
-        <v>1.8725887266969572E-4</v>
+        <v>1.5455746597154468E-3</v>
       </c>
       <c r="O4">
-        <v>-5.5656860961452946E-5</v>
+        <v>-1.6012246434244195E-4</v>
       </c>
       <c r="P4">
-        <v>-2.3943494467838302E-5</v>
+        <v>1.355569620648582E-4</v>
       </c>
       <c r="Q4">
-        <v>-1.1959580129725287E-4</v>
+        <v>-4.0592051832003314E-3</v>
       </c>
       <c r="R4">
-        <v>-1.8748297432304904E-4</v>
+        <v>-6.8407900016870166E-2</v>
       </c>
       <c r="S4">
-        <v>-8.0600599087710247E-5</v>
+        <v>0.30124604915231246</v>
       </c>
       <c r="T4">
-        <v>-5.4369636128645494E-4</v>
-      </c>
-      <c r="U4">
-        <v>-4.8929467061598619E-3</v>
-      </c>
-      <c r="V4">
-        <v>-9.9873072646448641E-4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.45">
+        <v>-8.2752379177145674E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>20</v>
       </c>
       <c r="B5">
-        <v>-0.22783090673449602</v>
+        <v>0.51253250347108481</v>
       </c>
       <c r="C5">
-        <v>-2.3345986039571015E-4</v>
+        <v>-2.0265612303830071E-2</v>
       </c>
       <c r="D5">
-        <v>5.2546146444083756E-6</v>
+        <v>2.8188516631445044E-4</v>
       </c>
       <c r="E5">
-        <v>8.3879515858163098E-3</v>
+        <v>0.12126255143521461</v>
       </c>
       <c r="F5">
-        <v>2.0521614328149581E-2</v>
+        <v>0.29610913661246624</v>
       </c>
       <c r="G5">
-        <v>-1.8375827991104604E-4</v>
+        <v>-2.0523851570687663E-3</v>
       </c>
       <c r="H5">
-        <v>-4.2414711611733107E-4</v>
+        <v>-5.5748919160981134E-3</v>
       </c>
       <c r="I5">
-        <v>-2.6347930415596284E-3</v>
+        <v>-1.0201417750941445E-2</v>
       </c>
       <c r="J5">
-        <v>-2.8407613334950495E-3</v>
+        <v>-5.6736148136043246E-2</v>
       </c>
       <c r="K5">
-        <v>-3.1384509701010851E-3</v>
+        <v>-7.7027476327307998E-2</v>
       </c>
       <c r="L5">
-        <v>-3.3070154860624307E-3</v>
+        <v>-8.1770922814993041E-2</v>
       </c>
       <c r="M5">
-        <v>5.1170044442761355E-4</v>
+        <v>-1.4128244206856454E-2</v>
       </c>
       <c r="N5">
-        <v>4.8792858602404206E-4</v>
+        <v>3.7743330456551441E-3</v>
       </c>
       <c r="O5">
-        <v>-8.8588823600110759E-5</v>
+        <v>4.1010163719783921E-5</v>
       </c>
       <c r="P5">
-        <v>3.9479249936121684E-5</v>
+        <v>-3.2386001734238438E-3</v>
       </c>
       <c r="Q5">
-        <v>-1.5371132259709943E-4</v>
+        <v>-9.4099951898566035E-3</v>
       </c>
       <c r="R5">
-        <v>-2.051110400056282E-3</v>
+        <v>-0.1559727397196512</v>
       </c>
       <c r="S5">
-        <v>-2.8195107445244433E-4</v>
+        <v>0.72103871899001937</v>
       </c>
       <c r="T5">
-        <v>-1.5058002440121805E-3</v>
-      </c>
-      <c r="U5">
-        <v>8.8085569933950437E-3</v>
-      </c>
-      <c r="V5">
-        <v>-2.8778994419941971E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.45">
+        <v>-0.18919198933201503</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>21</v>
       </c>
       <c r="B6">
-        <v>-5.2959442803548152E-3</v>
+        <v>-8.3198418879833133E-3</v>
       </c>
       <c r="C6">
-        <v>-9.3680138732286656E-6</v>
+        <v>1.3370746407315295E-4</v>
       </c>
       <c r="D6">
-        <v>5.2422896552103234E-8</v>
+        <v>-1.9314483790608535E-6</v>
       </c>
       <c r="E6">
-        <v>-2.8558812212106394E-4</v>
+        <v>-1.1755877478465294E-3</v>
       </c>
       <c r="F6">
-        <v>-1.8375827991104604E-4</v>
+        <v>-2.0523851570687663E-3</v>
       </c>
       <c r="G6">
-        <v>7.462237205378919E-6</v>
+        <v>2.2570121892340055E-5</v>
       </c>
       <c r="H6">
-        <v>4.9976680668069179E-6</v>
+        <v>3.9740276665226613E-5</v>
       </c>
       <c r="I6">
-        <v>1.053556201968413E-5</v>
+        <v>7.0028962324731811E-5</v>
       </c>
       <c r="J6">
-        <v>2.161755450795132E-6</v>
+        <v>4.0158225460101989E-4</v>
       </c>
       <c r="K6">
-        <v>1.563052923723596E-6</v>
+        <v>5.4720117425846907E-4</v>
       </c>
       <c r="L6">
-        <v>7.6963091676077292E-8</v>
+        <v>5.8375880180840079E-4</v>
       </c>
       <c r="M6">
-        <v>2.7261930927279043E-6</v>
+        <v>1.0004097159878229E-4</v>
       </c>
       <c r="N6">
-        <v>6.267467877346954E-6</v>
+        <v>-2.7168035820493756E-5</v>
       </c>
       <c r="O6">
-        <v>-3.1522496561707523E-6</v>
+        <v>4.0337807550530996E-6</v>
       </c>
       <c r="P6">
-        <v>-9.5672012432598871E-7</v>
+        <v>-7.3659072505228471E-6</v>
       </c>
       <c r="Q6">
-        <v>3.0251054641463584E-6</v>
+        <v>6.6020537148401342E-5</v>
       </c>
       <c r="R6">
-        <v>1.2364215652430843E-5</v>
+        <v>1.1240928838363129E-3</v>
       </c>
       <c r="S6">
-        <v>-3.4865252881937108E-6</v>
+        <v>-4.8352202094266196E-3</v>
       </c>
       <c r="T6">
-        <v>-6.2647933874519696E-6</v>
-      </c>
-      <c r="U6">
-        <v>2.8645474604507663E-4</v>
-      </c>
-      <c r="V6">
-        <v>-1.9206655342458081E-5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.45">
+        <v>1.3531557838357075E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>22</v>
       </c>
       <c r="B7">
-        <v>-7.0453206658569285E-3</v>
+        <v>-2.1880479028754417E-2</v>
       </c>
       <c r="C7">
-        <v>-3.362430436697574E-6</v>
+        <v>3.7653398782235557E-4</v>
       </c>
       <c r="D7">
-        <v>-2.0960584102242777E-8</v>
+        <v>-5.2578493946430514E-6</v>
       </c>
       <c r="E7">
-        <v>-1.9046224365598175E-4</v>
+        <v>-2.2998894430969023E-3</v>
       </c>
       <c r="F7">
-        <v>-4.2414711611733107E-4</v>
+        <v>-5.5748919160981134E-3</v>
       </c>
       <c r="G7">
-        <v>4.9976680668069179E-6</v>
+        <v>3.9740276665226613E-5</v>
       </c>
       <c r="H7">
-        <v>1.0129264667709616E-5</v>
+        <v>1.0611644233733637E-4</v>
       </c>
       <c r="I7">
-        <v>1.8460011237635669E-5</v>
+        <v>1.8927083347286644E-4</v>
       </c>
       <c r="J7">
-        <v>1.4677220051661651E-5</v>
+        <v>1.0562904122457732E-3</v>
       </c>
       <c r="K7">
-        <v>2.033546549201903E-5</v>
+        <v>1.4347362224340612E-3</v>
       </c>
       <c r="L7">
-        <v>1.9389534187140499E-5</v>
+        <v>1.5251723043399282E-3</v>
       </c>
       <c r="M7">
-        <v>5.5974118325599094E-7</v>
+        <v>2.556852075021928E-4</v>
       </c>
       <c r="N7">
-        <v>3.6842275101691257E-6</v>
+        <v>-7.665068383258956E-5</v>
       </c>
       <c r="O7">
-        <v>-3.9792124518817337E-6</v>
+        <v>-3.9783908999213959E-7</v>
       </c>
       <c r="P7">
-        <v>-1.6418138085716725E-6</v>
+        <v>3.6721636334114907E-5</v>
       </c>
       <c r="Q7">
-        <v>3.8730051560912073E-6</v>
+        <v>1.7520697002402873E-4</v>
       </c>
       <c r="R7">
-        <v>3.6942521814441489E-5</v>
+        <v>2.9002934541726079E-3</v>
       </c>
       <c r="S7">
-        <v>-2.9336995718296662E-7</v>
+        <v>-1.3347358877538382E-2</v>
       </c>
       <c r="T7">
-        <v>4.6701889924085084E-6</v>
-      </c>
-      <c r="U7">
-        <v>1.0943763645504119E-4</v>
-      </c>
-      <c r="V7">
-        <v>-3.4499374508852628E-6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.45">
+        <v>3.5094267267490775E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>23</v>
       </c>
       <c r="B8">
-        <v>-2.6062419482344289E-2</v>
+        <v>-5.5396583424861923E-2</v>
       </c>
       <c r="C8">
-        <v>4.7105205314027296E-4</v>
+        <v>7.9968457581548389E-4</v>
       </c>
       <c r="D8">
-        <v>-5.9805886387292323E-6</v>
+        <v>-1.1168184523026909E-5</v>
       </c>
       <c r="E8">
-        <v>-1.3911502880833444E-3</v>
+        <v>-4.4471348229542145E-3</v>
       </c>
       <c r="F8">
-        <v>-2.6347930415596284E-3</v>
+        <v>-1.0201417750941445E-2</v>
       </c>
       <c r="G8">
-        <v>1.053556201968413E-5</v>
+        <v>7.0028962324731811E-5</v>
       </c>
       <c r="H8">
-        <v>1.8460011237635669E-5</v>
+        <v>1.8927083347286644E-4</v>
       </c>
       <c r="I8">
-        <v>9.6581367292502648E-2</v>
+        <v>5.5353299770007643E-2</v>
       </c>
       <c r="J8">
-        <v>9.0645570088195779E-2</v>
+        <v>4.3795122115549964E-2</v>
       </c>
       <c r="K8">
-        <v>9.0856222784729393E-2</v>
+        <v>4.4604869406418654E-2</v>
       </c>
       <c r="L8">
-        <v>9.1146006910698574E-2</v>
+        <v>4.4709934292948478E-2</v>
       </c>
       <c r="M8">
-        <v>-8.8951944418063917E-4</v>
+        <v>8.7320163491517153E-4</v>
       </c>
       <c r="N8">
-        <v>-9.0858776315488562E-4</v>
+        <v>-1.1953480098399008E-5</v>
       </c>
       <c r="O8">
-        <v>6.7028825939564418E-5</v>
+        <v>-1.7736100685240619E-4</v>
       </c>
       <c r="P8">
-        <v>2.2030414203348443E-5</v>
+        <v>-1.1402777112008234E-3</v>
       </c>
       <c r="Q8">
-        <v>-1.1308127289165649E-4</v>
+        <v>1.1852506880836919E-4</v>
       </c>
       <c r="R8">
-        <v>2.8881097458283199E-3</v>
+        <v>6.4431993160991522E-3</v>
       </c>
       <c r="S8">
-        <v>3.1064610612354499E-4</v>
+        <v>-6.9270592836314038E-2</v>
       </c>
       <c r="T8">
-        <v>1.7018835840419834E-3</v>
-      </c>
-      <c r="U8">
-        <v>-0.10692744616444759</v>
-      </c>
-      <c r="V8">
-        <v>3.8280020027675328E-3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.45">
+        <v>7.812179491004238E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>24</v>
       </c>
       <c r="B9">
-        <v>-6.1238473009558557E-2</v>
+        <v>-0.16011140062029397</v>
       </c>
       <c r="C9">
-        <v>5.4099170654948775E-4</v>
+        <v>4.3769034469558826E-3</v>
       </c>
       <c r="D9">
-        <v>-6.7640489084881196E-6</v>
+        <v>-6.0518588547725908E-5</v>
       </c>
       <c r="E9">
-        <v>-1.3271723444661151E-3</v>
+        <v>-2.4710801373249946E-2</v>
       </c>
       <c r="F9">
-        <v>-2.8407613334950495E-3</v>
+        <v>-5.6736148136043246E-2</v>
       </c>
       <c r="G9">
-        <v>2.161755450795132E-6</v>
+        <v>4.0158225460101989E-4</v>
       </c>
       <c r="H9">
-        <v>1.4677220051661651E-5</v>
+        <v>1.0562904122457732E-3</v>
       </c>
       <c r="I9">
-        <v>9.0645570088195779E-2</v>
+        <v>4.3795122115549964E-2</v>
       </c>
       <c r="J9">
-        <v>9.2430530845569306E-2</v>
+        <v>5.6863469362350143E-2</v>
       </c>
       <c r="K9">
-        <v>9.1369564158280653E-2</v>
+        <v>5.8489155639837781E-2</v>
       </c>
       <c r="L9">
-        <v>9.1716522200272182E-2</v>
+        <v>5.9479081503938477E-2</v>
       </c>
       <c r="M9">
-        <v>-1.0574363652000266E-3</v>
+        <v>3.3059402744976462E-3</v>
       </c>
       <c r="N9">
-        <v>-1.0571718624436742E-3</v>
+        <v>-5.5609508843391996E-4</v>
       </c>
       <c r="O9">
-        <v>1.4680517044961798E-4</v>
+        <v>-8.8716315285371604E-5</v>
       </c>
       <c r="P9">
-        <v>6.3915464237709039E-5</v>
+        <v>-2.131734247621332E-3</v>
       </c>
       <c r="Q9">
-        <v>-9.8027294940902283E-5</v>
+        <v>1.8684618801026072E-3</v>
       </c>
       <c r="R9">
-        <v>2.3448777804044138E-3</v>
+        <v>3.4270333625740904E-2</v>
       </c>
       <c r="S9">
-        <v>4.4188724903328896E-4</v>
+        <v>-0.19698969867778937</v>
       </c>
       <c r="T9">
-        <v>2.1026754193476218E-3</v>
-      </c>
-      <c r="U9">
-        <v>-0.10919714688044999</v>
-      </c>
-      <c r="V9">
-        <v>4.513835269719357E-3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.45">
+        <v>4.1721895725155597E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>25</v>
       </c>
       <c r="B10">
-        <v>1.6140266443714923E-2</v>
+        <v>-0.28866039692929024</v>
       </c>
       <c r="C10">
-        <v>5.7640449670552456E-4</v>
+        <v>5.9237165945301117E-3</v>
       </c>
       <c r="D10">
-        <v>-7.1442242311663476E-6</v>
+        <v>-8.1860568817845208E-5</v>
       </c>
       <c r="E10">
-        <v>-1.3906501903379392E-3</v>
+        <v>-3.3575132480315642E-2</v>
       </c>
       <c r="F10">
-        <v>-3.1384509701010851E-3</v>
+        <v>-7.7027476327307998E-2</v>
       </c>
       <c r="G10">
-        <v>1.563052923723596E-6</v>
+        <v>5.4720117425846907E-4</v>
       </c>
       <c r="H10">
-        <v>2.033546549201903E-5</v>
+        <v>1.4347362224340612E-3</v>
       </c>
       <c r="I10">
-        <v>9.0856222784729393E-2</v>
+        <v>4.4604869406418654E-2</v>
       </c>
       <c r="J10">
-        <v>9.1369564158280653E-2</v>
+        <v>5.8489155639837781E-2</v>
       </c>
       <c r="K10">
-        <v>9.2005016390276584E-2</v>
+        <v>6.5243545616228457E-2</v>
       </c>
       <c r="L10">
-        <v>9.2162776601109914E-2</v>
+        <v>6.5969299160535816E-2</v>
       </c>
       <c r="M10">
-        <v>-1.1031736460954513E-3</v>
+        <v>4.4081159151507024E-3</v>
       </c>
       <c r="N10">
-        <v>-1.1397117037361499E-3</v>
+        <v>-8.9172638638251389E-4</v>
       </c>
       <c r="O10">
-        <v>1.6540192691081348E-4</v>
+        <v>-3.0053455918003991E-5</v>
       </c>
       <c r="P10">
-        <v>9.2895449377482841E-5</v>
+        <v>-1.8013649904540384E-3</v>
       </c>
       <c r="Q10">
-        <v>-1.3968121930578919E-4</v>
+        <v>2.55215395507626E-3</v>
       </c>
       <c r="R10">
-        <v>2.9874743074261301E-3</v>
+        <v>4.6456013976223259E-2</v>
       </c>
       <c r="S10">
-        <v>6.565299668557182E-4</v>
+        <v>-0.25334395825394951</v>
       </c>
       <c r="T10">
-        <v>2.2895906071473153E-3</v>
-      </c>
-      <c r="U10">
-        <v>-0.11156476857144779</v>
-      </c>
-      <c r="V10">
-        <v>4.9240621591487644E-3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.45">
+        <v>5.6576876983002775E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>26</v>
       </c>
       <c r="B11">
-        <v>3.9681247247912138E-2</v>
+        <v>-0.27259082724404204</v>
       </c>
       <c r="C11">
-        <v>6.4674039660667202E-4</v>
+        <v>6.2927493875592124E-3</v>
       </c>
       <c r="D11">
-        <v>-7.9460824939888855E-6</v>
+        <v>-8.6800235235100044E-5</v>
       </c>
       <c r="E11">
-        <v>-1.4525606013858741E-3</v>
+        <v>-3.570252592071399E-2</v>
       </c>
       <c r="F11">
-        <v>-3.3070154860624307E-3</v>
+        <v>-8.1770922814993041E-2</v>
       </c>
       <c r="G11">
-        <v>7.6963091676077292E-8</v>
+        <v>5.8375880180840079E-4</v>
       </c>
       <c r="H11">
-        <v>1.9389534187140499E-5</v>
+        <v>1.5251723043399282E-3</v>
       </c>
       <c r="I11">
-        <v>9.1146006910698574E-2</v>
+        <v>4.4709934292948478E-2</v>
       </c>
       <c r="J11">
-        <v>9.1716522200272182E-2</v>
+        <v>5.9479081503938477E-2</v>
       </c>
       <c r="K11">
-        <v>9.2162776601109914E-2</v>
+        <v>6.5969299160535816E-2</v>
       </c>
       <c r="L11">
-        <v>9.3400116919707885E-2</v>
+        <v>6.7926790292218514E-2</v>
       </c>
       <c r="M11">
-        <v>-1.2321033944326576E-3</v>
+        <v>4.5868831911670205E-3</v>
       </c>
       <c r="N11">
-        <v>-1.2512254646217667E-3</v>
+        <v>-1.0681460104759177E-3</v>
       </c>
       <c r="O11">
-        <v>2.5196717318878381E-4</v>
+        <v>-2.5572797711947569E-5</v>
       </c>
       <c r="P11">
-        <v>1.3666586484161879E-4</v>
+        <v>-2.0426300503802635E-3</v>
       </c>
       <c r="Q11">
-        <v>-1.1999188326779785E-4</v>
+        <v>2.7024253703038146E-3</v>
       </c>
       <c r="R11">
-        <v>2.5315197087920674E-3</v>
+        <v>4.9262113547301777E-2</v>
       </c>
       <c r="S11">
-        <v>7.5624436370591585E-4</v>
+        <v>-0.26667026506727448</v>
       </c>
       <c r="T11">
-        <v>2.4504579611552644E-3</v>
-      </c>
-      <c r="U11">
-        <v>-0.11360098510254368</v>
-      </c>
-      <c r="V11">
-        <v>5.426156981275224E-3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.45">
+        <v>6.006658768955999E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B12">
-        <v>-0.17777408674849585</v>
+        <v>-0.15762641565975188</v>
       </c>
       <c r="C12">
-        <v>-1.749208999402189E-4</v>
+        <v>1.0621101977395953E-3</v>
       </c>
       <c r="D12">
-        <v>2.1434261261617941E-6</v>
+        <v>-1.4683002654785681E-5</v>
       </c>
       <c r="E12">
-        <v>2.2220543106336079E-4</v>
+        <v>-6.3007133029446853E-3</v>
       </c>
       <c r="F12">
-        <v>5.1170044442761355E-4</v>
+        <v>-1.4128244206856454E-2</v>
       </c>
       <c r="G12">
-        <v>2.7261930927279043E-6</v>
+        <v>1.0004097159878229E-4</v>
       </c>
       <c r="H12">
-        <v>5.5974118325599094E-7</v>
+        <v>2.556852075021928E-4</v>
       </c>
       <c r="I12">
-        <v>-8.8951944418063917E-4</v>
+        <v>8.7320163491517153E-4</v>
       </c>
       <c r="J12">
-        <v>-1.0574363652000266E-3</v>
+        <v>3.3059402744976462E-3</v>
       </c>
       <c r="K12">
-        <v>-1.1031736460954513E-3</v>
+        <v>4.4081159151507024E-3</v>
       </c>
       <c r="L12">
-        <v>-1.2321033944326576E-3</v>
+        <v>4.5868831911670205E-3</v>
       </c>
       <c r="M12">
-        <v>1.8270483502629516E-3</v>
+        <v>2.7406391984675814E-3</v>
       </c>
       <c r="N12">
-        <v>1.1182534791166899E-3</v>
+        <v>6.2716865537271703E-4</v>
       </c>
       <c r="O12">
-        <v>6.5062221529567029E-4</v>
+        <v>4.1732682129020301E-5</v>
       </c>
       <c r="P12">
-        <v>7.4801487074346688E-4</v>
+        <v>6.6714407348064772E-4</v>
       </c>
       <c r="Q12">
-        <v>1.8150064821113531E-5</v>
+        <v>4.8985383672654672E-4</v>
       </c>
       <c r="R12">
-        <v>1.2064221123264341E-3</v>
+        <v>8.4729355973071907E-3</v>
       </c>
       <c r="S12">
-        <v>-2.4062783268692021E-4</v>
+        <v>-3.9968789002125263E-2</v>
       </c>
       <c r="T12">
-        <v>-6.8169546146573277E-4</v>
-      </c>
-      <c r="U12">
-        <v>4.1908342218757444E-3</v>
-      </c>
-      <c r="V12">
-        <v>-1.351217411376508E-3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.45">
+        <v>1.0233923159525492E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B13">
-        <v>-0.19847482200694386</v>
+        <v>-0.21271762331591532</v>
       </c>
       <c r="C13">
-        <v>-2.1360007519683209E-4</v>
+        <v>-2.9044547678024025E-4</v>
       </c>
       <c r="D13">
-        <v>2.6116226047795972E-6</v>
+        <v>3.9952425566370544E-6</v>
       </c>
       <c r="E13">
-        <v>1.8725887266969572E-4</v>
+        <v>1.5455746597154468E-3</v>
       </c>
       <c r="F13">
-        <v>4.8792858602404206E-4</v>
+        <v>3.7743330456551441E-3</v>
       </c>
       <c r="G13">
-        <v>6.267467877346954E-6</v>
+        <v>-2.7168035820493756E-5</v>
       </c>
       <c r="H13">
-        <v>3.6842275101691257E-6</v>
+        <v>-7.665068383258956E-5</v>
       </c>
       <c r="I13">
-        <v>-9.0858776315488562E-4</v>
+        <v>-1.1953480098399008E-5</v>
       </c>
       <c r="J13">
-        <v>-1.0571718624436742E-3</v>
+        <v>-5.5609508843391996E-4</v>
       </c>
       <c r="K13">
-        <v>-1.1397117037361499E-3</v>
+        <v>-8.9172638638251389E-4</v>
       </c>
       <c r="L13">
-        <v>-1.2512254646217667E-3</v>
+        <v>-1.0681460104759177E-3</v>
       </c>
       <c r="M13">
-        <v>1.1182534791166899E-3</v>
+        <v>6.2716865537271703E-4</v>
       </c>
       <c r="N13">
-        <v>3.3683438755707442E-3</v>
+        <v>1.2493878467098771E-3</v>
       </c>
       <c r="O13">
-        <v>6.2294898017937615E-4</v>
+        <v>-2.614811643676608E-5</v>
       </c>
       <c r="P13">
-        <v>7.4281589209324104E-4</v>
+        <v>-7.7252499261185303E-5</v>
       </c>
       <c r="Q13">
-        <v>1.2094670603611547E-5</v>
+        <v>-2.1406325106579954E-4</v>
       </c>
       <c r="R13">
-        <v>2.6933984859881053E-3</v>
+        <v>-2.1968277068782063E-3</v>
       </c>
       <c r="S13">
-        <v>-4.1507904617950353E-4</v>
+        <v>9.6168598505341728E-3</v>
       </c>
       <c r="T13">
-        <v>-8.8489101380520964E-4</v>
-      </c>
-      <c r="U13">
-        <v>3.9118650118738253E-3</v>
-      </c>
-      <c r="V13">
-        <v>-1.6797866840371082E-3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.45">
+        <v>-2.7205550790809908E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="B14">
-        <v>-2.8039147385485025E-3</v>
+        <v>0.33149340349755047</v>
       </c>
       <c r="C14">
-        <v>6.7007436290012043E-5</v>
+        <v>-1.4804344080751913E-5</v>
       </c>
       <c r="D14">
-        <v>-7.9323432294775308E-7</v>
+        <v>1.7884259920910494E-7</v>
       </c>
       <c r="E14">
-        <v>-5.5656860961452946E-5</v>
+        <v>-1.6012246434244195E-4</v>
       </c>
       <c r="F14">
-        <v>-8.8588823600110759E-5</v>
+        <v>4.1010163719783921E-5</v>
       </c>
       <c r="G14">
-        <v>-3.1522496561707523E-6</v>
+        <v>4.0337807550530996E-6</v>
       </c>
       <c r="H14">
-        <v>-3.9792124518817337E-6</v>
+        <v>-3.9783908999213959E-7</v>
       </c>
       <c r="I14">
-        <v>6.7028825939564418E-5</v>
+        <v>-1.7736100685240619E-4</v>
       </c>
       <c r="J14">
-        <v>1.4680517044961798E-4</v>
+        <v>-8.8716315285371604E-5</v>
       </c>
       <c r="K14">
-        <v>1.6540192691081348E-4</v>
+        <v>-3.0053455918003991E-5</v>
       </c>
       <c r="L14">
-        <v>2.5196717318878381E-4</v>
+        <v>-2.5572797711947569E-5</v>
       </c>
       <c r="M14">
-        <v>6.5062221529567029E-4</v>
+        <v>4.1732682129020301E-5</v>
       </c>
       <c r="N14">
-        <v>6.2294898017937615E-4</v>
+        <v>-2.614811643676608E-5</v>
       </c>
       <c r="O14">
-        <v>1.4466114539657248E-3</v>
+        <v>1.0670707105023521E-3</v>
       </c>
       <c r="P14">
-        <v>7.7277893388397732E-4</v>
+        <v>-9.2615969271980531E-4</v>
       </c>
       <c r="Q14">
-        <v>4.5117756285089599E-6</v>
+        <v>6.2115852264935244E-5</v>
       </c>
       <c r="R14">
-        <v>-9.7824641992792023E-4</v>
+        <v>1.0421874683790245E-5</v>
       </c>
       <c r="S14">
-        <v>1.0957233009678633E-4</v>
+        <v>1.1971924493168846E-3</v>
       </c>
       <c r="T14">
-        <v>2.2806369012781715E-4</v>
-      </c>
-      <c r="U14">
-        <v>-1.9282376813378054E-3</v>
-      </c>
-      <c r="V14">
-        <v>5.3514325010901496E-4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.45">
+        <v>-1.3371584209408589E-4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="B15">
-        <v>-6.1505877395688503E-2</v>
+        <v>0.8117378572031746</v>
       </c>
       <c r="C15">
-        <v>1.850901370848642E-7</v>
+        <v>2.6058364040966117E-4</v>
       </c>
       <c r="D15">
-        <v>-8.2744893217838418E-9</v>
+        <v>-2.8279888469960352E-6</v>
       </c>
       <c r="E15">
-        <v>-2.3943494467838302E-5</v>
+        <v>1.355569620648582E-4</v>
       </c>
       <c r="F15">
-        <v>3.9479249936121684E-5</v>
+        <v>-3.2386001734238438E-3</v>
       </c>
       <c r="G15">
-        <v>-9.5672012432598871E-7</v>
+        <v>-7.3659072505228471E-6</v>
       </c>
       <c r="H15">
-        <v>-1.6418138085716725E-6</v>
+        <v>3.6721636334114907E-5</v>
       </c>
       <c r="I15">
-        <v>2.2030414203348443E-5</v>
+        <v>-1.1402777112008234E-3</v>
       </c>
       <c r="J15">
-        <v>6.3915464237709039E-5</v>
+        <v>-2.131734247621332E-3</v>
       </c>
       <c r="K15">
-        <v>9.2895449377482841E-5</v>
+        <v>-1.8013649904540384E-3</v>
       </c>
       <c r="L15">
-        <v>1.3666586484161879E-4</v>
+        <v>-2.0426300503802635E-3</v>
       </c>
       <c r="M15">
-        <v>7.4801487074346688E-4</v>
+        <v>6.6714407348064772E-4</v>
       </c>
       <c r="N15">
-        <v>7.4281589209324104E-4</v>
+        <v>-7.7252499261185303E-5</v>
       </c>
       <c r="O15">
-        <v>7.7277893388397732E-4</v>
+        <v>-9.2615969271980531E-4</v>
       </c>
       <c r="P15">
-        <v>1.3800441039014703E-3</v>
+        <v>0.27617475264470925</v>
       </c>
       <c r="Q15">
-        <v>1.5554794786081872E-5</v>
+        <v>-7.2633618544547893E-3</v>
       </c>
       <c r="R15">
-        <v>1.0681945987410578E-4</v>
+        <v>-2.8504711963138929E-4</v>
       </c>
       <c r="S15">
-        <v>-5.8708703395426678E-6</v>
+        <v>-0.27701871732340788</v>
       </c>
       <c r="T15">
-        <v>9.3353140351223857E-6</v>
-      </c>
-      <c r="U15">
-        <v>-1.0406581705662919E-3</v>
-      </c>
-      <c r="V15">
-        <v>7.9087015533610582E-5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.45">
+        <v>1.6750707901950709E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B16">
-        <v>0.22638519924772518</v>
+        <v>4.3550871333755771E-2</v>
       </c>
       <c r="C16">
-        <v>-2.4740028022701483E-5</v>
+        <v>7.200729730301328E-4</v>
       </c>
       <c r="D16">
-        <v>2.8089554223575157E-7</v>
+        <v>-1.0010809839111577E-5</v>
       </c>
       <c r="E16">
-        <v>-1.1959580129725287E-4</v>
+        <v>-4.0592051832003314E-3</v>
       </c>
       <c r="F16">
-        <v>-1.5371132259709943E-4</v>
+        <v>-9.4099951898566035E-3</v>
       </c>
       <c r="G16">
-        <v>3.0251054641463584E-6</v>
+        <v>6.6020537148401342E-5</v>
       </c>
       <c r="H16">
-        <v>3.8730051560912073E-6</v>
+        <v>1.7520697002402873E-4</v>
       </c>
       <c r="I16">
-        <v>-1.1308127289165649E-4</v>
+        <v>1.1852506880836919E-4</v>
       </c>
       <c r="J16">
-        <v>-9.8027294940902283E-5</v>
+        <v>1.8684618801026072E-3</v>
       </c>
       <c r="K16">
-        <v>-1.3968121930578919E-4</v>
+        <v>2.55215395507626E-3</v>
       </c>
       <c r="L16">
-        <v>-1.1999188326779785E-4</v>
+        <v>2.7024253703038146E-3</v>
       </c>
       <c r="M16">
-        <v>1.8150064821113531E-5</v>
+        <v>4.8985383672654672E-4</v>
       </c>
       <c r="N16">
-        <v>1.2094670603611547E-5</v>
+        <v>-2.1406325106579954E-4</v>
       </c>
       <c r="O16">
-        <v>4.5117756285089599E-6</v>
+        <v>6.2115852264935244E-5</v>
       </c>
       <c r="P16">
-        <v>1.5554794786081872E-5</v>
+        <v>-7.2633618544547893E-3</v>
       </c>
       <c r="Q16">
-        <v>8.0485541134912917E-4</v>
+        <v>3.7622209003527413E-3</v>
       </c>
       <c r="R16">
-        <v>9.8119311318216481E-4</v>
+        <v>5.9654795575832462E-3</v>
       </c>
       <c r="S16">
-        <v>-1.1216893719790134E-4</v>
+        <v>-1.8561449755838601E-2</v>
       </c>
       <c r="T16">
-        <v>-8.3860062582489036E-5</v>
-      </c>
-      <c r="U16">
-        <v>-2.8717662976465426E-4</v>
-      </c>
-      <c r="V16">
-        <v>-1.8943193793154417E-4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.45">
+        <v>6.7769742737547435E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B17">
-        <v>0.14201612750564807</v>
+        <v>-6.0060539511240275E-2</v>
       </c>
       <c r="C17">
-        <v>-3.8238617730593032E-4</v>
+        <v>1.1985530162859139E-2</v>
       </c>
       <c r="D17">
-        <v>5.1241338089540094E-6</v>
+        <v>-1.6572941647627175E-4</v>
       </c>
       <c r="E17">
-        <v>-1.8748297432304904E-4</v>
+        <v>-6.8407900016870166E-2</v>
       </c>
       <c r="F17">
-        <v>-2.051110400056282E-3</v>
+        <v>-0.1559727397196512</v>
       </c>
       <c r="G17">
-        <v>1.2364215652430843E-5</v>
+        <v>1.1240928838363129E-3</v>
       </c>
       <c r="H17">
-        <v>3.6942521814441489E-5</v>
+        <v>2.9002934541726079E-3</v>
       </c>
       <c r="I17">
-        <v>2.8881097458283199E-3</v>
+        <v>6.4431993160991522E-3</v>
       </c>
       <c r="J17">
-        <v>2.3448777804044138E-3</v>
+        <v>3.4270333625740904E-2</v>
       </c>
       <c r="K17">
-        <v>2.9874743074261301E-3</v>
+        <v>4.6456013976223259E-2</v>
       </c>
       <c r="L17">
-        <v>2.5315197087920674E-3</v>
+        <v>4.9262113547301777E-2</v>
       </c>
       <c r="M17">
-        <v>1.2064221123264341E-3</v>
+        <v>8.4729355973071907E-3</v>
       </c>
       <c r="N17">
-        <v>2.6933984859881053E-3</v>
+        <v>-2.1968277068782063E-3</v>
       </c>
       <c r="O17">
-        <v>-9.7824641992792023E-4</v>
+        <v>1.0421874683790245E-5</v>
       </c>
       <c r="P17">
-        <v>1.0681945987410578E-4</v>
+        <v>-2.8504711963138929E-4</v>
       </c>
       <c r="Q17">
-        <v>9.8119311318216481E-4</v>
+        <v>5.9654795575832462E-3</v>
       </c>
       <c r="R17">
-        <v>1.0144047046431655</v>
+        <v>9.5233546156560836E-2</v>
       </c>
       <c r="S17">
-        <v>-4.7135620688310509E-2</v>
+        <v>-0.43158441294531047</v>
       </c>
       <c r="T17">
-        <v>-7.9902379597508507E-3</v>
-      </c>
-      <c r="U17">
-        <v>-0.99812461564508381</v>
-      </c>
-      <c r="V17">
-        <v>-3.5179069176411999E-3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.45">
+        <v>0.11439786779995534</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B18">
-        <v>-0.18062406896603223</v>
+        <v>3.08483115769122</v>
       </c>
       <c r="C18">
-        <v>1.2999972952604054E-4</v>
+        <v>-5.737608421471091E-2</v>
       </c>
       <c r="D18">
-        <v>-1.6162160863925796E-6</v>
+        <v>7.8522209373004361E-4</v>
       </c>
       <c r="E18">
-        <v>-8.0600599087710247E-5</v>
+        <v>0.30124604915231246</v>
       </c>
       <c r="F18">
-        <v>-2.8195107445244433E-4</v>
+        <v>0.72103871899001937</v>
       </c>
       <c r="G18">
-        <v>-3.4865252881937108E-6</v>
+        <v>-4.8352202094266196E-3</v>
       </c>
       <c r="H18">
-        <v>-2.9336995718296662E-7</v>
+        <v>-1.3347358877538382E-2</v>
       </c>
       <c r="I18">
-        <v>3.1064610612354499E-4</v>
+        <v>-6.9270592836314038E-2</v>
       </c>
       <c r="J18">
-        <v>4.4188724903328896E-4</v>
+        <v>-0.19698969867778937</v>
       </c>
       <c r="K18">
-        <v>6.565299668557182E-4</v>
+        <v>-0.25334395825394951</v>
       </c>
       <c r="L18">
-        <v>7.5624436370591585E-4</v>
+        <v>-0.26667026506727448</v>
       </c>
       <c r="M18">
-        <v>-2.4062783268692021E-4</v>
+        <v>-3.9968789002125263E-2</v>
       </c>
       <c r="N18">
-        <v>-4.1507904617950353E-4</v>
+        <v>9.6168598505341728E-3</v>
       </c>
       <c r="O18">
-        <v>1.0957233009678633E-4</v>
+        <v>1.1971924493168846E-3</v>
       </c>
       <c r="P18">
-        <v>-5.8708703395426678E-6</v>
+        <v>-0.27701871732340788</v>
       </c>
       <c r="Q18">
-        <v>-1.1216893719790134E-4</v>
+        <v>-1.8561449755838601E-2</v>
       </c>
       <c r="R18">
-        <v>-4.7135620688310509E-2</v>
+        <v>-0.43158441294531047</v>
       </c>
       <c r="S18">
-        <v>4.6658772898475641E-3</v>
+        <v>2.3483916259861988</v>
       </c>
       <c r="T18">
-        <v>1.0289481561818355E-3</v>
-      </c>
-      <c r="U18">
-        <v>4.2181682727426284E-2</v>
-      </c>
-      <c r="V18">
-        <v>1.0171249859269745E-3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.45">
+        <v>-0.52722657768765446</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B19">
-        <v>0.2011207480003466</v>
+        <v>-0.53536462599711887</v>
       </c>
       <c r="C19">
-        <v>3.8183766205598235E-4</v>
+        <v>1.4594643561502252E-2</v>
       </c>
       <c r="D19">
-        <v>-4.8521421125753751E-6</v>
+        <v>-2.0144398707996807E-4</v>
       </c>
       <c r="E19">
-        <v>-5.4369636128645494E-4</v>
+        <v>-8.2752379177145674E-2</v>
       </c>
       <c r="F19">
-        <v>-1.5058002440121805E-3</v>
+        <v>-0.18919198933201503</v>
       </c>
       <c r="G19">
-        <v>-6.2647933874519696E-6</v>
+        <v>1.3531557838357075E-3</v>
       </c>
       <c r="H19">
-        <v>4.6701889924085084E-6</v>
+        <v>3.5094267267490775E-3</v>
       </c>
       <c r="I19">
-        <v>1.7018835840419834E-3</v>
+        <v>7.812179491004238E-3</v>
       </c>
       <c r="J19">
-        <v>2.1026754193476218E-3</v>
+        <v>4.1721895725155597E-2</v>
       </c>
       <c r="K19">
-        <v>2.2895906071473153E-3</v>
+        <v>5.6576876983002775E-2</v>
       </c>
       <c r="L19">
-        <v>2.4504579611552644E-3</v>
+        <v>6.006658768955999E-2</v>
       </c>
       <c r="M19">
-        <v>-6.8169546146573277E-4</v>
+        <v>1.0233923159525492E-2</v>
       </c>
       <c r="N19">
-        <v>-8.8489101380520964E-4</v>
+        <v>-2.7205550790809908E-3</v>
       </c>
       <c r="O19">
-        <v>2.2806369012781715E-4</v>
+        <v>-1.3371584209408589E-4</v>
       </c>
       <c r="P19">
-        <v>9.3353140351223857E-6</v>
+        <v>1.6750707901950709E-3</v>
       </c>
       <c r="Q19">
-        <v>-8.3860062582489036E-5</v>
+        <v>6.7769742737547435E-3</v>
       </c>
       <c r="R19">
-        <v>-7.9902379597508507E-3</v>
+        <v>0.11439786779995534</v>
       </c>
       <c r="S19">
-        <v>1.0289481561818355E-3</v>
+        <v>-0.52722657768765446</v>
       </c>
       <c r="T19">
-        <v>2.6286196956847091E-3</v>
-      </c>
-      <c r="U19">
-        <v>-5.6574496396115514E-3</v>
-      </c>
-      <c r="V19">
-        <v>3.2641922777059619E-3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
-        <v>31</v>
-      </c>
-      <c r="B20">
-        <v>1.4666441633260661</v>
-      </c>
-      <c r="C20">
-        <v>-4.4001154657403816E-3</v>
-      </c>
-      <c r="D20">
-        <v>5.1068068989269206E-5</v>
-      </c>
-      <c r="E20">
-        <v>-4.8929467061598619E-3</v>
-      </c>
-      <c r="F20">
-        <v>8.8085569933950437E-3</v>
-      </c>
-      <c r="G20">
-        <v>2.8645474604507663E-4</v>
-      </c>
-      <c r="H20">
-        <v>1.0943763645504119E-4</v>
-      </c>
-      <c r="I20">
-        <v>-0.10692744616444759</v>
-      </c>
-      <c r="J20">
-        <v>-0.10919714688044999</v>
-      </c>
-      <c r="K20">
-        <v>-0.11156476857144779</v>
-      </c>
-      <c r="L20">
-        <v>-0.11360098510254368</v>
-      </c>
-      <c r="M20">
-        <v>4.1908342218757444E-3</v>
-      </c>
-      <c r="N20">
-        <v>3.9118650118738253E-3</v>
-      </c>
-      <c r="O20">
-        <v>-1.9282376813378054E-3</v>
-      </c>
-      <c r="P20">
-        <v>-1.0406581705662919E-3</v>
-      </c>
-      <c r="Q20">
-        <v>-2.8717662976465426E-4</v>
-      </c>
-      <c r="R20">
-        <v>-0.99812461564508381</v>
-      </c>
-      <c r="S20">
-        <v>4.2181682727426284E-2</v>
-      </c>
-      <c r="T20">
-        <v>-5.6574496396115514E-3</v>
-      </c>
-      <c r="U20">
-        <v>1.2211123254787692</v>
-      </c>
-      <c r="V20">
-        <v>-2.4737473280106677E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
-        <v>32</v>
-      </c>
-      <c r="B21">
-        <v>-8.0415068536276321E-2</v>
-      </c>
-      <c r="C21">
-        <v>7.9591477924982894E-4</v>
-      </c>
-      <c r="D21">
-        <v>-9.7768939686272123E-6</v>
-      </c>
-      <c r="E21">
-        <v>-9.9873072646448641E-4</v>
-      </c>
-      <c r="F21">
-        <v>-2.8778994419941971E-3</v>
-      </c>
-      <c r="G21">
-        <v>-1.9206655342458081E-5</v>
-      </c>
-      <c r="H21">
-        <v>-3.4499374508852628E-6</v>
-      </c>
-      <c r="I21">
-        <v>3.8280020027675328E-3</v>
-      </c>
-      <c r="J21">
-        <v>4.513835269719357E-3</v>
-      </c>
-      <c r="K21">
-        <v>4.9240621591487644E-3</v>
-      </c>
-      <c r="L21">
-        <v>5.426156981275224E-3</v>
-      </c>
-      <c r="M21">
-        <v>-1.351217411376508E-3</v>
-      </c>
-      <c r="N21">
-        <v>-1.6797866840371082E-3</v>
-      </c>
-      <c r="O21">
-        <v>5.3514325010901496E-4</v>
-      </c>
-      <c r="P21">
-        <v>7.9087015533610582E-5</v>
-      </c>
-      <c r="Q21">
-        <v>-1.8943193793154417E-4</v>
-      </c>
-      <c r="R21">
-        <v>-3.5179069176411999E-3</v>
-      </c>
-      <c r="S21">
-        <v>1.0171249859269745E-3</v>
-      </c>
-      <c r="T21">
-        <v>3.2641922777059619E-3</v>
-      </c>
-      <c r="U21">
-        <v>-2.4737473280106677E-2</v>
-      </c>
-      <c r="V21">
-        <v>6.6293679132419453E-3</v>
+        <v>0.13907650682396772</v>
       </c>
     </row>
   </sheetData>
@@ -2056,15 +1798,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3490A41A-6D87-4B5B-B2D0-88E95CB6FBA7}">
-  <dimension ref="A1:V21"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="25.3984375" style="3" customWidth="1"/>
-    <col min="2" max="16384" width="8.796875" style="3"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50576196-A00C-4289-8DCD-5A0DA898FED9}">
+  <dimension ref="A1:T19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -2102,1394 +1840,1144 @@
         <v>26</v>
       </c>
       <c r="M1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="P1" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="Q1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="R1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="S1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="T1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U1" t="s">
-        <v>31</v>
-      </c>
-      <c r="V1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>17</v>
       </c>
       <c r="B2">
-        <v>-2.9669433051061064E-2</v>
+        <v>2.5127462245898651E-3</v>
       </c>
       <c r="C2">
-        <v>3.9081627803521984E-4</v>
+        <v>2.7748835388063844E-4</v>
       </c>
       <c r="D2">
-        <v>-4.4090162002385397E-6</v>
+        <v>-3.3324849127577872E-6</v>
       </c>
       <c r="E2">
-        <v>1.3281992412589587E-3</v>
+        <v>1.3631435674891671E-4</v>
       </c>
       <c r="F2">
-        <v>9.9990881479170121E-4</v>
+        <v>-5.6870974876604692E-4</v>
       </c>
       <c r="G2">
-        <v>-3.538218719325758E-5</v>
+        <v>-5.5268156814191701E-6</v>
       </c>
       <c r="H2">
-        <v>-3.1486079503783646E-5</v>
+        <v>9.6920791057027229E-6</v>
       </c>
       <c r="I2">
-        <v>5.5639976230833252E-4</v>
+        <v>1.0561344541365939E-4</v>
       </c>
       <c r="J2">
-        <v>1.1675637912848015E-3</v>
+        <v>6.4197337521054363E-4</v>
       </c>
       <c r="K2">
-        <v>1.3869164121795507E-3</v>
+        <v>9.2662885093503118E-4</v>
       </c>
       <c r="L2">
-        <v>1.4345653258132879E-3</v>
+        <v>9.8025014067982521E-4</v>
       </c>
       <c r="M2">
-        <v>-2.6373133297332026E-4</v>
+        <v>2.1497684596107915E-4</v>
       </c>
       <c r="N2">
-        <v>-3.4561764356110436E-4</v>
+        <v>4.5933834910929559E-5</v>
       </c>
       <c r="O2">
-        <v>7.1041371454418236E-5</v>
+        <v>1.0518163849015625E-5</v>
       </c>
       <c r="P2">
-        <v>-7.4514739287516376E-5</v>
+        <v>1.6843542501061669E-4</v>
       </c>
       <c r="Q2">
-        <v>-4.0069415354043638E-5</v>
+        <v>-4.1953484894838145E-5</v>
       </c>
       <c r="R2">
-        <v>1.0178535903602043E-3</v>
+        <v>1.2405635695656668E-3</v>
       </c>
       <c r="S2">
-        <v>3.2956356521372985E-5</v>
+        <v>-8.570547031350512E-3</v>
       </c>
       <c r="T2">
-        <v>8.9855585784334529E-4</v>
-      </c>
-      <c r="U2">
-        <v>-1.233507789616157E-2</v>
-      </c>
-      <c r="V2">
-        <v>1.7378040542857525E-3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.45">
+        <v>1.4074107075818551E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>18</v>
       </c>
       <c r="B3">
-        <v>6.9275212565199828E-4</v>
+        <v>2.5913962210028174E-4</v>
       </c>
       <c r="C3">
-        <v>-4.4090162002385397E-6</v>
+        <v>-3.3324849127577872E-6</v>
       </c>
       <c r="D3">
-        <v>5.0594339158211628E-8</v>
+        <v>4.0683720646060523E-8</v>
       </c>
       <c r="E3">
-        <v>-1.2246621300320244E-5</v>
+        <v>5.2026049931435371E-7</v>
       </c>
       <c r="F3">
-        <v>-8.4501949221243826E-6</v>
+        <v>9.0814761644902768E-6</v>
       </c>
       <c r="G3">
-        <v>3.3302845748964256E-7</v>
+        <v>1.5250843002349512E-8</v>
       </c>
       <c r="H3">
-        <v>2.8744642199376778E-7</v>
+        <v>-1.6947886864624435E-7</v>
       </c>
       <c r="I3">
-        <v>-6.4335519140185978E-6</v>
+        <v>-1.2407835389964187E-6</v>
       </c>
       <c r="J3">
-        <v>-1.3353152540078492E-5</v>
+        <v>-7.7982017480690892E-6</v>
       </c>
       <c r="K3">
-        <v>-1.5790325323833678E-5</v>
+        <v>-1.1313881764555874E-5</v>
       </c>
       <c r="L3">
-        <v>-1.6265507169830022E-5</v>
+        <v>-1.1842316719569018E-5</v>
       </c>
       <c r="M3">
-        <v>2.9691023313931107E-6</v>
+        <v>-2.6403254197563478E-6</v>
       </c>
       <c r="N3">
-        <v>3.9225620470159594E-6</v>
+        <v>-5.6451543300086549E-7</v>
       </c>
       <c r="O3">
-        <v>-7.9851759209663876E-7</v>
+        <v>-1.0248032972903987E-7</v>
       </c>
       <c r="P3">
-        <v>8.2171609349213053E-7</v>
+        <v>-2.6114238761758571E-6</v>
       </c>
       <c r="Q3">
-        <v>4.5786965271716905E-7</v>
+        <v>4.7166859904195512E-7</v>
       </c>
       <c r="R3">
-        <v>-1.1835931006264559E-5</v>
+        <v>-1.5420111237877472E-5</v>
       </c>
       <c r="S3">
-        <v>-3.5181683395019974E-7</v>
+        <v>1.0311026181843879E-4</v>
       </c>
       <c r="T3">
-        <v>-1.0374106540976592E-5</v>
-      </c>
-      <c r="U3">
-        <v>1.3839164502240899E-4</v>
-      </c>
-      <c r="V3">
-        <v>-1.9841065727807784E-5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.45">
+        <v>-1.7350715294664254E-5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>19</v>
       </c>
       <c r="B4">
-        <v>0.14504045343199626</v>
+        <v>0.21582595774689969</v>
       </c>
       <c r="C4">
-        <v>1.3281992412589587E-3</v>
+        <v>1.3631435674891671E-4</v>
       </c>
       <c r="D4">
-        <v>-1.2246621300320244E-5</v>
+        <v>5.2026049931435371E-7</v>
       </c>
       <c r="E4">
-        <v>1.8234957794154412E-2</v>
+        <v>1.1441421119287141E-2</v>
       </c>
       <c r="F4">
-        <v>1.3769353347883331E-2</v>
+        <v>8.0736310493190692E-3</v>
       </c>
       <c r="G4">
-        <v>-4.2632374621440829E-4</v>
+        <v>-2.5648088596351892E-4</v>
       </c>
       <c r="H4">
-        <v>-3.3067013684280811E-4</v>
+        <v>-1.7776606959697875E-4</v>
       </c>
       <c r="I4">
-        <v>1.5221934197969514E-3</v>
+        <v>-1.2872891285415431E-5</v>
       </c>
       <c r="J4">
-        <v>3.242490434337753E-3</v>
+        <v>-1.0576185808446249E-4</v>
       </c>
       <c r="K4">
-        <v>3.8336879372775183E-3</v>
+        <v>-5.4367431124542642E-4</v>
       </c>
       <c r="L4">
-        <v>3.9892822878292138E-3</v>
+        <v>-6.278625932808824E-4</v>
       </c>
       <c r="M4">
-        <v>-8.0969661463702416E-4</v>
+        <v>-2.8838163065442879E-4</v>
       </c>
       <c r="N4">
-        <v>-1.0002781621347794E-3</v>
+        <v>-8.4626545141067703E-5</v>
       </c>
       <c r="O4">
-        <v>1.6447298587878571E-4</v>
+        <v>-1.9242775027066741E-5</v>
       </c>
       <c r="P4">
-        <v>-3.0494613737578924E-4</v>
+        <v>-3.0596535177101363E-3</v>
       </c>
       <c r="Q4">
-        <v>-3.1121627742052526E-4</v>
+        <v>-6.6937624251879558E-5</v>
       </c>
       <c r="R4">
-        <v>5.2315677125590451E-4</v>
+        <v>-1.2172986872614404E-3</v>
       </c>
       <c r="S4">
-        <v>7.8714768903603974E-5</v>
+        <v>-1.5496999104447735E-3</v>
       </c>
       <c r="T4">
-        <v>2.4994528145818669E-3</v>
-      </c>
-      <c r="U4">
-        <v>-4.2678044263341978E-2</v>
-      </c>
-      <c r="V4">
-        <v>4.7002637835900076E-3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.45">
+        <v>-1.2936357530068492E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>20</v>
       </c>
       <c r="B5">
-        <v>0.18721283302142613</v>
+        <v>-3.8850618958616037E-2</v>
       </c>
       <c r="C5">
-        <v>9.9990881479170121E-4</v>
+        <v>-5.6870974876604692E-4</v>
       </c>
       <c r="D5">
-        <v>-8.4501949221243826E-6</v>
+        <v>9.0814761644902768E-6</v>
       </c>
       <c r="E5">
-        <v>1.3769353347883331E-2</v>
+        <v>8.0736310493190692E-3</v>
       </c>
       <c r="F5">
-        <v>2.0493805313787885E-2</v>
+        <v>2.1989312511112431E-2</v>
       </c>
       <c r="G5">
-        <v>-3.181360082471566E-4</v>
+        <v>-1.7353348651210406E-4</v>
       </c>
       <c r="H5">
-        <v>-4.6587706113753336E-4</v>
+        <v>-4.5255240752942801E-4</v>
       </c>
       <c r="I5">
-        <v>-1.36609577614722E-4</v>
+        <v>2.8899445579537198E-4</v>
       </c>
       <c r="J5">
-        <v>1.0928958375391613E-3</v>
+        <v>-1.2630953105413688E-3</v>
       </c>
       <c r="K5">
-        <v>1.4885454725493542E-3</v>
+        <v>-2.5595966128751225E-3</v>
       </c>
       <c r="L5">
-        <v>1.6517948896749754E-3</v>
+        <v>-2.5967410587245734E-3</v>
       </c>
       <c r="M5">
-        <v>-7.0968306316874282E-4</v>
+        <v>-8.2826277553677376E-4</v>
       </c>
       <c r="N5">
-        <v>-8.9583803321836289E-4</v>
+        <v>-1.8278986326392783E-4</v>
       </c>
       <c r="O5">
-        <v>2.0106389131541516E-4</v>
+        <v>-1.9204225358828252E-5</v>
       </c>
       <c r="P5">
-        <v>-2.3246087189905426E-4</v>
+        <v>-2.2530209495521961E-3</v>
       </c>
       <c r="Q5">
-        <v>-3.329510704714162E-4</v>
+        <v>4.9376188440896489E-5</v>
       </c>
       <c r="R5">
-        <v>2.2307657966652958E-3</v>
+        <v>-3.9396196655281943E-3</v>
       </c>
       <c r="S5">
-        <v>-1.4138094750184623E-5</v>
+        <v>1.7605925671066544E-2</v>
       </c>
       <c r="T5">
-        <v>1.7667635796654849E-3</v>
-      </c>
-      <c r="U5">
-        <v>-3.407189062287648E-2</v>
-      </c>
-      <c r="V5">
-        <v>3.4514272779636707E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.45">
+        <v>-4.3650915803165585E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>21</v>
       </c>
       <c r="B6">
-        <v>-1.23299551377318E-2</v>
+        <v>-1.0899632130149817E-2</v>
       </c>
       <c r="C6">
-        <v>-3.538218719325758E-5</v>
+        <v>-5.5268156814191701E-6</v>
       </c>
       <c r="D6">
-        <v>3.3302845748964256E-7</v>
+        <v>1.5250843002349512E-8</v>
       </c>
       <c r="E6">
-        <v>-4.2632374621440829E-4</v>
+        <v>-2.5648088596351892E-4</v>
       </c>
       <c r="F6">
-        <v>-3.181360082471566E-4</v>
+        <v>-1.7353348651210406E-4</v>
       </c>
       <c r="G6">
-        <v>1.0795289941747121E-5</v>
+        <v>6.2596423465046498E-6</v>
       </c>
       <c r="H6">
-        <v>8.284040416473615E-6</v>
+        <v>4.1729434196563425E-6</v>
       </c>
       <c r="I6">
-        <v>-4.5043453403720651E-5</v>
+        <v>-1.7286528364508946E-6</v>
       </c>
       <c r="J6">
-        <v>-9.3212306797243522E-5</v>
+        <v>-5.0707707943149171E-6</v>
       </c>
       <c r="K6">
-        <v>-1.0826356545556584E-4</v>
+        <v>2.3049311295244433E-6</v>
       </c>
       <c r="L6">
-        <v>-1.1182664198758501E-4</v>
+        <v>5.0513350275245179E-6</v>
       </c>
       <c r="M6">
-        <v>2.1489722676526881E-5</v>
+        <v>1.9568236707160843E-6</v>
       </c>
       <c r="N6">
-        <v>2.7138390148315107E-5</v>
+        <v>-9.7290110017780979E-7</v>
       </c>
       <c r="O6">
-        <v>-5.040817583620771E-6</v>
+        <v>4.3194328451470078E-7</v>
       </c>
       <c r="P6">
-        <v>7.2214226431414631E-6</v>
+        <v>7.0205098390055932E-5</v>
       </c>
       <c r="Q6">
-        <v>8.4572136529967825E-6</v>
+        <v>2.1085908034808625E-6</v>
       </c>
       <c r="R6">
-        <v>-2.4766365197365221E-5</v>
+        <v>1.5494854214498646E-5</v>
       </c>
       <c r="S6">
-        <v>-2.0059177052181282E-6</v>
+        <v>1.0450543691211028E-4</v>
       </c>
       <c r="T6">
-        <v>-7.1055525657525066E-5</v>
-      </c>
-      <c r="U6">
-        <v>1.1259234136053887E-3</v>
-      </c>
-      <c r="V6">
-        <v>-1.33190021725481E-4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.45">
+        <v>1.5025751432026607E-5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>22</v>
       </c>
       <c r="B7">
-        <v>-1.6268975160127111E-2</v>
+        <v>-7.7668961658768536E-3</v>
       </c>
       <c r="C7">
-        <v>-3.1486079503783646E-5</v>
+        <v>9.6920791057027229E-6</v>
       </c>
       <c r="D7">
-        <v>2.8744642199376778E-7</v>
+        <v>-1.6947886864624435E-7</v>
       </c>
       <c r="E7">
-        <v>-3.3067013684280811E-4</v>
+        <v>-1.7776606959697875E-4</v>
       </c>
       <c r="F7">
-        <v>-4.6587706113753336E-4</v>
+        <v>-4.5255240752942801E-4</v>
       </c>
       <c r="G7">
-        <v>8.284040416473615E-6</v>
+        <v>4.1729434196563425E-6</v>
       </c>
       <c r="H7">
-        <v>1.1630355764769475E-5</v>
+        <v>9.9711395295159268E-6</v>
       </c>
       <c r="I7">
-        <v>-4.8974518579546894E-6</v>
+        <v>-8.657659271289689E-6</v>
       </c>
       <c r="J7">
-        <v>-4.8937729878632314E-5</v>
+        <v>1.7500056446864898E-5</v>
       </c>
       <c r="K7">
-        <v>-6.0650401049983401E-5</v>
+        <v>4.5292331258585327E-5</v>
       </c>
       <c r="L7">
-        <v>-6.3695924668608561E-5</v>
+        <v>4.7953768517520272E-5</v>
       </c>
       <c r="M7">
-        <v>1.9545271264859205E-5</v>
+        <v>9.9807757276566834E-6</v>
       </c>
       <c r="N7">
-        <v>2.5494989094964224E-5</v>
+        <v>-1.9137562342516396E-6</v>
       </c>
       <c r="O7">
-        <v>-6.2740710132694839E-6</v>
+        <v>4.48477012650032E-7</v>
       </c>
       <c r="P7">
-        <v>6.5863261958690026E-6</v>
+        <v>4.5234699321788291E-5</v>
       </c>
       <c r="Q7">
-        <v>8.7131140757192834E-6</v>
+        <v>6.865873835269971E-7</v>
       </c>
       <c r="R7">
-        <v>-5.4063141510708385E-5</v>
+        <v>7.4291131670276147E-5</v>
       </c>
       <c r="S7">
-        <v>-1.3074468063656592E-6</v>
+        <v>-2.9871973342737685E-4</v>
       </c>
       <c r="T7">
-        <v>-6.2632347463372669E-5</v>
-      </c>
-      <c r="U7">
-        <v>1.0200372494442761E-3</v>
-      </c>
-      <c r="V7">
-        <v>-1.239755230482082E-4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.45">
+        <v>8.0189668780557464E-5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>23</v>
       </c>
       <c r="B8">
-        <v>-0.39641428648557525</v>
+        <v>-6.4871421494279408E-2</v>
       </c>
       <c r="C8">
-        <v>5.5639976230833252E-4</v>
+        <v>1.0561344541365939E-4</v>
       </c>
       <c r="D8">
-        <v>-6.4335519140185978E-6</v>
+        <v>-1.2407835389964187E-6</v>
       </c>
       <c r="E8">
-        <v>1.5221934197969514E-3</v>
+        <v>-1.2872891285415431E-5</v>
       </c>
       <c r="F8">
-        <v>-1.36609577614722E-4</v>
+        <v>2.8899445579537198E-4</v>
       </c>
       <c r="G8">
-        <v>-4.5043453403720651E-5</v>
+        <v>-1.7286528364508946E-6</v>
       </c>
       <c r="H8">
-        <v>-4.8974518579546894E-6</v>
+        <v>-8.657659271289689E-6</v>
       </c>
       <c r="I8">
-        <v>7.8527449118659262E-2</v>
+        <v>3.6838329458069821E-2</v>
       </c>
       <c r="J8">
-        <v>7.0583155696546551E-2</v>
+        <v>2.6982688234631805E-2</v>
       </c>
       <c r="K8">
-        <v>7.1071168061882489E-2</v>
+        <v>2.7144731888682428E-2</v>
       </c>
       <c r="L8">
-        <v>7.1200654185635745E-2</v>
+        <v>2.7174435480453396E-2</v>
       </c>
       <c r="M8">
-        <v>-6.359701777776366E-4</v>
+        <v>-5.2732091900800483E-5</v>
       </c>
       <c r="N8">
-        <v>-7.6042543741273896E-4</v>
+        <v>-3.0048358953967781E-5</v>
       </c>
       <c r="O8">
-        <v>-1.5474673756698984E-4</v>
+        <v>1.6130929207926111E-4</v>
       </c>
       <c r="P8">
-        <v>-2.0961243839632041E-4</v>
+        <v>-2.3375785261367282E-4</v>
       </c>
       <c r="Q8">
-        <v>6.3319631257792208E-5</v>
+        <v>1.0804142710852199E-4</v>
       </c>
       <c r="R8">
-        <v>1.9975789608798855E-3</v>
+        <v>6.7538450528769407E-4</v>
       </c>
       <c r="S8">
-        <v>-2.3261887349925971E-4</v>
+        <v>-3.0076044732591609E-2</v>
       </c>
       <c r="T8">
-        <v>1.9202472109283333E-3</v>
-      </c>
-      <c r="U8">
-        <v>-8.7952893035028373E-2</v>
-      </c>
-      <c r="V8">
-        <v>3.3520492765034631E-3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.45">
+        <v>7.4210306867237294E-4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>24</v>
       </c>
       <c r="B9">
-        <v>-0.30849427442773475</v>
+        <v>-0.36807389269005519</v>
       </c>
       <c r="C9">
-        <v>1.1675637912848015E-3</v>
+        <v>6.4197337521054363E-4</v>
       </c>
       <c r="D9">
-        <v>-1.3353152540078492E-5</v>
+        <v>-7.7982017480690892E-6</v>
       </c>
       <c r="E9">
-        <v>3.242490434337753E-3</v>
+        <v>-1.0576185808446249E-4</v>
       </c>
       <c r="F9">
-        <v>1.0928958375391613E-3</v>
+        <v>-1.2630953105413688E-3</v>
       </c>
       <c r="G9">
-        <v>-9.3212306797243522E-5</v>
+        <v>-5.0707707943149171E-6</v>
       </c>
       <c r="H9">
-        <v>-4.8937729878632314E-5</v>
+        <v>1.7500056446864898E-5</v>
       </c>
       <c r="I9">
-        <v>7.0583155696546551E-2</v>
+        <v>2.6982688234631805E-2</v>
       </c>
       <c r="J9">
-        <v>7.4727896750541048E-2</v>
+        <v>3.1194142866079733E-2</v>
       </c>
       <c r="K9">
-        <v>7.4068544090974159E-2</v>
+        <v>2.9701015925005424E-2</v>
       </c>
       <c r="L9">
-        <v>7.4311635666193629E-2</v>
+        <v>2.9834572412733885E-2</v>
       </c>
       <c r="M9">
-        <v>-1.1739395603458293E-3</v>
+        <v>5.4289840862461797E-4</v>
       </c>
       <c r="N9">
-        <v>-1.5010885137434404E-3</v>
+        <v>5.7764809047221115E-5</v>
       </c>
       <c r="O9">
-        <v>1.9699563673611444E-5</v>
+        <v>1.5138120175842127E-4</v>
       </c>
       <c r="P9">
-        <v>-4.7984800121741138E-4</v>
+        <v>-1.2683230194570391E-3</v>
       </c>
       <c r="Q9">
-        <v>5.0244816251763109E-5</v>
+        <v>-1.041849343258328E-4</v>
       </c>
       <c r="R9">
-        <v>6.2866410532908413E-3</v>
+        <v>3.8442452435905883E-3</v>
       </c>
       <c r="S9">
-        <v>-4.0094291647785964E-4</v>
+        <v>-4.7169447666583521E-2</v>
       </c>
       <c r="T9">
-        <v>3.615740519479496E-3</v>
-      </c>
-      <c r="U9">
-        <v>-0.11147378422487911</v>
-      </c>
-      <c r="V9">
-        <v>6.7737990161020082E-3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.45">
+        <v>4.3421858495306786E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>25</v>
       </c>
       <c r="B10">
-        <v>-0.25285882864262527</v>
+        <v>-0.38004474102726576</v>
       </c>
       <c r="C10">
-        <v>1.3869164121795507E-3</v>
+        <v>9.2662885093503118E-4</v>
       </c>
       <c r="D10">
-        <v>-1.5790325323833678E-5</v>
+        <v>-1.1313881764555874E-5</v>
       </c>
       <c r="E10">
-        <v>3.8336879372775183E-3</v>
+        <v>-5.4367431124542642E-4</v>
       </c>
       <c r="F10">
-        <v>1.4885454725493542E-3</v>
+        <v>-2.5595966128751225E-3</v>
       </c>
       <c r="G10">
-        <v>-1.0826356545556584E-4</v>
+        <v>2.3049311295244433E-6</v>
       </c>
       <c r="H10">
-        <v>-6.0650401049983401E-5</v>
+        <v>4.5292331258585327E-5</v>
       </c>
       <c r="I10">
-        <v>7.1071168061882489E-2</v>
+        <v>2.7144731888682428E-2</v>
       </c>
       <c r="J10">
-        <v>7.4068544090974159E-2</v>
+        <v>2.9701015925005424E-2</v>
       </c>
       <c r="K10">
-        <v>7.5512390596420315E-2</v>
+        <v>3.1697358321957463E-2</v>
       </c>
       <c r="L10">
-        <v>7.5548869592013651E-2</v>
+        <v>3.1432162627367179E-2</v>
       </c>
       <c r="M10">
-        <v>-1.3471022602528273E-3</v>
+        <v>8.2879879058024987E-4</v>
       </c>
       <c r="N10">
-        <v>-1.64012926260927E-3</v>
+        <v>1.1393635359291999E-4</v>
       </c>
       <c r="O10">
-        <v>6.499989546751228E-5</v>
+        <v>2.5705569799342517E-4</v>
       </c>
       <c r="P10">
-        <v>-4.7227265177631693E-4</v>
+        <v>-1.0620019123079424E-3</v>
       </c>
       <c r="Q10">
-        <v>2.4605016995901176E-5</v>
+        <v>-1.0266645199894029E-4</v>
       </c>
       <c r="R10">
-        <v>7.8820102478737459E-3</v>
+        <v>5.6619033166906436E-3</v>
       </c>
       <c r="S10">
-        <v>-2.421942066308685E-4</v>
+        <v>-5.7328324758727192E-2</v>
       </c>
       <c r="T10">
-        <v>4.1850029766218669E-3</v>
-      </c>
-      <c r="U10">
-        <v>-0.12020328721952006</v>
-      </c>
-      <c r="V10">
-        <v>7.9635336881279974E-3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.45">
+        <v>6.3814372846918771E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>26</v>
       </c>
       <c r="B11">
-        <v>-0.24406721372254361</v>
+        <v>-0.37887523364432868</v>
       </c>
       <c r="C11">
-        <v>1.4345653258132879E-3</v>
+        <v>9.8025014067982521E-4</v>
       </c>
       <c r="D11">
-        <v>-1.6265507169830022E-5</v>
+        <v>-1.1842316719569018E-5</v>
       </c>
       <c r="E11">
-        <v>3.9892822878292138E-3</v>
+        <v>-6.278625932808824E-4</v>
       </c>
       <c r="F11">
-        <v>1.6517948896749754E-3</v>
+        <v>-2.5967410587245734E-3</v>
       </c>
       <c r="G11">
-        <v>-1.1182664198758501E-4</v>
+        <v>5.0513350275245179E-6</v>
       </c>
       <c r="H11">
-        <v>-6.3695924668608561E-5</v>
+        <v>4.7953768517520272E-5</v>
       </c>
       <c r="I11">
-        <v>7.1200654185635745E-2</v>
+        <v>2.7174435480453396E-2</v>
       </c>
       <c r="J11">
-        <v>7.4311635666193629E-2</v>
+        <v>2.9834572412733885E-2</v>
       </c>
       <c r="K11">
-        <v>7.5548869592013651E-2</v>
+        <v>3.1432162627367179E-2</v>
       </c>
       <c r="L11">
-        <v>7.6688587354726778E-2</v>
+        <v>3.2073091665059811E-2</v>
       </c>
       <c r="M11">
-        <v>-1.4252928366447486E-3</v>
+        <v>8.0731597818276728E-4</v>
       </c>
       <c r="N11">
-        <v>-1.7205446957052947E-3</v>
+        <v>3.9368145977293966E-5</v>
       </c>
       <c r="O11">
-        <v>9.6531722887065299E-5</v>
+        <v>2.5251763800769784E-4</v>
       </c>
       <c r="P11">
-        <v>-4.5703150725911427E-4</v>
+        <v>-1.2605830117288777E-3</v>
       </c>
       <c r="Q11">
-        <v>3.8294655318349345E-5</v>
+        <v>-1.5223921013691343E-4</v>
       </c>
       <c r="R11">
-        <v>8.5579214500962619E-3</v>
+        <v>5.9204562681120483E-3</v>
       </c>
       <c r="S11">
-        <v>-2.6898142877523527E-4</v>
+        <v>-5.9210929907645024E-2</v>
       </c>
       <c r="T11">
-        <v>4.2159512317142076E-3</v>
-      </c>
-      <c r="U11">
-        <v>-0.12257202324942776</v>
-      </c>
-      <c r="V11">
-        <v>8.2102293173974411E-3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.45">
+        <v>6.7126274747532728E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B12">
-        <v>-0.28784111128955792</v>
+        <v>-0.19114968280044459</v>
       </c>
       <c r="C12">
-        <v>-2.6373133297332026E-4</v>
+        <v>2.1497684596107915E-4</v>
       </c>
       <c r="D12">
-        <v>2.9691023313931107E-6</v>
+        <v>-2.6403254197563478E-6</v>
       </c>
       <c r="E12">
-        <v>-8.0969661463702416E-4</v>
+        <v>-2.8838163065442879E-4</v>
       </c>
       <c r="F12">
-        <v>-7.0968306316874282E-4</v>
+        <v>-8.2826277553677376E-4</v>
       </c>
       <c r="G12">
-        <v>2.1489722676526881E-5</v>
+        <v>1.9568236707160843E-6</v>
       </c>
       <c r="H12">
-        <v>1.9545271264859205E-5</v>
+        <v>9.9807757276566834E-6</v>
       </c>
       <c r="I12">
-        <v>-6.359701777776366E-4</v>
+        <v>-5.2732091900800483E-5</v>
       </c>
       <c r="J12">
-        <v>-1.1739395603458293E-3</v>
+        <v>5.4289840862461797E-4</v>
       </c>
       <c r="K12">
-        <v>-1.3471022602528273E-3</v>
+        <v>8.2879879058024987E-4</v>
       </c>
       <c r="L12">
-        <v>-1.4252928366447486E-3</v>
+        <v>8.0731597818276728E-4</v>
       </c>
       <c r="M12">
-        <v>1.7885131564973312E-3</v>
+        <v>1.6953868488904652E-3</v>
       </c>
       <c r="N12">
-        <v>1.1327007643671433E-3</v>
+        <v>6.2541677963080106E-4</v>
       </c>
       <c r="O12">
-        <v>7.92652227466468E-4</v>
+        <v>4.2048322920986535E-5</v>
       </c>
       <c r="P12">
-        <v>9.0604686135746081E-4</v>
+        <v>1.7849007217319719E-4</v>
       </c>
       <c r="Q12">
-        <v>-1.0935612360929478E-4</v>
+        <v>-7.5642365622926715E-5</v>
       </c>
       <c r="R12">
-        <v>-8.348619400626511E-4</v>
+        <v>1.2740872433671009E-3</v>
       </c>
       <c r="S12">
-        <v>-3.197473674906556E-5</v>
+        <v>-7.5553220902866381E-3</v>
       </c>
       <c r="T12">
-        <v>-7.48074739260978E-4</v>
-      </c>
-      <c r="U12">
-        <v>8.3338935773214304E-3</v>
-      </c>
-      <c r="V12">
-        <v>-1.3433702867380055E-3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.45">
+        <v>1.3771100386045427E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B13">
-        <v>-0.28446322535757856</v>
+        <v>-0.27787358165071818</v>
       </c>
       <c r="C13">
-        <v>-3.4561764356110436E-4</v>
+        <v>4.5933834910929559E-5</v>
       </c>
       <c r="D13">
-        <v>3.9225620470159594E-6</v>
+        <v>-5.6451543300086549E-7</v>
       </c>
       <c r="E13">
-        <v>-1.0002781621347794E-3</v>
+        <v>-8.4626545141067703E-5</v>
       </c>
       <c r="F13">
-        <v>-8.9583803321836289E-4</v>
+        <v>-1.8278986326392783E-4</v>
       </c>
       <c r="G13">
-        <v>2.7138390148315107E-5</v>
+        <v>-9.7290110017780979E-7</v>
       </c>
       <c r="H13">
-        <v>2.5494989094964224E-5</v>
+        <v>-1.9137562342516396E-6</v>
       </c>
       <c r="I13">
-        <v>-7.6042543741273896E-4</v>
+        <v>-3.0048358953967781E-5</v>
       </c>
       <c r="J13">
-        <v>-1.5010885137434404E-3</v>
+        <v>5.7764809047221115E-5</v>
       </c>
       <c r="K13">
-        <v>-1.64012926260927E-3</v>
+        <v>1.1393635359291999E-4</v>
       </c>
       <c r="L13">
-        <v>-1.7205446957052947E-3</v>
+        <v>3.9368145977293966E-5</v>
       </c>
       <c r="M13">
-        <v>1.1327007643671433E-3</v>
+        <v>6.2541677963080106E-4</v>
       </c>
       <c r="N13">
-        <v>3.0089488049155249E-3</v>
+        <v>8.5452730059245999E-4</v>
       </c>
       <c r="O13">
-        <v>7.7815616981531015E-4</v>
+        <v>-2.2705372454167009E-5</v>
       </c>
       <c r="P13">
-        <v>9.2606777267711232E-4</v>
+        <v>1.8102415868593584E-5</v>
       </c>
       <c r="Q13">
-        <v>-8.9938223164022572E-5</v>
+        <v>-4.2659364405839501E-5</v>
       </c>
       <c r="R13">
-        <v>-1.6202409493283249E-3</v>
+        <v>2.8058916023169513E-4</v>
       </c>
       <c r="S13">
-        <v>-6.2337682859058533E-5</v>
+        <v>-1.8196219294838562E-3</v>
       </c>
       <c r="T13">
-        <v>-9.7096183821023473E-4</v>
-      </c>
-      <c r="U13">
-        <v>1.1518218726753189E-2</v>
-      </c>
-      <c r="V13">
-        <v>-1.7702229038183573E-3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.45">
+        <v>2.7330195499934614E-4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="B14">
-        <v>-9.4620165516397944E-2</v>
+        <v>0.32561153467424542</v>
       </c>
       <c r="C14">
-        <v>7.1041371454418236E-5</v>
+        <v>1.0518163849015625E-5</v>
       </c>
       <c r="D14">
-        <v>-7.9851759209663876E-7</v>
+        <v>-1.0248032972903987E-7</v>
       </c>
       <c r="E14">
-        <v>1.6447298587878571E-4</v>
+        <v>-1.9242775027066741E-5</v>
       </c>
       <c r="F14">
-        <v>2.0106389131541516E-4</v>
+        <v>-1.9204225358828252E-5</v>
       </c>
       <c r="G14">
-        <v>-5.040817583620771E-6</v>
+        <v>4.3194328451470078E-7</v>
       </c>
       <c r="H14">
-        <v>-6.2740710132694839E-6</v>
+        <v>4.48477012650032E-7</v>
       </c>
       <c r="I14">
-        <v>-1.5474673756698984E-4</v>
+        <v>1.6130929207926111E-4</v>
       </c>
       <c r="J14">
-        <v>1.9699563673611444E-5</v>
+        <v>1.5138120175842127E-4</v>
       </c>
       <c r="K14">
-        <v>6.499989546751228E-5</v>
+        <v>2.5705569799342517E-4</v>
       </c>
       <c r="L14">
-        <v>9.6531722887065299E-5</v>
+        <v>2.5251763800769784E-4</v>
       </c>
       <c r="M14">
-        <v>7.92652227466468E-4</v>
+        <v>4.2048322920986535E-5</v>
       </c>
       <c r="N14">
-        <v>7.7815616981531015E-4</v>
+        <v>-2.2705372454167009E-5</v>
       </c>
       <c r="O14">
-        <v>1.7222089635572509E-3</v>
+        <v>1.3662946284048393E-3</v>
       </c>
       <c r="P14">
-        <v>8.285407989719652E-4</v>
+        <v>-3.7910564334305908E-4</v>
       </c>
       <c r="Q14">
-        <v>-6.3363926394498286E-5</v>
+        <v>-5.1024757581792998E-5</v>
       </c>
       <c r="R14">
-        <v>-2.9591776057674197E-4</v>
+        <v>1.2705710136711663E-4</v>
       </c>
       <c r="S14">
-        <v>8.6991517679262827E-6</v>
+        <v>-3.2657744937649293E-4</v>
       </c>
       <c r="T14">
-        <v>1.0522118485355687E-4</v>
-      </c>
-      <c r="U14">
-        <v>-2.3893455076486629E-3</v>
-      </c>
-      <c r="V14">
-        <v>3.151558691569424E-4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.45">
+        <v>1.3709084435104662E-5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="B15">
-        <v>-0.16227143399654154</v>
+        <v>3.325241906939596E-2</v>
       </c>
       <c r="C15">
-        <v>-7.4514739287516376E-5</v>
+        <v>1.6843542501061669E-4</v>
       </c>
       <c r="D15">
-        <v>8.2171609349213053E-7</v>
+        <v>-2.6114238761758571E-6</v>
       </c>
       <c r="E15">
-        <v>-3.0494613737578924E-4</v>
+        <v>-3.0596535177101363E-3</v>
       </c>
       <c r="F15">
-        <v>-2.3246087189905426E-4</v>
+        <v>-2.2530209495521961E-3</v>
       </c>
       <c r="G15">
-        <v>7.2214226431414631E-6</v>
+        <v>7.0205098390055932E-5</v>
       </c>
       <c r="H15">
-        <v>6.5863261958690026E-6</v>
+        <v>4.5234699321788291E-5</v>
       </c>
       <c r="I15">
-        <v>-2.0961243839632041E-4</v>
+        <v>-2.3375785261367282E-4</v>
       </c>
       <c r="J15">
-        <v>-4.7984800121741138E-4</v>
+        <v>-1.2683230194570391E-3</v>
       </c>
       <c r="K15">
-        <v>-4.7227265177631693E-4</v>
+        <v>-1.0620019123079424E-3</v>
       </c>
       <c r="L15">
-        <v>-4.5703150725911427E-4</v>
+        <v>-1.2605830117288777E-3</v>
       </c>
       <c r="M15">
-        <v>9.0604686135746081E-4</v>
+        <v>1.7849007217319719E-4</v>
       </c>
       <c r="N15">
-        <v>9.2606777267711232E-4</v>
+        <v>1.8102415868593584E-5</v>
       </c>
       <c r="O15">
-        <v>8.285407989719652E-4</v>
+        <v>-3.7910564334305908E-4</v>
       </c>
       <c r="P15">
-        <v>1.6527953819159564E-3</v>
+        <v>0.22474821214951704</v>
       </c>
       <c r="Q15">
-        <v>-3.9398339655465704E-5</v>
+        <v>-5.7557415753208075E-3</v>
       </c>
       <c r="R15">
-        <v>-4.7948422165328337E-4</v>
+        <v>9.9041834593460222E-4</v>
       </c>
       <c r="S15">
-        <v>-1.656438191792344E-5</v>
+        <v>-0.22468253837009325</v>
       </c>
       <c r="T15">
-        <v>-2.6323040627437952E-4</v>
-      </c>
-      <c r="U15">
-        <v>2.1662198583644503E-3</v>
-      </c>
-      <c r="V15">
-        <v>-4.0273379679480224E-4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.45">
+        <v>2.0754995302198361E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B16">
-        <v>0.19105694479741814</v>
+        <v>-7.3729733933239191E-3</v>
       </c>
       <c r="C16">
-        <v>-4.0069415354043638E-5</v>
+        <v>-4.1953484894838145E-5</v>
       </c>
       <c r="D16">
-        <v>4.5786965271716905E-7</v>
+        <v>4.7166859904195512E-7</v>
       </c>
       <c r="E16">
-        <v>-3.1121627742052526E-4</v>
+        <v>-6.6937624251879558E-5</v>
       </c>
       <c r="F16">
-        <v>-3.329510704714162E-4</v>
+        <v>4.9376188440896489E-5</v>
       </c>
       <c r="G16">
-        <v>8.4572136529967825E-6</v>
+        <v>2.1085908034808625E-6</v>
       </c>
       <c r="H16">
-        <v>8.7131140757192834E-6</v>
+        <v>6.865873835269971E-7</v>
       </c>
       <c r="I16">
-        <v>6.3319631257792208E-5</v>
+        <v>1.0804142710852199E-4</v>
       </c>
       <c r="J16">
-        <v>5.0244816251763109E-5</v>
+        <v>-1.041849343258328E-4</v>
       </c>
       <c r="K16">
-        <v>2.4605016995901176E-5</v>
+        <v>-1.0266645199894029E-4</v>
       </c>
       <c r="L16">
-        <v>3.8294655318349345E-5</v>
+        <v>-1.5223921013691343E-4</v>
       </c>
       <c r="M16">
-        <v>-1.0935612360929478E-4</v>
+        <v>-7.5642365622926715E-5</v>
       </c>
       <c r="N16">
-        <v>-8.9938223164022572E-5</v>
+        <v>-4.2659364405839501E-5</v>
       </c>
       <c r="O16">
-        <v>-6.3363926394498286E-5</v>
+        <v>-5.1024757581792998E-5</v>
       </c>
       <c r="P16">
-        <v>-3.9398339655465704E-5</v>
+        <v>-5.7557415753208075E-3</v>
       </c>
       <c r="Q16">
-        <v>1.8808340461037324E-3</v>
+        <v>3.5650446892478145E-3</v>
       </c>
       <c r="R16">
-        <v>1.0177609892077482E-3</v>
+        <v>-1.4768352332386187E-5</v>
       </c>
       <c r="S16">
-        <v>-6.6507812811103761E-5</v>
+        <v>6.9143890249376127E-3</v>
       </c>
       <c r="T16">
-        <v>-9.1183202878818967E-5</v>
-      </c>
-      <c r="U16">
-        <v>-1.6803802571622362E-5</v>
-      </c>
-      <c r="V16">
-        <v>-2.9806649915364023E-4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.45">
+        <v>-3.2421830791484058E-4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B17">
-        <v>3.7748185520421057E-3</v>
+        <v>-0.15831305061490342</v>
       </c>
       <c r="C17">
-        <v>1.0178535903602043E-3</v>
+        <v>1.2405635695656668E-3</v>
       </c>
       <c r="D17">
-        <v>-1.1835931006264559E-5</v>
+        <v>-1.5420111237877472E-5</v>
       </c>
       <c r="E17">
-        <v>5.2315677125590451E-4</v>
+        <v>-1.2172986872614404E-3</v>
       </c>
       <c r="F17">
-        <v>2.2307657966652958E-3</v>
+        <v>-3.9396196655281943E-3</v>
       </c>
       <c r="G17">
-        <v>-2.4766365197365221E-5</v>
+        <v>1.5494854214498646E-5</v>
       </c>
       <c r="H17">
-        <v>-5.4063141510708385E-5</v>
+        <v>7.4291131670276147E-5</v>
       </c>
       <c r="I17">
-        <v>1.9975789608798855E-3</v>
+        <v>6.7538450528769407E-4</v>
       </c>
       <c r="J17">
-        <v>6.2866410532908413E-3</v>
+        <v>3.8442452435905883E-3</v>
       </c>
       <c r="K17">
-        <v>7.8820102478737459E-3</v>
+        <v>5.6619033166906436E-3</v>
       </c>
       <c r="L17">
-        <v>8.5579214500962619E-3</v>
+        <v>5.9204562681120483E-3</v>
       </c>
       <c r="M17">
-        <v>-8.348619400626511E-4</v>
+        <v>1.2740872433671009E-3</v>
       </c>
       <c r="N17">
-        <v>-1.6202409493283249E-3</v>
+        <v>2.8058916023169513E-4</v>
       </c>
       <c r="O17">
-        <v>-2.9591776057674197E-4</v>
+        <v>1.2705710136711663E-4</v>
       </c>
       <c r="P17">
-        <v>-4.7948422165328337E-4</v>
+        <v>9.9041834593460222E-4</v>
       </c>
       <c r="Q17">
-        <v>1.0177609892077482E-3</v>
+        <v>-1.4768352332386187E-5</v>
       </c>
       <c r="R17">
-        <v>1.1751762426028149</v>
+        <v>8.1785003654975021E-3</v>
       </c>
       <c r="S17">
-        <v>-5.3656696730576527E-2</v>
+        <v>-4.2524186895629645E-2</v>
       </c>
       <c r="T17">
-        <v>-4.0170271131596026E-3</v>
-      </c>
-      <c r="U17">
-        <v>-1.2004932883604431</v>
-      </c>
-      <c r="V17">
-        <v>5.4473525965925244E-3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.45">
+        <v>8.2972138467305046E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B18">
-        <v>-0.12699552434998035</v>
+        <v>2.4896359891646282</v>
       </c>
       <c r="C18">
-        <v>3.2956356521372985E-5</v>
+        <v>-8.570547031350512E-3</v>
       </c>
       <c r="D18">
-        <v>-3.5181683395019974E-7</v>
+        <v>1.0311026181843879E-4</v>
       </c>
       <c r="E18">
-        <v>7.8714768903603974E-5</v>
+        <v>-1.5496999104447735E-3</v>
       </c>
       <c r="F18">
-        <v>-1.4138094750184623E-5</v>
+        <v>1.7605925671066544E-2</v>
       </c>
       <c r="G18">
-        <v>-2.0059177052181282E-6</v>
+        <v>1.0450543691211028E-4</v>
       </c>
       <c r="H18">
-        <v>-1.3074468063656592E-6</v>
+        <v>-2.9871973342737685E-4</v>
       </c>
       <c r="I18">
-        <v>-2.3261887349925971E-4</v>
+        <v>-3.0076044732591609E-2</v>
       </c>
       <c r="J18">
-        <v>-4.0094291647785964E-4</v>
+        <v>-4.7169447666583521E-2</v>
       </c>
       <c r="K18">
-        <v>-2.421942066308685E-4</v>
+        <v>-5.7328324758727192E-2</v>
       </c>
       <c r="L18">
-        <v>-2.6898142877523527E-4</v>
+        <v>-5.9210929907645024E-2</v>
       </c>
       <c r="M18">
-        <v>-3.197473674906556E-5</v>
+        <v>-7.5553220902866381E-3</v>
       </c>
       <c r="N18">
-        <v>-6.2337682859058533E-5</v>
+        <v>-1.8196219294838562E-3</v>
       </c>
       <c r="O18">
-        <v>8.6991517679262827E-6</v>
+        <v>-3.2657744937649293E-4</v>
       </c>
       <c r="P18">
-        <v>-1.656438191792344E-5</v>
+        <v>-0.22468253837009325</v>
       </c>
       <c r="Q18">
-        <v>-6.6507812811103761E-5</v>
+        <v>6.9143890249376127E-3</v>
       </c>
       <c r="R18">
-        <v>-5.3656696730576527E-2</v>
+        <v>-4.2524186895629645E-2</v>
       </c>
       <c r="S18">
-        <v>5.7753008254731513E-3</v>
+        <v>0.51744913374414025</v>
       </c>
       <c r="T18">
-        <v>5.9696487525139129E-4</v>
-      </c>
-      <c r="U18">
-        <v>5.2492418216069439E-2</v>
-      </c>
-      <c r="V18">
-        <v>7.4388529200147536E-5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.45">
+        <v>-4.8767281529901153E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B19">
-        <v>-3.8344144679979479E-2</v>
+        <v>-0.41786783951176787</v>
       </c>
       <c r="C19">
-        <v>8.9855585784334529E-4</v>
+        <v>1.4074107075818551E-3</v>
       </c>
       <c r="D19">
-        <v>-1.0374106540976592E-5</v>
+        <v>-1.7350715294664254E-5</v>
       </c>
       <c r="E19">
-        <v>2.4994528145818669E-3</v>
+        <v>-1.2936357530068492E-3</v>
       </c>
       <c r="F19">
-        <v>1.7667635796654849E-3</v>
+        <v>-4.3650915803165585E-3</v>
       </c>
       <c r="G19">
-        <v>-7.1055525657525066E-5</v>
+        <v>1.5025751432026607E-5</v>
       </c>
       <c r="H19">
-        <v>-6.2632347463372669E-5</v>
+        <v>8.0189668780557464E-5</v>
       </c>
       <c r="I19">
-        <v>1.9202472109283333E-3</v>
+        <v>7.4210306867237294E-4</v>
       </c>
       <c r="J19">
-        <v>3.615740519479496E-3</v>
+        <v>4.3421858495306786E-3</v>
       </c>
       <c r="K19">
-        <v>4.1850029766218669E-3</v>
+        <v>6.3814372846918771E-3</v>
       </c>
       <c r="L19">
-        <v>4.2159512317142076E-3</v>
+        <v>6.7126274747532728E-3</v>
       </c>
       <c r="M19">
-        <v>-7.48074739260978E-4</v>
+        <v>1.3771100386045427E-3</v>
       </c>
       <c r="N19">
-        <v>-9.7096183821023473E-4</v>
+        <v>2.7330195499934614E-4</v>
       </c>
       <c r="O19">
-        <v>1.0522118485355687E-4</v>
+        <v>1.3709084435104662E-5</v>
       </c>
       <c r="P19">
-        <v>-2.6323040627437952E-4</v>
+        <v>2.0754995302198361E-3</v>
       </c>
       <c r="Q19">
-        <v>-9.1183202878818967E-5</v>
+        <v>-3.2421830791484058E-4</v>
       </c>
       <c r="R19">
-        <v>-4.0170271131596026E-3</v>
+        <v>8.2972138467305046E-3</v>
       </c>
       <c r="S19">
-        <v>5.9696487525139129E-4</v>
+        <v>-4.8767281529901153E-2</v>
       </c>
       <c r="T19">
-        <v>3.6682744097145362E-3</v>
-      </c>
-      <c r="U19">
-        <v>-2.4029722648938108E-2</v>
-      </c>
-      <c r="V19">
-        <v>4.9771212603583626E-3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
-        <v>31</v>
-      </c>
-      <c r="B20">
-        <v>3.4531576224331753</v>
-      </c>
-      <c r="C20">
-        <v>-1.233507789616157E-2</v>
-      </c>
-      <c r="D20">
-        <v>1.3839164502240899E-4</v>
-      </c>
-      <c r="E20">
-        <v>-4.2678044263341978E-2</v>
-      </c>
-      <c r="F20">
-        <v>-3.407189062287648E-2</v>
-      </c>
-      <c r="G20">
-        <v>1.1259234136053887E-3</v>
-      </c>
-      <c r="H20">
-        <v>1.0200372494442761E-3</v>
-      </c>
-      <c r="I20">
-        <v>-8.7952893035028373E-2</v>
-      </c>
-      <c r="J20">
-        <v>-0.11147378422487911</v>
-      </c>
-      <c r="K20">
-        <v>-0.12020328721952006</v>
-      </c>
-      <c r="L20">
-        <v>-0.12257202324942776</v>
-      </c>
-      <c r="M20">
-        <v>8.3338935773214304E-3</v>
-      </c>
-      <c r="N20">
-        <v>1.1518218726753189E-2</v>
-      </c>
-      <c r="O20">
-        <v>-2.3893455076486629E-3</v>
-      </c>
-      <c r="P20">
-        <v>2.1662198583644503E-3</v>
-      </c>
-      <c r="Q20">
-        <v>-1.6803802571622362E-5</v>
-      </c>
-      <c r="R20">
-        <v>-1.2004932883604431</v>
-      </c>
-      <c r="S20">
-        <v>5.2492418216069439E-2</v>
-      </c>
-      <c r="T20">
-        <v>-2.4029722648938108E-2</v>
-      </c>
-      <c r="U20">
-        <v>1.6330943179458481</v>
-      </c>
-      <c r="V20">
-        <v>-5.9092536508592426E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
-        <v>32</v>
-      </c>
-      <c r="B21">
-        <v>-0.44444973705211444</v>
-      </c>
-      <c r="C21">
-        <v>1.7378040542857525E-3</v>
-      </c>
-      <c r="D21">
-        <v>-1.9841065727807784E-5</v>
-      </c>
-      <c r="E21">
-        <v>4.7002637835900076E-3</v>
-      </c>
-      <c r="F21">
-        <v>3.4514272779636707E-3</v>
-      </c>
-      <c r="G21">
-        <v>-1.33190021725481E-4</v>
-      </c>
-      <c r="H21">
-        <v>-1.239755230482082E-4</v>
-      </c>
-      <c r="I21">
-        <v>3.3520492765034631E-3</v>
-      </c>
-      <c r="J21">
-        <v>6.7737990161020082E-3</v>
-      </c>
-      <c r="K21">
-        <v>7.9635336881279974E-3</v>
-      </c>
-      <c r="L21">
-        <v>8.2102293173974411E-3</v>
-      </c>
-      <c r="M21">
-        <v>-1.3433702867380055E-3</v>
-      </c>
-      <c r="N21">
-        <v>-1.7702229038183573E-3</v>
-      </c>
-      <c r="O21">
-        <v>3.151558691569424E-4</v>
-      </c>
-      <c r="P21">
-        <v>-4.0273379679480224E-4</v>
-      </c>
-      <c r="Q21">
-        <v>-2.9806649915364023E-4</v>
-      </c>
-      <c r="R21">
-        <v>5.4473525965925244E-3</v>
-      </c>
-      <c r="S21">
-        <v>7.4388529200147536E-5</v>
-      </c>
-      <c r="T21">
-        <v>4.9771212603583626E-3</v>
-      </c>
-      <c r="U21">
-        <v>-5.9092536508592426E-2</v>
-      </c>
-      <c r="V21">
-        <v>9.4283437431565819E-3</v>
+        <v>9.2438258889787801E-3</v>
       </c>
     </row>
   </sheetData>
@@ -3498,15 +2986,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A591251-B8B9-4A10-AB23-25F5FD4E43E4}">
-  <dimension ref="A1:W22"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="22.796875" style="3" customWidth="1"/>
-    <col min="2" max="16384" width="8.796875" style="3"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{667FB774-38BC-456A-974D-0F96B7706E3F}">
+  <dimension ref="A1:U20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -3547,1525 +3031,1263 @@
         <v>26</v>
       </c>
       <c r="N1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="Q1" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="R1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="S1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="T1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="U1" t="s">
-        <v>30</v>
-      </c>
-      <c r="V1" t="s">
-        <v>31</v>
-      </c>
-      <c r="W1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>33</v>
       </c>
       <c r="B2">
-        <v>0.68199805324324614</v>
+        <v>0.70444662784674161</v>
       </c>
       <c r="C2">
-        <v>1.913777950428031E-5</v>
+        <v>2.55925562960899E-5</v>
       </c>
       <c r="D2">
-        <v>1.2062722649235683E-6</v>
+        <v>-6.6275198178114756E-8</v>
       </c>
       <c r="E2">
-        <v>-1.5335942244663383E-8</v>
+        <v>-3.385177248881596E-9</v>
       </c>
       <c r="F2">
-        <v>5.6212268631333927E-6</v>
+        <v>-1.3466126083910126E-6</v>
       </c>
       <c r="G2">
-        <v>6.6107113643827647E-7</v>
+        <v>5.3241183228490012E-6</v>
       </c>
       <c r="H2">
-        <v>-2.7293942404443159E-8</v>
+        <v>2.3045470066833303E-7</v>
       </c>
       <c r="I2">
-        <v>1.426627382113471E-7</v>
+        <v>3.1099242269706228E-7</v>
       </c>
       <c r="J2">
-        <v>-3.7084880603664447E-7</v>
+        <v>-6.3607146434105838E-6</v>
       </c>
       <c r="K2">
-        <v>1.4129040881132856E-6</v>
+        <v>3.8440363792378153E-7</v>
       </c>
       <c r="L2">
-        <v>1.3478501141988566E-6</v>
+        <v>-2.9221140068869368E-6</v>
       </c>
       <c r="M2">
-        <v>1.0375116457096504E-6</v>
+        <v>-3.6594190018443604E-6</v>
       </c>
       <c r="N2">
-        <v>5.7398308912253866E-7</v>
+        <v>3.5135483902333456E-6</v>
       </c>
       <c r="O2">
-        <v>7.7075650811588849E-7</v>
+        <v>4.6027290081153889E-6</v>
       </c>
       <c r="P2">
-        <v>-2.9784157159202246E-7</v>
+        <v>-2.1637286615195698E-6</v>
       </c>
       <c r="Q2">
-        <v>1.5001927198533433E-6</v>
+        <v>1.6071421113095425E-6</v>
       </c>
       <c r="R2">
-        <v>1.3906312380880917E-6</v>
+        <v>-2.5374116243815132E-6</v>
       </c>
       <c r="S2">
-        <v>-7.0691951341782136E-6</v>
+        <v>-1.6414537382816952E-6</v>
       </c>
       <c r="T2">
-        <v>-7.5948170724471779E-7</v>
+        <v>-5.1187967636433514E-5</v>
       </c>
       <c r="U2">
-        <v>8.6317135121308638E-7</v>
-      </c>
-      <c r="V2">
-        <v>-7.4086508817265836E-5</v>
-      </c>
-      <c r="W2">
-        <v>3.2240865191396875E-5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.45">
+        <v>2.8241923374578404E-5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>17</v>
       </c>
       <c r="B3">
-        <v>6.9976285246309096E-3</v>
+        <v>4.1870787931736408E-3</v>
       </c>
       <c r="C3">
-        <v>1.2062722649235683E-6</v>
+        <v>-6.6275198178114756E-8</v>
       </c>
       <c r="D3">
-        <v>8.5742690850671856E-5</v>
+        <v>9.6984405011341296E-5</v>
       </c>
       <c r="E3">
-        <v>-8.6415738549963426E-7</v>
+        <v>-9.9471289947576514E-7</v>
       </c>
       <c r="F3">
-        <v>2.0654309350709086E-4</v>
+        <v>2.0854018038729777E-4</v>
       </c>
       <c r="G3">
-        <v>1.4541237358777534E-4</v>
+        <v>-1.7012484153403534E-4</v>
       </c>
       <c r="H3">
-        <v>-5.2373873195704753E-6</v>
+        <v>-7.3126794786031499E-6</v>
       </c>
       <c r="I3">
-        <v>-5.8841786333292284E-6</v>
+        <v>-7.1765534734731563E-7</v>
       </c>
       <c r="J3">
-        <v>-2.540163134975293E-5</v>
+        <v>-1.7209008254988003E-4</v>
       </c>
       <c r="K3">
-        <v>3.2703675722657206E-5</v>
+        <v>3.7940281876692349E-5</v>
       </c>
       <c r="L3">
-        <v>5.6300441924130787E-5</v>
+        <v>3.3600878968898944E-5</v>
       </c>
       <c r="M3">
-        <v>5.559680290513329E-5</v>
+        <v>4.078854008343755E-5</v>
       </c>
       <c r="N3">
-        <v>-1.0746006814810015E-4</v>
+        <v>5.5136692772434005E-5</v>
       </c>
       <c r="O3">
-        <v>-5.7565696572321141E-5</v>
+        <v>-4.8525121217208445E-5</v>
       </c>
       <c r="P3">
-        <v>-2.7754129565687366E-6</v>
+        <v>2.0227647801336496E-6</v>
       </c>
       <c r="Q3">
-        <v>-2.5813570343207516E-5</v>
+        <v>-2.4247127969965733E-6</v>
       </c>
       <c r="R3">
-        <v>1.627180787194121E-6</v>
+        <v>-4.8391164136628428E-7</v>
       </c>
       <c r="S3">
-        <v>5.467962896406415E-6</v>
+        <v>8.5029570664378222E-5</v>
       </c>
       <c r="T3">
-        <v>-3.9780246746363259E-5</v>
+        <v>-2.5828106685665091E-3</v>
       </c>
       <c r="U3">
-        <v>1.8019385684666995E-5</v>
-      </c>
-      <c r="V3">
-        <v>-2.2652255543339898E-3</v>
-      </c>
-      <c r="W3">
-        <v>1.1875109946579677E-3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.45">
+        <v>1.8640065982554416E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
       <c r="B4">
-        <v>-3.6881000130816143E-5</v>
+        <v>-1.2642707185819521E-5</v>
       </c>
       <c r="C4">
-        <v>-1.5335942244663383E-8</v>
+        <v>-3.385177248881596E-9</v>
       </c>
       <c r="D4">
-        <v>-8.6415738549963426E-7</v>
+        <v>-9.9471289947576514E-7</v>
       </c>
       <c r="E4">
-        <v>8.7385684962492631E-9</v>
+        <v>1.0261104479508791E-8</v>
       </c>
       <c r="F4">
-        <v>-1.9796566657837449E-6</v>
+        <v>-1.9686771968842052E-6</v>
       </c>
       <c r="G4">
-        <v>-1.3532304079459995E-6</v>
+        <v>1.962496705509775E-6</v>
       </c>
       <c r="H4">
-        <v>5.0464555632425923E-8</v>
+        <v>7.0756700506271222E-8</v>
       </c>
       <c r="I4">
-        <v>5.6705086261879623E-8</v>
+        <v>1.8885967671682553E-9</v>
       </c>
       <c r="J4">
-        <v>2.5664571837439581E-7</v>
+        <v>1.7435209782330382E-6</v>
       </c>
       <c r="K4">
-        <v>-3.2565318431923075E-7</v>
+        <v>-3.8909253363848838E-7</v>
       </c>
       <c r="L4">
-        <v>-5.6007045846756847E-7</v>
+        <v>-3.4020700249857606E-7</v>
       </c>
       <c r="M4">
-        <v>-5.503446542352879E-7</v>
+        <v>-4.0428589305832336E-7</v>
       </c>
       <c r="N4">
-        <v>1.0781525743160867E-6</v>
+        <v>-5.6065622020098916E-7</v>
       </c>
       <c r="O4">
-        <v>5.7533296806500287E-7</v>
+        <v>4.8979998580436864E-7</v>
       </c>
       <c r="P4">
-        <v>2.8281866792697337E-8</v>
+        <v>-2.1776161982176701E-8</v>
       </c>
       <c r="Q4">
-        <v>2.5846477606465287E-7</v>
+        <v>5.2324652763723268E-8</v>
       </c>
       <c r="R4">
-        <v>-1.5991186959250754E-8</v>
+        <v>1.1649462992848133E-9</v>
       </c>
       <c r="S4">
-        <v>-2.5448308861917681E-8</v>
+        <v>-8.662661218887003E-7</v>
       </c>
       <c r="T4">
-        <v>3.9794192450660095E-7</v>
+        <v>2.6315024181110647E-5</v>
       </c>
       <c r="U4">
-        <v>-1.8334525627835875E-7</v>
-      </c>
-      <c r="V4">
-        <v>2.2736778076506119E-5</v>
-      </c>
-      <c r="W4">
-        <v>-1.1937540316577405E-5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.45">
+        <v>-1.8913848531903118E-5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>19</v>
       </c>
       <c r="B5">
-        <v>-8.1135991991942574E-2</v>
+        <v>-6.3772574046631531E-2</v>
       </c>
       <c r="C5">
-        <v>5.6212268631333927E-6</v>
+        <v>-1.3466126083910126E-6</v>
       </c>
       <c r="D5">
-        <v>2.0654309350709086E-4</v>
+        <v>2.0854018038729777E-4</v>
       </c>
       <c r="E5">
-        <v>-1.9796566657837449E-6</v>
+        <v>-1.9686771968842052E-6</v>
       </c>
       <c r="F5">
-        <v>1.1983033493765611E-3</v>
+        <v>1.8483127820734697E-3</v>
       </c>
       <c r="G5">
-        <v>8.0367069169660595E-4</v>
+        <v>3.9079711460392923E-4</v>
       </c>
       <c r="H5">
-        <v>-2.7366327288283479E-5</v>
+        <v>-4.6293612680910955E-5</v>
       </c>
       <c r="I5">
-        <v>-2.357063202698037E-5</v>
+        <v>-1.813698985349595E-5</v>
       </c>
       <c r="J5">
-        <v>-6.1710564716978749E-5</v>
+        <v>-3.6437414123013852E-4</v>
       </c>
       <c r="K5">
-        <v>7.7171593957509082E-5</v>
+        <v>7.4279409165906165E-5</v>
       </c>
       <c r="L5">
-        <v>1.3302421491643581E-4</v>
+        <v>6.631788429553294E-5</v>
       </c>
       <c r="M5">
-        <v>1.3163072179445904E-4</v>
+        <v>7.8298315096359664E-5</v>
       </c>
       <c r="N5">
-        <v>-2.536675896453388E-4</v>
+        <v>9.9303941158715165E-5</v>
       </c>
       <c r="O5">
-        <v>-1.4153668741321608E-4</v>
+        <v>-1.1550260112877276E-4</v>
       </c>
       <c r="P5">
-        <v>-6.6659062486234025E-6</v>
+        <v>-9.0069218443686958E-6</v>
       </c>
       <c r="Q5">
-        <v>-6.329812428127924E-5</v>
+        <v>-6.133358385325096E-5</v>
       </c>
       <c r="R5">
-        <v>1.610155841920046E-7</v>
+        <v>5.8403213702296391E-6</v>
       </c>
       <c r="S5">
-        <v>-3.9226460914701242E-5</v>
+        <v>1.8551643582976764E-4</v>
       </c>
       <c r="T5">
-        <v>-8.8653091652942132E-5</v>
+        <v>-5.8462323867154485E-3</v>
       </c>
       <c r="U5">
-        <v>4.3662075074686928E-5</v>
-      </c>
-      <c r="V5">
-        <v>-5.6321439965972223E-3</v>
-      </c>
-      <c r="W5">
-        <v>2.7802959490674716E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.45">
+        <v>4.0242024343237655E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>20</v>
       </c>
       <c r="B6">
-        <v>-4.5838392236215018E-2</v>
+        <v>-0.21012387749847009</v>
       </c>
       <c r="C6">
-        <v>6.6107113643827647E-7</v>
+        <v>5.3241183228490012E-6</v>
       </c>
       <c r="D6">
-        <v>1.4541237358777534E-4</v>
+        <v>-1.7012484153403534E-4</v>
       </c>
       <c r="E6">
-        <v>-1.3532304079459995E-6</v>
+        <v>1.962496705509775E-6</v>
       </c>
       <c r="F6">
-        <v>8.0367069169660595E-4</v>
+        <v>3.9079711460392923E-4</v>
       </c>
       <c r="G6">
-        <v>1.6096149882882185E-3</v>
+        <v>3.5116644394358452E-3</v>
       </c>
       <c r="H6">
-        <v>-1.8552602411372245E-5</v>
+        <v>-4.564372028637862E-6</v>
       </c>
       <c r="I6">
-        <v>-3.7772340557620939E-5</v>
+        <v>-6.3533018336514601E-5</v>
       </c>
       <c r="J6">
-        <v>-3.4079829090298148E-5</v>
+        <v>3.2601048389023588E-4</v>
       </c>
       <c r="K6">
-        <v>6.3380973823649167E-5</v>
+        <v>2.2955663997336599E-5</v>
       </c>
       <c r="L6">
-        <v>1.0285443519936444E-4</v>
+        <v>2.3524683180634687E-7</v>
       </c>
       <c r="M6">
-        <v>1.0658971475805844E-4</v>
+        <v>-1.0952322238119691E-5</v>
       </c>
       <c r="N6">
-        <v>-1.9197720208730812E-4</v>
+        <v>-1.1215207575576643E-4</v>
       </c>
       <c r="O6">
-        <v>-1.0328493783283753E-4</v>
+        <v>6.1388476342005854E-5</v>
       </c>
       <c r="P6">
-        <v>2.0422376462822073E-7</v>
+        <v>-1.008149083633379E-5</v>
       </c>
       <c r="Q6">
-        <v>-4.083919170041362E-5</v>
+        <v>-1.7590527124388252E-4</v>
       </c>
       <c r="R6">
-        <v>-1.8121544406037796E-6</v>
+        <v>2.6103277936852485E-6</v>
       </c>
       <c r="S6">
-        <v>-5.8921022495535959E-5</v>
+        <v>-1.2721917423309689E-4</v>
       </c>
       <c r="T6">
-        <v>-5.9915900245017501E-5</v>
+        <v>4.1072258374827524E-3</v>
       </c>
       <c r="U6">
-        <v>3.7105349461015292E-5</v>
-      </c>
-      <c r="V6">
-        <v>-4.0411483732586111E-3</v>
-      </c>
-      <c r="W6">
-        <v>2.0359568289005175E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.45">
+        <v>-2.7713591052152611E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>21</v>
       </c>
       <c r="B7">
-        <v>-4.4875491933232906E-4</v>
+        <v>-7.7503477518538297E-4</v>
       </c>
       <c r="C7">
-        <v>-2.7293942404443159E-8</v>
+        <v>2.3045470066833303E-7</v>
       </c>
       <c r="D7">
-        <v>-5.2373873195704753E-6</v>
+        <v>-7.3126794786031499E-6</v>
       </c>
       <c r="E7">
-        <v>5.0464555632425923E-8</v>
+        <v>7.0756700506271222E-8</v>
       </c>
       <c r="F7">
-        <v>-2.7366327288283479E-5</v>
+        <v>-4.6293612680910955E-5</v>
       </c>
       <c r="G7">
-        <v>-1.8552602411372245E-5</v>
+        <v>-4.564372028637862E-6</v>
       </c>
       <c r="H7">
-        <v>6.4715594227930877E-7</v>
+        <v>1.2614810660113389E-6</v>
       </c>
       <c r="I7">
-        <v>5.7252754356328463E-7</v>
+        <v>4.6926667174429041E-7</v>
       </c>
       <c r="J7">
-        <v>1.5962264268634294E-6</v>
+        <v>1.3363340363892324E-5</v>
       </c>
       <c r="K7">
-        <v>-1.9606571559199221E-6</v>
+        <v>-2.7638759478830496E-6</v>
       </c>
       <c r="L7">
-        <v>-3.3716940174969441E-6</v>
+        <v>-2.494794715941288E-6</v>
       </c>
       <c r="M7">
-        <v>-3.3191059559450883E-6</v>
+        <v>-2.8796096422015379E-6</v>
       </c>
       <c r="N7">
-        <v>6.5476651279201855E-6</v>
+        <v>-4.0838548655603047E-6</v>
       </c>
       <c r="O7">
-        <v>3.6464293863072883E-6</v>
+        <v>3.9416203266348401E-6</v>
       </c>
       <c r="P7">
-        <v>1.6099206125369656E-7</v>
+        <v>2.2231485827970002E-7</v>
       </c>
       <c r="Q7">
-        <v>1.6385784382750396E-6</v>
+        <v>1.2747633177756428E-6</v>
       </c>
       <c r="R7">
-        <v>-3.3500612307447998E-8</v>
+        <v>-7.7492252143978982E-8</v>
       </c>
       <c r="S7">
-        <v>9.8153138123749723E-9</v>
+        <v>-6.7215954720780031E-6</v>
       </c>
       <c r="T7">
-        <v>2.3738642955860579E-6</v>
+        <v>2.0222620732515234E-4</v>
       </c>
       <c r="U7">
-        <v>-1.0597640867246595E-6</v>
-      </c>
-      <c r="V7">
-        <v>1.4248623538029207E-4</v>
-      </c>
-      <c r="W7">
-        <v>-7.1339167302083472E-5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.45">
+        <v>-1.4668225517273107E-4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>22</v>
       </c>
       <c r="B8">
-        <v>-3.449279352949787E-3</v>
+        <v>1.5804475291118563E-4</v>
       </c>
       <c r="C8">
-        <v>1.426627382113471E-7</v>
+        <v>3.1099242269706228E-7</v>
       </c>
       <c r="D8">
-        <v>-5.8841786333292284E-6</v>
+        <v>-7.1765534734731563E-7</v>
       </c>
       <c r="E8">
-        <v>5.6705086261879623E-8</v>
+        <v>1.8885967671682553E-9</v>
       </c>
       <c r="F8">
-        <v>-2.357063202698037E-5</v>
+        <v>-1.813698985349595E-5</v>
       </c>
       <c r="G8">
-        <v>-3.7772340557620939E-5</v>
+        <v>-6.3533018336514601E-5</v>
       </c>
       <c r="H8">
-        <v>5.7252754356328463E-7</v>
+        <v>4.6926667174429041E-7</v>
       </c>
       <c r="I8">
-        <v>1.0002211703389787E-6</v>
+        <v>1.3936261027134123E-6</v>
       </c>
       <c r="J8">
-        <v>1.5663691944885896E-6</v>
+        <v>1.6938133690807772E-6</v>
       </c>
       <c r="K8">
-        <v>-2.4777930228292852E-6</v>
+        <v>-2.2246676577273958E-6</v>
       </c>
       <c r="L8">
-        <v>-4.0556197383099327E-6</v>
+        <v>-1.5327351296640433E-6</v>
       </c>
       <c r="M8">
-        <v>-4.0597873330843452E-6</v>
+        <v>-1.4558738875667821E-6</v>
       </c>
       <c r="N8">
-        <v>7.7990107241565899E-6</v>
+        <v>-7.7756384650957789E-7</v>
       </c>
       <c r="O8">
-        <v>4.2202690337804907E-6</v>
+        <v>7.7574237496193468E-7</v>
       </c>
       <c r="P8">
-        <v>1.0260164020246128E-7</v>
+        <v>1.4077321424812022E-7</v>
       </c>
       <c r="Q8">
-        <v>1.8121790944371676E-6</v>
+        <v>1.8990739162986638E-6</v>
       </c>
       <c r="R8">
-        <v>-9.3580775300956445E-8</v>
+        <v>1.2009006659913461E-7</v>
       </c>
       <c r="S8">
-        <v>-5.0551416430700296E-7</v>
+        <v>-1.41945531849079E-6</v>
       </c>
       <c r="T8">
-        <v>2.7901328274622864E-6</v>
+        <v>3.1740002688147276E-5</v>
       </c>
       <c r="U8">
-        <v>-1.3050336012559556E-6</v>
-      </c>
-      <c r="V8">
-        <v>1.6100255253928916E-4</v>
-      </c>
-      <c r="W8">
-        <v>-8.3881507304688877E-5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.45">
+        <v>-3.3730814438468432E-5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>23</v>
       </c>
       <c r="B9">
-        <v>3.6146009348822436E-2</v>
+        <v>-4.3891455670292324E-2</v>
       </c>
       <c r="C9">
-        <v>-3.7084880603664447E-7</v>
+        <v>-6.3607146434105838E-6</v>
       </c>
       <c r="D9">
-        <v>-2.540163134975293E-5</v>
+        <v>-1.7209008254988003E-4</v>
       </c>
       <c r="E9">
-        <v>2.5664571837439581E-7</v>
+        <v>1.7435209782330382E-6</v>
       </c>
       <c r="F9">
-        <v>-6.1710564716978749E-5</v>
+        <v>-3.6437414123013852E-4</v>
       </c>
       <c r="G9">
-        <v>-3.4079829090298148E-5</v>
+        <v>3.2601048389023588E-4</v>
       </c>
       <c r="H9">
-        <v>1.5962264268634294E-6</v>
+        <v>1.3363340363892324E-5</v>
       </c>
       <c r="I9">
-        <v>1.5663691944885896E-6</v>
+        <v>1.6938133690807772E-6</v>
       </c>
       <c r="J9">
-        <v>2.1062253287329811E-3</v>
+        <v>5.5738775019643638E-3</v>
       </c>
       <c r="K9">
-        <v>1.836834620196784E-3</v>
+        <v>4.1797555933629823E-3</v>
       </c>
       <c r="L9">
-        <v>1.8316860588078652E-3</v>
+        <v>4.1822003109149679E-3</v>
       </c>
       <c r="M9">
-        <v>1.8324813797798265E-3</v>
+        <v>4.1663060843376634E-3</v>
       </c>
       <c r="N9">
-        <v>3.6184611053922967E-5</v>
+        <v>-1.1803916288042663E-4</v>
       </c>
       <c r="O9">
-        <v>1.7180071106018847E-5</v>
+        <v>8.857459217771814E-5</v>
       </c>
       <c r="P9">
-        <v>-2.553400153066509E-6</v>
+        <v>-1.1855538644957763E-5</v>
       </c>
       <c r="Q9">
-        <v>7.381091666825412E-6</v>
+        <v>6.0633252841709387E-6</v>
       </c>
       <c r="R9">
-        <v>-8.2137912488988113E-7</v>
+        <v>2.3623519637163027E-6</v>
       </c>
       <c r="S9">
-        <v>-4.5526137591991797E-6</v>
+        <v>-1.6076130827024626E-4</v>
       </c>
       <c r="T9">
-        <v>2.9314539417184183E-5</v>
+        <v>4.7508719705828057E-4</v>
       </c>
       <c r="U9">
-        <v>-5.3787837133823911E-6</v>
-      </c>
-      <c r="V9">
-        <v>-1.1754736240627934E-3</v>
-      </c>
-      <c r="W9">
-        <v>-3.6194870595737623E-4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.45">
+        <v>-3.7408359453159892E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>24</v>
       </c>
       <c r="B10">
-        <v>3.6740312485211028E-2</v>
+        <v>-0.11044663387961527</v>
       </c>
       <c r="C10">
-        <v>1.4129040881132856E-6</v>
+        <v>3.8440363792378153E-7</v>
       </c>
       <c r="D10">
-        <v>3.2703675722657206E-5</v>
+        <v>3.7940281876692349E-5</v>
       </c>
       <c r="E10">
-        <v>-3.2565318431923075E-7</v>
+        <v>-3.8909253363848838E-7</v>
       </c>
       <c r="F10">
-        <v>7.7171593957509082E-5</v>
+        <v>7.4279409165906165E-5</v>
       </c>
       <c r="G10">
-        <v>6.3380973823649167E-5</v>
+        <v>2.2955663997336599E-5</v>
       </c>
       <c r="H10">
-        <v>-1.9606571559199221E-6</v>
+        <v>-2.7638759478830496E-6</v>
       </c>
       <c r="I10">
-        <v>-2.4777930228292852E-6</v>
+        <v>-2.2246676577273958E-6</v>
       </c>
       <c r="J10">
-        <v>1.836834620196784E-3</v>
+        <v>4.1797555933629823E-3</v>
       </c>
       <c r="K10">
-        <v>1.9055937108851176E-3</v>
+        <v>4.4599082408250416E-3</v>
       </c>
       <c r="L10">
-        <v>1.8761558155290328E-3</v>
+        <v>4.2641994068801101E-3</v>
       </c>
       <c r="M10">
-        <v>1.8763102210595686E-3</v>
+        <v>4.2640008965946757E-3</v>
       </c>
       <c r="N10">
-        <v>-4.2465302452158812E-5</v>
+        <v>1.6224346374568973E-5</v>
       </c>
       <c r="O10">
-        <v>-2.3796836505771281E-5</v>
+        <v>-2.6834768102195747E-5</v>
       </c>
       <c r="P10">
-        <v>-4.338520810470387E-6</v>
+        <v>-5.1541275405934642E-6</v>
       </c>
       <c r="Q10">
-        <v>-1.0682151576128863E-5</v>
+        <v>-3.4640216728461011E-5</v>
       </c>
       <c r="R10">
-        <v>1.2291135965287135E-6</v>
+        <v>-4.9895580883846182E-7</v>
       </c>
       <c r="S10">
-        <v>1.3930702664055563E-5</v>
+        <v>4.0548109607782179E-5</v>
       </c>
       <c r="T10">
-        <v>2.8579166551748782E-6</v>
+        <v>-5.2295556058031614E-3</v>
       </c>
       <c r="U10">
-        <v>6.3538034709517348E-6</v>
-      </c>
-      <c r="V10">
-        <v>-2.750179872518705E-3</v>
-      </c>
-      <c r="W10">
-        <v>4.9904101544946764E-4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.45">
+        <v>7.8270386951266883E-4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>25</v>
       </c>
       <c r="B11">
-        <v>3.6978234740322739E-2</v>
+        <v>-8.4154680587342004E-2</v>
       </c>
       <c r="C11">
-        <v>1.3478501141988566E-6</v>
+        <v>-2.9221140068869368E-6</v>
       </c>
       <c r="D11">
-        <v>5.6300441924130787E-5</v>
+        <v>3.3600878968898944E-5</v>
       </c>
       <c r="E11">
-        <v>-5.6007045846756847E-7</v>
+        <v>-3.4020700249857606E-7</v>
       </c>
       <c r="F11">
-        <v>1.3302421491643581E-4</v>
+        <v>6.631788429553294E-5</v>
       </c>
       <c r="G11">
-        <v>1.0285443519936444E-4</v>
+        <v>2.3524683180634687E-7</v>
       </c>
       <c r="H11">
-        <v>-3.3716940174969441E-6</v>
+        <v>-2.494794715941288E-6</v>
       </c>
       <c r="I11">
-        <v>-4.0556197383099327E-6</v>
+        <v>-1.5327351296640433E-6</v>
       </c>
       <c r="J11">
-        <v>1.8316860588078652E-3</v>
+        <v>4.1822003109149679E-3</v>
       </c>
       <c r="K11">
-        <v>1.8761558155290328E-3</v>
+        <v>4.2641994068801101E-3</v>
       </c>
       <c r="L11">
-        <v>1.907242560913365E-3</v>
+        <v>4.304270918784125E-3</v>
       </c>
       <c r="M11">
-        <v>1.8993070393110143E-3</v>
+        <v>4.266727767872785E-3</v>
       </c>
       <c r="N11">
-        <v>-7.32204663600155E-5</v>
+        <v>1.5845030855779911E-5</v>
       </c>
       <c r="O11">
-        <v>-4.0966640079084679E-5</v>
+        <v>-2.8620039535931719E-5</v>
       </c>
       <c r="P11">
-        <v>-6.1134282176976586E-6</v>
+        <v>-3.4651590291337226E-6</v>
       </c>
       <c r="Q11">
-        <v>-1.8775840803964985E-5</v>
+        <v>-8.1097074513955124E-7</v>
       </c>
       <c r="R11">
-        <v>2.0551628121100457E-6</v>
+        <v>-5.8620454134168989E-6</v>
       </c>
       <c r="S11">
-        <v>3.0636856456968994E-5</v>
+        <v>3.6624208365914773E-5</v>
       </c>
       <c r="T11">
-        <v>-2.8332843778281255E-6</v>
+        <v>-5.1572529014125568E-3</v>
       </c>
       <c r="U11">
-        <v>1.0493262944508814E-5</v>
-      </c>
-      <c r="V11">
-        <v>-3.4062851109594606E-3</v>
-      </c>
-      <c r="W11">
-        <v>8.4688284908119779E-4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.45">
+        <v>7.2708015208512201E-4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>26</v>
       </c>
       <c r="B12">
-        <v>4.2913822300698422E-2</v>
+        <v>-7.4607083648567551E-2</v>
       </c>
       <c r="C12">
-        <v>1.0375116457096504E-6</v>
+        <v>-3.6594190018443604E-6</v>
       </c>
       <c r="D12">
-        <v>5.559680290513329E-5</v>
+        <v>4.078854008343755E-5</v>
       </c>
       <c r="E12">
-        <v>-5.503446542352879E-7</v>
+        <v>-4.0428589305832336E-7</v>
       </c>
       <c r="F12">
-        <v>1.3163072179445904E-4</v>
+        <v>7.8298315096359664E-5</v>
       </c>
       <c r="G12">
-        <v>1.0658971475805844E-4</v>
+        <v>-1.0952322238119691E-5</v>
       </c>
       <c r="H12">
-        <v>-3.3191059559450883E-6</v>
+        <v>-2.8796096422015379E-6</v>
       </c>
       <c r="I12">
-        <v>-4.0597873330843452E-6</v>
+        <v>-1.4558738875667821E-6</v>
       </c>
       <c r="J12">
-        <v>1.8324813797798265E-3</v>
+        <v>4.1663060843376634E-3</v>
       </c>
       <c r="K12">
-        <v>1.8763102210595686E-3</v>
+        <v>4.2640008965946757E-3</v>
       </c>
       <c r="L12">
-        <v>1.8993070393110143E-3</v>
+        <v>4.266727767872785E-3</v>
       </c>
       <c r="M12">
-        <v>1.9453502921422863E-3</v>
+        <v>4.2987595346222762E-3</v>
       </c>
       <c r="N12">
-        <v>-7.131298125782464E-5</v>
+        <v>1.6473391570085116E-5</v>
       </c>
       <c r="O12">
-        <v>-3.8954860224197613E-5</v>
+        <v>-3.790877498557876E-5</v>
       </c>
       <c r="P12">
-        <v>-3.9108617258394377E-6</v>
+        <v>-2.3632442730154072E-6</v>
       </c>
       <c r="Q12">
-        <v>-1.7327950802995363E-5</v>
+        <v>-1.5476522138213294E-5</v>
       </c>
       <c r="R12">
-        <v>3.1371917244796915E-6</v>
+        <v>-6.7220670584399397E-6</v>
       </c>
       <c r="S12">
-        <v>5.6268678595463889E-5</v>
+        <v>3.9331344733839463E-5</v>
       </c>
       <c r="T12">
-        <v>-2.0125873921162316E-6</v>
+        <v>-5.3573670549304899E-3</v>
       </c>
       <c r="U12">
-        <v>6.182308034329773E-6</v>
-      </c>
-      <c r="V12">
-        <v>-3.4190645496195793E-3</v>
-      </c>
-      <c r="W12">
-        <v>8.2353806270582476E-4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.45">
+        <v>8.647467645670065E-4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B13">
-        <v>-6.2786905017787303E-2</v>
+        <v>-2.568813524133727E-2</v>
       </c>
       <c r="C13">
-        <v>5.7398308912253866E-7</v>
+        <v>3.5135483902333456E-6</v>
       </c>
       <c r="D13">
-        <v>-1.0746006814810015E-4</v>
+        <v>5.5136692772434005E-5</v>
       </c>
       <c r="E13">
-        <v>1.0781525743160867E-6</v>
+        <v>-5.6065622020098916E-7</v>
       </c>
       <c r="F13">
-        <v>-2.536675896453388E-4</v>
+        <v>9.9303941158715165E-5</v>
       </c>
       <c r="G13">
-        <v>-1.9197720208730812E-4</v>
+        <v>-1.1215207575576643E-4</v>
       </c>
       <c r="H13">
-        <v>6.5476651279201855E-6</v>
+        <v>-4.0838548655603047E-6</v>
       </c>
       <c r="I13">
-        <v>7.7990107241565899E-6</v>
+        <v>-7.7756384650957789E-7</v>
       </c>
       <c r="J13">
-        <v>3.6184611053922967E-5</v>
+        <v>-1.1803916288042663E-4</v>
       </c>
       <c r="K13">
-        <v>-4.2465302452158812E-5</v>
+        <v>1.6224346374568973E-5</v>
       </c>
       <c r="L13">
-        <v>-7.32204663600155E-5</v>
+        <v>1.5845030855779911E-5</v>
       </c>
       <c r="M13">
-        <v>-7.131298125782464E-5</v>
+        <v>1.6473391570085116E-5</v>
       </c>
       <c r="N13">
-        <v>2.1407971357716271E-4</v>
+        <v>1.5596066342240812E-4</v>
       </c>
       <c r="O13">
-        <v>1.0062938331568394E-4</v>
+        <v>2.1323912915937235E-5</v>
       </c>
       <c r="P13">
-        <v>2.671941348306832E-5</v>
+        <v>-9.0089823011908898E-7</v>
       </c>
       <c r="Q13">
-        <v>5.7826264804505199E-5</v>
+        <v>1.163581100916914E-5</v>
       </c>
       <c r="R13">
-        <v>-3.8142493212426126E-6</v>
+        <v>-7.8217993877330865E-6</v>
       </c>
       <c r="S13">
-        <v>4.0443986987236523E-6</v>
+        <v>5.8167725188375754E-5</v>
       </c>
       <c r="T13">
-        <v>5.3783725873561484E-5</v>
+        <v>-1.5561830990838393E-3</v>
       </c>
       <c r="U13">
-        <v>-2.3192887817426128E-5</v>
-      </c>
-      <c r="V13">
-        <v>2.8248111853020497E-3</v>
-      </c>
-      <c r="W13">
-        <v>-1.5784969544392696E-3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.45">
+        <v>1.1915622719449789E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B14">
-        <v>-3.6690909025168139E-2</v>
+        <v>-5.1687945953892415E-2</v>
       </c>
       <c r="C14">
-        <v>7.7075650811588849E-7</v>
+        <v>4.6027290081153889E-6</v>
       </c>
       <c r="D14">
-        <v>-5.7565696572321141E-5</v>
+        <v>-4.8525121217208445E-5</v>
       </c>
       <c r="E14">
-        <v>5.7533296806500287E-7</v>
+        <v>4.8979998580436864E-7</v>
       </c>
       <c r="F14">
-        <v>-1.4153668741321608E-4</v>
+        <v>-1.1550260112877276E-4</v>
       </c>
       <c r="G14">
-        <v>-1.0328493783283753E-4</v>
+        <v>6.1388476342005854E-5</v>
       </c>
       <c r="H14">
-        <v>3.6464293863072883E-6</v>
+        <v>3.9416203266348401E-6</v>
       </c>
       <c r="I14">
-        <v>4.2202690337804907E-6</v>
+        <v>7.7574237496193468E-7</v>
       </c>
       <c r="J14">
-        <v>1.7180071106018847E-5</v>
+        <v>8.857459217771814E-5</v>
       </c>
       <c r="K14">
-        <v>-2.3796836505771281E-5</v>
+        <v>-2.6834768102195747E-5</v>
       </c>
       <c r="L14">
-        <v>-4.0966640079084679E-5</v>
+        <v>-2.8620039535931719E-5</v>
       </c>
       <c r="M14">
-        <v>-3.8954860224197613E-5</v>
+        <v>-3.790877498557876E-5</v>
       </c>
       <c r="N14">
-        <v>1.0062938331568394E-4</v>
+        <v>2.1323912915937235E-5</v>
       </c>
       <c r="O14">
-        <v>1.7269037588486081E-4</v>
+        <v>1.0252414620196049E-4</v>
       </c>
       <c r="P14">
-        <v>2.5180825863007809E-5</v>
+        <v>-6.0506874897368079E-6</v>
       </c>
       <c r="Q14">
-        <v>4.1947629783644746E-5</v>
+        <v>-5.333638587673852E-5</v>
       </c>
       <c r="R14">
-        <v>-3.970860629549847E-6</v>
+        <v>1.5715042321958162E-6</v>
       </c>
       <c r="S14">
-        <v>-9.4241981174902815E-6</v>
+        <v>-4.2449584481618208E-5</v>
       </c>
       <c r="T14">
-        <v>2.8203438483300844E-5</v>
+        <v>1.3368772944533929E-3</v>
       </c>
       <c r="U14">
-        <v>-1.4177483850043127E-5</v>
-      </c>
-      <c r="V14">
-        <v>1.51914610809646E-3</v>
-      </c>
-      <c r="W14">
-        <v>-8.4625518848837256E-4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.45">
+        <v>-1.0213636773996086E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="B15">
-        <v>3.7913005940314096E-3</v>
+        <v>0.21819316223464902</v>
       </c>
       <c r="C15">
-        <v>-2.9784157159202246E-7</v>
+        <v>-2.1637286615195698E-6</v>
       </c>
       <c r="D15">
-        <v>-2.7754129565687366E-6</v>
+        <v>2.0227647801336496E-6</v>
       </c>
       <c r="E15">
-        <v>2.8281866792697337E-8</v>
+        <v>-2.1776161982176701E-8</v>
       </c>
       <c r="F15">
-        <v>-6.6659062486234025E-6</v>
+        <v>-9.0069218443686958E-6</v>
       </c>
       <c r="G15">
-        <v>2.0422376462822073E-7</v>
+        <v>-1.008149083633379E-5</v>
       </c>
       <c r="H15">
-        <v>1.6099206125369656E-7</v>
+        <v>2.2231485827970002E-7</v>
       </c>
       <c r="I15">
-        <v>1.0260164020246128E-7</v>
+        <v>1.4077321424812022E-7</v>
       </c>
       <c r="J15">
-        <v>-2.553400153066509E-6</v>
+        <v>-1.1855538644957763E-5</v>
       </c>
       <c r="K15">
-        <v>-4.338520810470387E-6</v>
+        <v>-5.1541275405934642E-6</v>
       </c>
       <c r="L15">
-        <v>-6.1134282176976586E-6</v>
+        <v>-3.4651590291337226E-6</v>
       </c>
       <c r="M15">
-        <v>-3.9108617258394377E-6</v>
+        <v>-2.3632442730154072E-6</v>
       </c>
       <c r="N15">
-        <v>2.671941348306832E-5</v>
+        <v>-9.0089823011908898E-7</v>
       </c>
       <c r="O15">
-        <v>2.5180825863007809E-5</v>
+        <v>-6.0506874897368079E-6</v>
       </c>
       <c r="P15">
-        <v>4.4479702942609576E-5</v>
+        <v>9.1436484934081751E-5</v>
       </c>
       <c r="Q15">
-        <v>2.4100973915409327E-5</v>
+        <v>-3.2521541333749049E-5</v>
       </c>
       <c r="R15">
-        <v>-6.8818256352395403E-7</v>
+        <v>3.4209545550742377E-6</v>
       </c>
       <c r="S15">
-        <v>-1.1665975927933552E-5</v>
+        <v>5.0054903447701701E-6</v>
       </c>
       <c r="T15">
-        <v>1.222620573190338E-6</v>
+        <v>-2.2696171234633265E-5</v>
       </c>
       <c r="U15">
-        <v>-2.2647862753571203E-6</v>
-      </c>
-      <c r="V15">
-        <v>6.5999442224629626E-5</v>
-      </c>
-      <c r="W15">
-        <v>-4.0579380572970645E-5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.45">
+        <v>2.6371945460480941E-5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="B16">
-        <v>-3.6365925836343155E-2</v>
+        <v>-0.53551084427280216</v>
       </c>
       <c r="C16">
-        <v>1.5001927198533433E-6</v>
+        <v>1.6071421113095425E-6</v>
       </c>
       <c r="D16">
-        <v>-2.5813570343207516E-5</v>
+        <v>-2.4247127969965733E-6</v>
       </c>
       <c r="E16">
-        <v>2.5846477606465287E-7</v>
+        <v>5.2324652763723268E-8</v>
       </c>
       <c r="F16">
-        <v>-6.329812428127924E-5</v>
+        <v>-6.133358385325096E-5</v>
       </c>
       <c r="G16">
-        <v>-4.083919170041362E-5</v>
+        <v>-1.7590527124388252E-4</v>
       </c>
       <c r="H16">
-        <v>1.6385784382750396E-6</v>
+        <v>1.2747633177756428E-6</v>
       </c>
       <c r="I16">
-        <v>1.8121790944371676E-6</v>
+        <v>1.8990739162986638E-6</v>
       </c>
       <c r="J16">
-        <v>7.381091666825412E-6</v>
+        <v>6.0633252841709387E-6</v>
       </c>
       <c r="K16">
-        <v>-1.0682151576128863E-5</v>
+        <v>-3.4640216728461011E-5</v>
       </c>
       <c r="L16">
-        <v>-1.8775840803964985E-5</v>
+        <v>-8.1097074513955124E-7</v>
       </c>
       <c r="M16">
-        <v>-1.7327950802995363E-5</v>
+        <v>-1.5476522138213294E-5</v>
       </c>
       <c r="N16">
-        <v>5.7826264804505199E-5</v>
+        <v>1.163581100916914E-5</v>
       </c>
       <c r="O16">
-        <v>4.1947629783644746E-5</v>
+        <v>-5.333638587673852E-5</v>
       </c>
       <c r="P16">
-        <v>2.4100973915409327E-5</v>
+        <v>-3.2521541333749049E-5</v>
       </c>
       <c r="Q16">
-        <v>5.5310630585243274E-5</v>
+        <v>1.2572723998411185E-2</v>
       </c>
       <c r="R16">
-        <v>-3.5587051547677424E-7</v>
+        <v>-3.3423098011658764E-4</v>
       </c>
       <c r="S16">
-        <v>9.7628022692527762E-6</v>
+        <v>-5.9033952317516222E-5</v>
       </c>
       <c r="T16">
-        <v>1.1471251804363177E-5</v>
+        <v>-1.2297435254865629E-2</v>
       </c>
       <c r="U16">
-        <v>-6.7615312172203561E-6</v>
-      </c>
-      <c r="V16">
-        <v>6.4989906821625904E-4</v>
-      </c>
-      <c r="W16">
-        <v>-3.7794635132694523E-4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.45">
+        <v>5.15279944403783E-5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B17">
-        <v>0.15740567496528374</v>
+        <v>7.2252506531975735E-2</v>
       </c>
       <c r="C17">
-        <v>1.3906312380880917E-6</v>
+        <v>-2.5374116243815132E-6</v>
       </c>
       <c r="D17">
-        <v>1.627180787194121E-6</v>
+        <v>-4.8391164136628428E-7</v>
       </c>
       <c r="E17">
-        <v>-1.5991186959250754E-8</v>
+        <v>1.1649462992848133E-9</v>
       </c>
       <c r="F17">
-        <v>1.610155841920046E-7</v>
+        <v>5.8403213702296391E-6</v>
       </c>
       <c r="G17">
-        <v>-1.8121544406037796E-6</v>
+        <v>2.6103277936852485E-6</v>
       </c>
       <c r="H17">
-        <v>-3.3500612307447998E-8</v>
+        <v>-7.7492252143978982E-8</v>
       </c>
       <c r="I17">
-        <v>-9.3580775300956445E-8</v>
+        <v>1.2009006659913461E-7</v>
       </c>
       <c r="J17">
-        <v>-8.2137912488988113E-7</v>
+        <v>2.3623519637163027E-6</v>
       </c>
       <c r="K17">
-        <v>1.2291135965287135E-6</v>
+        <v>-4.9895580883846182E-7</v>
       </c>
       <c r="L17">
-        <v>2.0551628121100457E-6</v>
+        <v>-5.8620454134168989E-6</v>
       </c>
       <c r="M17">
-        <v>3.1371917244796915E-6</v>
+        <v>-6.7220670584399397E-6</v>
       </c>
       <c r="N17">
-        <v>-3.8142493212426126E-6</v>
+        <v>-7.8217993877330865E-6</v>
       </c>
       <c r="O17">
-        <v>-3.970860629549847E-6</v>
+        <v>1.5715042321958162E-6</v>
       </c>
       <c r="P17">
-        <v>-6.8818256352395403E-7</v>
+        <v>3.4209545550742377E-6</v>
       </c>
       <c r="Q17">
-        <v>-3.5587051547677424E-7</v>
+        <v>-3.3423098011658764E-4</v>
       </c>
       <c r="R17">
-        <v>4.1438530826023537E-5</v>
+        <v>1.5695919880497528E-4</v>
       </c>
       <c r="S17">
-        <v>3.264676691871017E-5</v>
+        <v>1.5241574608089785E-5</v>
       </c>
       <c r="T17">
-        <v>-5.2613657812706994E-6</v>
+        <v>3.4966042221498206E-4</v>
       </c>
       <c r="U17">
-        <v>-2.626628956494159E-6</v>
-      </c>
-      <c r="V17">
-        <v>-8.6812781026367354E-5</v>
-      </c>
-      <c r="W17">
-        <v>2.6232957421267347E-5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.45">
+        <v>-4.273164986400144E-5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B18">
-        <v>0.48015576231408746</v>
+        <v>2.5829438695206475E-2</v>
       </c>
       <c r="C18">
-        <v>-7.0691951341782136E-6</v>
+        <v>-1.6414537382816952E-6</v>
       </c>
       <c r="D18">
-        <v>5.467962896406415E-6</v>
+        <v>8.5029570664378222E-5</v>
       </c>
       <c r="E18">
-        <v>-2.5448308861917681E-8</v>
+        <v>-8.662661218887003E-7</v>
       </c>
       <c r="F18">
-        <v>-3.9226460914701242E-5</v>
+        <v>1.8551643582976764E-4</v>
       </c>
       <c r="G18">
-        <v>-5.8921022495535959E-5</v>
+        <v>-1.2721917423309689E-4</v>
       </c>
       <c r="H18">
-        <v>9.8153138123749723E-9</v>
+        <v>-6.7215954720780031E-6</v>
       </c>
       <c r="I18">
-        <v>-5.0551416430700296E-7</v>
+        <v>-1.41945531849079E-6</v>
       </c>
       <c r="J18">
-        <v>-4.5526137591991797E-6</v>
+        <v>-1.6076130827024626E-4</v>
       </c>
       <c r="K18">
-        <v>1.3930702664055563E-5</v>
+        <v>4.0548109607782179E-5</v>
       </c>
       <c r="L18">
-        <v>3.0636856456968994E-5</v>
+        <v>3.6624208365914773E-5</v>
       </c>
       <c r="M18">
-        <v>5.6268678595463889E-5</v>
+        <v>3.9331344733839463E-5</v>
       </c>
       <c r="N18">
-        <v>4.0443986987236523E-6</v>
+        <v>5.8167725188375754E-5</v>
       </c>
       <c r="O18">
-        <v>-9.4241981174902815E-6</v>
+        <v>-4.2449584481618208E-5</v>
       </c>
       <c r="P18">
-        <v>-1.1665975927933552E-5</v>
+        <v>5.0054903447701701E-6</v>
       </c>
       <c r="Q18">
-        <v>9.7628022692527762E-6</v>
+        <v>-5.9033952317516222E-5</v>
       </c>
       <c r="R18">
-        <v>3.264676691871017E-5</v>
+        <v>1.5241574608089785E-5</v>
       </c>
       <c r="S18">
-        <v>2.9054198014762712E-2</v>
+        <v>4.8637198705920524E-4</v>
       </c>
       <c r="T18">
-        <v>-1.3551738159395081E-3</v>
+        <v>-2.2684931991448476E-3</v>
       </c>
       <c r="U18">
-        <v>-1.8630420779778591E-4</v>
-      </c>
-      <c r="V18">
-        <v>-2.904110621973164E-2</v>
-      </c>
-      <c r="W18">
-        <v>1.9977937923217913E-4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.45">
+        <v>1.8068068332244554E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B19">
-        <v>-3.2030001731774463E-2</v>
+        <v>1.1116238100308307</v>
       </c>
       <c r="C19">
-        <v>-7.5948170724471779E-7</v>
+        <v>-5.1187967636433514E-5</v>
       </c>
       <c r="D19">
-        <v>-3.9780246746363259E-5</v>
+        <v>-2.5828106685665091E-3</v>
       </c>
       <c r="E19">
-        <v>3.9794192450660095E-7</v>
+        <v>2.6315024181110647E-5</v>
       </c>
       <c r="F19">
-        <v>-8.8653091652942132E-5</v>
+        <v>-5.8462323867154485E-3</v>
       </c>
       <c r="G19">
-        <v>-5.9915900245017501E-5</v>
+        <v>4.1072258374827524E-3</v>
       </c>
       <c r="H19">
-        <v>2.3738642955860579E-6</v>
+        <v>2.0222620732515234E-4</v>
       </c>
       <c r="I19">
-        <v>2.7901328274622864E-6</v>
+        <v>3.1740002688147276E-5</v>
       </c>
       <c r="J19">
-        <v>2.9314539417184183E-5</v>
+        <v>4.7508719705828057E-4</v>
       </c>
       <c r="K19">
-        <v>2.8579166551748782E-6</v>
+        <v>-5.2295556058031614E-3</v>
       </c>
       <c r="L19">
-        <v>-2.8332843778281255E-6</v>
+        <v>-5.1572529014125568E-3</v>
       </c>
       <c r="M19">
-        <v>-2.0125873921162316E-6</v>
+        <v>-5.3573670549304899E-3</v>
       </c>
       <c r="N19">
-        <v>5.3783725873561484E-5</v>
+        <v>-1.5561830990838393E-3</v>
       </c>
       <c r="O19">
-        <v>2.8203438483300844E-5</v>
+        <v>1.3368772944533929E-3</v>
       </c>
       <c r="P19">
-        <v>1.222620573190338E-6</v>
+        <v>-2.2696171234633265E-5</v>
       </c>
       <c r="Q19">
-        <v>1.1471251804363177E-5</v>
+        <v>-1.2297435254865629E-2</v>
       </c>
       <c r="R19">
-        <v>-5.2613657812706994E-6</v>
+        <v>3.4966042221498206E-4</v>
       </c>
       <c r="S19">
-        <v>-1.3551738159395081E-3</v>
+        <v>-2.2684931991448476E-3</v>
       </c>
       <c r="T19">
-        <v>1.5146730138316944E-4</v>
+        <v>8.5859695855301343E-2</v>
       </c>
       <c r="U19">
-        <v>7.6094633783630541E-6</v>
-      </c>
-      <c r="V19">
-        <v>2.3752172976495849E-3</v>
-      </c>
-      <c r="W19">
-        <v>-5.9669651050922221E-4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.45">
+        <v>-5.0954484881990655E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B20">
-        <v>1.0533777099858411E-2</v>
+        <v>-0.23352263357129702</v>
       </c>
       <c r="C20">
-        <v>8.6317135121308638E-7</v>
+        <v>2.8241923374578404E-5</v>
       </c>
       <c r="D20">
-        <v>1.8019385684666995E-5</v>
+        <v>1.8640065982554416E-3</v>
       </c>
       <c r="E20">
-        <v>-1.8334525627835875E-7</v>
+        <v>-1.8913848531903118E-5</v>
       </c>
       <c r="F20">
-        <v>4.3662075074686928E-5</v>
+        <v>4.0242024343237655E-3</v>
       </c>
       <c r="G20">
-        <v>3.7105349461015292E-5</v>
+        <v>-2.7713591052152611E-3</v>
       </c>
       <c r="H20">
-        <v>-1.0597640867246595E-6</v>
+        <v>-1.4668225517273107E-4</v>
       </c>
       <c r="I20">
-        <v>-1.3050336012559556E-6</v>
+        <v>-3.3730814438468432E-5</v>
       </c>
       <c r="J20">
-        <v>-5.3787837133823911E-6</v>
+        <v>-3.7408359453159892E-3</v>
       </c>
       <c r="K20">
-        <v>6.3538034709517348E-6</v>
+        <v>7.8270386951266883E-4</v>
       </c>
       <c r="L20">
-        <v>1.0493262944508814E-5</v>
+        <v>7.2708015208512201E-4</v>
       </c>
       <c r="M20">
-        <v>6.182308034329773E-6</v>
+        <v>8.647467645670065E-4</v>
       </c>
       <c r="N20">
-        <v>-2.3192887817426128E-5</v>
+        <v>1.1915622719449789E-3</v>
       </c>
       <c r="O20">
-        <v>-1.4177483850043127E-5</v>
+        <v>-1.0213636773996086E-3</v>
       </c>
       <c r="P20">
-        <v>-2.2647862753571203E-6</v>
+        <v>2.6371945460480941E-5</v>
       </c>
       <c r="Q20">
-        <v>-6.7615312172203561E-6</v>
+        <v>5.15279944403783E-5</v>
       </c>
       <c r="R20">
-        <v>-2.626628956494159E-6</v>
+        <v>-4.273164986400144E-5</v>
       </c>
       <c r="S20">
-        <v>-1.8630420779778591E-4</v>
+        <v>1.8068068332244554E-3</v>
       </c>
       <c r="T20">
-        <v>7.6094633783630541E-6</v>
+        <v>-5.0954484881990655E-2</v>
       </c>
       <c r="U20">
-        <v>1.1630635122169052E-4</v>
-      </c>
-      <c r="V20">
-        <v>-2.9439591014323641E-4</v>
-      </c>
-      <c r="W20">
-        <v>2.5389509136379936E-4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
-        <v>31</v>
-      </c>
-      <c r="B21">
-        <v>0.11509229884264148</v>
-      </c>
-      <c r="C21">
-        <v>-7.4086508817265836E-5</v>
-      </c>
-      <c r="D21">
-        <v>-2.2652255543339898E-3</v>
-      </c>
-      <c r="E21">
-        <v>2.2736778076506119E-5</v>
-      </c>
-      <c r="F21">
-        <v>-5.6321439965972223E-3</v>
-      </c>
-      <c r="G21">
-        <v>-4.0411483732586111E-3</v>
-      </c>
-      <c r="H21">
-        <v>1.4248623538029207E-4</v>
-      </c>
-      <c r="I21">
-        <v>1.6100255253928916E-4</v>
-      </c>
-      <c r="J21">
-        <v>-1.1754736240627934E-3</v>
-      </c>
-      <c r="K21">
-        <v>-2.750179872518705E-3</v>
-      </c>
-      <c r="L21">
-        <v>-3.4062851109594606E-3</v>
-      </c>
-      <c r="M21">
-        <v>-3.4190645496195793E-3</v>
-      </c>
-      <c r="N21">
-        <v>2.8248111853020497E-3</v>
-      </c>
-      <c r="O21">
-        <v>1.51914610809646E-3</v>
-      </c>
-      <c r="P21">
-        <v>6.5999442224629626E-5</v>
-      </c>
-      <c r="Q21">
-        <v>6.4989906821625904E-4</v>
-      </c>
-      <c r="R21">
-        <v>-8.6812781026367354E-5</v>
-      </c>
-      <c r="S21">
-        <v>-2.904110621973164E-2</v>
-      </c>
-      <c r="T21">
-        <v>2.3752172976495849E-3</v>
-      </c>
-      <c r="U21">
-        <v>-2.9439591014323641E-4</v>
-      </c>
-      <c r="V21">
-        <v>9.0830545642533622E-2</v>
-      </c>
-      <c r="W21">
-        <v>-3.1806348184477369E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A22" t="s">
-        <v>32</v>
-      </c>
-      <c r="B22">
-        <v>3.265821705265709E-2</v>
-      </c>
-      <c r="C22">
-        <v>3.2240865191396875E-5</v>
-      </c>
-      <c r="D22">
-        <v>1.1875109946579677E-3</v>
-      </c>
-      <c r="E22">
-        <v>-1.1937540316577405E-5</v>
-      </c>
-      <c r="F22">
-        <v>2.7802959490674716E-3</v>
-      </c>
-      <c r="G22">
-        <v>2.0359568289005175E-3</v>
-      </c>
-      <c r="H22">
-        <v>-7.1339167302083472E-5</v>
-      </c>
-      <c r="I22">
-        <v>-8.3881507304688877E-5</v>
-      </c>
-      <c r="J22">
-        <v>-3.6194870595737623E-4</v>
-      </c>
-      <c r="K22">
-        <v>4.9904101544946764E-4</v>
-      </c>
-      <c r="L22">
-        <v>8.4688284908119779E-4</v>
-      </c>
-      <c r="M22">
-        <v>8.2353806270582476E-4</v>
-      </c>
-      <c r="N22">
-        <v>-1.5784969544392696E-3</v>
-      </c>
-      <c r="O22">
-        <v>-8.4625518848837256E-4</v>
-      </c>
-      <c r="P22">
-        <v>-4.0579380572970645E-5</v>
-      </c>
-      <c r="Q22">
-        <v>-3.7794635132694523E-4</v>
-      </c>
-      <c r="R22">
-        <v>2.6232957421267347E-5</v>
-      </c>
-      <c r="S22">
-        <v>1.9977937923217913E-4</v>
-      </c>
-      <c r="T22">
-        <v>-5.9669651050922221E-4</v>
-      </c>
-      <c r="U22">
-        <v>2.5389509136379936E-4</v>
-      </c>
-      <c r="V22">
-        <v>-3.1806348184477369E-2</v>
-      </c>
-      <c r="W22">
-        <v>1.7410829615613594E-2</v>
+        <v>4.0013143377933151E-2</v>
       </c>
     </row>
   </sheetData>
@@ -5074,15 +4296,14 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73F2BEA0-597B-4485-ACA5-1CD080E9A9A0}">
-  <dimension ref="A1:W22"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02BCCC82-57D2-4C56-AE59-3F571BDBC9FF}">
+  <dimension ref="A1:U20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.1328125" style="3" customWidth="1"/>
-    <col min="2" max="16384" width="8.796875" style="3"/>
+    <col min="1" max="1" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -5123,1525 +4344,1263 @@
         <v>26</v>
       </c>
       <c r="N1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="Q1" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="R1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="S1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="T1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="U1" t="s">
-        <v>30</v>
-      </c>
-      <c r="V1" t="s">
-        <v>31</v>
-      </c>
-      <c r="W1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>33</v>
       </c>
       <c r="B2">
-        <v>0.71835254988724717</v>
+        <v>0.6464311948383431</v>
       </c>
       <c r="C2">
-        <v>1.6303351396028679E-5</v>
+        <v>2.1525724936193362E-5</v>
       </c>
       <c r="D2">
-        <v>1.7547339333539598E-7</v>
+        <v>3.6459842074238659E-8</v>
       </c>
       <c r="E2">
-        <v>-4.4945874167293671E-9</v>
+        <v>-4.2252569616882885E-9</v>
       </c>
       <c r="F2">
-        <v>1.4090401949160334E-6</v>
+        <v>-2.0554704484303957E-6</v>
       </c>
       <c r="G2">
-        <v>1.5004864624340579E-6</v>
+        <v>-4.5006462940247194E-7</v>
       </c>
       <c r="H2">
-        <v>7.2056975055918557E-8</v>
+        <v>1.8128937740921625E-7</v>
       </c>
       <c r="I2">
-        <v>1.2285768535794783E-7</v>
+        <v>2.5567363716093332E-7</v>
       </c>
       <c r="J2">
-        <v>4.9465286511252464E-7</v>
+        <v>-2.2287655080149516E-7</v>
       </c>
       <c r="K2">
-        <v>2.8687659084389223E-6</v>
+        <v>2.7644644421040512E-6</v>
       </c>
       <c r="L2">
-        <v>2.6335966356199407E-6</v>
+        <v>2.8081022101108737E-6</v>
       </c>
       <c r="M2">
-        <v>2.7992277031282489E-6</v>
+        <v>2.7430428857450632E-6</v>
       </c>
       <c r="N2">
-        <v>2.9718236342099566E-6</v>
+        <v>4.7364175858175044E-6</v>
       </c>
       <c r="O2">
-        <v>2.8473061505325477E-6</v>
+        <v>5.0539195195592791E-6</v>
       </c>
       <c r="P2">
-        <v>1.15861999703872E-7</v>
+        <v>-1.9918594693689529E-6</v>
       </c>
       <c r="Q2">
-        <v>1.324184518156341E-6</v>
+        <v>-2.261633797723317E-5</v>
       </c>
       <c r="R2">
-        <v>1.8573554142188454E-6</v>
+        <v>-2.3206980646331955E-6</v>
       </c>
       <c r="S2">
-        <v>-1.8239916828318502E-6</v>
+        <v>-5.375278451964147E-7</v>
       </c>
       <c r="T2">
-        <v>2.8199712562863171E-7</v>
+        <v>-2.8495996887924806E-5</v>
       </c>
       <c r="U2">
-        <v>1.0127149257330256E-6</v>
-      </c>
-      <c r="V2">
-        <v>-5.0012701591296718E-5</v>
-      </c>
-      <c r="W2">
-        <v>2.1378860634480102E-5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.45">
+        <v>3.3400908656451228E-5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>17</v>
       </c>
       <c r="B3">
-        <v>-2.0515540037959162E-2</v>
+        <v>-7.8229336873264031E-3</v>
       </c>
       <c r="C3">
-        <v>1.7547339333539598E-7</v>
+        <v>3.6459842074238659E-8</v>
       </c>
       <c r="D3">
-        <v>2.2441357944678571E-5</v>
+        <v>2.3767965557152226E-5</v>
       </c>
       <c r="E3">
-        <v>-2.2900972211353223E-7</v>
+        <v>-2.5295172784506652E-7</v>
       </c>
       <c r="F3">
-        <v>7.3246045950192825E-5</v>
+        <v>2.7505577306368287E-5</v>
       </c>
       <c r="G3">
-        <v>6.7655169636937244E-5</v>
+        <v>-1.6996497542585478E-5</v>
       </c>
       <c r="H3">
-        <v>-1.5395413879801532E-6</v>
+        <v>-6.5711150787628687E-7</v>
       </c>
       <c r="I3">
-        <v>-1.6938742646853549E-6</v>
+        <v>1.3859879469894194E-7</v>
       </c>
       <c r="J3">
-        <v>2.9813033533101482E-6</v>
+        <v>-5.9686288869017799E-6</v>
       </c>
       <c r="K3">
-        <v>3.1464499328568696E-5</v>
+        <v>2.1815901571309511E-5</v>
       </c>
       <c r="L3">
-        <v>3.9246793016656807E-5</v>
+        <v>3.1767703422975361E-5</v>
       </c>
       <c r="M3">
-        <v>4.2234062237637261E-5</v>
+        <v>3.7126248998635143E-5</v>
       </c>
       <c r="N3">
-        <v>-1.2437899613630297E-5</v>
+        <v>1.6395655201893257E-5</v>
       </c>
       <c r="O3">
-        <v>-1.5764014027498564E-5</v>
+        <v>5.9750754693512659E-6</v>
       </c>
       <c r="P3">
-        <v>4.2467888931914201E-6</v>
+        <v>-7.6871715231379226E-7</v>
       </c>
       <c r="Q3">
-        <v>-2.1119288033155075E-6</v>
+        <v>1.0577363743545562E-5</v>
       </c>
       <c r="R3">
-        <v>-1.2944719989901626E-6</v>
+        <v>-1.1204095755877535E-5</v>
       </c>
       <c r="S3">
-        <v>1.9190157050088914E-5</v>
+        <v>4.4854611064389594E-6</v>
       </c>
       <c r="T3">
-        <v>1.2052841715803317E-7</v>
+        <v>-6.2990448320602069E-4</v>
       </c>
       <c r="U3">
-        <v>2.3051571026915804E-6</v>
-      </c>
-      <c r="V3">
-        <v>-6.2685745198527731E-4</v>
-      </c>
-      <c r="W3">
-        <v>2.9465105283169789E-4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.45">
+        <v>3.243104769141132E-4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
       <c r="B4">
-        <v>2.2551036474475957E-4</v>
+        <v>1.2899197172574716E-4</v>
       </c>
       <c r="C4">
-        <v>-4.4945874167293671E-9</v>
+        <v>-4.2252569616882885E-9</v>
       </c>
       <c r="D4">
-        <v>-2.2900972211353223E-7</v>
+        <v>-2.5295172784506652E-7</v>
       </c>
       <c r="E4">
-        <v>2.3832923850630445E-9</v>
+        <v>2.7329569675016531E-9</v>
       </c>
       <c r="F4">
-        <v>-5.6972855985963401E-7</v>
+        <v>-1.4183838089817926E-7</v>
       </c>
       <c r="G4">
-        <v>-5.0479782193885858E-7</v>
+        <v>3.4614921453495114E-7</v>
       </c>
       <c r="H4">
-        <v>1.1761313779342742E-8</v>
+        <v>3.6277435662496451E-9</v>
       </c>
       <c r="I4">
-        <v>1.3176124712494457E-8</v>
+        <v>-5.1538833228810418E-9</v>
       </c>
       <c r="J4">
-        <v>-3.3462492476694522E-8</v>
+        <v>5.9713635079580149E-8</v>
       </c>
       <c r="K4">
-        <v>-3.2250573770744651E-7</v>
+        <v>-2.3536327206634472E-7</v>
       </c>
       <c r="L4">
-        <v>-3.9887005209638081E-7</v>
+        <v>-3.3861163247316275E-7</v>
       </c>
       <c r="M4">
-        <v>-4.2635381214481957E-7</v>
+        <v>-3.8845059099772941E-7</v>
       </c>
       <c r="N4">
-        <v>1.2524339671124664E-7</v>
+        <v>-1.7643455025132864E-7</v>
       </c>
       <c r="O4">
-        <v>1.5820641188975016E-7</v>
+        <v>-6.6218356420928218E-8</v>
       </c>
       <c r="P4">
-        <v>-4.3608499776935663E-8</v>
+        <v>6.1593021946309984E-9</v>
       </c>
       <c r="Q4">
-        <v>2.0638354094057532E-8</v>
+        <v>-1.0234665606111987E-7</v>
       </c>
       <c r="R4">
-        <v>1.238923164125611E-8</v>
+        <v>1.1778250427632278E-7</v>
       </c>
       <c r="S4">
-        <v>-1.7693622905436588E-7</v>
+        <v>-5.100077019583918E-8</v>
       </c>
       <c r="T4">
-        <v>-2.1626391960687828E-9</v>
+        <v>6.6142515820950594E-6</v>
       </c>
       <c r="U4">
-        <v>-2.5269969845861938E-8</v>
-      </c>
-      <c r="V4">
-        <v>6.2862118604283118E-6</v>
-      </c>
-      <c r="W4">
-        <v>-3.0122832065336327E-6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.45">
+        <v>-3.4596873607089386E-6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>19</v>
       </c>
       <c r="B5">
-        <v>-0.14039038314715069</v>
+        <v>-3.0721983951913143E-2</v>
       </c>
       <c r="C5">
-        <v>1.4090401949160334E-6</v>
+        <v>-2.0554704484303957E-6</v>
       </c>
       <c r="D5">
-        <v>7.3246045950192825E-5</v>
+        <v>2.7505577306368287E-5</v>
       </c>
       <c r="E5">
-        <v>-5.6972855985963401E-7</v>
+        <v>-1.4183838089817926E-7</v>
       </c>
       <c r="F5">
-        <v>1.2674475002104127E-3</v>
+        <v>1.1093131198780595E-3</v>
       </c>
       <c r="G5">
-        <v>9.9626996479717372E-4</v>
+        <v>6.6819361907847824E-4</v>
       </c>
       <c r="H5">
-        <v>-2.6696692483678875E-5</v>
+        <v>-2.367378804988892E-5</v>
       </c>
       <c r="I5">
-        <v>-2.1636183270292765E-5</v>
+        <v>-1.4121749269530696E-5</v>
       </c>
       <c r="J5">
-        <v>-1.3105769678143396E-5</v>
+        <v>1.0643308796671806E-5</v>
       </c>
       <c r="K5">
-        <v>6.8000449396316858E-5</v>
+        <v>1.4220464448169221E-5</v>
       </c>
       <c r="L5">
-        <v>8.7380955628812079E-5</v>
+        <v>7.7784703233698198E-6</v>
       </c>
       <c r="M5">
-        <v>9.4866471937474705E-5</v>
+        <v>9.3721047078729681E-6</v>
       </c>
       <c r="N5">
-        <v>-3.7107296506780204E-5</v>
+        <v>-1.270450407042831E-5</v>
       </c>
       <c r="O5">
-        <v>-4.6972799054695908E-5</v>
+        <v>-8.2624567209048868E-6</v>
       </c>
       <c r="P5">
-        <v>8.9277054095561946E-6</v>
+        <v>-7.015310864216234E-6</v>
       </c>
       <c r="Q5">
-        <v>-8.0531133634012627E-6</v>
+        <v>-3.0546250743166751E-5</v>
       </c>
       <c r="R5">
-        <v>-6.5516493156464271E-6</v>
+        <v>2.9161169865678648E-6</v>
       </c>
       <c r="S5">
-        <v>2.3382755582126885E-7</v>
+        <v>-2.278679682226448E-6</v>
       </c>
       <c r="T5">
-        <v>5.7316363664208842E-6</v>
+        <v>-9.3585712986965172E-4</v>
       </c>
       <c r="U5">
-        <v>9.5561292791707846E-6</v>
-      </c>
-      <c r="V5">
-        <v>-2.3377388348329526E-3</v>
-      </c>
-      <c r="W5">
-        <v>7.7653937438297777E-4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.45">
+        <v>-1.2378767889783856E-5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>20</v>
       </c>
       <c r="B6">
-        <v>-0.12567972791506374</v>
+        <v>-3.5335292011911636E-2</v>
       </c>
       <c r="C6">
-        <v>1.5004864624340579E-6</v>
+        <v>-4.5006462940247194E-7</v>
       </c>
       <c r="D6">
-        <v>6.7655169636937244E-5</v>
+        <v>-1.6996497542585478E-5</v>
       </c>
       <c r="E6">
-        <v>-5.0479782193885858E-7</v>
+        <v>3.4614921453495114E-7</v>
       </c>
       <c r="F6">
-        <v>9.9626996479717372E-4</v>
+        <v>6.6819361907847824E-4</v>
       </c>
       <c r="G6">
-        <v>1.5797697825240336E-3</v>
+        <v>1.8627018115815255E-3</v>
       </c>
       <c r="H6">
-        <v>-2.0947994067738106E-5</v>
+        <v>-1.4085869937191316E-5</v>
       </c>
       <c r="I6">
-        <v>-3.3479396769055127E-5</v>
+        <v>-3.74298595933907E-5</v>
       </c>
       <c r="J6">
-        <v>-6.6736555344113776E-6</v>
+        <v>1.2959305159916805E-5</v>
       </c>
       <c r="K6">
-        <v>7.7547953123757566E-5</v>
+        <v>-7.6595635447559339E-6</v>
       </c>
       <c r="L6">
-        <v>9.728112798719897E-5</v>
+        <v>-2.8258596470489865E-5</v>
       </c>
       <c r="M6">
-        <v>1.0932698119692947E-4</v>
+        <v>-3.1771020796248287E-5</v>
       </c>
       <c r="N6">
-        <v>-4.0503602467025285E-5</v>
+        <v>-3.0803416369324852E-5</v>
       </c>
       <c r="O6">
-        <v>-5.2123255469744171E-5</v>
+        <v>-1.3320796514955353E-5</v>
       </c>
       <c r="P6">
-        <v>1.2946824081673961E-5</v>
+        <v>-1.1842598769301752E-5</v>
       </c>
       <c r="Q6">
-        <v>-7.9645095598033423E-6</v>
+        <v>-1.0259374370570414E-4</v>
       </c>
       <c r="R6">
-        <v>-9.1421173142486355E-6</v>
+        <v>1.6325253551525015E-5</v>
       </c>
       <c r="S6">
-        <v>3.4509049998175171E-6</v>
+        <v>-9.2633027618852164E-6</v>
       </c>
       <c r="T6">
-        <v>7.0481532951945561E-6</v>
+        <v>1.8485757553787183E-4</v>
       </c>
       <c r="U6">
-        <v>1.0746960888671472E-5</v>
-      </c>
-      <c r="V6">
-        <v>-2.2464638235496596E-3</v>
-      </c>
-      <c r="W6">
-        <v>8.2786208586273777E-4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.45">
+        <v>-3.0460249242618084E-4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>21</v>
       </c>
       <c r="B7">
-        <v>1.1175813526407461E-3</v>
+        <v>-1.3043278596420863E-3</v>
       </c>
       <c r="C7">
-        <v>7.2056975055918557E-8</v>
+        <v>1.8128937740921625E-7</v>
       </c>
       <c r="D7">
-        <v>-1.5395413879801532E-6</v>
+        <v>-6.5711150787628687E-7</v>
       </c>
       <c r="E7">
-        <v>1.1761313779342742E-8</v>
+        <v>3.6277435662496451E-9</v>
       </c>
       <c r="F7">
-        <v>-2.6696692483678875E-5</v>
+        <v>-2.367378804988892E-5</v>
       </c>
       <c r="G7">
-        <v>-2.0947994067738106E-5</v>
+        <v>-1.4085869937191316E-5</v>
       </c>
       <c r="H7">
-        <v>5.8771165788142284E-7</v>
+        <v>5.3139280933372227E-7</v>
       </c>
       <c r="I7">
-        <v>4.7368926516382002E-7</v>
+        <v>3.1559623422607023E-7</v>
       </c>
       <c r="J7">
-        <v>3.5756064061246721E-7</v>
+        <v>-2.0647985275707413E-7</v>
       </c>
       <c r="K7">
-        <v>-1.3182754850795199E-6</v>
+        <v>-4.0661655386114098E-7</v>
       </c>
       <c r="L7">
-        <v>-1.6955197855407486E-6</v>
+        <v>-2.7098354988197037E-7</v>
       </c>
       <c r="M7">
-        <v>-1.8326968270670328E-6</v>
+        <v>-2.6995167403556711E-7</v>
       </c>
       <c r="N7">
-        <v>7.9997492373173848E-7</v>
+        <v>8.9892401572749909E-8</v>
       </c>
       <c r="O7">
-        <v>1.0112088385392049E-6</v>
+        <v>4.1862667872116245E-8</v>
       </c>
       <c r="P7">
-        <v>-1.9533043758396552E-7</v>
+        <v>2.68724245280614E-7</v>
       </c>
       <c r="Q7">
-        <v>1.8793086379134331E-7</v>
+        <v>3.3670090684140515E-7</v>
       </c>
       <c r="R7">
-        <v>1.8993985454557722E-7</v>
+        <v>-6.8842857815248791E-8</v>
       </c>
       <c r="S7">
-        <v>-4.5496877356901355E-7</v>
+        <v>-2.7102098256135022E-8</v>
       </c>
       <c r="T7">
-        <v>-6.7847864033554756E-8</v>
+        <v>2.1492767901664677E-5</v>
       </c>
       <c r="U7">
-        <v>-1.6356565566752908E-7</v>
-      </c>
-      <c r="V7">
-        <v>4.8744899103976281E-5</v>
-      </c>
-      <c r="W7">
-        <v>-1.603347548514183E-5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.45">
+        <v>-6.2775345936743219E-7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>22</v>
       </c>
       <c r="B8">
-        <v>-1.0944786890884469E-4</v>
+        <v>-2.5806773079082098E-3</v>
       </c>
       <c r="C8">
-        <v>1.2285768535794783E-7</v>
+        <v>2.5567363716093332E-7</v>
       </c>
       <c r="D8">
-        <v>-1.6938742646853549E-6</v>
+        <v>1.3859879469894194E-7</v>
       </c>
       <c r="E8">
-        <v>1.3176124712494457E-8</v>
+        <v>-5.1538833228810418E-9</v>
       </c>
       <c r="F8">
-        <v>-2.1636183270292765E-5</v>
+        <v>-1.4121749269530696E-5</v>
       </c>
       <c r="G8">
-        <v>-3.3479396769055127E-5</v>
+        <v>-3.74298595933907E-5</v>
       </c>
       <c r="H8">
-        <v>4.7368926516382002E-7</v>
+        <v>3.1559623422607023E-7</v>
       </c>
       <c r="I8">
-        <v>7.4269359601156429E-7</v>
+        <v>7.9004621093129046E-7</v>
       </c>
       <c r="J8">
-        <v>1.3589538522893591E-7</v>
+        <v>-1.4768997645120499E-7</v>
       </c>
       <c r="K8">
-        <v>-2.0039981976639221E-6</v>
+        <v>-2.7318205784183965E-8</v>
       </c>
       <c r="L8">
-        <v>-2.4634162913635244E-6</v>
+        <v>3.6966687244227342E-7</v>
       </c>
       <c r="M8">
-        <v>-2.7084393352035457E-6</v>
+        <v>4.8059695875529428E-7</v>
       </c>
       <c r="N8">
-        <v>1.0221062166961624E-6</v>
+        <v>1.8374355702125318E-7</v>
       </c>
       <c r="O8">
-        <v>1.298110209157914E-6</v>
+        <v>-4.0833743917399509E-8</v>
       </c>
       <c r="P8">
-        <v>-3.2669584848022407E-7</v>
+        <v>3.2349531009760185E-7</v>
       </c>
       <c r="Q8">
-        <v>2.2016969511219327E-7</v>
+        <v>9.5023478963270239E-7</v>
       </c>
       <c r="R8">
-        <v>2.7087888057171046E-7</v>
+        <v>-1.8425939804758231E-7</v>
       </c>
       <c r="S8">
-        <v>-1.1964061610944252E-6</v>
+        <v>1.57810107149551E-7</v>
       </c>
       <c r="T8">
-        <v>-5.4238952475956513E-8</v>
+        <v>2.3693752831160384E-6</v>
       </c>
       <c r="U8">
-        <v>-1.976633410679357E-7</v>
-      </c>
-      <c r="V8">
-        <v>5.4894777969478775E-5</v>
-      </c>
-      <c r="W8">
-        <v>-2.1509721161781432E-5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.45">
+        <v>2.8061988311814311E-6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>23</v>
       </c>
       <c r="B9">
-        <v>3.2255952797199158E-2</v>
+        <v>8.0994142722698059E-2</v>
       </c>
       <c r="C9">
-        <v>4.9465286511252464E-7</v>
+        <v>-2.2287655080149516E-7</v>
       </c>
       <c r="D9">
-        <v>2.9813033533101482E-6</v>
+        <v>-5.9686288869017799E-6</v>
       </c>
       <c r="E9">
-        <v>-3.3462492476694522E-8</v>
+        <v>5.9713635079580149E-8</v>
       </c>
       <c r="F9">
-        <v>-1.3105769678143396E-5</v>
+        <v>1.0643308796671806E-5</v>
       </c>
       <c r="G9">
-        <v>-6.6736555344113776E-6</v>
+        <v>1.2959305159916805E-5</v>
       </c>
       <c r="H9">
-        <v>3.5756064061246721E-7</v>
+        <v>-2.0647985275707413E-7</v>
       </c>
       <c r="I9">
-        <v>1.3589538522893591E-7</v>
+        <v>-1.4768997645120499E-7</v>
       </c>
       <c r="J9">
-        <v>2.8642247129168075E-3</v>
+        <v>4.0232371413046536E-3</v>
       </c>
       <c r="K9">
-        <v>2.5392754093704218E-3</v>
+        <v>3.1927927968750823E-3</v>
       </c>
       <c r="L9">
-        <v>2.5426559848724826E-3</v>
+        <v>3.1861596212260385E-3</v>
       </c>
       <c r="M9">
-        <v>2.5435396742546821E-3</v>
+        <v>3.1816486951738851E-3</v>
       </c>
       <c r="N9">
-        <v>-3.7250265582858625E-6</v>
+        <v>-7.2681679952023072E-6</v>
       </c>
       <c r="O9">
-        <v>7.0032496232342435E-8</v>
+        <v>-5.4422580018637085E-6</v>
       </c>
       <c r="P9">
-        <v>-1.9914024795460371E-7</v>
+        <v>2.1826934984450652E-5</v>
       </c>
       <c r="Q9">
-        <v>-1.7697519355566548E-6</v>
+        <v>-1.5461488643818974E-5</v>
       </c>
       <c r="R9">
-        <v>4.0388644227300385E-6</v>
+        <v>1.1605062230001735E-5</v>
       </c>
       <c r="S9">
-        <v>7.8306577448568995E-6</v>
+        <v>1.3934506193137656E-5</v>
       </c>
       <c r="T9">
-        <v>9.2735509986471001E-6</v>
+        <v>-3.0025362150266962E-3</v>
       </c>
       <c r="U9">
-        <v>-2.6720890300179575E-6</v>
-      </c>
-      <c r="V9">
-        <v>-2.6267445222933842E-3</v>
-      </c>
-      <c r="W9">
-        <v>6.7844952853593699E-5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.45">
+        <v>-1.5489028766759905E-4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>24</v>
       </c>
       <c r="B10">
-        <v>-3.356420120250022E-2</v>
+        <v>2.3103509438096307E-2</v>
       </c>
       <c r="C10">
-        <v>2.8687659084389223E-6</v>
+        <v>2.7644644421040512E-6</v>
       </c>
       <c r="D10">
-        <v>3.1464499328568696E-5</v>
+        <v>2.1815901571309511E-5</v>
       </c>
       <c r="E10">
-        <v>-3.2250573770744651E-7</v>
+        <v>-2.3536327206634472E-7</v>
       </c>
       <c r="F10">
-        <v>6.8000449396316858E-5</v>
+        <v>1.4220464448169221E-5</v>
       </c>
       <c r="G10">
-        <v>7.7547953123757566E-5</v>
+        <v>-7.6595635447559339E-6</v>
       </c>
       <c r="H10">
-        <v>-1.3182754850795199E-6</v>
+        <v>-4.0661655386114098E-7</v>
       </c>
       <c r="I10">
-        <v>-2.0039981976639221E-6</v>
+        <v>-2.7318205784183965E-8</v>
       </c>
       <c r="J10">
-        <v>2.5392754093704218E-3</v>
+        <v>3.1927927968750823E-3</v>
       </c>
       <c r="K10">
-        <v>2.6484806083585956E-3</v>
+        <v>3.381988217041105E-3</v>
       </c>
       <c r="L10">
-        <v>2.6134892070101522E-3</v>
+        <v>3.2386336581835991E-3</v>
       </c>
       <c r="M10">
-        <v>2.6185485390188925E-3</v>
+        <v>3.2423083437026841E-3</v>
       </c>
       <c r="N10">
-        <v>-2.3223182967144752E-5</v>
+        <v>2.328946943943988E-5</v>
       </c>
       <c r="O10">
-        <v>-2.6111584476447046E-5</v>
+        <v>4.7637723401074809E-6</v>
       </c>
       <c r="P10">
-        <v>6.9181164143731065E-6</v>
+        <v>1.7741146102088135E-5</v>
       </c>
       <c r="Q10">
-        <v>-7.0719894357277852E-6</v>
+        <v>-2.4273836368412498E-5</v>
       </c>
       <c r="R10">
-        <v>2.3848706351348173E-6</v>
+        <v>-1.1621253568057011E-5</v>
       </c>
       <c r="S10">
-        <v>1.1807934433278602E-4</v>
+        <v>1.2209105936053659E-5</v>
       </c>
       <c r="T10">
-        <v>8.1734425687767358E-6</v>
+        <v>-3.766285087327449E-3</v>
       </c>
       <c r="U10">
-        <v>-6.2444390719011679E-7</v>
-      </c>
-      <c r="V10">
-        <v>-3.5554864354012351E-3</v>
-      </c>
-      <c r="W10">
-        <v>5.5799824350713392E-4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.45">
+        <v>3.8447340903228697E-4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>25</v>
       </c>
       <c r="B11">
-        <v>-2.4551514403650481E-2</v>
+        <v>3.5348516039389523E-2</v>
       </c>
       <c r="C11">
-        <v>2.6335966356199407E-6</v>
+        <v>2.8081022101108737E-6</v>
       </c>
       <c r="D11">
-        <v>3.9246793016656807E-5</v>
+        <v>3.1767703422975361E-5</v>
       </c>
       <c r="E11">
-        <v>-3.9887005209638081E-7</v>
+        <v>-3.3861163247316275E-7</v>
       </c>
       <c r="F11">
-        <v>8.7380955628812079E-5</v>
+        <v>7.7784703233698198E-6</v>
       </c>
       <c r="G11">
-        <v>9.728112798719897E-5</v>
+        <v>-2.8258596470489865E-5</v>
       </c>
       <c r="H11">
-        <v>-1.6955197855407486E-6</v>
+        <v>-2.7098354988197037E-7</v>
       </c>
       <c r="I11">
-        <v>-2.4634162913635244E-6</v>
+        <v>3.6966687244227342E-7</v>
       </c>
       <c r="J11">
-        <v>2.5426559848724826E-3</v>
+        <v>3.1861596212260385E-3</v>
       </c>
       <c r="K11">
-        <v>2.6134892070101522E-3</v>
+        <v>3.2386336581835991E-3</v>
       </c>
       <c r="L11">
-        <v>2.6482413915537959E-3</v>
+        <v>3.2916047257282926E-3</v>
       </c>
       <c r="M11">
-        <v>2.6454446604495963E-3</v>
+        <v>3.2715667741035227E-3</v>
       </c>
       <c r="N11">
-        <v>-2.8960234355481772E-5</v>
+        <v>3.2635992775283912E-5</v>
       </c>
       <c r="O11">
-        <v>-3.4185088637758902E-5</v>
+        <v>6.7049248395991233E-6</v>
       </c>
       <c r="P11">
-        <v>7.145411072683734E-6</v>
+        <v>2.0459233778254596E-5</v>
       </c>
       <c r="Q11">
-        <v>-8.1763748841089523E-6</v>
+        <v>-6.310889790181778E-6</v>
       </c>
       <c r="R11">
-        <v>2.256350803842415E-6</v>
+        <v>-2.0671618955317537E-5</v>
       </c>
       <c r="S11">
-        <v>1.4107667849242535E-4</v>
+        <v>1.6979332093816417E-5</v>
       </c>
       <c r="T11">
-        <v>1.5362881205400485E-5</v>
+        <v>-4.0762727415602704E-3</v>
       </c>
       <c r="U11">
-        <v>-4.4731984229143145E-7</v>
-      </c>
-      <c r="V11">
-        <v>-3.8124755160822833E-3</v>
-      </c>
-      <c r="W11">
-        <v>6.9560184880447669E-4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.45">
+        <v>6.1222643644266673E-4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>26</v>
       </c>
       <c r="B12">
-        <v>-3.4192332210288862E-2</v>
+        <v>2.7097561311855825E-2</v>
       </c>
       <c r="C12">
-        <v>2.7992277031282489E-6</v>
+        <v>2.7430428857450632E-6</v>
       </c>
       <c r="D12">
-        <v>4.2234062237637261E-5</v>
+        <v>3.7126248998635143E-5</v>
       </c>
       <c r="E12">
-        <v>-4.2635381214481957E-7</v>
+        <v>-3.8845059099772941E-7</v>
       </c>
       <c r="F12">
-        <v>9.4866471937474705E-5</v>
+        <v>9.3721047078729681E-6</v>
       </c>
       <c r="G12">
-        <v>1.0932698119692947E-4</v>
+        <v>-3.1771020796248287E-5</v>
       </c>
       <c r="H12">
-        <v>-1.8326968270670328E-6</v>
+        <v>-2.6995167403556711E-7</v>
       </c>
       <c r="I12">
-        <v>-2.7084393352035457E-6</v>
+        <v>4.8059695875529428E-7</v>
       </c>
       <c r="J12">
-        <v>2.5435396742546821E-3</v>
+        <v>3.1816486951738851E-3</v>
       </c>
       <c r="K12">
-        <v>2.6185485390188925E-3</v>
+        <v>3.2423083437026841E-3</v>
       </c>
       <c r="L12">
-        <v>2.6454446604495963E-3</v>
+        <v>3.2715667741035227E-3</v>
       </c>
       <c r="M12">
-        <v>2.6994461973817835E-3</v>
+        <v>3.3027819362213399E-3</v>
       </c>
       <c r="N12">
-        <v>-3.0612549629151339E-5</v>
+        <v>3.337012596740756E-5</v>
       </c>
       <c r="O12">
-        <v>-3.6565603226693423E-5</v>
+        <v>3.0889352392191577E-6</v>
       </c>
       <c r="P12">
-        <v>9.7911810835837239E-6</v>
+        <v>2.1108675502138436E-5</v>
       </c>
       <c r="Q12">
-        <v>-6.7291821495881638E-6</v>
+        <v>-1.5201247641458733E-5</v>
       </c>
       <c r="R12">
-        <v>2.2569700347841747E-6</v>
+        <v>-2.6008443834098809E-5</v>
       </c>
       <c r="S12">
-        <v>1.7483824373639963E-4</v>
+        <v>1.482583959514276E-5</v>
       </c>
       <c r="T12">
-        <v>1.5044757119755261E-5</v>
+        <v>-4.2292452948967186E-3</v>
       </c>
       <c r="U12">
-        <v>-3.6228831573026625E-6</v>
-      </c>
-      <c r="V12">
-        <v>-3.9380059355757476E-3</v>
-      </c>
-      <c r="W12">
-        <v>7.3398082930585138E-4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.45">
+        <v>7.0375258898957779E-4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B13">
-        <v>-5.3266211276001334E-2</v>
+        <v>-6.1679274751921441E-2</v>
       </c>
       <c r="C13">
-        <v>2.9718236342099566E-6</v>
+        <v>4.7364175858175044E-6</v>
       </c>
       <c r="D13">
-        <v>-1.2437899613630297E-5</v>
+        <v>1.6395655201893257E-5</v>
       </c>
       <c r="E13">
-        <v>1.2524339671124664E-7</v>
+        <v>-1.7643455025132864E-7</v>
       </c>
       <c r="F13">
-        <v>-3.7107296506780204E-5</v>
+        <v>-1.270450407042831E-5</v>
       </c>
       <c r="G13">
-        <v>-4.0503602467025285E-5</v>
+        <v>-3.0803416369324852E-5</v>
       </c>
       <c r="H13">
-        <v>7.9997492373173848E-7</v>
+        <v>8.9892401572749909E-8</v>
       </c>
       <c r="I13">
-        <v>1.0221062166961624E-6</v>
+        <v>1.8374355702125318E-7</v>
       </c>
       <c r="J13">
-        <v>-3.7250265582858625E-6</v>
+        <v>-7.2681679952023072E-6</v>
       </c>
       <c r="K13">
-        <v>-2.3223182967144752E-5</v>
+        <v>2.328946943943988E-5</v>
       </c>
       <c r="L13">
-        <v>-2.8960234355481772E-5</v>
+        <v>3.2635992775283912E-5</v>
       </c>
       <c r="M13">
-        <v>-3.0612549629151339E-5</v>
+        <v>3.337012596740756E-5</v>
       </c>
       <c r="N13">
-        <v>8.0445399332861476E-5</v>
+        <v>1.1056588037331457E-4</v>
       </c>
       <c r="O13">
-        <v>4.225335034183435E-5</v>
+        <v>4.9522654167313564E-5</v>
       </c>
       <c r="P13">
-        <v>2.6759482897629269E-5</v>
+        <v>-3.1809446013446385E-6</v>
       </c>
       <c r="Q13">
-        <v>3.1553857507695399E-5</v>
+        <v>1.4062535347730912E-5</v>
       </c>
       <c r="R13">
-        <v>-1.7509455489535438E-6</v>
+        <v>-1.5762217455902998E-5</v>
       </c>
       <c r="S13">
-        <v>-3.7119641501914243E-6</v>
+        <v>6.327325099000233E-6</v>
       </c>
       <c r="T13">
-        <v>7.9498183436670184E-8</v>
+        <v>-5.0608888404134449E-4</v>
       </c>
       <c r="U13">
-        <v>-1.6756877274354683E-6</v>
-      </c>
-      <c r="V13">
-        <v>3.1924699009309255E-4</v>
-      </c>
-      <c r="W13">
-        <v>-2.0546633531777535E-4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.45">
+        <v>3.1919171980802826E-4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B14">
-        <v>-3.8830409663654634E-2</v>
+        <v>-6.1294310481274594E-2</v>
       </c>
       <c r="C14">
-        <v>2.8473061505325477E-6</v>
+        <v>5.0539195195592791E-6</v>
       </c>
       <c r="D14">
-        <v>-1.5764014027498564E-5</v>
+        <v>5.9750754693512659E-6</v>
       </c>
       <c r="E14">
-        <v>1.5820641188975016E-7</v>
+        <v>-6.6218356420928218E-8</v>
       </c>
       <c r="F14">
-        <v>-4.6972799054695908E-5</v>
+        <v>-8.2624567209048868E-6</v>
       </c>
       <c r="G14">
-        <v>-5.2123255469744171E-5</v>
+        <v>-1.3320796514955353E-5</v>
       </c>
       <c r="H14">
-        <v>1.0112088385392049E-6</v>
+        <v>4.1862667872116245E-8</v>
       </c>
       <c r="I14">
-        <v>1.298110209157914E-6</v>
+        <v>-4.0833743917399509E-8</v>
       </c>
       <c r="J14">
-        <v>7.0032496232342435E-8</v>
+        <v>-5.4422580018637085E-6</v>
       </c>
       <c r="K14">
-        <v>-2.6111584476447046E-5</v>
+        <v>4.7637723401074809E-6</v>
       </c>
       <c r="L14">
-        <v>-3.4185088637758902E-5</v>
+        <v>6.7049248395991233E-6</v>
       </c>
       <c r="M14">
-        <v>-3.6565603226693423E-5</v>
+        <v>3.0889352392191577E-6</v>
       </c>
       <c r="N14">
-        <v>4.225335034183435E-5</v>
+        <v>4.9522654167313564E-5</v>
       </c>
       <c r="O14">
-        <v>1.4919833252049507E-4</v>
+        <v>6.2198570690010036E-5</v>
       </c>
       <c r="P14">
-        <v>2.5879443800240732E-5</v>
+        <v>-3.1449399523678988E-6</v>
       </c>
       <c r="Q14">
-        <v>3.2011420996526319E-5</v>
+        <v>-3.671580174796903E-5</v>
       </c>
       <c r="R14">
-        <v>-2.58443613349294E-6</v>
+        <v>-4.8390083203356405E-6</v>
       </c>
       <c r="S14">
-        <v>-1.4327073570559808E-5</v>
+        <v>3.7012402553372236E-6</v>
       </c>
       <c r="T14">
-        <v>-3.5292826003465642E-7</v>
+        <v>-1.6263061799684292E-4</v>
       </c>
       <c r="U14">
-        <v>-2.8082113530195288E-6</v>
-      </c>
-      <c r="V14">
-        <v>4.2442419265868215E-4</v>
-      </c>
-      <c r="W14">
-        <v>-2.6651702802524778E-4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.45">
+        <v>1.1896883282957796E-4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="B15">
-        <v>9.3279193436869266E-3</v>
+        <v>0.29463597886319459</v>
       </c>
       <c r="C15">
-        <v>1.15861999703872E-7</v>
+        <v>-1.9918594693689529E-6</v>
       </c>
       <c r="D15">
-        <v>4.2467888931914201E-6</v>
+        <v>-7.6871715231379226E-7</v>
       </c>
       <c r="E15">
-        <v>-4.3608499776935663E-8</v>
+        <v>6.1593021946309984E-9</v>
       </c>
       <c r="F15">
-        <v>8.9277054095561946E-6</v>
+        <v>-7.015310864216234E-6</v>
       </c>
       <c r="G15">
-        <v>1.2946824081673961E-5</v>
+        <v>-1.1842598769301752E-5</v>
       </c>
       <c r="H15">
-        <v>-1.9533043758396552E-7</v>
+        <v>2.68724245280614E-7</v>
       </c>
       <c r="I15">
-        <v>-3.2669584848022407E-7</v>
+        <v>3.2349531009760185E-7</v>
       </c>
       <c r="J15">
-        <v>-1.9914024795460371E-7</v>
+        <v>2.1826934984450652E-5</v>
       </c>
       <c r="K15">
-        <v>6.9181164143731065E-6</v>
+        <v>1.7741146102088135E-5</v>
       </c>
       <c r="L15">
-        <v>7.145411072683734E-6</v>
+        <v>2.0459233778254596E-5</v>
       </c>
       <c r="M15">
-        <v>9.7911810835837239E-6</v>
+        <v>2.1108675502138436E-5</v>
       </c>
       <c r="N15">
-        <v>2.6759482897629269E-5</v>
+        <v>-3.1809446013446385E-6</v>
       </c>
       <c r="O15">
-        <v>2.5879443800240732E-5</v>
+        <v>-3.1449399523678988E-6</v>
       </c>
       <c r="P15">
-        <v>5.7322698331140436E-5</v>
+        <v>1.3229390646684697E-4</v>
       </c>
       <c r="Q15">
-        <v>2.9446666584593115E-5</v>
+        <v>-1.21207659223302E-5</v>
       </c>
       <c r="R15">
-        <v>-1.3038066367662722E-6</v>
+        <v>3.5057637163605316E-6</v>
       </c>
       <c r="S15">
-        <v>-6.8044908192458442E-6</v>
+        <v>2.2169827299104398E-6</v>
       </c>
       <c r="T15">
-        <v>-4.3124288494604043E-7</v>
+        <v>1.3624314115512884E-5</v>
       </c>
       <c r="U15">
-        <v>-1.1666680441287802E-6</v>
-      </c>
-      <c r="V15">
-        <v>-1.4001632013869336E-4</v>
-      </c>
-      <c r="W15">
-        <v>7.1833566270694156E-5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.45">
+        <v>-3.8227642096468008E-5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="B16">
-        <v>-2.2586640404677161E-2</v>
+        <v>-0.37309598505994529</v>
       </c>
       <c r="C16">
-        <v>1.324184518156341E-6</v>
+        <v>-2.261633797723317E-5</v>
       </c>
       <c r="D16">
-        <v>-2.1119288033155075E-6</v>
+        <v>1.0577363743545562E-5</v>
       </c>
       <c r="E16">
-        <v>2.0638354094057532E-8</v>
+        <v>-1.0234665606111987E-7</v>
       </c>
       <c r="F16">
-        <v>-8.0531133634012627E-6</v>
+        <v>-3.0546250743166751E-5</v>
       </c>
       <c r="G16">
-        <v>-7.9645095598033423E-6</v>
+        <v>-1.0259374370570414E-4</v>
       </c>
       <c r="H16">
-        <v>1.8793086379134331E-7</v>
+        <v>3.3670090684140515E-7</v>
       </c>
       <c r="I16">
-        <v>2.2016969511219327E-7</v>
+        <v>9.5023478963270239E-7</v>
       </c>
       <c r="J16">
-        <v>-1.7697519355566548E-6</v>
+        <v>-1.5461488643818974E-5</v>
       </c>
       <c r="K16">
-        <v>-7.0719894357277852E-6</v>
+        <v>-2.4273836368412498E-5</v>
       </c>
       <c r="L16">
-        <v>-8.1763748841089523E-6</v>
+        <v>-6.310889790181778E-6</v>
       </c>
       <c r="M16">
-        <v>-6.7291821495881638E-6</v>
+        <v>-1.5201247641458733E-5</v>
       </c>
       <c r="N16">
-        <v>3.1553857507695399E-5</v>
+        <v>1.4062535347730912E-5</v>
       </c>
       <c r="O16">
-        <v>3.2011420996526319E-5</v>
+        <v>-3.671580174796903E-5</v>
       </c>
       <c r="P16">
-        <v>2.9446666584593115E-5</v>
+        <v>-1.21207659223302E-5</v>
       </c>
       <c r="Q16">
-        <v>5.8661286931204477E-5</v>
+        <v>7.6381807823350583E-3</v>
       </c>
       <c r="R16">
-        <v>-1.4973123295637502E-6</v>
+        <v>-1.9994250174936264E-4</v>
       </c>
       <c r="S16">
-        <v>4.6569588712090673E-6</v>
+        <v>-2.7704999812598897E-5</v>
       </c>
       <c r="T16">
-        <v>-1.9453218024746484E-6</v>
+        <v>-7.689128583991788E-3</v>
       </c>
       <c r="U16">
-        <v>-2.3796589842250263E-6</v>
-      </c>
-      <c r="V16">
-        <v>2.5459858211885287E-5</v>
-      </c>
-      <c r="W16">
-        <v>-3.1928770958030743E-5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.45">
+        <v>1.5894146537651123E-4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B17">
-        <v>0.22062206853999652</v>
+        <v>5.6758125091124441E-2</v>
       </c>
       <c r="C17">
-        <v>1.8573554142188454E-6</v>
+        <v>-2.3206980646331955E-6</v>
       </c>
       <c r="D17">
-        <v>-1.2944719989901626E-6</v>
+        <v>-1.1204095755877535E-5</v>
       </c>
       <c r="E17">
-        <v>1.238923164125611E-8</v>
+        <v>1.1778250427632278E-7</v>
       </c>
       <c r="F17">
-        <v>-6.5516493156464271E-6</v>
+        <v>2.9161169865678648E-6</v>
       </c>
       <c r="G17">
-        <v>-9.1421173142486355E-6</v>
+        <v>1.6325253551525015E-5</v>
       </c>
       <c r="H17">
-        <v>1.8993985454557722E-7</v>
+        <v>-6.8842857815248791E-8</v>
       </c>
       <c r="I17">
-        <v>2.7087888057171046E-7</v>
+        <v>-1.8425939804758231E-7</v>
       </c>
       <c r="J17">
-        <v>4.0388644227300385E-6</v>
+        <v>1.1605062230001735E-5</v>
       </c>
       <c r="K17">
-        <v>2.3848706351348173E-6</v>
+        <v>-1.1621253568057011E-5</v>
       </c>
       <c r="L17">
-        <v>2.256350803842415E-6</v>
+        <v>-2.0671618955317537E-5</v>
       </c>
       <c r="M17">
-        <v>2.2569700347841747E-6</v>
+        <v>-2.6008443834098809E-5</v>
       </c>
       <c r="N17">
-        <v>-1.7509455489535438E-6</v>
+        <v>-1.5762217455902998E-5</v>
       </c>
       <c r="O17">
-        <v>-2.58443613349294E-6</v>
+        <v>-4.8390083203356405E-6</v>
       </c>
       <c r="P17">
-        <v>-1.3038066367662722E-6</v>
+        <v>3.5057637163605316E-6</v>
       </c>
       <c r="Q17">
-        <v>-1.4973123295637502E-6</v>
+        <v>-1.9994250174936264E-4</v>
       </c>
       <c r="R17">
-        <v>1.7020519363412096E-4</v>
+        <v>1.2130353810205798E-4</v>
       </c>
       <c r="S17">
-        <v>1.7911955084868853E-5</v>
+        <v>9.2527459014721615E-6</v>
       </c>
       <c r="T17">
-        <v>-3.6344338966347246E-6</v>
+        <v>5.0639849691018978E-4</v>
       </c>
       <c r="U17">
-        <v>-3.1376794018717686E-6</v>
-      </c>
-      <c r="V17">
-        <v>8.8089808868483223E-6</v>
-      </c>
-      <c r="W17">
-        <v>-4.5819555673522193E-5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.45">
+        <v>-2.2971777593252832E-4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B18">
-        <v>0.30187284346812931</v>
+        <v>4.2881680301542387E-2</v>
       </c>
       <c r="C18">
-        <v>-1.8239916828318502E-6</v>
+        <v>-5.375278451964147E-7</v>
       </c>
       <c r="D18">
-        <v>1.9190157050088914E-5</v>
+        <v>4.4854611064389594E-6</v>
       </c>
       <c r="E18">
-        <v>-1.7693622905436588E-7</v>
+        <v>-5.100077019583918E-8</v>
       </c>
       <c r="F18">
-        <v>2.3382755582126885E-7</v>
+        <v>-2.278679682226448E-6</v>
       </c>
       <c r="G18">
-        <v>3.4509049998175171E-6</v>
+        <v>-9.2633027618852164E-6</v>
       </c>
       <c r="H18">
-        <v>-4.5496877356901355E-7</v>
+        <v>-2.7102098256135022E-8</v>
       </c>
       <c r="I18">
-        <v>-1.1964061610944252E-6</v>
+        <v>1.57810107149551E-7</v>
       </c>
       <c r="J18">
-        <v>7.8306577448568995E-6</v>
+        <v>1.3934506193137656E-5</v>
       </c>
       <c r="K18">
-        <v>1.1807934433278602E-4</v>
+        <v>1.2209105936053659E-5</v>
       </c>
       <c r="L18">
-        <v>1.4107667849242535E-4</v>
+        <v>1.6979332093816417E-5</v>
       </c>
       <c r="M18">
-        <v>1.7483824373639963E-4</v>
+        <v>1.482583959514276E-5</v>
       </c>
       <c r="N18">
-        <v>-3.7119641501914243E-6</v>
+        <v>6.327325099000233E-6</v>
       </c>
       <c r="O18">
-        <v>-1.4327073570559808E-5</v>
+        <v>3.7012402553372236E-6</v>
       </c>
       <c r="P18">
-        <v>-6.8044908192458442E-6</v>
+        <v>2.2169827299104398E-6</v>
       </c>
       <c r="Q18">
-        <v>4.6569588712090673E-6</v>
+        <v>-2.7704999812598897E-5</v>
       </c>
       <c r="R18">
-        <v>1.7911955084868853E-5</v>
+        <v>9.2527459014721615E-6</v>
       </c>
       <c r="S18">
-        <v>2.7609622359417128E-2</v>
+        <v>3.102211291663031E-4</v>
       </c>
       <c r="T18">
-        <v>-1.2742169894164879E-3</v>
+        <v>-1.0389612482083259E-4</v>
       </c>
       <c r="U18">
-        <v>-1.7314808494309463E-4</v>
-      </c>
-      <c r="V18">
-        <v>-2.8064748417598172E-2</v>
-      </c>
-      <c r="W18">
-        <v>4.4980673216845528E-4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.45">
+        <v>7.4064429160461496E-5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B19">
-        <v>-4.7752604057982422E-2</v>
+        <v>1.2853209460053439</v>
       </c>
       <c r="C19">
-        <v>2.8199712562863171E-7</v>
+        <v>-2.8495996887924806E-5</v>
       </c>
       <c r="D19">
-        <v>1.2052841715803317E-7</v>
+        <v>-6.2990448320602069E-4</v>
       </c>
       <c r="E19">
-        <v>-2.1626391960687828E-9</v>
+        <v>6.6142515820950594E-6</v>
       </c>
       <c r="F19">
-        <v>5.7316363664208842E-6</v>
+        <v>-9.3585712986965172E-4</v>
       </c>
       <c r="G19">
-        <v>7.0481532951945561E-6</v>
+        <v>1.8485757553787183E-4</v>
       </c>
       <c r="H19">
-        <v>-6.7847864033554756E-8</v>
+        <v>2.1492767901664677E-5</v>
       </c>
       <c r="I19">
-        <v>-5.4238952475956513E-8</v>
+        <v>2.3693752831160384E-6</v>
       </c>
       <c r="J19">
-        <v>9.2735509986471001E-6</v>
+        <v>-3.0025362150266962E-3</v>
       </c>
       <c r="K19">
-        <v>8.1734425687767358E-6</v>
+        <v>-3.766285087327449E-3</v>
       </c>
       <c r="L19">
-        <v>1.5362881205400485E-5</v>
+        <v>-4.0762727415602704E-3</v>
       </c>
       <c r="M19">
-        <v>1.5044757119755261E-5</v>
+        <v>-4.2292452948967186E-3</v>
       </c>
       <c r="N19">
-        <v>7.9498183436670184E-8</v>
+        <v>-5.0608888404134449E-4</v>
       </c>
       <c r="O19">
-        <v>-3.5292826003465642E-7</v>
+        <v>-1.6263061799684292E-4</v>
       </c>
       <c r="P19">
-        <v>-4.3124288494604043E-7</v>
+        <v>1.3624314115512884E-5</v>
       </c>
       <c r="Q19">
-        <v>-1.9453218024746484E-6</v>
+        <v>-7.689128583991788E-3</v>
       </c>
       <c r="R19">
-        <v>-3.6344338966347246E-6</v>
+        <v>5.0639849691018978E-4</v>
       </c>
       <c r="S19">
-        <v>-1.2742169894164879E-3</v>
+        <v>-1.0389612482083259E-4</v>
       </c>
       <c r="T19">
-        <v>1.415254419010871E-4</v>
+        <v>2.7562421961780995E-2</v>
       </c>
       <c r="U19">
-        <v>1.6534183169072125E-5</v>
-      </c>
-      <c r="V19">
-        <v>1.2394124261522954E-3</v>
-      </c>
-      <c r="W19">
-        <v>-8.5820753660859732E-6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.45">
+        <v>-9.1474116049959486E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B20">
-        <v>3.5865700987642544E-2</v>
+        <v>-0.48266477731072754</v>
       </c>
       <c r="C20">
-        <v>1.0127149257330256E-6</v>
+        <v>3.3400908656451228E-5</v>
       </c>
       <c r="D20">
-        <v>2.3051571026915804E-6</v>
+        <v>3.243104769141132E-4</v>
       </c>
       <c r="E20">
-        <v>-2.5269969845861938E-8</v>
+        <v>-3.4596873607089386E-6</v>
       </c>
       <c r="F20">
-        <v>9.5561292791707846E-6</v>
+        <v>-1.2378767889783856E-5</v>
       </c>
       <c r="G20">
-        <v>1.0746960888671472E-5</v>
+        <v>-3.0460249242618084E-4</v>
       </c>
       <c r="H20">
-        <v>-1.6356565566752908E-7</v>
+        <v>-6.2775345936743219E-7</v>
       </c>
       <c r="I20">
-        <v>-1.976633410679357E-7</v>
+        <v>2.8061988311814311E-6</v>
       </c>
       <c r="J20">
-        <v>-2.6720890300179575E-6</v>
+        <v>-1.5489028766759905E-4</v>
       </c>
       <c r="K20">
-        <v>-6.2444390719011679E-7</v>
+        <v>3.8447340903228697E-4</v>
       </c>
       <c r="L20">
-        <v>-4.4731984229143145E-7</v>
+        <v>6.1222643644266673E-4</v>
       </c>
       <c r="M20">
-        <v>-3.6228831573026625E-6</v>
+        <v>7.0375258898957779E-4</v>
       </c>
       <c r="N20">
-        <v>-1.6756877274354683E-6</v>
+        <v>3.1919171980802826E-4</v>
       </c>
       <c r="O20">
-        <v>-2.8082113530195288E-6</v>
+        <v>1.1896883282957796E-4</v>
       </c>
       <c r="P20">
-        <v>-1.1666680441287802E-6</v>
+        <v>-3.8227642096468008E-5</v>
       </c>
       <c r="Q20">
-        <v>-2.3796589842250263E-6</v>
+        <v>1.5894146537651123E-4</v>
       </c>
       <c r="R20">
-        <v>-3.1376794018717686E-6</v>
+        <v>-2.2971777593252832E-4</v>
       </c>
       <c r="S20">
-        <v>-1.7314808494309463E-4</v>
+        <v>7.4064429160461496E-5</v>
       </c>
       <c r="T20">
-        <v>1.6534183169072125E-5</v>
+        <v>-9.1474116049959486E-3</v>
       </c>
       <c r="U20">
-        <v>1.4408137156465565E-4</v>
-      </c>
-      <c r="V20">
-        <v>1.0668213322493742E-4</v>
-      </c>
-      <c r="W20">
-        <v>2.995462991893964E-5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
-        <v>31</v>
-      </c>
-      <c r="B21">
-        <v>1.0681872028844559</v>
-      </c>
-      <c r="C21">
-        <v>-5.0012701591296718E-5</v>
-      </c>
-      <c r="D21">
-        <v>-6.2685745198527731E-4</v>
-      </c>
-      <c r="E21">
-        <v>6.2862118604283118E-6</v>
-      </c>
-      <c r="F21">
-        <v>-2.3377388348329526E-3</v>
-      </c>
-      <c r="G21">
-        <v>-2.2464638235496596E-3</v>
-      </c>
-      <c r="H21">
-        <v>4.8744899103976281E-5</v>
-      </c>
-      <c r="I21">
-        <v>5.4894777969478775E-5</v>
-      </c>
-      <c r="J21">
-        <v>-2.6267445222933842E-3</v>
-      </c>
-      <c r="K21">
-        <v>-3.5554864354012351E-3</v>
-      </c>
-      <c r="L21">
-        <v>-3.8124755160822833E-3</v>
-      </c>
-      <c r="M21">
-        <v>-3.9380059355757476E-3</v>
-      </c>
-      <c r="N21">
-        <v>3.1924699009309255E-4</v>
-      </c>
-      <c r="O21">
-        <v>4.2442419265868215E-4</v>
-      </c>
-      <c r="P21">
-        <v>-1.4001632013869336E-4</v>
-      </c>
-      <c r="Q21">
-        <v>2.5459858211885287E-5</v>
-      </c>
-      <c r="R21">
-        <v>8.8089808868483223E-6</v>
-      </c>
-      <c r="S21">
-        <v>-2.8064748417598172E-2</v>
-      </c>
-      <c r="T21">
-        <v>1.2394124261522954E-3</v>
-      </c>
-      <c r="U21">
-        <v>1.0668213322493742E-4</v>
-      </c>
-      <c r="V21">
-        <v>4.8032124416744884E-2</v>
-      </c>
-      <c r="W21">
-        <v>-8.8081470588456078E-3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.45">
-      <c r="A22" t="s">
-        <v>32</v>
-      </c>
-      <c r="B22">
-        <v>-0.52313008397066696</v>
-      </c>
-      <c r="C22">
-        <v>2.1378860634480102E-5</v>
-      </c>
-      <c r="D22">
-        <v>2.9465105283169789E-4</v>
-      </c>
-      <c r="E22">
-        <v>-3.0122832065336327E-6</v>
-      </c>
-      <c r="F22">
-        <v>7.7653937438297777E-4</v>
-      </c>
-      <c r="G22">
-        <v>8.2786208586273777E-4</v>
-      </c>
-      <c r="H22">
-        <v>-1.603347548514183E-5</v>
-      </c>
-      <c r="I22">
-        <v>-2.1509721161781432E-5</v>
-      </c>
-      <c r="J22">
-        <v>6.7844952853593699E-5</v>
-      </c>
-      <c r="K22">
-        <v>5.5799824350713392E-4</v>
-      </c>
-      <c r="L22">
-        <v>6.9560184880447669E-4</v>
-      </c>
-      <c r="M22">
-        <v>7.3398082930585138E-4</v>
-      </c>
-      <c r="N22">
-        <v>-2.0546633531777535E-4</v>
-      </c>
-      <c r="O22">
-        <v>-2.6651702802524778E-4</v>
-      </c>
-      <c r="P22">
-        <v>7.1833566270694156E-5</v>
-      </c>
-      <c r="Q22">
-        <v>-3.1928770958030743E-5</v>
-      </c>
-      <c r="R22">
-        <v>-4.5819555673522193E-5</v>
-      </c>
-      <c r="S22">
-        <v>4.4980673216845528E-4</v>
-      </c>
-      <c r="T22">
-        <v>-8.5820753660859732E-6</v>
-      </c>
-      <c r="U22">
-        <v>2.995462991893964E-5</v>
-      </c>
-      <c r="V22">
-        <v>-8.8081470588456078E-3</v>
-      </c>
-      <c r="W22">
-        <v>4.973116826669793E-3</v>
+        <v>6.3123124322273187E-3</v>
       </c>
     </row>
   </sheetData>
